--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,43 +163,16 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-3.8% → -1.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-3.8%</t>
-  </si>
-  <si>
-    <t>-1.0%</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -790,8 +762,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -924,10 +895,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1121</v>
+        <v>1173.8</v>
       </c>
       <c r="D2">
-        <v>2.19</v>
+        <v>4.71</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -936,46 +907,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-9.720000000000001</v>
+        <v>-5.47</v>
       </c>
       <c r="H2">
-        <v>49.8</v>
+        <v>56.85</v>
       </c>
       <c r="I2">
-        <v>2.33</v>
+        <v>8.84</v>
       </c>
       <c r="J2">
-        <v>2.73</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="K2">
-        <v>11.14</v>
+        <v>13.6</v>
       </c>
       <c r="L2">
-        <v>22.41</v>
+        <v>29.9</v>
       </c>
       <c r="M2">
-        <v>10.23</v>
+        <v>10.99</v>
       </c>
       <c r="N2">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>1089.46</v>
+        <v>1108.52</v>
       </c>
       <c r="Q2">
-        <v>1075.1</v>
+        <v>1080.48</v>
       </c>
       <c r="R2">
-        <v>1092.46</v>
+        <v>1095.33</v>
       </c>
       <c r="S2">
-        <v>927.46</v>
+        <v>928.78</v>
       </c>
       <c r="T2">
-        <v>20.87</v>
+        <v>26.38</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +961,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.71</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="Z2">
-        <v>-0.22</v>
+        <v>6.94</v>
       </c>
       <c r="AA2">
-        <v>-5.43</v>
+        <v>-2.96</v>
       </c>
       <c r="AB2">
-        <v>5.22</v>
+        <v>9.9</v>
       </c>
       <c r="AC2">
-        <v>81.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="AD2">
-        <v>71.22</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="AE2">
-        <v>39.35</v>
+        <v>42.33</v>
       </c>
       <c r="AF2">
-        <v>140.73</v>
+        <v>113.22</v>
       </c>
       <c r="AG2">
-        <v>1109.32</v>
+        <v>1136.01</v>
       </c>
       <c r="AH2">
-        <v>1040.88</v>
+        <v>1024.95</v>
       </c>
       <c r="AI2">
-        <v>1166.89</v>
+        <v>1017.47</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>28.6</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1008,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1020,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.98</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="H3">
-        <v>66.01000000000001</v>
+        <v>66.39</v>
       </c>
       <c r="I3">
-        <v>6.4</v>
+        <v>0.11</v>
       </c>
       <c r="J3">
-        <v>-4.1</v>
+        <v>-2.71</v>
       </c>
       <c r="K3">
-        <v>5.43</v>
+        <v>4.01</v>
       </c>
       <c r="L3">
-        <v>33.02</v>
+        <v>29.8</v>
       </c>
       <c r="M3">
-        <v>62.77</v>
+        <v>63.87</v>
       </c>
       <c r="N3">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O3">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P3">
-        <v>880.71</v>
+        <v>880.9</v>
       </c>
       <c r="Q3">
-        <v>881.91</v>
+        <v>880.26</v>
       </c>
       <c r="R3">
-        <v>910.15</v>
+        <v>909.88</v>
       </c>
       <c r="S3">
-        <v>761.5700000000001</v>
+        <v>762.29</v>
       </c>
       <c r="T3">
-        <v>15.42</v>
+        <v>15.57</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,43 +1074,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.46</v>
+        <v>48.95</v>
       </c>
       <c r="Z3">
-        <v>-10.89</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="AA3">
-        <v>-13.3</v>
+        <v>-12.55</v>
       </c>
       <c r="AB3">
-        <v>2.41</v>
+        <v>3.02</v>
       </c>
       <c r="AC3">
-        <v>87.98</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="AD3">
-        <v>90.43000000000001</v>
+        <v>89.87</v>
       </c>
       <c r="AE3">
-        <v>27.28</v>
+        <v>26.41</v>
       </c>
       <c r="AF3">
-        <v>-70.88</v>
+        <v>-74.02</v>
       </c>
       <c r="AG3">
-        <v>944.77</v>
+        <v>941.3</v>
       </c>
       <c r="AH3">
-        <v>819.05</v>
+        <v>819.23</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
       </c>
       <c r="AJ3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK3">
-        <v>25.08</v>
+        <v>24.27</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1121,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1920</v>
+        <v>1914.4</v>
       </c>
       <c r="D4">
-        <v>2.88</v>
+        <v>-0.29</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1133,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-1.03</v>
+        <v>-1.32</v>
       </c>
       <c r="H4">
-        <v>41.73</v>
+        <v>41.32</v>
       </c>
       <c r="I4">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="J4">
-        <v>6.21</v>
+        <v>5.72</v>
       </c>
       <c r="K4">
-        <v>23</v>
+        <v>21.58</v>
       </c>
       <c r="L4">
-        <v>30.52</v>
+        <v>30.14</v>
       </c>
       <c r="M4">
-        <v>30.57</v>
+        <v>30.96</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P4">
-        <v>1896.24</v>
+        <v>1904.12</v>
       </c>
       <c r="Q4">
-        <v>1810.75</v>
+        <v>1817.89</v>
       </c>
       <c r="R4">
-        <v>1727.18</v>
+        <v>1735.61</v>
       </c>
       <c r="S4">
-        <v>1662.21</v>
+        <v>1663.44</v>
       </c>
       <c r="T4">
-        <v>15.51</v>
+        <v>15.09</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,43 +1187,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>62.18</v>
+        <v>61.43</v>
       </c>
       <c r="Z4">
-        <v>44.87</v>
+        <v>46.28</v>
       </c>
       <c r="AA4">
-        <v>35.72</v>
+        <v>37.83</v>
       </c>
       <c r="AB4">
-        <v>9.15</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AC4">
-        <v>75.09999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="AD4">
-        <v>83.37</v>
+        <v>73.81</v>
       </c>
       <c r="AE4">
-        <v>58.66</v>
+        <v>56.83</v>
       </c>
       <c r="AF4">
-        <v>0.68</v>
+        <v>-10.42</v>
       </c>
       <c r="AG4">
-        <v>1942.29</v>
+        <v>1955.83</v>
       </c>
       <c r="AH4">
-        <v>1679.2</v>
+        <v>1679.95</v>
       </c>
       <c r="AI4">
         <v>1740.04</v>
       </c>
       <c r="AJ4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK4">
-        <v>29.03</v>
+        <v>30.37</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,58 +1234,58 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2098.3</v>
+        <v>2085.2</v>
       </c>
       <c r="D5">
-        <v>1.4</v>
+        <v>-0.62</v>
       </c>
       <c r="E5">
-        <v>2608.72</v>
+        <v>2494.57</v>
       </c>
       <c r="F5">
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.57</v>
+        <v>-16.41</v>
       </c>
       <c r="H5">
-        <v>20.21</v>
+        <v>19.45</v>
       </c>
       <c r="I5">
-        <v>-0.8</v>
+        <v>-1.43</v>
       </c>
       <c r="J5">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="K5">
-        <v>12.05</v>
+        <v>12.08</v>
       </c>
       <c r="L5">
-        <v>-17.14</v>
+        <v>-20.07</v>
       </c>
       <c r="M5">
-        <v>21.47</v>
+        <v>21.62</v>
       </c>
       <c r="N5">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P5">
-        <v>2090.52</v>
+        <v>2084.46</v>
       </c>
       <c r="Q5">
-        <v>2053.29</v>
+        <v>2053.97</v>
       </c>
       <c r="R5">
-        <v>1990.03</v>
+        <v>1995.98</v>
       </c>
       <c r="S5">
-        <v>2110.04</v>
+        <v>2109.62</v>
       </c>
       <c r="T5">
-        <v>-0.5600000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,43 +1300,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>58.96</v>
+        <v>56.47</v>
       </c>
       <c r="Z5">
-        <v>24.91</v>
+        <v>24.16</v>
       </c>
       <c r="AA5">
-        <v>23.35</v>
+        <v>23.51</v>
       </c>
       <c r="AB5">
-        <v>1.56</v>
+        <v>0.64</v>
       </c>
       <c r="AC5">
-        <v>63.14</v>
+        <v>61.33</v>
       </c>
       <c r="AD5">
-        <v>67.41</v>
+        <v>61.91</v>
       </c>
       <c r="AE5">
-        <v>54.53</v>
+        <v>52.39</v>
       </c>
       <c r="AF5">
-        <v>59.34</v>
+        <v>-75.89</v>
       </c>
       <c r="AG5">
-        <v>2125.72</v>
+        <v>2127.37</v>
       </c>
       <c r="AH5">
-        <v>1980.86</v>
+        <v>1980.57</v>
       </c>
       <c r="AI5">
         <v>1954.68</v>
       </c>
       <c r="AJ5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK5">
-        <v>18.77</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1347,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>791.25</v>
+        <v>788.5</v>
       </c>
       <c r="D6">
-        <v>-1.72</v>
+        <v>-0.35</v>
       </c>
       <c r="E6">
         <v>1196.6</v>
@@ -1388,46 +1359,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-33.88</v>
+        <v>-34.1</v>
       </c>
       <c r="H6">
-        <v>12.38</v>
+        <v>11.99</v>
       </c>
       <c r="I6">
-        <v>1.4</v>
+        <v>-1.82</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>0.48</v>
       </c>
       <c r="K6">
-        <v>-1.6</v>
+        <v>-2.09</v>
       </c>
       <c r="L6">
-        <v>-33.57</v>
+        <v>-34.04</v>
       </c>
       <c r="M6">
-        <v>16.23</v>
+        <v>16.39</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P6">
-        <v>806.49</v>
+        <v>803.5700000000001</v>
       </c>
       <c r="Q6">
-        <v>777.3</v>
+        <v>777.77</v>
       </c>
       <c r="R6">
-        <v>750.59</v>
+        <v>751.53</v>
       </c>
       <c r="S6">
-        <v>876.08</v>
+        <v>874.83</v>
       </c>
       <c r="T6">
-        <v>-9.68</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,43 +1413,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>55.63</v>
+        <v>54.65</v>
       </c>
       <c r="Z6">
-        <v>13.59</v>
+        <v>12.6</v>
       </c>
       <c r="AA6">
-        <v>10.66</v>
+        <v>11.04</v>
       </c>
       <c r="AB6">
-        <v>2.93</v>
+        <v>1.56</v>
       </c>
       <c r="AC6">
-        <v>51.98</v>
+        <v>36.61</v>
       </c>
       <c r="AD6">
-        <v>72.48</v>
+        <v>54.79</v>
       </c>
       <c r="AE6">
-        <v>21.72</v>
+        <v>21.94</v>
       </c>
       <c r="AF6">
-        <v>185.96</v>
+        <v>357.36</v>
       </c>
       <c r="AG6">
-        <v>816.5700000000001</v>
+        <v>817.36</v>
       </c>
       <c r="AH6">
-        <v>738.02</v>
+        <v>738.1799999999999</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
       </c>
       <c r="AJ6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK6">
-        <v>32.11</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,58 +1460,58 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2675.3</v>
+        <v>2608.9</v>
       </c>
       <c r="D7">
-        <v>-0.68</v>
+        <v>-2.48</v>
       </c>
       <c r="E7">
-        <v>3178.08</v>
+        <v>3163.9</v>
       </c>
       <c r="F7">
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-15.82</v>
+        <v>-17.54</v>
       </c>
       <c r="H7">
-        <v>41.44</v>
+        <v>37.93</v>
       </c>
       <c r="I7">
-        <v>1.79</v>
+        <v>-1.14</v>
       </c>
       <c r="J7">
-        <v>7.91</v>
+        <v>5.82</v>
       </c>
       <c r="K7">
-        <v>8.77</v>
+        <v>5.87</v>
       </c>
       <c r="L7">
-        <v>-14.08</v>
+        <v>-17.91</v>
       </c>
       <c r="M7">
-        <v>31.83</v>
+        <v>30.9</v>
       </c>
       <c r="N7">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O7">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="P7">
-        <v>2654.22</v>
+        <v>2648.22</v>
       </c>
       <c r="Q7">
-        <v>2577.43</v>
+        <v>2584.53</v>
       </c>
       <c r="R7">
-        <v>2544.16</v>
+        <v>2548.63</v>
       </c>
       <c r="S7">
-        <v>2362.05</v>
+        <v>2363.22</v>
       </c>
       <c r="T7">
-        <v>13.26</v>
+        <v>10.4</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,43 +1526,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>62.25</v>
+        <v>52.98</v>
       </c>
       <c r="Z7">
-        <v>35.14</v>
+        <v>31.72</v>
       </c>
       <c r="AA7">
-        <v>23.13</v>
+        <v>24.85</v>
       </c>
       <c r="AB7">
-        <v>12.01</v>
+        <v>6.87</v>
       </c>
       <c r="AC7">
-        <v>87.73999999999999</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="AD7">
-        <v>86.2</v>
+        <v>79.89</v>
       </c>
       <c r="AE7">
-        <v>84.06</v>
+        <v>85.98</v>
       </c>
       <c r="AF7">
-        <v>24.11</v>
+        <v>167.41</v>
       </c>
       <c r="AG7">
-        <v>2706.44</v>
+        <v>2703.15</v>
       </c>
       <c r="AH7">
-        <v>2448.43</v>
+        <v>2465.91</v>
       </c>
       <c r="AI7">
         <v>2439.82</v>
       </c>
       <c r="AJ7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK7">
-        <v>47.03</v>
+        <v>43.47</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1573,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8124.5</v>
+        <v>8017</v>
       </c>
       <c r="D8">
-        <v>-0.33</v>
+        <v>-1.32</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1614,46 +1585,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-20.6</v>
+        <v>-21.65</v>
       </c>
       <c r="H8">
-        <v>37.13</v>
+        <v>35.32</v>
       </c>
       <c r="I8">
-        <v>-0.99</v>
+        <v>-1.05</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="K8">
-        <v>17.61</v>
+        <v>16</v>
       </c>
       <c r="L8">
-        <v>-18.9</v>
+        <v>-18.25</v>
       </c>
       <c r="M8">
-        <v>14.75</v>
+        <v>14.95</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P8">
-        <v>8098.6</v>
+        <v>8081.6</v>
       </c>
       <c r="Q8">
-        <v>7948.2</v>
+        <v>7957.72</v>
       </c>
       <c r="R8">
-        <v>7709.92</v>
+        <v>7732.45</v>
       </c>
       <c r="S8">
-        <v>7439.56</v>
+        <v>7434.1</v>
       </c>
       <c r="T8">
-        <v>9.210000000000001</v>
+        <v>7.84</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,43 +1639,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.41</v>
+        <v>52.84</v>
       </c>
       <c r="Z8">
-        <v>123</v>
+        <v>109.5</v>
       </c>
       <c r="AA8">
-        <v>126.71</v>
+        <v>123.27</v>
       </c>
       <c r="AB8">
-        <v>-3.71</v>
+        <v>-13.77</v>
       </c>
       <c r="AC8">
-        <v>64.28</v>
+        <v>60.34</v>
       </c>
       <c r="AD8">
-        <v>62.05</v>
+        <v>62.12</v>
       </c>
       <c r="AE8">
-        <v>247.96</v>
+        <v>244.5</v>
       </c>
       <c r="AF8">
-        <v>-53.99</v>
+        <v>-54.44</v>
       </c>
       <c r="AG8">
-        <v>8524.09</v>
+        <v>8531.440000000001</v>
       </c>
       <c r="AH8">
-        <v>7372.31</v>
+        <v>7384.01</v>
       </c>
       <c r="AI8">
         <v>7451.92</v>
       </c>
       <c r="AJ8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK8">
-        <v>28.32</v>
+        <v>25.28</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1865,47 +1836,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,921 +1849,1040 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>2.73</v>
       </c>
-      <c r="E7" s="7">
-        <v>2.07</v>
+      <c r="D7" s="5">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="E7" s="6">
+        <v>6.66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-4.1</v>
       </c>
-      <c r="E8" s="8">
-        <v>-0.6</v>
+      <c r="D8" s="5">
+        <v>-2.71</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.39</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>4.15</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>6.21</v>
       </c>
+      <c r="D9" s="5">
+        <v>5.72</v>
+      </c>
       <c r="E9" s="7">
-        <v>2.06</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>2.73</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>1.47</v>
       </c>
-      <c r="E10" s="8">
-        <v>-1.26</v>
+      <c r="D10" s="5">
+        <v>1.22</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>7.46</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>4.3</v>
       </c>
-      <c r="E11" s="8">
-        <v>-3.16</v>
+      <c r="D11" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.82</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>7.75</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>7.91</v>
       </c>
+      <c r="D12" s="5">
+        <v>5.82</v>
+      </c>
       <c r="E12" s="7">
-        <v>0.16</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>5.77</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>3.6</v>
       </c>
-      <c r="E13" s="8">
-        <v>-2.17</v>
+      <c r="D13" s="5">
+        <v>2.53</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>3.12</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>2.33</v>
       </c>
-      <c r="E14" s="8">
-        <v>-0.79</v>
+      <c r="D14" s="5">
+        <v>8.84</v>
+      </c>
+      <c r="E14" s="6">
+        <v>6.51</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>1.81</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>6.4</v>
       </c>
+      <c r="D15" s="5">
+        <v>0.11</v>
+      </c>
       <c r="E15" s="7">
-        <v>4.59</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>1.68</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.8</v>
+      <c r="D16" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.42</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-0.21</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-0.8</v>
       </c>
-      <c r="E17" s="8">
-        <v>-0.59</v>
+      <c r="D17" s="5">
+        <v>-1.43</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>5.93</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>1.4</v>
       </c>
-      <c r="E18" s="8">
-        <v>-4.53</v>
+      <c r="D18" s="5">
+        <v>-1.82</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>4.38</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>1.79</v>
       </c>
-      <c r="E19" s="8">
-        <v>-2.59</v>
+      <c r="D19" s="5">
+        <v>-1.14</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.93</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-0.99</v>
       </c>
-      <c r="E20" s="8">
-        <v>-0.3</v>
+      <c r="D20" s="5">
+        <v>-1.05</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>18.7</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>22.41</v>
       </c>
-      <c r="E21" s="7">
-        <v>3.71</v>
+      <c r="D21" s="5">
+        <v>29.9</v>
+      </c>
+      <c r="E21" s="6">
+        <v>7.49</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>35.26</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>33.02</v>
       </c>
-      <c r="E22" s="8">
-        <v>-2.24</v>
+      <c r="D22" s="5">
+        <v>29.8</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3.22</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>31.29</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>30.52</v>
       </c>
-      <c r="E23" s="8">
-        <v>-0.77</v>
+      <c r="D23" s="5">
+        <v>30.14</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>-19.8</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>-17.14</v>
       </c>
+      <c r="D24" s="5">
+        <v>-20.07</v>
+      </c>
       <c r="E24" s="7">
-        <v>2.66</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-33.16</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>-33.57</v>
       </c>
-      <c r="E25" s="8">
-        <v>-0.41</v>
+      <c r="D25" s="5">
+        <v>-34.04</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>-13.26</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>-14.08</v>
       </c>
-      <c r="E26" s="8">
-        <v>-0.82</v>
+      <c r="D26" s="5">
+        <v>-17.91</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3.83</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>-16.79</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>-18.9</v>
       </c>
-      <c r="E27" s="8">
-        <v>-2.11</v>
+      <c r="D27" s="5">
+        <v>-18.25</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.65</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="6">
-        <v>5.58</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>11.14</v>
       </c>
-      <c r="E28" s="7">
-        <v>5.56</v>
+      <c r="D28" s="5">
+        <v>13.6</v>
+      </c>
+      <c r="E28" s="6">
+        <v>2.46</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6">
-        <v>2.44</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>5.43</v>
       </c>
+      <c r="D29" s="5">
+        <v>4.01</v>
+      </c>
       <c r="E29" s="7">
-        <v>2.99</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6">
-        <v>14.88</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>23</v>
       </c>
+      <c r="D30" s="5">
+        <v>21.58</v>
+      </c>
       <c r="E30" s="7">
-        <v>8.119999999999999</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6">
-        <v>10.88</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C31" s="5">
         <v>12.05</v>
       </c>
-      <c r="E31" s="7">
-        <v>1.17</v>
+      <c r="D31" s="5">
+        <v>12.08</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.03</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6">
-        <v>-1.81</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="5">
         <v>-1.6</v>
       </c>
+      <c r="D32" s="5">
+        <v>-2.09</v>
+      </c>
       <c r="E32" s="7">
-        <v>0.21</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="6">
-        <v>5.26</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C33" s="5">
         <v>8.77</v>
       </c>
+      <c r="D33" s="5">
+        <v>5.87</v>
+      </c>
       <c r="E33" s="7">
-        <v>3.51</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6">
-        <v>12.46</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="C34" s="5">
         <v>17.61</v>
       </c>
+      <c r="D34" s="5">
+        <v>16</v>
+      </c>
       <c r="E34" s="7">
-        <v>5.15</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="6">
-        <v>-11.65</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C35" s="5">
         <v>-9.720000000000001</v>
       </c>
-      <c r="E35" s="7">
-        <v>1.93</v>
+      <c r="D35" s="5">
+        <v>-5.47</v>
+      </c>
+      <c r="E35" s="6">
+        <v>4.25</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-9.98</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="6">
-        <v>-3.8</v>
-      </c>
-      <c r="D36" s="6">
+      <c r="C37" s="5">
         <v>-1.03</v>
       </c>
-      <c r="E36" s="7">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="D37" s="5">
+        <v>-1.32</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="6">
-        <v>-20.68</v>
-      </c>
-      <c r="D37" s="6">
+      <c r="C38" s="5">
         <v>-19.57</v>
       </c>
-      <c r="E37" s="7">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="D38" s="5">
+        <v>-16.41</v>
+      </c>
+      <c r="E38" s="6">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="6">
-        <v>-32.72</v>
-      </c>
-      <c r="D38" s="6">
+      <c r="C39" s="5">
         <v>-33.88</v>
       </c>
-      <c r="E38" s="8">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="D39" s="5">
+        <v>-34.1</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="6">
-        <v>-15.25</v>
-      </c>
-      <c r="D39" s="6">
+      <c r="C40" s="5">
         <v>-15.82</v>
       </c>
-      <c r="E39" s="8">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="D40" s="5">
+        <v>-17.54</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="6">
-        <v>-20.35</v>
-      </c>
-      <c r="D40" s="6">
+      <c r="C41" s="5">
         <v>-20.6</v>
       </c>
-      <c r="E40" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="D41" s="5">
+        <v>-21.65</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="6">
-        <v>1097</v>
-      </c>
-      <c r="D41" s="6">
+      <c r="C42" s="5">
         <v>1121</v>
       </c>
-      <c r="E41" s="7">
+      <c r="D42" s="5">
+        <v>1173.8</v>
+      </c>
+      <c r="E42" s="6">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>879</v>
+      </c>
+      <c r="D43" s="5">
+        <v>881</v>
+      </c>
+      <c r="E43" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1920</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1914.4</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2098.3</v>
+      </c>
+      <c r="D45" s="5">
+        <v>2085.2</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-13.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>791.25</v>
+      </c>
+      <c r="D46" s="5">
+        <v>788.5</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>2675.3</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2608.9</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-66.40000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>8124.5</v>
+      </c>
+      <c r="D48" s="5">
+        <v>8017</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-107.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>71</v>
+      </c>
+      <c r="D49" s="5">
+        <v>85</v>
+      </c>
+      <c r="E49" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5">
+        <v>85</v>
+      </c>
+      <c r="D50" s="5">
+        <v>71</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="5">
+        <v>29</v>
+      </c>
+      <c r="D51" s="5">
+        <v>43</v>
+      </c>
+      <c r="E51" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="5">
+        <v>43</v>
+      </c>
+      <c r="D52" s="5">
+        <v>29</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="C53" s="5">
+        <v>58.71</v>
+      </c>
+      <c r="D53" s="5">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="E53" s="6">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>48.46</v>
+      </c>
+      <c r="D54" s="5">
+        <v>48.95</v>
+      </c>
+      <c r="E54" s="6">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1866.2</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1920</v>
-      </c>
-      <c r="E42" s="7">
-        <v>53.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>62.18</v>
+      </c>
+      <c r="D55" s="5">
+        <v>61.43</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>2069.3</v>
-      </c>
-      <c r="D43" s="6">
-        <v>2098.3</v>
-      </c>
-      <c r="E43" s="7">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>58.96</v>
+      </c>
+      <c r="D56" s="5">
+        <v>56.47</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>805.1</v>
-      </c>
-      <c r="D44" s="6">
-        <v>791.25</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-13.85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>55.63</v>
+      </c>
+      <c r="D57" s="5">
+        <v>54.65</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>2693.5</v>
-      </c>
-      <c r="D45" s="6">
-        <v>2675.3</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-18.2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>62.25</v>
+      </c>
+      <c r="D58" s="5">
+        <v>52.98</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-9.27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>8151</v>
-      </c>
-      <c r="D46" s="6">
-        <v>8124.5</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-26.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>57.41</v>
+      </c>
+      <c r="D59" s="5">
+        <v>52.84</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-4.57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>53.8</v>
-      </c>
-      <c r="D47" s="6">
-        <v>58.71</v>
-      </c>
-      <c r="E47" s="7">
-        <v>4.91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>140.73</v>
+      </c>
+      <c r="D60" s="5">
+        <v>113.22</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-27.51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-70.88</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-74.02</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-3.14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>57.59</v>
-      </c>
-      <c r="D48" s="6">
-        <v>62.18</v>
-      </c>
-      <c r="E48" s="7">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
+        <v>0.68</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-10.42</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>54.87</v>
-      </c>
-      <c r="D49" s="6">
-        <v>58.96</v>
-      </c>
-      <c r="E49" s="7">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>59.34</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-75.89</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-135.23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>60.76</v>
-      </c>
-      <c r="D50" s="6">
-        <v>55.63</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-5.13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>185.96</v>
+      </c>
+      <c r="D64" s="5">
+        <v>357.36</v>
+      </c>
+      <c r="E64" s="6">
+        <v>171.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>65.15000000000001</v>
-      </c>
-      <c r="D51" s="6">
-        <v>62.25</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>24.11</v>
+      </c>
+      <c r="D65" s="5">
+        <v>167.41</v>
+      </c>
+      <c r="E65" s="6">
+        <v>143.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>58.56</v>
-      </c>
-      <c r="D52" s="6">
-        <v>57.41</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
+      <c r="B66" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C53" s="6">
-        <v>263.92</v>
-      </c>
-      <c r="D53" s="6">
-        <v>140.73</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-123.19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>-64.3</v>
-      </c>
-      <c r="D54" s="6">
-        <v>-70.88</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-6.58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>3.26</v>
-      </c>
-      <c r="D55" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="6">
-        <v>-16.16</v>
-      </c>
-      <c r="D56" s="6">
-        <v>59.34</v>
-      </c>
-      <c r="E56" s="7">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>-50.82</v>
-      </c>
-      <c r="D57" s="6">
-        <v>185.96</v>
-      </c>
-      <c r="E57" s="7">
-        <v>236.78</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>189.59</v>
-      </c>
-      <c r="D58" s="6">
-        <v>24.11</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-165.48</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>-43.14</v>
-      </c>
-      <c r="D59" s="6">
+      <c r="C66" s="5">
         <v>-53.99</v>
       </c>
-      <c r="E59" s="8">
-        <v>-10.85</v>
+      <c r="D66" s="5">
+        <v>-54.44</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -2853,60 +2908,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="11">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>56.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>57.7</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>3.2</v>
       </c>
-      <c r="G2" s="11">
-        <v>10.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="G2" s="10">
+        <v>10.2</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -3008,49 +3063,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.6277</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3183</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.3057</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2147</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1623</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1475</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.1023</v>
+      <c r="A2" s="13">
+        <v>0.6386999999999999</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3096</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.309</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.2162</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1639</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.1495</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.1099</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,61 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>49.0 → 50.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>49.0</t>
+  </si>
+  <si>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>53.0 → 71.5</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>53.0</t>
+  </si>
+  <si>
+    <t>71.5</t>
+  </si>
+  <si>
+    <t>54.6 → 49.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>54.6</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -224,7 +278,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -265,13 +319,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,6 +360,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,21 +441,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -397,7 +467,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -895,10 +965,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1173.8</v>
+        <v>1154.2</v>
       </c>
       <c r="D2">
-        <v>4.71</v>
+        <v>-1.67</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -907,46 +977,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-5.47</v>
+        <v>-7.05</v>
       </c>
       <c r="H2">
-        <v>56.85</v>
+        <v>54.23</v>
       </c>
       <c r="I2">
-        <v>8.84</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>9.390000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="K2">
-        <v>13.6</v>
+        <v>11.26</v>
       </c>
       <c r="L2">
-        <v>29.9</v>
+        <v>30.65</v>
       </c>
       <c r="M2">
-        <v>10.99</v>
+        <v>10.5</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>1108.52</v>
+        <v>1123.02</v>
       </c>
       <c r="Q2">
-        <v>1080.48</v>
+        <v>1084.1</v>
       </c>
       <c r="R2">
-        <v>1095.33</v>
+        <v>1097.95</v>
       </c>
       <c r="S2">
-        <v>928.78</v>
+        <v>930.03</v>
       </c>
       <c r="T2">
-        <v>26.38</v>
+        <v>24.1</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -961,43 +1031,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>67.01000000000001</v>
+        <v>62.03</v>
       </c>
       <c r="Z2">
-        <v>6.94</v>
+        <v>10.9</v>
       </c>
       <c r="AA2">
-        <v>-2.96</v>
+        <v>-0.19</v>
       </c>
       <c r="AB2">
-        <v>9.9</v>
+        <v>11.09</v>
       </c>
       <c r="AC2">
-        <v>100</v>
+        <v>93.42</v>
       </c>
       <c r="AD2">
-        <v>84.51000000000001</v>
+        <v>91.66</v>
       </c>
       <c r="AE2">
-        <v>42.33</v>
+        <v>42.83</v>
       </c>
       <c r="AF2">
-        <v>113.22</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="AG2">
-        <v>1136.01</v>
+        <v>1148.69</v>
       </c>
       <c r="AH2">
-        <v>1024.95</v>
+        <v>1019.51</v>
       </c>
       <c r="AI2">
-        <v>1017.47</v>
+        <v>1042.8</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>34.14</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1008,10 +1078,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="D3">
-        <v>0.23</v>
+        <v>0.79</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1020,25 +1090,25 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.779999999999999</v>
+        <v>-9.06</v>
       </c>
       <c r="H3">
-        <v>66.39</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="I3">
-        <v>0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="J3">
-        <v>-2.71</v>
+        <v>-2.83</v>
       </c>
       <c r="K3">
-        <v>4.01</v>
+        <v>4.69</v>
       </c>
       <c r="L3">
-        <v>29.8</v>
+        <v>30.77</v>
       </c>
       <c r="M3">
-        <v>63.87</v>
+        <v>62.54</v>
       </c>
       <c r="N3">
         <v>71</v>
@@ -1047,19 +1117,19 @@
         <v>73</v>
       </c>
       <c r="P3">
-        <v>880.9</v>
+        <v>880.6</v>
       </c>
       <c r="Q3">
-        <v>880.26</v>
+        <v>878.21</v>
       </c>
       <c r="R3">
-        <v>909.88</v>
+        <v>909.48</v>
       </c>
       <c r="S3">
-        <v>762.29</v>
+        <v>763.0700000000001</v>
       </c>
       <c r="T3">
-        <v>15.57</v>
+        <v>16.37</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1074,34 +1144,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.95</v>
+        <v>50.71</v>
       </c>
       <c r="Z3">
-        <v>-9.529999999999999</v>
+        <v>-7.8</v>
       </c>
       <c r="AA3">
-        <v>-12.55</v>
+        <v>-11.6</v>
       </c>
       <c r="AB3">
-        <v>3.02</v>
+        <v>3.8</v>
       </c>
       <c r="AC3">
-        <v>90.04000000000001</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="AD3">
-        <v>89.87</v>
+        <v>90.56</v>
       </c>
       <c r="AE3">
-        <v>26.41</v>
+        <v>25.67</v>
       </c>
       <c r="AF3">
-        <v>-74.02</v>
+        <v>-56.54</v>
       </c>
       <c r="AG3">
-        <v>941.3</v>
+        <v>934.92</v>
       </c>
       <c r="AH3">
-        <v>819.23</v>
+        <v>821.49</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1110,7 +1180,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>24.27</v>
+        <v>22.19</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1121,10 +1191,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1914.4</v>
+        <v>1917.6</v>
       </c>
       <c r="D4">
-        <v>-0.29</v>
+        <v>0.17</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1133,46 +1203,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-1.32</v>
+        <v>-1.15</v>
       </c>
       <c r="H4">
-        <v>41.32</v>
+        <v>41.55</v>
       </c>
       <c r="I4">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>5.72</v>
+        <v>8.25</v>
       </c>
       <c r="K4">
-        <v>21.58</v>
+        <v>22.37</v>
       </c>
       <c r="L4">
-        <v>30.14</v>
+        <v>31.9</v>
       </c>
       <c r="M4">
-        <v>30.96</v>
+        <v>30.46</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P4">
-        <v>1904.12</v>
+        <v>1911.64</v>
       </c>
       <c r="Q4">
-        <v>1817.89</v>
+        <v>1823.58</v>
       </c>
       <c r="R4">
-        <v>1735.61</v>
+        <v>1744.31</v>
       </c>
       <c r="S4">
-        <v>1663.44</v>
+        <v>1664.61</v>
       </c>
       <c r="T4">
-        <v>15.09</v>
+        <v>15.2</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1187,34 +1257,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>61.43</v>
+        <v>61.71</v>
       </c>
       <c r="Z4">
-        <v>46.28</v>
+        <v>47.12</v>
       </c>
       <c r="AA4">
-        <v>37.83</v>
+        <v>39.69</v>
       </c>
       <c r="AB4">
-        <v>8.449999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="AC4">
-        <v>64.98999999999999</v>
+        <v>70.69</v>
       </c>
       <c r="AD4">
-        <v>73.81</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="AE4">
-        <v>56.83</v>
+        <v>54.86</v>
       </c>
       <c r="AF4">
-        <v>-10.42</v>
+        <v>-67.5</v>
       </c>
       <c r="AG4">
-        <v>1955.83</v>
+        <v>1968.29</v>
       </c>
       <c r="AH4">
-        <v>1679.95</v>
+        <v>1678.86</v>
       </c>
       <c r="AI4">
         <v>1740.04</v>
@@ -1223,7 +1293,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>30.37</v>
+        <v>30.95</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1234,58 +1304,58 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2085.2</v>
+        <v>2073.3</v>
       </c>
       <c r="D5">
-        <v>-0.62</v>
+        <v>-0.57</v>
       </c>
       <c r="E5">
-        <v>2494.57</v>
+        <v>2436.99</v>
       </c>
       <c r="F5">
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-16.41</v>
+        <v>-14.92</v>
       </c>
       <c r="H5">
-        <v>19.45</v>
+        <v>18.77</v>
       </c>
       <c r="I5">
-        <v>-1.43</v>
+        <v>-0.63</v>
       </c>
       <c r="J5">
-        <v>1.22</v>
+        <v>0.08</v>
       </c>
       <c r="K5">
-        <v>12.08</v>
+        <v>11.45</v>
       </c>
       <c r="L5">
-        <v>-20.07</v>
+        <v>-16.89</v>
       </c>
       <c r="M5">
-        <v>21.62</v>
+        <v>21.27</v>
       </c>
       <c r="N5">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P5">
-        <v>2084.46</v>
+        <v>2081.84</v>
       </c>
       <c r="Q5">
-        <v>2053.97</v>
+        <v>2054.83</v>
       </c>
       <c r="R5">
-        <v>1995.98</v>
+        <v>2002.28</v>
       </c>
       <c r="S5">
-        <v>2109.62</v>
+        <v>2109.21</v>
       </c>
       <c r="T5">
-        <v>-1.16</v>
+        <v>-1.7</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1300,34 +1370,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>56.47</v>
+        <v>54.24</v>
       </c>
       <c r="Z5">
-        <v>24.16</v>
+        <v>22.34</v>
       </c>
       <c r="AA5">
-        <v>23.51</v>
+        <v>23.28</v>
       </c>
       <c r="AB5">
-        <v>0.64</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AC5">
-        <v>61.33</v>
+        <v>60.07</v>
       </c>
       <c r="AD5">
-        <v>61.91</v>
+        <v>61.52</v>
       </c>
       <c r="AE5">
-        <v>52.39</v>
+        <v>51.07</v>
       </c>
       <c r="AF5">
-        <v>-75.89</v>
+        <v>-18.38</v>
       </c>
       <c r="AG5">
-        <v>2127.37</v>
+        <v>2128.74</v>
       </c>
       <c r="AH5">
-        <v>1980.57</v>
+        <v>1980.92</v>
       </c>
       <c r="AI5">
         <v>1954.68</v>
@@ -1336,7 +1406,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>19.49</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1347,58 +1417,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>788.5</v>
+        <v>772.5</v>
       </c>
       <c r="D6">
-        <v>-0.35</v>
+        <v>-2.03</v>
       </c>
       <c r="E6">
-        <v>1196.6</v>
+        <v>1178</v>
       </c>
       <c r="F6">
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-34.1</v>
+        <v>-34.42</v>
       </c>
       <c r="H6">
-        <v>11.99</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="I6">
-        <v>-1.82</v>
+        <v>-6.15</v>
       </c>
       <c r="J6">
-        <v>0.48</v>
+        <v>-0.83</v>
       </c>
       <c r="K6">
-        <v>-2.09</v>
+        <v>-2.98</v>
       </c>
       <c r="L6">
-        <v>-34.04</v>
+        <v>-35.44</v>
       </c>
       <c r="M6">
-        <v>16.39</v>
+        <v>14.78</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P6">
-        <v>803.5700000000001</v>
+        <v>793.4400000000001</v>
       </c>
       <c r="Q6">
-        <v>777.77</v>
+        <v>777.46</v>
       </c>
       <c r="R6">
-        <v>751.53</v>
+        <v>751.88</v>
       </c>
       <c r="S6">
-        <v>874.83</v>
+        <v>873.47</v>
       </c>
       <c r="T6">
-        <v>-9.869999999999999</v>
+        <v>-11.56</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1413,34 +1483,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>54.65</v>
+        <v>49.18</v>
       </c>
       <c r="Z6">
-        <v>12.6</v>
+        <v>10.41</v>
       </c>
       <c r="AA6">
-        <v>11.04</v>
+        <v>10.92</v>
       </c>
       <c r="AB6">
-        <v>1.56</v>
+        <v>-0.51</v>
       </c>
       <c r="AC6">
-        <v>36.61</v>
+        <v>17.16</v>
       </c>
       <c r="AD6">
-        <v>54.79</v>
+        <v>35.25</v>
       </c>
       <c r="AE6">
-        <v>21.94</v>
+        <v>22.72</v>
       </c>
       <c r="AF6">
-        <v>357.36</v>
+        <v>126.32</v>
       </c>
       <c r="AG6">
-        <v>817.36</v>
+        <v>817.12</v>
       </c>
       <c r="AH6">
-        <v>738.1799999999999</v>
+        <v>737.8099999999999</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1449,7 +1519,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>29.89</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1460,58 +1530,58 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2608.9</v>
+        <v>2878.3</v>
       </c>
       <c r="D7">
-        <v>-2.48</v>
+        <v>10.33</v>
       </c>
       <c r="E7">
-        <v>3163.9</v>
+        <v>3047.85</v>
       </c>
       <c r="F7">
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-17.54</v>
+        <v>-5.56</v>
       </c>
       <c r="H7">
-        <v>37.93</v>
+        <v>52.17</v>
       </c>
       <c r="I7">
-        <v>-1.14</v>
+        <v>9.52</v>
       </c>
       <c r="J7">
-        <v>5.82</v>
+        <v>16.67</v>
       </c>
       <c r="K7">
-        <v>5.87</v>
+        <v>18.06</v>
       </c>
       <c r="L7">
-        <v>-17.91</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="M7">
-        <v>30.9</v>
+        <v>32.16</v>
       </c>
       <c r="N7">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="O7">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="P7">
-        <v>2648.22</v>
+        <v>2698.24</v>
       </c>
       <c r="Q7">
-        <v>2584.53</v>
+        <v>2604.02</v>
       </c>
       <c r="R7">
-        <v>2548.63</v>
+        <v>2557.37</v>
       </c>
       <c r="S7">
-        <v>2363.22</v>
+        <v>2365.06</v>
       </c>
       <c r="T7">
-        <v>10.4</v>
+        <v>21.7</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1526,43 +1596,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>52.98</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="Z7">
-        <v>31.72</v>
+        <v>50.17</v>
       </c>
       <c r="AA7">
-        <v>24.85</v>
+        <v>29.91</v>
       </c>
       <c r="AB7">
-        <v>6.87</v>
+        <v>20.26</v>
       </c>
       <c r="AC7">
         <v>65.56999999999999</v>
       </c>
       <c r="AD7">
-        <v>79.89</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="AE7">
-        <v>85.98</v>
+        <v>102.41</v>
       </c>
       <c r="AF7">
-        <v>167.41</v>
+        <v>1798.83</v>
       </c>
       <c r="AG7">
-        <v>2703.15</v>
+        <v>2773.43</v>
       </c>
       <c r="AH7">
-        <v>2465.91</v>
+        <v>2434.61</v>
       </c>
       <c r="AI7">
-        <v>2439.82</v>
+        <v>2480.26</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>43.47</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1573,10 +1643,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8017</v>
+        <v>7954.5</v>
       </c>
       <c r="D8">
-        <v>-1.32</v>
+        <v>-0.78</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1585,46 +1655,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-21.65</v>
+        <v>-22.27</v>
       </c>
       <c r="H8">
-        <v>35.32</v>
+        <v>34.26</v>
       </c>
       <c r="I8">
-        <v>-1.05</v>
+        <v>-1.21</v>
       </c>
       <c r="J8">
-        <v>2.53</v>
+        <v>1.64</v>
       </c>
       <c r="K8">
-        <v>16</v>
+        <v>15.53</v>
       </c>
       <c r="L8">
-        <v>-18.25</v>
+        <v>-17.63</v>
       </c>
       <c r="M8">
-        <v>14.95</v>
+        <v>13.87</v>
       </c>
       <c r="N8">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O8">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P8">
-        <v>8081.6</v>
+        <v>8062.1</v>
       </c>
       <c r="Q8">
-        <v>7957.72</v>
+        <v>7966.52</v>
       </c>
       <c r="R8">
-        <v>7732.45</v>
+        <v>7754.79</v>
       </c>
       <c r="S8">
-        <v>7434.1</v>
+        <v>7428.6</v>
       </c>
       <c r="T8">
-        <v>7.84</v>
+        <v>7.08</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1639,34 +1709,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>52.84</v>
+        <v>50.34</v>
       </c>
       <c r="Z8">
-        <v>109.5</v>
+        <v>92.69</v>
       </c>
       <c r="AA8">
-        <v>123.27</v>
+        <v>117.15</v>
       </c>
       <c r="AB8">
-        <v>-13.77</v>
+        <v>-24.46</v>
       </c>
       <c r="AC8">
-        <v>60.34</v>
+        <v>37.2</v>
       </c>
       <c r="AD8">
-        <v>62.12</v>
+        <v>53.94</v>
       </c>
       <c r="AE8">
-        <v>244.5</v>
+        <v>237.78</v>
       </c>
       <c r="AF8">
-        <v>-54.44</v>
+        <v>-58</v>
       </c>
       <c r="AG8">
-        <v>8531.440000000001</v>
+        <v>8534.030000000001</v>
       </c>
       <c r="AH8">
-        <v>7384.01</v>
+        <v>7399.02</v>
       </c>
       <c r="AI8">
         <v>7451.92</v>
@@ -1675,7 +1745,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>25.28</v>
+        <v>22.49</v>
       </c>
     </row>
   </sheetData>
@@ -1816,7 +1886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1836,1059 +1906,1117 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="A5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>55</v>
       </c>
+      <c r="C5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>2.73</v>
-      </c>
-      <c r="D7" s="5">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="E7" s="6">
-        <v>6.66</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="8">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="D9" s="8">
+        <v>8.25</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-4.1</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="8">
         <v>-2.71</v>
       </c>
-      <c r="E8" s="6">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="8">
+        <v>-2.83</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>6.21</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="8">
         <v>5.72</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="8">
+        <v>8.25</v>
+      </c>
+      <c r="E11" s="10">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C12" s="8">
         <v>1.22</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D12" s="8">
+        <v>0.08</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>4.3</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C13" s="8">
         <v>0.48</v>
       </c>
-      <c r="E11" s="7">
-        <v>-3.82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D13" s="8">
+        <v>-0.83</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>7.91</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C14" s="8">
         <v>5.82</v>
       </c>
-      <c r="E12" s="7">
+      <c r="D14" s="8">
+        <v>16.67</v>
+      </c>
+      <c r="E14" s="10">
+        <v>10.85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8">
+        <v>2.53</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1.64</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="8">
+        <v>8.84</v>
+      </c>
+      <c r="D16" s="8">
+        <v>6.7</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.11</v>
+      </c>
+      <c r="D17" s="8">
+        <v>-0.17</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="D18" s="8">
+        <v>2</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="8">
+        <v>-1.43</v>
+      </c>
+      <c r="D19" s="8">
+        <v>-0.63</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="8">
+        <v>-1.82</v>
+      </c>
+      <c r="D20" s="8">
+        <v>-6.15</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-4.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-1.14</v>
+      </c>
+      <c r="D21" s="8">
+        <v>9.52</v>
+      </c>
+      <c r="E21" s="10">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>-1.05</v>
+      </c>
+      <c r="D22" s="8">
+        <v>-1.21</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="8">
+        <v>29.9</v>
+      </c>
+      <c r="D23" s="8">
+        <v>30.65</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="8">
+        <v>29.8</v>
+      </c>
+      <c r="D24" s="8">
+        <v>30.77</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="8">
+        <v>30.14</v>
+      </c>
+      <c r="D25" s="8">
+        <v>31.9</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="8">
+        <v>-20.07</v>
+      </c>
+      <c r="D26" s="8">
+        <v>-16.89</v>
+      </c>
+      <c r="E26" s="10">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-34.04</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-35.44</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="8">
+        <v>-17.91</v>
+      </c>
+      <c r="D28" s="8">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="E28" s="10">
+        <v>8.880000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8">
+        <v>-18.25</v>
+      </c>
+      <c r="D29" s="8">
+        <v>-17.63</v>
+      </c>
+      <c r="E29" s="10">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="8">
+        <v>13.6</v>
+      </c>
+      <c r="D30" s="8">
+        <v>11.26</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="8">
+        <v>4.01</v>
+      </c>
+      <c r="D31" s="8">
+        <v>4.69</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="8">
+        <v>21.58</v>
+      </c>
+      <c r="D32" s="8">
+        <v>22.37</v>
+      </c>
+      <c r="E32" s="10">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="8">
+        <v>12.08</v>
+      </c>
+      <c r="D33" s="8">
+        <v>11.45</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="8">
         <v>-2.09</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D34" s="8">
+        <v>-2.98</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="8">
+        <v>5.87</v>
+      </c>
+      <c r="D35" s="8">
+        <v>18.06</v>
+      </c>
+      <c r="E35" s="10">
+        <v>12.19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="D13" s="5">
-        <v>2.53</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="8">
+        <v>16</v>
+      </c>
+      <c r="D36" s="8">
+        <v>15.53</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>2.33</v>
-      </c>
-      <c r="D14" s="5">
-        <v>8.84</v>
-      </c>
-      <c r="E14" s="6">
-        <v>6.51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="8">
+        <v>-5.47</v>
+      </c>
+      <c r="D37" s="8">
+        <v>-7.05</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>6.4</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-6.29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="8">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="D38" s="8">
+        <v>-9.06</v>
+      </c>
+      <c r="E38" s="10">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1.68</v>
-      </c>
-      <c r="D16" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-1.32</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-1.15</v>
+      </c>
+      <c r="E39" s="10">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.8</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-1.43</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="8">
+        <v>-16.41</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-14.92</v>
+      </c>
+      <c r="E40" s="10">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.82</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B41" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="8">
+        <v>-34.1</v>
+      </c>
+      <c r="D41" s="8">
+        <v>-34.42</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-1.14</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="8">
+        <v>-17.54</v>
+      </c>
+      <c r="D42" s="8">
+        <v>-5.56</v>
+      </c>
+      <c r="E42" s="10">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-0.99</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-1.05</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B43" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-21.65</v>
+      </c>
+      <c r="D43" s="8">
+        <v>-22.27</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>22.41</v>
-      </c>
-      <c r="D21" s="5">
-        <v>29.9</v>
-      </c>
-      <c r="E21" s="6">
-        <v>7.49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B44" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1173.8</v>
+      </c>
+      <c r="D44" s="8">
+        <v>1154.2</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-19.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>33.02</v>
-      </c>
-      <c r="D22" s="5">
-        <v>29.8</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B45" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="8">
+        <v>881</v>
+      </c>
+      <c r="D45" s="8">
+        <v>888</v>
+      </c>
+      <c r="E45" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>30.52</v>
-      </c>
-      <c r="D23" s="5">
-        <v>30.14</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B46" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1914.4</v>
+      </c>
+      <c r="D46" s="8">
+        <v>1917.6</v>
+      </c>
+      <c r="E46" s="10">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-17.14</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-20.07</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B47" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="8">
+        <v>2085.2</v>
+      </c>
+      <c r="D47" s="8">
+        <v>2073.3</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-11.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-33.57</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-34.04</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B48" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="8">
+        <v>788.5</v>
+      </c>
+      <c r="D48" s="8">
+        <v>772.5</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-14.08</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-17.91</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B49" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="8">
+        <v>2608.9</v>
+      </c>
+      <c r="D49" s="8">
+        <v>2878.3</v>
+      </c>
+      <c r="E49" s="10">
+        <v>269.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-18.9</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-18.25</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B50" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="8">
+        <v>8017</v>
+      </c>
+      <c r="D50" s="8">
+        <v>7954.5</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-62.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="8">
+        <v>43</v>
+      </c>
+      <c r="D51" s="8">
+        <v>29</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="8">
+        <v>29</v>
+      </c>
+      <c r="D52" s="8">
+        <v>57</v>
+      </c>
+      <c r="E52" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="8">
+        <v>57</v>
+      </c>
+      <c r="D53" s="8">
+        <v>43</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>11.14</v>
-      </c>
-      <c r="D28" s="5">
-        <v>13.6</v>
-      </c>
-      <c r="E28" s="6">
-        <v>2.46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="8">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="D54" s="8">
+        <v>62.03</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-4.98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>5.43</v>
-      </c>
-      <c r="D29" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B55" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="8">
+        <v>48.95</v>
+      </c>
+      <c r="D55" s="8">
+        <v>50.71</v>
+      </c>
+      <c r="E55" s="10">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>23</v>
-      </c>
-      <c r="D30" s="5">
-        <v>21.58</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B56" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="8">
+        <v>61.43</v>
+      </c>
+      <c r="D56" s="8">
+        <v>61.71</v>
+      </c>
+      <c r="E56" s="10">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>12.05</v>
-      </c>
-      <c r="D31" s="5">
-        <v>12.08</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B57" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="8">
+        <v>56.47</v>
+      </c>
+      <c r="D57" s="8">
+        <v>54.24</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-2.09</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="8">
+        <v>54.65</v>
+      </c>
+      <c r="D58" s="8">
+        <v>49.18</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-5.47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>8.77</v>
-      </c>
-      <c r="D33" s="5">
-        <v>5.87</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B59" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="8">
+        <v>52.98</v>
+      </c>
+      <c r="D59" s="8">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="E59" s="10">
+        <v>18.53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>17.61</v>
-      </c>
-      <c r="D34" s="5">
-        <v>16</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B60" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="8">
+        <v>52.84</v>
+      </c>
+      <c r="D60" s="8">
+        <v>50.34</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-5.47</v>
-      </c>
-      <c r="E35" s="6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B61" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="8">
+        <v>113.22</v>
+      </c>
+      <c r="D61" s="8">
+        <v>64.56999999999999</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-48.65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-9.98</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B62" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="8">
+        <v>-74.02</v>
+      </c>
+      <c r="D62" s="8">
+        <v>-56.54</v>
+      </c>
+      <c r="E62" s="10">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-1.03</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-1.32</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B63" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="8">
+        <v>-10.42</v>
+      </c>
+      <c r="D63" s="8">
+        <v>-67.5</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-57.08</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-19.57</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-16.41</v>
-      </c>
-      <c r="E38" s="6">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B64" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="8">
+        <v>-75.89</v>
+      </c>
+      <c r="D64" s="8">
+        <v>-18.38</v>
+      </c>
+      <c r="E64" s="10">
+        <v>57.51</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-33.88</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-34.1</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B65" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="8">
+        <v>357.36</v>
+      </c>
+      <c r="D65" s="8">
+        <v>126.32</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-231.04</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-15.82</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-17.54</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B66" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="8">
+        <v>167.41</v>
+      </c>
+      <c r="D66" s="8">
+        <v>1798.83</v>
+      </c>
+      <c r="E66" s="10">
+        <v>1631.42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-20.6</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-21.65</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1121</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1173.8</v>
-      </c>
-      <c r="E42" s="6">
-        <v>52.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>879</v>
-      </c>
-      <c r="D43" s="5">
-        <v>881</v>
-      </c>
-      <c r="E43" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1920</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1914.4</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>2098.3</v>
-      </c>
-      <c r="D45" s="5">
-        <v>2085.2</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-13.1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>791.25</v>
-      </c>
-      <c r="D46" s="5">
-        <v>788.5</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>2675.3</v>
-      </c>
-      <c r="D47" s="5">
-        <v>2608.9</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-66.40000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>8124.5</v>
-      </c>
-      <c r="D48" s="5">
-        <v>8017</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-107.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5">
-        <v>71</v>
-      </c>
-      <c r="D49" s="5">
-        <v>85</v>
-      </c>
-      <c r="E49" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5">
-        <v>85</v>
-      </c>
-      <c r="D50" s="5">
-        <v>71</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="5">
-        <v>29</v>
-      </c>
-      <c r="D51" s="5">
-        <v>43</v>
-      </c>
-      <c r="E51" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="5">
-        <v>43</v>
-      </c>
-      <c r="D52" s="5">
-        <v>29</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>58.71</v>
-      </c>
-      <c r="D53" s="5">
-        <v>67.01000000000001</v>
-      </c>
-      <c r="E53" s="6">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>48.46</v>
-      </c>
-      <c r="D54" s="5">
-        <v>48.95</v>
-      </c>
-      <c r="E54" s="6">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>62.18</v>
-      </c>
-      <c r="D55" s="5">
-        <v>61.43</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>58.96</v>
-      </c>
-      <c r="D56" s="5">
-        <v>56.47</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>55.63</v>
-      </c>
-      <c r="D57" s="5">
-        <v>54.65</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>62.25</v>
-      </c>
-      <c r="D58" s="5">
-        <v>52.98</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-9.27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>57.41</v>
-      </c>
-      <c r="D59" s="5">
-        <v>52.84</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-4.57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="3" t="s">
+      <c r="B67" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="5">
-        <v>140.73</v>
-      </c>
-      <c r="D60" s="5">
-        <v>113.22</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-27.51</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-70.88</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-74.02</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-3.14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>0.68</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-10.42</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-11.1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>59.34</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-75.89</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-135.23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>185.96</v>
-      </c>
-      <c r="D64" s="5">
-        <v>357.36</v>
-      </c>
-      <c r="E64" s="6">
-        <v>171.4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>24.11</v>
-      </c>
-      <c r="D65" s="5">
-        <v>167.41</v>
-      </c>
-      <c r="E65" s="6">
-        <v>143.3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-53.99</v>
-      </c>
-      <c r="D66" s="5">
+      <c r="C67" s="8">
         <v>-54.44</v>
       </c>
-      <c r="E66" s="7">
-        <v>-0.45</v>
+      <c r="D67" s="8">
+        <v>-58</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-3.56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2908,60 +3036,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="13">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="14">
+        <v>7</v>
+      </c>
+      <c r="D2" s="13">
+        <v>57.1</v>
+      </c>
+      <c r="E2" s="13">
+        <v>70</v>
+      </c>
+      <c r="F2" s="13">
+        <v>4.5</v>
+      </c>
+      <c r="G2" s="13">
+        <v>11.5</v>
+      </c>
+      <c r="H2" s="13">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>56.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>70</v>
-      </c>
-      <c r="F2" s="10">
-        <v>3.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>10.2</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="13">
         <v>40</v>
       </c>
     </row>
@@ -3063,49 +3191,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.6386999999999999</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3096</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.309</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.2162</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1639</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1495</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.1099</v>
+      <c r="A2" s="16">
+        <v>0.6254</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.3215999999999999</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.3046</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.2127</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1478</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.1387</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.105</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,43 +190,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.0 → 50.7</t>
+    <t>49.2 → 51.7</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>49.0</t>
-  </si>
-  <si>
-    <t>50.7</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>53.0 → 71.5</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>53.0</t>
-  </si>
-  <si>
-    <t>71.5</t>
-  </si>
-  <si>
-    <t>54.6 → 49.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.6</t>
-  </si>
-  <si>
     <t>49.2</t>
+  </si>
+  <si>
+    <t>51.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -278,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,20 +292,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,12 +326,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -449,16 +409,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -467,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -965,10 +923,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1154.2</v>
+        <v>1184.6</v>
       </c>
       <c r="D2">
-        <v>-1.67</v>
+        <v>2.63</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -977,46 +935,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-7.05</v>
+        <v>-4.6</v>
       </c>
       <c r="H2">
-        <v>54.23</v>
+        <v>58.29</v>
       </c>
       <c r="I2">
-        <v>6.7</v>
+        <v>10.8</v>
       </c>
       <c r="J2">
-        <v>8.25</v>
+        <v>9.5</v>
       </c>
       <c r="K2">
-        <v>11.26</v>
+        <v>7.46</v>
       </c>
       <c r="L2">
-        <v>30.65</v>
+        <v>38.68</v>
       </c>
       <c r="M2">
-        <v>10.5</v>
+        <v>10.71</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>1123.02</v>
+        <v>1146.12</v>
       </c>
       <c r="Q2">
-        <v>1084.1</v>
+        <v>1089.06</v>
       </c>
       <c r="R2">
-        <v>1097.95</v>
+        <v>1101.41</v>
       </c>
       <c r="S2">
-        <v>930.03</v>
+        <v>931.48</v>
       </c>
       <c r="T2">
-        <v>24.1</v>
+        <v>27.17</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1031,34 +989,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>62.03</v>
+        <v>66.22</v>
       </c>
       <c r="Z2">
-        <v>10.9</v>
+        <v>16.3</v>
       </c>
       <c r="AA2">
-        <v>-0.19</v>
+        <v>3.11</v>
       </c>
       <c r="AB2">
-        <v>11.09</v>
+        <v>13.19</v>
       </c>
       <c r="AC2">
-        <v>93.42</v>
+        <v>92.37</v>
       </c>
       <c r="AD2">
-        <v>91.66</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="AE2">
-        <v>42.83</v>
+        <v>44.07</v>
       </c>
       <c r="AF2">
-        <v>64.56999999999999</v>
+        <v>30.26</v>
       </c>
       <c r="AG2">
-        <v>1148.69</v>
+        <v>1167.77</v>
       </c>
       <c r="AH2">
-        <v>1019.51</v>
+        <v>1010.36</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1067,7 +1025,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>39.28</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1078,10 +1036,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>888</v>
+        <v>886.55</v>
       </c>
       <c r="D3">
-        <v>0.79</v>
+        <v>-0.16</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1090,46 +1048,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.06</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="H3">
-        <v>67.70999999999999</v>
+        <v>67.44</v>
       </c>
       <c r="I3">
-        <v>-0.17</v>
+        <v>1.2</v>
       </c>
       <c r="J3">
-        <v>-2.83</v>
+        <v>-4.58</v>
       </c>
       <c r="K3">
-        <v>4.69</v>
+        <v>5.77</v>
       </c>
       <c r="L3">
-        <v>30.77</v>
+        <v>30.37</v>
       </c>
       <c r="M3">
-        <v>62.54</v>
+        <v>62.16</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P3">
-        <v>880.6</v>
+        <v>882.71</v>
       </c>
       <c r="Q3">
-        <v>878.21</v>
+        <v>876.4400000000001</v>
       </c>
       <c r="R3">
-        <v>909.48</v>
+        <v>909.08</v>
       </c>
       <c r="S3">
-        <v>763.0700000000001</v>
+        <v>763.89</v>
       </c>
       <c r="T3">
-        <v>16.37</v>
+        <v>16.06</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1144,34 +1102,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>50.71</v>
+        <v>50.32</v>
       </c>
       <c r="Z3">
-        <v>-7.8</v>
+        <v>-6.46</v>
       </c>
       <c r="AA3">
-        <v>-11.6</v>
+        <v>-10.57</v>
       </c>
       <c r="AB3">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="AC3">
-        <v>93.65000000000001</v>
+        <v>96.58</v>
       </c>
       <c r="AD3">
-        <v>90.56</v>
+        <v>93.42</v>
       </c>
       <c r="AE3">
-        <v>25.67</v>
+        <v>25.01</v>
       </c>
       <c r="AF3">
-        <v>-56.54</v>
+        <v>-65.15000000000001</v>
       </c>
       <c r="AG3">
-        <v>934.92</v>
+        <v>929.5</v>
       </c>
       <c r="AH3">
-        <v>821.49</v>
+        <v>823.38</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1180,7 +1138,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>22.19</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1191,10 +1149,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1917.6</v>
+        <v>1927.9</v>
       </c>
       <c r="D4">
-        <v>0.17</v>
+        <v>0.54</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1203,46 +1161,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-1.15</v>
+        <v>-0.62</v>
       </c>
       <c r="H4">
-        <v>41.55</v>
+        <v>42.31</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>-0.62</v>
       </c>
       <c r="J4">
-        <v>8.25</v>
+        <v>6.87</v>
       </c>
       <c r="K4">
-        <v>22.37</v>
+        <v>24.68</v>
       </c>
       <c r="L4">
-        <v>31.9</v>
+        <v>29.66</v>
       </c>
       <c r="M4">
-        <v>30.46</v>
+        <v>31.05</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P4">
-        <v>1911.64</v>
+        <v>1909.22</v>
       </c>
       <c r="Q4">
-        <v>1823.58</v>
+        <v>1830.52</v>
       </c>
       <c r="R4">
-        <v>1744.31</v>
+        <v>1753.45</v>
       </c>
       <c r="S4">
-        <v>1664.61</v>
+        <v>1665.59</v>
       </c>
       <c r="T4">
-        <v>15.2</v>
+        <v>15.75</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1257,43 +1215,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>61.71</v>
+        <v>62.66</v>
       </c>
       <c r="Z4">
-        <v>47.12</v>
+        <v>48.05</v>
       </c>
       <c r="AA4">
-        <v>39.69</v>
+        <v>41.36</v>
       </c>
       <c r="AB4">
-        <v>7.43</v>
+        <v>6.69</v>
       </c>
       <c r="AC4">
-        <v>70.69</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="AD4">
-        <v>70.26000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="AE4">
-        <v>54.86</v>
+        <v>53.26</v>
       </c>
       <c r="AF4">
-        <v>-67.5</v>
+        <v>-46.59</v>
       </c>
       <c r="AG4">
-        <v>1968.29</v>
+        <v>1981.45</v>
       </c>
       <c r="AH4">
-        <v>1678.86</v>
+        <v>1679.58</v>
       </c>
       <c r="AI4">
-        <v>1740.04</v>
+        <v>1751.87</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>30.95</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1304,58 +1262,58 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2073.3</v>
+        <v>2088.8</v>
       </c>
       <c r="D5">
-        <v>-0.57</v>
+        <v>0.75</v>
       </c>
       <c r="E5">
-        <v>2436.99</v>
+        <v>2432.01</v>
       </c>
       <c r="F5">
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-14.92</v>
+        <v>-14.11</v>
       </c>
       <c r="H5">
-        <v>18.77</v>
+        <v>19.66</v>
       </c>
       <c r="I5">
-        <v>-0.63</v>
+        <v>0.27</v>
       </c>
       <c r="J5">
-        <v>0.08</v>
+        <v>1.59</v>
       </c>
       <c r="K5">
-        <v>11.45</v>
+        <v>11.95</v>
       </c>
       <c r="L5">
-        <v>-16.89</v>
+        <v>-14.29</v>
       </c>
       <c r="M5">
-        <v>21.27</v>
+        <v>21.1</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>2081.84</v>
+        <v>2082.98</v>
       </c>
       <c r="Q5">
-        <v>2054.83</v>
+        <v>2058.16</v>
       </c>
       <c r="R5">
-        <v>2002.28</v>
+        <v>2009.15</v>
       </c>
       <c r="S5">
-        <v>2109.21</v>
+        <v>2108.88</v>
       </c>
       <c r="T5">
-        <v>-1.7</v>
+        <v>-0.95</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1370,34 +1328,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>54.24</v>
+        <v>56.64</v>
       </c>
       <c r="Z5">
-        <v>22.34</v>
+        <v>21.9</v>
       </c>
       <c r="AA5">
-        <v>23.28</v>
+        <v>23</v>
       </c>
       <c r="AB5">
-        <v>-0.9399999999999999</v>
+        <v>-1.1</v>
       </c>
       <c r="AC5">
-        <v>60.07</v>
+        <v>52.48</v>
       </c>
       <c r="AD5">
-        <v>61.52</v>
+        <v>57.96</v>
       </c>
       <c r="AE5">
-        <v>51.07</v>
+        <v>49.4</v>
       </c>
       <c r="AF5">
-        <v>-18.38</v>
+        <v>-53.98</v>
       </c>
       <c r="AG5">
-        <v>2128.74</v>
+        <v>2131.88</v>
       </c>
       <c r="AH5">
-        <v>1980.92</v>
+        <v>1984.44</v>
       </c>
       <c r="AI5">
         <v>1954.68</v>
@@ -1406,7 +1364,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>17.4</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1417,10 +1375,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>772.5</v>
+        <v>780.3</v>
       </c>
       <c r="D6">
-        <v>-2.03</v>
+        <v>1.01</v>
       </c>
       <c r="E6">
         <v>1178</v>
@@ -1429,46 +1387,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-34.42</v>
+        <v>-33.76</v>
       </c>
       <c r="H6">
-        <v>9.710000000000001</v>
+        <v>10.82</v>
       </c>
       <c r="I6">
-        <v>-6.15</v>
+        <v>-3.65</v>
       </c>
       <c r="J6">
-        <v>-0.83</v>
+        <v>0.21</v>
       </c>
       <c r="K6">
-        <v>-2.98</v>
+        <v>-1.16</v>
       </c>
       <c r="L6">
-        <v>-35.44</v>
+        <v>-31.74</v>
       </c>
       <c r="M6">
-        <v>14.78</v>
+        <v>15.35</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P6">
-        <v>793.4400000000001</v>
+        <v>787.53</v>
       </c>
       <c r="Q6">
-        <v>777.46</v>
+        <v>777.95</v>
       </c>
       <c r="R6">
-        <v>751.88</v>
+        <v>752.34</v>
       </c>
       <c r="S6">
-        <v>873.47</v>
+        <v>872.1799999999999</v>
       </c>
       <c r="T6">
-        <v>-11.56</v>
+        <v>-10.53</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1483,34 +1441,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>49.18</v>
+        <v>51.72</v>
       </c>
       <c r="Z6">
-        <v>10.41</v>
+        <v>9.19</v>
       </c>
       <c r="AA6">
-        <v>10.92</v>
+        <v>10.57</v>
       </c>
       <c r="AB6">
-        <v>-0.51</v>
+        <v>-1.38</v>
       </c>
       <c r="AC6">
-        <v>17.16</v>
+        <v>12.13</v>
       </c>
       <c r="AD6">
-        <v>35.25</v>
+        <v>21.97</v>
       </c>
       <c r="AE6">
-        <v>22.72</v>
+        <v>22.67</v>
       </c>
       <c r="AF6">
-        <v>126.32</v>
+        <v>-18.78</v>
       </c>
       <c r="AG6">
-        <v>817.12</v>
+        <v>817.49</v>
       </c>
       <c r="AH6">
-        <v>737.8099999999999</v>
+        <v>738.42</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1519,7 +1477,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>28.19</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1530,58 +1488,58 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2878.3</v>
+        <v>2887.6</v>
       </c>
       <c r="D7">
-        <v>10.33</v>
+        <v>0.32</v>
       </c>
       <c r="E7">
-        <v>3047.85</v>
+        <v>2959.97</v>
       </c>
       <c r="F7">
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-5.56</v>
+        <v>-2.44</v>
       </c>
       <c r="H7">
-        <v>52.17</v>
+        <v>52.67</v>
       </c>
       <c r="I7">
-        <v>9.52</v>
+        <v>9.58</v>
       </c>
       <c r="J7">
-        <v>16.67</v>
+        <v>16.04</v>
       </c>
       <c r="K7">
-        <v>18.06</v>
+        <v>20.92</v>
       </c>
       <c r="L7">
-        <v>-9.029999999999999</v>
+        <v>-5.26</v>
       </c>
       <c r="M7">
-        <v>32.16</v>
+        <v>29.19</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="P7">
-        <v>2698.24</v>
+        <v>2748.72</v>
       </c>
       <c r="Q7">
-        <v>2604.02</v>
+        <v>2625.7</v>
       </c>
       <c r="R7">
-        <v>2557.37</v>
+        <v>2566.46</v>
       </c>
       <c r="S7">
-        <v>2365.06</v>
+        <v>2367.14</v>
       </c>
       <c r="T7">
-        <v>21.7</v>
+        <v>21.99</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1596,43 +1554,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>71.51000000000001</v>
+        <v>71.92</v>
       </c>
       <c r="Z7">
-        <v>50.17</v>
+        <v>64.8</v>
       </c>
       <c r="AA7">
-        <v>29.91</v>
+        <v>36.89</v>
       </c>
       <c r="AB7">
-        <v>20.26</v>
+        <v>27.91</v>
       </c>
       <c r="AC7">
-        <v>65.56999999999999</v>
+        <v>72.11</v>
       </c>
       <c r="AD7">
-        <v>72.95999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="AE7">
-        <v>102.41</v>
+        <v>107.32</v>
       </c>
       <c r="AF7">
-        <v>1798.83</v>
+        <v>474.08</v>
       </c>
       <c r="AG7">
-        <v>2773.43</v>
+        <v>2822.95</v>
       </c>
       <c r="AH7">
-        <v>2434.61</v>
+        <v>2428.46</v>
       </c>
       <c r="AI7">
-        <v>2480.26</v>
+        <v>2612.49</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>46.16</v>
+        <v>49.46</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1643,10 +1601,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7954.5</v>
+        <v>7985</v>
       </c>
       <c r="D8">
-        <v>-0.78</v>
+        <v>0.38</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1655,46 +1613,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-22.27</v>
+        <v>-21.97</v>
       </c>
       <c r="H8">
-        <v>34.26</v>
+        <v>34.78</v>
       </c>
       <c r="I8">
-        <v>-1.21</v>
+        <v>-0.97</v>
       </c>
       <c r="J8">
-        <v>1.64</v>
+        <v>2.65</v>
       </c>
       <c r="K8">
-        <v>15.53</v>
+        <v>15.86</v>
       </c>
       <c r="L8">
-        <v>-17.63</v>
+        <v>-18.06</v>
       </c>
       <c r="M8">
-        <v>13.87</v>
+        <v>14.25</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P8">
-        <v>8062.1</v>
+        <v>8046.4</v>
       </c>
       <c r="Q8">
-        <v>7966.52</v>
+        <v>7976.7</v>
       </c>
       <c r="R8">
-        <v>7754.79</v>
+        <v>7777.85</v>
       </c>
       <c r="S8">
-        <v>7428.6</v>
+        <v>7423.98</v>
       </c>
       <c r="T8">
-        <v>7.08</v>
+        <v>7.56</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1709,34 +1667,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>50.34</v>
+        <v>51.55</v>
       </c>
       <c r="Z8">
-        <v>92.69</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AA8">
-        <v>117.15</v>
+        <v>109.9</v>
       </c>
       <c r="AB8">
-        <v>-24.46</v>
+        <v>-29</v>
       </c>
       <c r="AC8">
-        <v>37.2</v>
+        <v>18.11</v>
       </c>
       <c r="AD8">
-        <v>53.94</v>
+        <v>38.55</v>
       </c>
       <c r="AE8">
-        <v>237.78</v>
+        <v>230.8</v>
       </c>
       <c r="AF8">
-        <v>-58</v>
+        <v>-55.83</v>
       </c>
       <c r="AG8">
-        <v>8534.030000000001</v>
+        <v>8537.49</v>
       </c>
       <c r="AH8">
-        <v>7399.02</v>
+        <v>7415.91</v>
       </c>
       <c r="AI8">
         <v>7451.92</v>
@@ -1745,7 +1703,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>22.49</v>
+        <v>19.57</v>
       </c>
     </row>
   </sheetData>
@@ -1886,7 +1844,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1926,7 +1884,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1944,1079 +1902,988 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>8.25</v>
+      </c>
+      <c r="D7" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-2.83</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-4.58</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>8.25</v>
+      </c>
+      <c r="D9" s="6">
+        <v>6.87</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.59</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-0.83</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>16.67</v>
+      </c>
+      <c r="D12" s="6">
+        <v>16.04</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.64</v>
+      </c>
+      <c r="D13" s="6">
+        <v>2.65</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="D14" s="6">
+        <v>10.8</v>
+      </c>
+      <c r="E14" s="7">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.17</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.62</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-0.63</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="7" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-6.15</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-3.65</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>9.52</v>
+      </c>
+      <c r="D19" s="6">
+        <v>9.58</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-1.21</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-0.97</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="D9" s="8">
-        <v>8.25</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>30.65</v>
+      </c>
+      <c r="D21" s="6">
+        <v>38.68</v>
+      </c>
+      <c r="E21" s="7">
+        <v>8.029999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8">
-        <v>-2.71</v>
-      </c>
-      <c r="D10" s="8">
-        <v>-2.83</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>30.77</v>
+      </c>
+      <c r="D22" s="6">
+        <v>30.37</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>5.72</v>
-      </c>
-      <c r="D11" s="8">
-        <v>8.25</v>
-      </c>
-      <c r="E11" s="10">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>31.9</v>
+      </c>
+      <c r="D23" s="6">
+        <v>29.66</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>1.22</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.08</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-16.89</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-14.29</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0.48</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-0.83</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-35.44</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-31.74</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>5.82</v>
-      </c>
-      <c r="D14" s="8">
-        <v>16.67</v>
-      </c>
-      <c r="E14" s="10">
-        <v>10.85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-5.26</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>2.53</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.64</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-17.63</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-18.06</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="8">
-        <v>8.84</v>
-      </c>
-      <c r="D16" s="8">
-        <v>6.7</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>11.26</v>
+      </c>
+      <c r="D28" s="6">
+        <v>7.46</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0.11</v>
-      </c>
-      <c r="D17" s="8">
-        <v>-0.17</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>4.69</v>
+      </c>
+      <c r="D29" s="6">
+        <v>5.77</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="8">
-        <v>2.1</v>
-      </c>
-      <c r="D18" s="8">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>22.37</v>
+      </c>
+      <c r="D30" s="6">
+        <v>24.68</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>11.45</v>
+      </c>
+      <c r="D31" s="6">
+        <v>11.95</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-2.98</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-1.16</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>18.06</v>
+      </c>
+      <c r="D33" s="6">
+        <v>20.92</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>15.53</v>
+      </c>
+      <c r="D34" s="6">
+        <v>15.86</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-7.05</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-4.6</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-9.06</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-1.15</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0.62</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-14.92</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-14.11</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-34.42</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-33.76</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-5.56</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-2.44</v>
+      </c>
+      <c r="E40" s="7">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-22.27</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-21.97</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="9">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="C42" s="6">
+        <v>1154.2</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1184.6</v>
+      </c>
+      <c r="E42" s="7">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>888</v>
+      </c>
+      <c r="D43" s="6">
+        <v>886.55</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1917.6</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1927.9</v>
+      </c>
+      <c r="E44" s="7">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-1.43</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-0.63</v>
-      </c>
-      <c r="E19" s="10">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2073.3</v>
+      </c>
+      <c r="D45" s="6">
+        <v>2088.8</v>
+      </c>
+      <c r="E45" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="8">
-        <v>-1.82</v>
-      </c>
-      <c r="D20" s="8">
-        <v>-6.15</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-4.33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>772.5</v>
+      </c>
+      <c r="D46" s="6">
+        <v>780.3</v>
+      </c>
+      <c r="E46" s="7">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>-1.14</v>
-      </c>
-      <c r="D21" s="8">
-        <v>9.52</v>
-      </c>
-      <c r="E21" s="10">
-        <v>10.66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2878.3</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2887.6</v>
+      </c>
+      <c r="E47" s="7">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-1.05</v>
-      </c>
-      <c r="D22" s="8">
-        <v>-1.21</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>7954.5</v>
+      </c>
+      <c r="D48" s="6">
+        <v>7985</v>
+      </c>
+      <c r="E48" s="7">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="8">
-        <v>29.9</v>
-      </c>
-      <c r="D23" s="8">
-        <v>30.65</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>62.03</v>
+      </c>
+      <c r="D49" s="6">
+        <v>66.22</v>
+      </c>
+      <c r="E49" s="7">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="8">
-        <v>29.8</v>
-      </c>
-      <c r="D24" s="8">
-        <v>30.77</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>50.71</v>
+      </c>
+      <c r="D50" s="6">
+        <v>50.32</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="8">
-        <v>30.14</v>
-      </c>
-      <c r="D25" s="8">
-        <v>31.9</v>
-      </c>
-      <c r="E25" s="10">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>61.71</v>
+      </c>
+      <c r="D51" s="6">
+        <v>62.66</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="8">
-        <v>-20.07</v>
-      </c>
-      <c r="D26" s="8">
-        <v>-16.89</v>
-      </c>
-      <c r="E26" s="10">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>54.24</v>
+      </c>
+      <c r="D52" s="6">
+        <v>56.64</v>
+      </c>
+      <c r="E52" s="7">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-34.04</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-35.44</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>49.18</v>
+      </c>
+      <c r="D53" s="6">
+        <v>51.72</v>
+      </c>
+      <c r="E53" s="7">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="8">
-        <v>-17.91</v>
-      </c>
-      <c r="D28" s="8">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="E28" s="10">
-        <v>8.880000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="D54" s="6">
+        <v>71.92</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>-18.25</v>
-      </c>
-      <c r="D29" s="8">
-        <v>-17.63</v>
-      </c>
-      <c r="E29" s="10">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>50.34</v>
+      </c>
+      <c r="D55" s="6">
+        <v>51.55</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="8">
-        <v>13.6</v>
-      </c>
-      <c r="D30" s="8">
-        <v>11.26</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>64.56999999999999</v>
+      </c>
+      <c r="D56" s="6">
+        <v>30.26</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-34.31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="8">
-        <v>4.01</v>
-      </c>
-      <c r="D31" s="8">
-        <v>4.69</v>
-      </c>
-      <c r="E31" s="10">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-56.54</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-65.15000000000001</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-8.609999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="8">
-        <v>21.58</v>
-      </c>
-      <c r="D32" s="8">
-        <v>22.37</v>
-      </c>
-      <c r="E32" s="10">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-67.5</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-46.59</v>
+      </c>
+      <c r="E58" s="7">
+        <v>20.91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="8">
-        <v>12.08</v>
-      </c>
-      <c r="D33" s="8">
-        <v>11.45</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-18.38</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-53.98</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-35.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="8">
-        <v>-2.09</v>
-      </c>
-      <c r="D34" s="8">
-        <v>-2.98</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>126.32</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-18.78</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-145.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="8">
-        <v>5.87</v>
-      </c>
-      <c r="D35" s="8">
-        <v>18.06</v>
-      </c>
-      <c r="E35" s="10">
-        <v>12.19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1798.83</v>
+      </c>
+      <c r="D61" s="6">
+        <v>474.08</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-1324.75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="8">
-        <v>16</v>
-      </c>
-      <c r="D36" s="8">
-        <v>15.53</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="8">
-        <v>-5.47</v>
-      </c>
-      <c r="D37" s="8">
-        <v>-7.05</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="8">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="D38" s="8">
-        <v>-9.06</v>
-      </c>
-      <c r="E38" s="10">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="8">
-        <v>-1.32</v>
-      </c>
-      <c r="D39" s="8">
-        <v>-1.15</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-16.41</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-14.92</v>
-      </c>
-      <c r="E40" s="10">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="8">
-        <v>-34.1</v>
-      </c>
-      <c r="D41" s="8">
-        <v>-34.42</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="8">
-        <v>-17.54</v>
-      </c>
-      <c r="D42" s="8">
-        <v>-5.56</v>
-      </c>
-      <c r="E42" s="10">
-        <v>11.98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-21.65</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-22.27</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="8">
-        <v>1173.8</v>
-      </c>
-      <c r="D44" s="8">
-        <v>1154.2</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-19.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="8">
-        <v>881</v>
-      </c>
-      <c r="D45" s="8">
-        <v>888</v>
-      </c>
-      <c r="E45" s="10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="8">
-        <v>1914.4</v>
-      </c>
-      <c r="D46" s="8">
-        <v>1917.6</v>
-      </c>
-      <c r="E46" s="10">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="8">
-        <v>2085.2</v>
-      </c>
-      <c r="D47" s="8">
-        <v>2073.3</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-11.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="8">
-        <v>788.5</v>
-      </c>
-      <c r="D48" s="8">
-        <v>772.5</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="8">
-        <v>2608.9</v>
-      </c>
-      <c r="D49" s="8">
-        <v>2878.3</v>
-      </c>
-      <c r="E49" s="10">
-        <v>269.4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="8">
-        <v>8017</v>
-      </c>
-      <c r="D50" s="8">
-        <v>7954.5</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-62.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="8">
-        <v>43</v>
-      </c>
-      <c r="D51" s="8">
-        <v>29</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="8">
-        <v>29</v>
-      </c>
-      <c r="D52" s="8">
-        <v>57</v>
-      </c>
-      <c r="E52" s="10">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="8">
-        <v>57</v>
-      </c>
-      <c r="D53" s="8">
-        <v>43</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="8">
-        <v>67.01000000000001</v>
-      </c>
-      <c r="D54" s="8">
-        <v>62.03</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-4.98</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="8">
-        <v>48.95</v>
-      </c>
-      <c r="D55" s="8">
-        <v>50.71</v>
-      </c>
-      <c r="E55" s="10">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="8">
-        <v>61.43</v>
-      </c>
-      <c r="D56" s="8">
-        <v>61.71</v>
-      </c>
-      <c r="E56" s="10">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="8">
-        <v>56.47</v>
-      </c>
-      <c r="D57" s="8">
-        <v>54.24</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="8">
-        <v>54.65</v>
-      </c>
-      <c r="D58" s="8">
-        <v>49.18</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-5.47</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="8">
-        <v>52.98</v>
-      </c>
-      <c r="D59" s="8">
-        <v>71.51000000000001</v>
-      </c>
-      <c r="E59" s="10">
-        <v>18.53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="8">
-        <v>52.84</v>
-      </c>
-      <c r="D60" s="8">
-        <v>50.34</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="7" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="8">
-        <v>113.22</v>
-      </c>
-      <c r="D61" s="8">
-        <v>64.56999999999999</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-48.65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="8">
-        <v>-74.02</v>
-      </c>
-      <c r="D62" s="8">
-        <v>-56.54</v>
-      </c>
-      <c r="E62" s="10">
-        <v>17.48</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="8">
-        <v>-10.42</v>
-      </c>
-      <c r="D63" s="8">
-        <v>-67.5</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-57.08</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="8">
-        <v>-75.89</v>
-      </c>
-      <c r="D64" s="8">
-        <v>-18.38</v>
-      </c>
-      <c r="E64" s="10">
-        <v>57.51</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="8">
-        <v>357.36</v>
-      </c>
-      <c r="D65" s="8">
-        <v>126.32</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-231.04</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="8">
-        <v>167.41</v>
-      </c>
-      <c r="D66" s="8">
-        <v>1798.83</v>
-      </c>
-      <c r="E66" s="10">
-        <v>1631.42</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="8">
-        <v>-54.44</v>
-      </c>
-      <c r="D67" s="8">
+      <c r="C62" s="6">
         <v>-58</v>
       </c>
-      <c r="E67" s="9">
-        <v>-3.56</v>
+      <c r="D62" s="6">
+        <v>-55.83</v>
+      </c>
+      <c r="E62" s="7">
+        <v>2.17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3036,60 +2903,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>81</v>
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="11">
         <v>60.8</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="13">
-        <v>57.1</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="11">
+        <v>58.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="G2" s="13">
-        <v>11.5</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="11">
+        <v>4.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3191,49 +3058,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="16">
-        <v>0.6254</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.3215999999999999</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.3046</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.2127</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1478</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.1387</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.105</v>
+      <c r="A2" s="14">
+        <v>0.6215999999999999</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3105</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2919</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.211</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1535</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1425</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1071</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="85">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,19 +187,55 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.4% → 0.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.4%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-0.6% → -2.4%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-0.6%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.2 → 51.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.2</t>
+    <t>51.7 → 50.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.7</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>51.5 → 49.3</t>
+  </si>
+  <si>
+    <t>51.5</t>
+  </si>
+  <si>
+    <t>49.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -251,7 +287,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,13 +328,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,6 +369,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -409,14 +458,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -425,7 +476,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -923,10 +974,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1184.6</v>
+        <v>1151.6</v>
       </c>
       <c r="D2">
-        <v>2.63</v>
+        <v>-2.79</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -935,46 +986,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-4.6</v>
+        <v>-7.26</v>
       </c>
       <c r="H2">
-        <v>58.29</v>
+        <v>53.89</v>
       </c>
       <c r="I2">
-        <v>10.8</v>
+        <v>4.98</v>
       </c>
       <c r="J2">
-        <v>9.5</v>
+        <v>6.11</v>
       </c>
       <c r="K2">
-        <v>7.46</v>
+        <v>4.86</v>
       </c>
       <c r="L2">
-        <v>38.68</v>
+        <v>37.14</v>
       </c>
       <c r="M2">
-        <v>10.71</v>
+        <v>10.64</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>1146.12</v>
+        <v>1157.04</v>
       </c>
       <c r="Q2">
-        <v>1089.06</v>
+        <v>1093.65</v>
       </c>
       <c r="R2">
-        <v>1101.41</v>
+        <v>1103.87</v>
       </c>
       <c r="S2">
-        <v>931.48</v>
+        <v>932.7</v>
       </c>
       <c r="T2">
-        <v>27.17</v>
+        <v>23.47</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -989,34 +1040,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>66.22</v>
+        <v>58.64</v>
       </c>
       <c r="Z2">
-        <v>16.3</v>
+        <v>17.72</v>
       </c>
       <c r="AA2">
-        <v>3.11</v>
+        <v>6.03</v>
       </c>
       <c r="AB2">
-        <v>13.19</v>
+        <v>11.69</v>
       </c>
       <c r="AC2">
-        <v>92.37</v>
+        <v>81.33</v>
       </c>
       <c r="AD2">
-        <v>95.26000000000001</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="AE2">
-        <v>44.07</v>
+        <v>44.66</v>
       </c>
       <c r="AF2">
-        <v>30.26</v>
+        <v>22.28</v>
       </c>
       <c r="AG2">
-        <v>1167.77</v>
+        <v>1175.81</v>
       </c>
       <c r="AH2">
-        <v>1010.36</v>
+        <v>1011.5</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1025,7 +1076,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>41.1</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1036,10 +1087,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>886.55</v>
+        <v>890.15</v>
       </c>
       <c r="D3">
-        <v>-0.16</v>
+        <v>0.41</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1048,46 +1099,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.210000000000001</v>
+        <v>-8.84</v>
       </c>
       <c r="H3">
-        <v>67.44</v>
+        <v>68.12</v>
       </c>
       <c r="I3">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="J3">
-        <v>-4.58</v>
+        <v>-3.45</v>
       </c>
       <c r="K3">
-        <v>5.77</v>
+        <v>10.06</v>
       </c>
       <c r="L3">
-        <v>30.37</v>
+        <v>33.87</v>
       </c>
       <c r="M3">
-        <v>62.16</v>
+        <v>62.12</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>882.71</v>
+        <v>884.9400000000001</v>
       </c>
       <c r="Q3">
-        <v>876.4400000000001</v>
+        <v>875.6900000000001</v>
       </c>
       <c r="R3">
-        <v>909.08</v>
+        <v>908.13</v>
       </c>
       <c r="S3">
-        <v>763.89</v>
+        <v>764.71</v>
       </c>
       <c r="T3">
-        <v>16.06</v>
+        <v>16.4</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1102,34 +1153,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>50.32</v>
+        <v>51.31</v>
       </c>
       <c r="Z3">
-        <v>-6.46</v>
+        <v>-5.06</v>
       </c>
       <c r="AA3">
-        <v>-10.57</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="AB3">
-        <v>4.11</v>
+        <v>4.41</v>
       </c>
       <c r="AC3">
-        <v>96.58</v>
+        <v>99.31</v>
       </c>
       <c r="AD3">
-        <v>93.42</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="AE3">
-        <v>25.01</v>
+        <v>24.25</v>
       </c>
       <c r="AF3">
-        <v>-65.15000000000001</v>
+        <v>-59.36</v>
       </c>
       <c r="AG3">
-        <v>929.5</v>
+        <v>927.47</v>
       </c>
       <c r="AH3">
-        <v>823.38</v>
+        <v>823.92</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1138,7 +1189,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>19.32</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1149,10 +1200,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1927.9</v>
+        <v>1894.4</v>
       </c>
       <c r="D4">
-        <v>0.54</v>
+        <v>-1.74</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1161,25 +1212,25 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-0.62</v>
+        <v>-2.35</v>
       </c>
       <c r="H4">
-        <v>42.31</v>
+        <v>39.84</v>
       </c>
       <c r="I4">
-        <v>-0.62</v>
+        <v>1.51</v>
       </c>
       <c r="J4">
-        <v>6.87</v>
+        <v>5.89</v>
       </c>
       <c r="K4">
-        <v>24.68</v>
+        <v>23.99</v>
       </c>
       <c r="L4">
-        <v>29.66</v>
+        <v>30.65</v>
       </c>
       <c r="M4">
-        <v>31.05</v>
+        <v>30.74</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1188,19 +1239,19 @@
         <v>82</v>
       </c>
       <c r="P4">
-        <v>1909.22</v>
+        <v>1914.86</v>
       </c>
       <c r="Q4">
-        <v>1830.52</v>
+        <v>1834.99</v>
       </c>
       <c r="R4">
-        <v>1753.45</v>
+        <v>1761.62</v>
       </c>
       <c r="S4">
-        <v>1665.59</v>
+        <v>1666.41</v>
       </c>
       <c r="T4">
-        <v>15.75</v>
+        <v>13.68</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1215,34 +1266,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>62.66</v>
+        <v>57.67</v>
       </c>
       <c r="Z4">
-        <v>48.05</v>
+        <v>45.57</v>
       </c>
       <c r="AA4">
-        <v>41.36</v>
+        <v>42.2</v>
       </c>
       <c r="AB4">
-        <v>6.69</v>
+        <v>3.36</v>
       </c>
       <c r="AC4">
-        <v>68.93000000000001</v>
+        <v>58.45</v>
       </c>
       <c r="AD4">
-        <v>68.2</v>
+        <v>66.02</v>
       </c>
       <c r="AE4">
-        <v>53.26</v>
+        <v>52.52</v>
       </c>
       <c r="AF4">
-        <v>-46.59</v>
+        <v>-60.72</v>
       </c>
       <c r="AG4">
-        <v>1981.45</v>
+        <v>1988.02</v>
       </c>
       <c r="AH4">
-        <v>1679.58</v>
+        <v>1681.96</v>
       </c>
       <c r="AI4">
         <v>1751.87</v>
@@ -1251,7 +1302,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>32.11</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1262,10 +1313,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2088.8</v>
+        <v>2095.3</v>
       </c>
       <c r="D5">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="E5">
         <v>2432.01</v>
@@ -1274,46 +1325,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-14.11</v>
+        <v>-13.84</v>
       </c>
       <c r="H5">
-        <v>19.66</v>
+        <v>20.03</v>
       </c>
       <c r="I5">
-        <v>0.27</v>
+        <v>1.26</v>
       </c>
       <c r="J5">
-        <v>1.59</v>
+        <v>3.61</v>
       </c>
       <c r="K5">
-        <v>11.95</v>
+        <v>14.05</v>
       </c>
       <c r="L5">
-        <v>-14.29</v>
+        <v>-13.08</v>
       </c>
       <c r="M5">
-        <v>21.1</v>
+        <v>21.53</v>
       </c>
       <c r="N5">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P5">
-        <v>2082.98</v>
+        <v>2088.18</v>
       </c>
       <c r="Q5">
-        <v>2058.16</v>
+        <v>2061.21</v>
       </c>
       <c r="R5">
-        <v>2009.15</v>
+        <v>2015.79</v>
       </c>
       <c r="S5">
-        <v>2108.88</v>
+        <v>2108.17</v>
       </c>
       <c r="T5">
-        <v>-0.95</v>
+        <v>-0.61</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1328,34 +1379,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>56.64</v>
+        <v>57.65</v>
       </c>
       <c r="Z5">
-        <v>21.9</v>
+        <v>21.82</v>
       </c>
       <c r="AA5">
-        <v>23</v>
+        <v>22.77</v>
       </c>
       <c r="AB5">
-        <v>-1.1</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AC5">
-        <v>52.48</v>
+        <v>48.3</v>
       </c>
       <c r="AD5">
-        <v>57.96</v>
+        <v>53.62</v>
       </c>
       <c r="AE5">
-        <v>49.4</v>
+        <v>48.08</v>
       </c>
       <c r="AF5">
-        <v>-53.98</v>
+        <v>-30.63</v>
       </c>
       <c r="AG5">
-        <v>2131.88</v>
+        <v>2135.82</v>
       </c>
       <c r="AH5">
-        <v>1984.44</v>
+        <v>1986.6</v>
       </c>
       <c r="AI5">
         <v>1954.68</v>
@@ -1364,7 +1415,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>16.3</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1375,10 +1426,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>780.3</v>
+        <v>775.2</v>
       </c>
       <c r="D6">
-        <v>1.01</v>
+        <v>-0.65</v>
       </c>
       <c r="E6">
         <v>1178</v>
@@ -1387,25 +1438,25 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-33.76</v>
+        <v>-34.19</v>
       </c>
       <c r="H6">
-        <v>10.82</v>
+        <v>10.1</v>
       </c>
       <c r="I6">
-        <v>-3.65</v>
+        <v>-3.71</v>
       </c>
       <c r="J6">
-        <v>0.21</v>
+        <v>0.61</v>
       </c>
       <c r="K6">
-        <v>-1.16</v>
+        <v>-0.76</v>
       </c>
       <c r="L6">
-        <v>-31.74</v>
+        <v>-30.64</v>
       </c>
       <c r="M6">
-        <v>15.35</v>
+        <v>14.71</v>
       </c>
       <c r="N6">
         <v>15</v>
@@ -1414,19 +1465,19 @@
         <v>21</v>
       </c>
       <c r="P6">
-        <v>787.53</v>
+        <v>781.55</v>
       </c>
       <c r="Q6">
-        <v>777.95</v>
+        <v>779.16</v>
       </c>
       <c r="R6">
-        <v>752.34</v>
+        <v>752.8200000000001</v>
       </c>
       <c r="S6">
-        <v>872.1799999999999</v>
+        <v>870.72</v>
       </c>
       <c r="T6">
-        <v>-10.53</v>
+        <v>-10.97</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1441,34 +1492,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>51.72</v>
+        <v>49.96</v>
       </c>
       <c r="Z6">
-        <v>9.19</v>
+        <v>7.73</v>
       </c>
       <c r="AA6">
-        <v>10.57</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>-1.38</v>
+        <v>-2.27</v>
       </c>
       <c r="AC6">
-        <v>12.13</v>
+        <v>5.89</v>
       </c>
       <c r="AD6">
-        <v>21.97</v>
+        <v>11.73</v>
       </c>
       <c r="AE6">
-        <v>22.67</v>
+        <v>23.1</v>
       </c>
       <c r="AF6">
-        <v>-18.78</v>
+        <v>22.78</v>
       </c>
       <c r="AG6">
-        <v>817.49</v>
+        <v>816.66</v>
       </c>
       <c r="AH6">
-        <v>738.42</v>
+        <v>741.67</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1477,7 +1528,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>26.71</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1488,58 +1539,58 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2887.6</v>
+        <v>3088.7</v>
       </c>
       <c r="D7">
-        <v>0.32</v>
+        <v>6.96</v>
       </c>
       <c r="E7">
-        <v>2959.97</v>
+        <v>3088.7</v>
       </c>
       <c r="F7">
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-2.44</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>52.67</v>
+        <v>63.3</v>
       </c>
       <c r="I7">
-        <v>9.58</v>
+        <v>14.67</v>
       </c>
       <c r="J7">
-        <v>16.04</v>
+        <v>25.87</v>
       </c>
       <c r="K7">
-        <v>20.92</v>
+        <v>20.67</v>
       </c>
       <c r="L7">
-        <v>-5.26</v>
+        <v>4.35</v>
       </c>
       <c r="M7">
-        <v>29.19</v>
+        <v>32.41</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>2748.72</v>
+        <v>2827.76</v>
       </c>
       <c r="Q7">
-        <v>2625.7</v>
+        <v>2653.22</v>
       </c>
       <c r="R7">
-        <v>2566.46</v>
+        <v>2578.08</v>
       </c>
       <c r="S7">
-        <v>2367.14</v>
+        <v>2370.27</v>
       </c>
       <c r="T7">
-        <v>21.99</v>
+        <v>30.31</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1554,43 +1605,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>71.92</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="Z7">
-        <v>64.8</v>
+        <v>91.56</v>
       </c>
       <c r="AA7">
-        <v>36.89</v>
+        <v>47.82</v>
       </c>
       <c r="AB7">
-        <v>27.91</v>
+        <v>43.73</v>
       </c>
       <c r="AC7">
-        <v>72.11</v>
+        <v>100</v>
       </c>
       <c r="AD7">
-        <v>67.75</v>
+        <v>79.23</v>
       </c>
       <c r="AE7">
-        <v>107.32</v>
+        <v>129.1</v>
       </c>
       <c r="AF7">
-        <v>474.08</v>
+        <v>2773.38</v>
       </c>
       <c r="AG7">
-        <v>2822.95</v>
+        <v>2934.72</v>
       </c>
       <c r="AH7">
-        <v>2428.46</v>
+        <v>2371.73</v>
       </c>
       <c r="AI7">
-        <v>2612.49</v>
+        <v>2788.64</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>49.46</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1601,10 +1652,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7985</v>
+        <v>7932</v>
       </c>
       <c r="D8">
-        <v>0.38</v>
+        <v>-0.66</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1613,46 +1664,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-21.97</v>
+        <v>-22.49</v>
       </c>
       <c r="H8">
-        <v>34.78</v>
+        <v>33.88</v>
       </c>
       <c r="I8">
-        <v>-0.97</v>
+        <v>-2.69</v>
       </c>
       <c r="J8">
-        <v>2.65</v>
+        <v>1.93</v>
       </c>
       <c r="K8">
-        <v>15.86</v>
+        <v>16.89</v>
       </c>
       <c r="L8">
-        <v>-18.06</v>
+        <v>-18.44</v>
       </c>
       <c r="M8">
-        <v>14.25</v>
+        <v>14.28</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O8">
         <v>49</v>
       </c>
       <c r="P8">
-        <v>8046.4</v>
+        <v>8002.6</v>
       </c>
       <c r="Q8">
-        <v>7976.7</v>
+        <v>7994.12</v>
       </c>
       <c r="R8">
-        <v>7777.85</v>
+        <v>7798.95</v>
       </c>
       <c r="S8">
-        <v>7423.98</v>
+        <v>7419.98</v>
       </c>
       <c r="T8">
-        <v>7.56</v>
+        <v>6.9</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1667,34 +1718,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>51.55</v>
+        <v>49.3</v>
       </c>
       <c r="Z8">
-        <v>80.90000000000001</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="AA8">
-        <v>109.9</v>
+        <v>101.23</v>
       </c>
       <c r="AB8">
-        <v>-29</v>
+        <v>-34.71</v>
       </c>
       <c r="AC8">
-        <v>18.11</v>
+        <v>2.52</v>
       </c>
       <c r="AD8">
-        <v>38.55</v>
+        <v>19.28</v>
       </c>
       <c r="AE8">
-        <v>230.8</v>
+        <v>230.35</v>
       </c>
       <c r="AF8">
-        <v>-55.83</v>
+        <v>-71.34</v>
       </c>
       <c r="AG8">
-        <v>8537.49</v>
+        <v>8524.299999999999</v>
       </c>
       <c r="AH8">
-        <v>7415.91</v>
+        <v>7463.95</v>
       </c>
       <c r="AI8">
         <v>7451.92</v>
@@ -1703,7 +1754,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>19.57</v>
+        <v>18.21</v>
       </c>
     </row>
   </sheetData>
@@ -1844,7 +1895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1884,7 +1935,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1902,988 +1953,1082 @@
         <v>59</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>8.25</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C10" s="8">
         <v>9.5</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D10" s="8">
+        <v>6.11</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-3.39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-2.83</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C11" s="8">
         <v>-4.58</v>
       </c>
-      <c r="E8" s="8">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D11" s="8">
+        <v>-3.45</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>8.25</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C12" s="8">
         <v>6.87</v>
       </c>
-      <c r="E9" s="8">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D12" s="8">
+        <v>5.89</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>0.08</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C13" s="8">
         <v>1.59</v>
       </c>
-      <c r="E10" s="7">
+      <c r="D13" s="8">
+        <v>3.61</v>
+      </c>
+      <c r="E13" s="10">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.61</v>
+      </c>
+      <c r="E14" s="10">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8">
+        <v>16.04</v>
+      </c>
+      <c r="D15" s="8">
+        <v>25.87</v>
+      </c>
+      <c r="E15" s="10">
+        <v>9.83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2.65</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1.93</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="8">
+        <v>10.8</v>
+      </c>
+      <c r="D17" s="8">
+        <v>4.98</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-5.82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1.27</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="8">
+        <v>-0.62</v>
+      </c>
+      <c r="D19" s="8">
         <v>1.51</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="E19" s="10">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="D20" s="8">
+        <v>1.26</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-0.83</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.21</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-3.65</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-3.71</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>16.67</v>
-      </c>
-      <c r="D12" s="6">
-        <v>16.04</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>9.58</v>
+      </c>
+      <c r="D22" s="8">
+        <v>14.67</v>
+      </c>
+      <c r="E22" s="10">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1.64</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2.65</v>
-      </c>
-      <c r="E13" s="7">
+      <c r="B23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="8">
+        <v>-0.97</v>
+      </c>
+      <c r="D23" s="8">
+        <v>-2.69</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="8">
+        <v>38.68</v>
+      </c>
+      <c r="D24" s="8">
+        <v>37.14</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="8">
+        <v>30.37</v>
+      </c>
+      <c r="D25" s="8">
+        <v>33.87</v>
+      </c>
+      <c r="E25" s="10">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="8">
+        <v>29.66</v>
+      </c>
+      <c r="D26" s="8">
+        <v>30.65</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-14.29</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-13.08</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="8">
+        <v>-31.74</v>
+      </c>
+      <c r="D28" s="8">
+        <v>-30.64</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8">
+        <v>-5.26</v>
+      </c>
+      <c r="D29" s="8">
+        <v>4.35</v>
+      </c>
+      <c r="E29" s="10">
+        <v>9.609999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="8">
+        <v>-18.06</v>
+      </c>
+      <c r="D30" s="8">
+        <v>-18.44</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="8">
+        <v>7.46</v>
+      </c>
+      <c r="D31" s="8">
+        <v>4.86</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="8">
+        <v>5.77</v>
+      </c>
+      <c r="D32" s="8">
+        <v>10.06</v>
+      </c>
+      <c r="E32" s="10">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="8">
+        <v>24.68</v>
+      </c>
+      <c r="D33" s="8">
+        <v>23.99</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="8">
+        <v>11.95</v>
+      </c>
+      <c r="D34" s="8">
+        <v>14.05</v>
+      </c>
+      <c r="E34" s="10">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="8">
+        <v>-1.16</v>
+      </c>
+      <c r="D35" s="8">
+        <v>-0.76</v>
+      </c>
+      <c r="E35" s="10">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="8">
+        <v>20.92</v>
+      </c>
+      <c r="D36" s="8">
+        <v>20.67</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="8">
+        <v>15.86</v>
+      </c>
+      <c r="D37" s="8">
+        <v>16.89</v>
+      </c>
+      <c r="E37" s="10">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="8">
+        <v>-4.6</v>
+      </c>
+      <c r="D38" s="8">
+        <v>-7.26</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-8.84</v>
+      </c>
+      <c r="E39" s="10">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="8">
+        <v>-0.62</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-2.35</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="8">
+        <v>-14.11</v>
+      </c>
+      <c r="D41" s="8">
+        <v>-13.84</v>
+      </c>
+      <c r="E41" s="10">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="8">
+        <v>-33.76</v>
+      </c>
+      <c r="D42" s="8">
+        <v>-34.19</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-2.44</v>
+      </c>
+      <c r="D43" s="8">
+        <v>0</v>
+      </c>
+      <c r="E43" s="10">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="8">
+        <v>-21.97</v>
+      </c>
+      <c r="D44" s="8">
+        <v>-22.49</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1184.6</v>
+      </c>
+      <c r="D45" s="8">
+        <v>1151.6</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="8">
+        <v>886.55</v>
+      </c>
+      <c r="D46" s="8">
+        <v>890.15</v>
+      </c>
+      <c r="E46" s="10">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1927.9</v>
+      </c>
+      <c r="D47" s="8">
+        <v>1894.4</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-33.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="8">
+        <v>2088.8</v>
+      </c>
+      <c r="D48" s="8">
+        <v>2095.3</v>
+      </c>
+      <c r="E48" s="10">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="8">
+        <v>780.3</v>
+      </c>
+      <c r="D49" s="8">
+        <v>775.2</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="8">
+        <v>2887.6</v>
+      </c>
+      <c r="D50" s="8">
+        <v>3088.7</v>
+      </c>
+      <c r="E50" s="10">
+        <v>201.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="8">
+        <v>7985</v>
+      </c>
+      <c r="D51" s="8">
+        <v>7932</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="8">
+        <v>29</v>
+      </c>
+      <c r="D52" s="8">
+        <v>43</v>
+      </c>
+      <c r="E52" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="8">
+        <v>43</v>
+      </c>
+      <c r="D53" s="8">
+        <v>29</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="8">
+        <v>66.22</v>
+      </c>
+      <c r="D54" s="8">
+        <v>58.64</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-7.58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="8">
+        <v>50.32</v>
+      </c>
+      <c r="D55" s="8">
+        <v>51.31</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="8">
+        <v>62.66</v>
+      </c>
+      <c r="D56" s="8">
+        <v>57.67</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-4.99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="8">
+        <v>56.64</v>
+      </c>
+      <c r="D57" s="8">
+        <v>57.65</v>
+      </c>
+      <c r="E57" s="10">
         <v>1.01</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="8">
+        <v>51.72</v>
+      </c>
+      <c r="D58" s="8">
+        <v>49.96</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="8">
+        <v>71.92</v>
+      </c>
+      <c r="D59" s="8">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="E59" s="10">
+        <v>7.07</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="8">
+        <v>51.55</v>
+      </c>
+      <c r="D60" s="8">
+        <v>49.3</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>6.7</v>
-      </c>
-      <c r="D14" s="6">
-        <v>10.8</v>
-      </c>
-      <c r="E14" s="7">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B61" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="8">
+        <v>30.26</v>
+      </c>
+      <c r="D61" s="8">
+        <v>22.28</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-7.98</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.17</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B62" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="8">
+        <v>-65.15000000000001</v>
+      </c>
+      <c r="D62" s="8">
+        <v>-59.36</v>
+      </c>
+      <c r="E62" s="10">
+        <v>5.79</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>2</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.62</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B63" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="8">
+        <v>-46.59</v>
+      </c>
+      <c r="D63" s="8">
+        <v>-60.72</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-14.13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-0.63</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.27</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B64" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="8">
+        <v>-53.98</v>
+      </c>
+      <c r="D64" s="8">
+        <v>-30.63</v>
+      </c>
+      <c r="E64" s="10">
+        <v>23.35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-6.15</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-3.65</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B65" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="8">
+        <v>-18.78</v>
+      </c>
+      <c r="D65" s="8">
+        <v>22.78</v>
+      </c>
+      <c r="E65" s="10">
+        <v>41.56</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>9.52</v>
-      </c>
-      <c r="D19" s="6">
-        <v>9.58</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B66" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="8">
+        <v>474.08</v>
+      </c>
+      <c r="D66" s="8">
+        <v>2773.38</v>
+      </c>
+      <c r="E66" s="10">
+        <v>2299.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.21</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-0.97</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>30.65</v>
-      </c>
-      <c r="D21" s="6">
-        <v>38.68</v>
-      </c>
-      <c r="E21" s="7">
-        <v>8.029999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>30.77</v>
-      </c>
-      <c r="D22" s="6">
-        <v>30.37</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>31.9</v>
-      </c>
-      <c r="D23" s="6">
-        <v>29.66</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-16.89</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-14.29</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-35.44</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-31.74</v>
-      </c>
-      <c r="E25" s="7">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-5.26</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-17.63</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-18.06</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>11.26</v>
-      </c>
-      <c r="D28" s="6">
-        <v>7.46</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>4.69</v>
-      </c>
-      <c r="D29" s="6">
-        <v>5.77</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>22.37</v>
-      </c>
-      <c r="D30" s="6">
-        <v>24.68</v>
-      </c>
-      <c r="E30" s="7">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>11.45</v>
-      </c>
-      <c r="D31" s="6">
-        <v>11.95</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>18.06</v>
-      </c>
-      <c r="D33" s="6">
-        <v>20.92</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>15.53</v>
-      </c>
-      <c r="D34" s="6">
-        <v>15.86</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-7.05</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-4.6</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-9.06</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-0.62</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-14.92</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-14.11</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-34.42</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-33.76</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-5.56</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="E40" s="7">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-22.27</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-21.97</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1154.2</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1184.6</v>
-      </c>
-      <c r="E42" s="7">
-        <v>30.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>888</v>
-      </c>
-      <c r="D43" s="6">
-        <v>886.55</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1917.6</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1927.9</v>
-      </c>
-      <c r="E44" s="7">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>2073.3</v>
-      </c>
-      <c r="D45" s="6">
-        <v>2088.8</v>
-      </c>
-      <c r="E45" s="7">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>772.5</v>
-      </c>
-      <c r="D46" s="6">
-        <v>780.3</v>
-      </c>
-      <c r="E46" s="7">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>2878.3</v>
-      </c>
-      <c r="D47" s="6">
-        <v>2887.6</v>
-      </c>
-      <c r="E47" s="7">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>7954.5</v>
-      </c>
-      <c r="D48" s="6">
-        <v>7985</v>
-      </c>
-      <c r="E48" s="7">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>62.03</v>
-      </c>
-      <c r="D49" s="6">
-        <v>66.22</v>
-      </c>
-      <c r="E49" s="7">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>50.71</v>
-      </c>
-      <c r="D50" s="6">
-        <v>50.32</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>61.71</v>
-      </c>
-      <c r="D51" s="6">
-        <v>62.66</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>54.24</v>
-      </c>
-      <c r="D52" s="6">
-        <v>56.64</v>
-      </c>
-      <c r="E52" s="7">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>49.18</v>
-      </c>
-      <c r="D53" s="6">
-        <v>51.72</v>
-      </c>
-      <c r="E53" s="7">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>71.51000000000001</v>
-      </c>
-      <c r="D54" s="6">
-        <v>71.92</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>50.34</v>
-      </c>
-      <c r="D55" s="6">
-        <v>51.55</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="B67" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>64.56999999999999</v>
-      </c>
-      <c r="D56" s="6">
-        <v>30.26</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-34.31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>-56.54</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-65.15000000000001</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-8.609999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-67.5</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-46.59</v>
-      </c>
-      <c r="E58" s="7">
-        <v>20.91</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>-18.38</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-53.98</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-35.6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>126.32</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-18.78</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-145.1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>1798.83</v>
-      </c>
-      <c r="D61" s="6">
-        <v>474.08</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-1324.75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-58</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C67" s="8">
         <v>-55.83</v>
       </c>
-      <c r="E62" s="7">
-        <v>2.17</v>
+      <c r="D67" s="8">
+        <v>-71.34</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-15.51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2903,60 +3048,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="13">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="14">
+        <v>7</v>
+      </c>
+      <c r="D2" s="13">
+        <v>57.6</v>
+      </c>
+      <c r="E2" s="13">
         <v>70</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>58.7</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>4.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>12.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="13">
+        <v>5.8</v>
+      </c>
+      <c r="G2" s="13">
+        <v>12.8</v>
+      </c>
+      <c r="H2" s="13">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>40</v>
       </c>
     </row>
@@ -3058,49 +3203,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.6215999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3105</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2919</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.211</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1535</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1425</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.1071</v>
+      <c r="A2" s="16">
+        <v>0.6212</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.3240999999999999</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.3074</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.2153</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1471</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.1428</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.1064</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,55 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.4% → 0.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.4%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-0.6% → -2.4%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-0.6%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.7 → 50.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.7</t>
+    <t>50.0 → 55.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>50.0</t>
   </si>
   <si>
-    <t>51.5 → 49.3</t>
-  </si>
-  <si>
-    <t>51.5</t>
-  </si>
-  <si>
-    <t>49.3</t>
+    <t>55.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -287,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,20 +292,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,12 +326,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -458,16 +409,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -476,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -841,7 +790,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -974,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1151.6</v>
+        <v>1122.7</v>
       </c>
       <c r="D2">
-        <v>-2.79</v>
+        <v>-2.51</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -986,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-7.26</v>
+        <v>-9.58</v>
       </c>
       <c r="H2">
-        <v>53.89</v>
+        <v>50.02</v>
       </c>
       <c r="I2">
-        <v>4.98</v>
+        <v>0.15</v>
       </c>
       <c r="J2">
-        <v>6.11</v>
+        <v>5.94</v>
       </c>
       <c r="K2">
-        <v>4.86</v>
+        <v>4.32</v>
       </c>
       <c r="L2">
-        <v>37.14</v>
+        <v>32.45</v>
       </c>
       <c r="M2">
-        <v>10.64</v>
+        <v>10</v>
       </c>
       <c r="N2">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>1157.04</v>
+        <v>1157.38</v>
       </c>
       <c r="Q2">
-        <v>1093.65</v>
+        <v>1095.43</v>
       </c>
       <c r="R2">
-        <v>1103.87</v>
+        <v>1105.53</v>
       </c>
       <c r="S2">
-        <v>932.7</v>
+        <v>933.78</v>
       </c>
       <c r="T2">
-        <v>23.47</v>
+        <v>20.23</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1040,34 +990,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.64</v>
+        <v>52.93</v>
       </c>
       <c r="Z2">
-        <v>17.72</v>
+        <v>16.32</v>
       </c>
       <c r="AA2">
-        <v>6.03</v>
+        <v>8.09</v>
       </c>
       <c r="AB2">
-        <v>11.69</v>
+        <v>8.23</v>
       </c>
       <c r="AC2">
-        <v>81.33</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="AD2">
-        <v>89.04000000000001</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="AE2">
-        <v>44.66</v>
+        <v>44.18</v>
       </c>
       <c r="AF2">
-        <v>22.28</v>
+        <v>-23.61</v>
       </c>
       <c r="AG2">
-        <v>1175.81</v>
+        <v>1178.52</v>
       </c>
       <c r="AH2">
-        <v>1011.5</v>
+        <v>1012.34</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1076,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>42.68</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1087,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>890.15</v>
+        <v>898.8</v>
       </c>
       <c r="D3">
-        <v>0.41</v>
+        <v>0.97</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1099,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.84</v>
+        <v>-7.96</v>
       </c>
       <c r="H3">
-        <v>68.12</v>
+        <v>69.75</v>
       </c>
       <c r="I3">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="J3">
-        <v>-3.45</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K3">
-        <v>10.06</v>
+        <v>9.69</v>
       </c>
       <c r="L3">
-        <v>33.87</v>
+        <v>35.48</v>
       </c>
       <c r="M3">
-        <v>62.12</v>
+        <v>61.75</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P3">
-        <v>884.9400000000001</v>
+        <v>888.9</v>
       </c>
       <c r="Q3">
-        <v>875.6900000000001</v>
+        <v>875.01</v>
       </c>
       <c r="R3">
-        <v>908.13</v>
+        <v>907.35</v>
       </c>
       <c r="S3">
-        <v>764.71</v>
+        <v>765.6</v>
       </c>
       <c r="T3">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1153,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>51.31</v>
+        <v>53.7</v>
       </c>
       <c r="Z3">
-        <v>-5.06</v>
+        <v>-3.21</v>
       </c>
       <c r="AA3">
-        <v>-9.470000000000001</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="AB3">
-        <v>4.41</v>
+        <v>5.01</v>
       </c>
       <c r="AC3">
         <v>99.31</v>
       </c>
       <c r="AD3">
-        <v>96.51000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE3">
-        <v>24.25</v>
+        <v>23.4</v>
       </c>
       <c r="AF3">
-        <v>-59.36</v>
+        <v>-44.08</v>
       </c>
       <c r="AG3">
-        <v>927.47</v>
+        <v>925.08</v>
       </c>
       <c r="AH3">
-        <v>823.92</v>
+        <v>824.9400000000001</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1189,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>16.83</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1203,7 +1153,7 @@
         <v>1894.4</v>
       </c>
       <c r="D4">
-        <v>-1.74</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1218,19 +1168,19 @@
         <v>39.84</v>
       </c>
       <c r="I4">
-        <v>1.51</v>
+        <v>-1.33</v>
       </c>
       <c r="J4">
-        <v>5.89</v>
+        <v>4.96</v>
       </c>
       <c r="K4">
-        <v>23.99</v>
+        <v>25.34</v>
       </c>
       <c r="L4">
-        <v>30.65</v>
+        <v>27.84</v>
       </c>
       <c r="M4">
-        <v>30.74</v>
+        <v>30.28</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1239,19 +1189,19 @@
         <v>82</v>
       </c>
       <c r="P4">
-        <v>1914.86</v>
+        <v>1909.74</v>
       </c>
       <c r="Q4">
-        <v>1834.99</v>
+        <v>1840.57</v>
       </c>
       <c r="R4">
-        <v>1761.62</v>
+        <v>1769.44</v>
       </c>
       <c r="S4">
-        <v>1666.41</v>
+        <v>1667.27</v>
       </c>
       <c r="T4">
-        <v>13.68</v>
+        <v>13.62</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1269,31 +1219,31 @@
         <v>57.67</v>
       </c>
       <c r="Z4">
-        <v>45.57</v>
+        <v>43.1</v>
       </c>
       <c r="AA4">
-        <v>42.2</v>
+        <v>42.38</v>
       </c>
       <c r="AB4">
-        <v>3.36</v>
+        <v>0.72</v>
       </c>
       <c r="AC4">
-        <v>58.45</v>
+        <v>45.4</v>
       </c>
       <c r="AD4">
-        <v>66.02</v>
+        <v>57.6</v>
       </c>
       <c r="AE4">
-        <v>52.52</v>
+        <v>50.82</v>
       </c>
       <c r="AF4">
-        <v>-60.72</v>
+        <v>-50.24</v>
       </c>
       <c r="AG4">
-        <v>1988.02</v>
+        <v>1993.72</v>
       </c>
       <c r="AH4">
-        <v>1681.96</v>
+        <v>1687.42</v>
       </c>
       <c r="AI4">
         <v>1751.87</v>
@@ -1302,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>31.62</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1316,55 +1266,55 @@
         <v>2095.3</v>
       </c>
       <c r="D5">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2432.01</v>
+        <v>2419.36</v>
       </c>
       <c r="F5">
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-13.84</v>
+        <v>-13.39</v>
       </c>
       <c r="H5">
         <v>20.03</v>
       </c>
       <c r="I5">
-        <v>1.26</v>
+        <v>-0.14</v>
       </c>
       <c r="J5">
-        <v>3.61</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>14.05</v>
+        <v>11.62</v>
       </c>
       <c r="L5">
-        <v>-13.08</v>
+        <v>-13.84</v>
       </c>
       <c r="M5">
-        <v>21.53</v>
+        <v>21.46</v>
       </c>
       <c r="N5">
         <v>43</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P5">
-        <v>2088.18</v>
+        <v>2087.58</v>
       </c>
       <c r="Q5">
-        <v>2061.21</v>
+        <v>2064.96</v>
       </c>
       <c r="R5">
-        <v>2015.79</v>
+        <v>2021.76</v>
       </c>
       <c r="S5">
-        <v>2108.17</v>
+        <v>2107.49</v>
       </c>
       <c r="T5">
-        <v>-0.61</v>
+        <v>-0.58</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1382,31 +1332,31 @@
         <v>57.65</v>
       </c>
       <c r="Z5">
-        <v>21.82</v>
+        <v>21.51</v>
       </c>
       <c r="AA5">
-        <v>22.77</v>
+        <v>22.52</v>
       </c>
       <c r="AB5">
-        <v>-0.9399999999999999</v>
+        <v>-1</v>
       </c>
       <c r="AC5">
-        <v>48.3</v>
+        <v>45.84</v>
       </c>
       <c r="AD5">
-        <v>53.62</v>
+        <v>48.87</v>
       </c>
       <c r="AE5">
-        <v>48.08</v>
+        <v>46.85</v>
       </c>
       <c r="AF5">
-        <v>-30.63</v>
+        <v>-12.38</v>
       </c>
       <c r="AG5">
-        <v>2135.82</v>
+        <v>2138.45</v>
       </c>
       <c r="AH5">
-        <v>1986.6</v>
+        <v>1991.46</v>
       </c>
       <c r="AI5">
         <v>1954.68</v>
@@ -1415,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>16.65</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1426,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>775.2</v>
+        <v>792.05</v>
       </c>
       <c r="D6">
-        <v>-0.65</v>
+        <v>2.17</v>
       </c>
       <c r="E6">
         <v>1178</v>
@@ -1438,46 +1388,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-34.19</v>
+        <v>-32.76</v>
       </c>
       <c r="H6">
-        <v>10.1</v>
+        <v>12.49</v>
       </c>
       <c r="I6">
-        <v>-3.71</v>
+        <v>0.1</v>
       </c>
       <c r="J6">
-        <v>0.61</v>
+        <v>5.47</v>
       </c>
       <c r="K6">
-        <v>-0.76</v>
+        <v>0.19</v>
       </c>
       <c r="L6">
-        <v>-30.64</v>
+        <v>-31.03</v>
       </c>
       <c r="M6">
-        <v>14.71</v>
+        <v>14.89</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P6">
-        <v>781.55</v>
+        <v>781.71</v>
       </c>
       <c r="Q6">
-        <v>779.16</v>
+        <v>780.65</v>
       </c>
       <c r="R6">
-        <v>752.8200000000001</v>
+        <v>753.96</v>
       </c>
       <c r="S6">
-        <v>870.72</v>
+        <v>869.33</v>
       </c>
       <c r="T6">
-        <v>-10.97</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1492,34 +1442,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>49.96</v>
+        <v>55.35</v>
       </c>
       <c r="Z6">
-        <v>7.73</v>
+        <v>7.84</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>9.57</v>
       </c>
       <c r="AB6">
-        <v>-2.27</v>
+        <v>-1.73</v>
       </c>
       <c r="AC6">
-        <v>5.89</v>
+        <v>16.85</v>
       </c>
       <c r="AD6">
-        <v>11.73</v>
+        <v>11.62</v>
       </c>
       <c r="AE6">
-        <v>23.1</v>
+        <v>22.86</v>
       </c>
       <c r="AF6">
-        <v>22.78</v>
+        <v>-6.12</v>
       </c>
       <c r="AG6">
-        <v>816.66</v>
+        <v>817.6799999999999</v>
       </c>
       <c r="AH6">
-        <v>741.67</v>
+        <v>743.63</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1528,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>24.04</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1539,13 +1489,13 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3088.7</v>
+        <v>3097.2</v>
       </c>
       <c r="D7">
-        <v>6.96</v>
+        <v>0.28</v>
       </c>
       <c r="E7">
-        <v>3088.7</v>
+        <v>3097.2</v>
       </c>
       <c r="F7">
         <v>1891.45</v>
@@ -1554,43 +1504,43 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>63.3</v>
+        <v>63.75</v>
       </c>
       <c r="I7">
-        <v>14.67</v>
+        <v>15.77</v>
       </c>
       <c r="J7">
-        <v>25.87</v>
+        <v>22.02</v>
       </c>
       <c r="K7">
-        <v>20.67</v>
+        <v>19.71</v>
       </c>
       <c r="L7">
-        <v>4.35</v>
+        <v>13.94</v>
       </c>
       <c r="M7">
-        <v>32.41</v>
+        <v>31.92</v>
       </c>
       <c r="N7">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P7">
-        <v>2827.76</v>
+        <v>2912.14</v>
       </c>
       <c r="Q7">
-        <v>2653.22</v>
+        <v>2679.73</v>
       </c>
       <c r="R7">
-        <v>2578.08</v>
+        <v>2589.92</v>
       </c>
       <c r="S7">
-        <v>2370.27</v>
+        <v>2373.73</v>
       </c>
       <c r="T7">
-        <v>30.31</v>
+        <v>30.48</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1605,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>78.98999999999999</v>
+        <v>79.23</v>
       </c>
       <c r="Z7">
-        <v>91.56</v>
+        <v>112.16</v>
       </c>
       <c r="AA7">
-        <v>47.82</v>
+        <v>60.69</v>
       </c>
       <c r="AB7">
-        <v>43.73</v>
+        <v>51.47</v>
       </c>
       <c r="AC7">
         <v>100</v>
       </c>
       <c r="AD7">
-        <v>79.23</v>
+        <v>90.7</v>
       </c>
       <c r="AE7">
-        <v>129.1</v>
+        <v>132.25</v>
       </c>
       <c r="AF7">
-        <v>2773.38</v>
+        <v>74.8</v>
       </c>
       <c r="AG7">
-        <v>2934.72</v>
+        <v>3020.63</v>
       </c>
       <c r="AH7">
-        <v>2371.73</v>
+        <v>2338.83</v>
       </c>
       <c r="AI7">
         <v>2788.64</v>
@@ -1641,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>53.89</v>
+        <v>57.72</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1655,7 +1605,7 @@
         <v>7932</v>
       </c>
       <c r="D8">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1670,19 +1620,19 @@
         <v>33.88</v>
       </c>
       <c r="I8">
-        <v>-2.69</v>
+        <v>-2.37</v>
       </c>
       <c r="J8">
-        <v>1.93</v>
+        <v>4.6</v>
       </c>
       <c r="K8">
-        <v>16.89</v>
+        <v>14.77</v>
       </c>
       <c r="L8">
-        <v>-18.44</v>
+        <v>-17.89</v>
       </c>
       <c r="M8">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N8">
         <v>29</v>
@@ -1691,19 +1641,19 @@
         <v>49</v>
       </c>
       <c r="P8">
-        <v>8002.6</v>
+        <v>7964.1</v>
       </c>
       <c r="Q8">
-        <v>7994.12</v>
+        <v>8011.78</v>
       </c>
       <c r="R8">
-        <v>7798.95</v>
+        <v>7821.57</v>
       </c>
       <c r="S8">
-        <v>7419.98</v>
+        <v>7416.35</v>
       </c>
       <c r="T8">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1721,31 +1671,31 @@
         <v>49.3</v>
       </c>
       <c r="Z8">
-        <v>66.51000000000001</v>
+        <v>54.48</v>
       </c>
       <c r="AA8">
-        <v>101.23</v>
+        <v>91.88</v>
       </c>
       <c r="AB8">
-        <v>-34.71</v>
+        <v>-37.4</v>
       </c>
       <c r="AC8">
         <v>2.52</v>
       </c>
       <c r="AD8">
-        <v>19.28</v>
+        <v>7.72</v>
       </c>
       <c r="AE8">
-        <v>230.35</v>
+        <v>229.93</v>
       </c>
       <c r="AF8">
-        <v>-71.34</v>
+        <v>-42.38</v>
       </c>
       <c r="AG8">
-        <v>8524.299999999999</v>
+        <v>8506.049999999999</v>
       </c>
       <c r="AH8">
-        <v>7463.95</v>
+        <v>7517.5</v>
       </c>
       <c r="AI8">
         <v>7451.92</v>
@@ -1754,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>18.21</v>
+        <v>17.03</v>
       </c>
     </row>
   </sheetData>
@@ -1895,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1935,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1953,1082 +1903,886 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>6.11</v>
+      </c>
+      <c r="D7" s="6">
+        <v>5.94</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-3.45</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>5.89</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4.96</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>3.61</v>
+      </c>
+      <c r="D10" s="6">
+        <v>3</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.61</v>
+      </c>
+      <c r="D11" s="6">
+        <v>5.47</v>
+      </c>
+      <c r="E11" s="8">
+        <v>4.86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>25.87</v>
+      </c>
+      <c r="D12" s="6">
+        <v>22.02</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.93</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4.6</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>4.98</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-4.83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1.27</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2.25</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1.51</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.33</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1.26</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.14</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-3.71</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>14.67</v>
+      </c>
+      <c r="D19" s="6">
+        <v>15.77</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.69</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.37</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>37.14</v>
+      </c>
+      <c r="D21" s="6">
+        <v>32.45</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-4.69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>33.87</v>
+      </c>
+      <c r="D22" s="6">
+        <v>35.48</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>30.65</v>
+      </c>
+      <c r="D23" s="6">
+        <v>27.84</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-13.08</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-13.84</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-30.64</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-31.03</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>4.35</v>
+      </c>
+      <c r="D26" s="6">
+        <v>13.94</v>
+      </c>
+      <c r="E26" s="8">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-18.44</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-17.89</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>4.86</v>
+      </c>
+      <c r="D28" s="6">
+        <v>4.32</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>10.06</v>
+      </c>
+      <c r="D29" s="6">
+        <v>9.69</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>23.99</v>
+      </c>
+      <c r="D30" s="6">
+        <v>25.34</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>14.05</v>
+      </c>
+      <c r="D31" s="6">
+        <v>11.62</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-0.76</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>20.67</v>
+      </c>
+      <c r="D33" s="6">
+        <v>19.71</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>16.89</v>
+      </c>
+      <c r="D34" s="6">
+        <v>14.77</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-7.26</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-9.58</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-8.84</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-7.96</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-13.84</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-13.39</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-34.19</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-32.76</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>1151.6</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1122.7</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-28.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>890.15</v>
+      </c>
+      <c r="D40" s="6">
+        <v>898.8</v>
+      </c>
+      <c r="E40" s="8">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>775.2</v>
+      </c>
+      <c r="D41" s="6">
+        <v>792.05</v>
+      </c>
+      <c r="E41" s="8">
+        <v>16.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>3088.7</v>
+      </c>
+      <c r="D42" s="6">
+        <v>3097.2</v>
+      </c>
+      <c r="E42" s="8">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="6">
+        <v>85</v>
+      </c>
+      <c r="D43" s="6">
+        <v>57</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="6">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="D44" s="6">
+        <v>85</v>
+      </c>
+      <c r="E44" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="6">
+        <v>57</v>
+      </c>
+      <c r="D45" s="6">
+        <v>71</v>
+      </c>
+      <c r="E45" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8">
-        <v>9.5</v>
-      </c>
-      <c r="D10" s="8">
-        <v>6.11</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-3.39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>58.64</v>
+      </c>
+      <c r="D46" s="6">
+        <v>52.93</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-5.71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-4.58</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-3.45</v>
-      </c>
-      <c r="E11" s="10">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>51.31</v>
+      </c>
+      <c r="D47" s="6">
+        <v>53.7</v>
+      </c>
+      <c r="E47" s="8">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>49.96</v>
+      </c>
+      <c r="D48" s="6">
+        <v>55.35</v>
+      </c>
+      <c r="E48" s="8">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="D49" s="6">
+        <v>79.23</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>22.28</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-23.61</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-45.89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-59.36</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-44.08</v>
+      </c>
+      <c r="E51" s="8">
+        <v>15.28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>6.87</v>
-      </c>
-      <c r="D12" s="8">
-        <v>5.89</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-60.72</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-50.24</v>
+      </c>
+      <c r="E52" s="8">
+        <v>10.48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>1.59</v>
-      </c>
-      <c r="D13" s="8">
-        <v>3.61</v>
-      </c>
-      <c r="E13" s="10">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-30.63</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-12.38</v>
+      </c>
+      <c r="E53" s="8">
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0.21</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0.61</v>
-      </c>
-      <c r="E14" s="10">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B54" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="6">
+        <v>22.78</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-6.12</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-28.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>16.04</v>
-      </c>
-      <c r="D15" s="8">
-        <v>25.87</v>
-      </c>
-      <c r="E15" s="10">
-        <v>9.83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
+        <v>2773.38</v>
+      </c>
+      <c r="D55" s="6">
+        <v>74.8</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-2698.58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>2.65</v>
-      </c>
-      <c r="D16" s="8">
-        <v>1.93</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="8">
-        <v>10.8</v>
-      </c>
-      <c r="D17" s="8">
-        <v>4.98</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-5.82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1.27</v>
-      </c>
-      <c r="E18" s="10">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-0.62</v>
-      </c>
-      <c r="D19" s="8">
-        <v>1.51</v>
-      </c>
-      <c r="E19" s="10">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="8">
-        <v>0.27</v>
-      </c>
-      <c r="D20" s="8">
-        <v>1.26</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>-3.65</v>
-      </c>
-      <c r="D21" s="8">
-        <v>-3.71</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>9.58</v>
-      </c>
-      <c r="D22" s="8">
-        <v>14.67</v>
-      </c>
-      <c r="E22" s="10">
-        <v>5.09</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-0.97</v>
-      </c>
-      <c r="D23" s="8">
-        <v>-2.69</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="8">
-        <v>38.68</v>
-      </c>
-      <c r="D24" s="8">
-        <v>37.14</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="8">
-        <v>30.37</v>
-      </c>
-      <c r="D25" s="8">
-        <v>33.87</v>
-      </c>
-      <c r="E25" s="10">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="8">
-        <v>29.66</v>
-      </c>
-      <c r="D26" s="8">
-        <v>30.65</v>
-      </c>
-      <c r="E26" s="10">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-14.29</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-13.08</v>
-      </c>
-      <c r="E27" s="10">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="8">
-        <v>-31.74</v>
-      </c>
-      <c r="D28" s="8">
-        <v>-30.64</v>
-      </c>
-      <c r="E28" s="10">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>-5.26</v>
-      </c>
-      <c r="D29" s="8">
-        <v>4.35</v>
-      </c>
-      <c r="E29" s="10">
-        <v>9.609999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="8">
-        <v>-18.06</v>
-      </c>
-      <c r="D30" s="8">
-        <v>-18.44</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="8">
-        <v>7.46</v>
-      </c>
-      <c r="D31" s="8">
-        <v>4.86</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="8">
-        <v>5.77</v>
-      </c>
-      <c r="D32" s="8">
-        <v>10.06</v>
-      </c>
-      <c r="E32" s="10">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="8">
-        <v>24.68</v>
-      </c>
-      <c r="D33" s="8">
-        <v>23.99</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="8">
-        <v>11.95</v>
-      </c>
-      <c r="D34" s="8">
-        <v>14.05</v>
-      </c>
-      <c r="E34" s="10">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="8">
-        <v>-1.16</v>
-      </c>
-      <c r="D35" s="8">
-        <v>-0.76</v>
-      </c>
-      <c r="E35" s="10">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="8">
-        <v>20.92</v>
-      </c>
-      <c r="D36" s="8">
-        <v>20.67</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="8">
-        <v>15.86</v>
-      </c>
-      <c r="D37" s="8">
-        <v>16.89</v>
-      </c>
-      <c r="E37" s="10">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="8">
-        <v>-4.6</v>
-      </c>
-      <c r="D38" s="8">
-        <v>-7.26</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="8">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="D39" s="8">
-        <v>-8.84</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-0.62</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-2.35</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="8">
-        <v>-14.11</v>
-      </c>
-      <c r="D41" s="8">
-        <v>-13.84</v>
-      </c>
-      <c r="E41" s="10">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="8">
-        <v>-33.76</v>
-      </c>
-      <c r="D42" s="8">
-        <v>-34.19</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-2.44</v>
-      </c>
-      <c r="D43" s="8">
-        <v>0</v>
-      </c>
-      <c r="E43" s="10">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="8">
-        <v>-21.97</v>
-      </c>
-      <c r="D44" s="8">
-        <v>-22.49</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="8">
-        <v>1184.6</v>
-      </c>
-      <c r="D45" s="8">
-        <v>1151.6</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-33</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="8">
-        <v>886.55</v>
-      </c>
-      <c r="D46" s="8">
-        <v>890.15</v>
-      </c>
-      <c r="E46" s="10">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="8">
-        <v>1927.9</v>
-      </c>
-      <c r="D47" s="8">
-        <v>1894.4</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-33.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="8">
-        <v>2088.8</v>
-      </c>
-      <c r="D48" s="8">
-        <v>2095.3</v>
-      </c>
-      <c r="E48" s="10">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="8">
-        <v>780.3</v>
-      </c>
-      <c r="D49" s="8">
-        <v>775.2</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-5.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="8">
-        <v>2887.6</v>
-      </c>
-      <c r="D50" s="8">
-        <v>3088.7</v>
-      </c>
-      <c r="E50" s="10">
-        <v>201.1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="8">
-        <v>7985</v>
-      </c>
-      <c r="D51" s="8">
-        <v>7932</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="8">
-        <v>29</v>
-      </c>
-      <c r="D52" s="8">
-        <v>43</v>
-      </c>
-      <c r="E52" s="10">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="8">
-        <v>43</v>
-      </c>
-      <c r="D53" s="8">
-        <v>29</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="8">
-        <v>66.22</v>
-      </c>
-      <c r="D54" s="8">
-        <v>58.64</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-7.58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="8">
-        <v>50.32</v>
-      </c>
-      <c r="D55" s="8">
-        <v>51.31</v>
-      </c>
-      <c r="E55" s="10">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="8">
-        <v>62.66</v>
-      </c>
-      <c r="D56" s="8">
-        <v>57.67</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-4.99</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="8">
-        <v>56.64</v>
-      </c>
-      <c r="D57" s="8">
-        <v>57.65</v>
-      </c>
-      <c r="E57" s="10">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="8">
-        <v>51.72</v>
-      </c>
-      <c r="D58" s="8">
-        <v>49.96</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="8">
-        <v>71.92</v>
-      </c>
-      <c r="D59" s="8">
-        <v>78.98999999999999</v>
-      </c>
-      <c r="E59" s="10">
-        <v>7.07</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="8">
-        <v>51.55</v>
-      </c>
-      <c r="D60" s="8">
-        <v>49.3</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="7" t="s">
+      <c r="B56" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="8">
-        <v>30.26</v>
-      </c>
-      <c r="D61" s="8">
-        <v>22.28</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-7.98</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="8">
-        <v>-65.15000000000001</v>
-      </c>
-      <c r="D62" s="8">
-        <v>-59.36</v>
-      </c>
-      <c r="E62" s="10">
-        <v>5.79</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="8">
-        <v>-46.59</v>
-      </c>
-      <c r="D63" s="8">
-        <v>-60.72</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-14.13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="8">
-        <v>-53.98</v>
-      </c>
-      <c r="D64" s="8">
-        <v>-30.63</v>
-      </c>
-      <c r="E64" s="10">
-        <v>23.35</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="8">
-        <v>-18.78</v>
-      </c>
-      <c r="D65" s="8">
-        <v>22.78</v>
-      </c>
-      <c r="E65" s="10">
-        <v>41.56</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="8">
-        <v>474.08</v>
-      </c>
-      <c r="D66" s="8">
-        <v>2773.38</v>
-      </c>
-      <c r="E66" s="10">
-        <v>2299.3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="8">
-        <v>-55.83</v>
-      </c>
-      <c r="D67" s="8">
+      <c r="C56" s="6">
         <v>-71.34</v>
       </c>
-      <c r="E67" s="9">
-        <v>-15.51</v>
+      <c r="D56" s="6">
+        <v>-42.38</v>
+      </c>
+      <c r="E56" s="8">
+        <v>28.96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3048,60 +2802,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>84</v>
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="11">
         <v>60.8</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="13">
-        <v>57.6</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="11">
+        <v>58</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="13">
-        <v>5.8</v>
-      </c>
-      <c r="G2" s="13">
-        <v>12.8</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3203,49 +2957,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="16">
-        <v>0.6212</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.3240999999999999</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.3074</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.2153</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1471</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.1428</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.1064</v>
+      <c r="A2" s="14">
+        <v>0.6175</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3192</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.3028</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2146</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1489</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.142</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,7 +190,7 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.0 → 55.4</t>
+    <t>50.0 → 51.3</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
@@ -199,7 +199,16 @@
     <t>50.0</t>
   </si>
   <si>
-    <t>55.4</t>
+    <t>51.3</t>
+  </si>
+  <si>
+    <t>49.3 → 54.6</t>
+  </si>
+  <si>
+    <t>49.3</t>
+  </si>
+  <si>
+    <t>54.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -924,10 +933,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1122.7</v>
+        <v>1126</v>
       </c>
       <c r="D2">
-        <v>-2.51</v>
+        <v>0.29</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -936,46 +945,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-9.58</v>
+        <v>-9.32</v>
       </c>
       <c r="H2">
-        <v>50.02</v>
+        <v>50.46</v>
       </c>
       <c r="I2">
-        <v>0.15</v>
+        <v>-4.07</v>
       </c>
       <c r="J2">
-        <v>5.94</v>
+        <v>3.57</v>
       </c>
       <c r="K2">
-        <v>4.32</v>
+        <v>6.31</v>
       </c>
       <c r="L2">
-        <v>32.45</v>
+        <v>33.12</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>10.06</v>
       </c>
       <c r="N2">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O2">
         <v>75</v>
       </c>
       <c r="P2">
-        <v>1157.38</v>
+        <v>1147.82</v>
       </c>
       <c r="Q2">
-        <v>1095.43</v>
+        <v>1097.52</v>
       </c>
       <c r="R2">
-        <v>1105.53</v>
+        <v>1106.96</v>
       </c>
       <c r="S2">
-        <v>933.78</v>
+        <v>934.76</v>
       </c>
       <c r="T2">
-        <v>20.23</v>
+        <v>20.46</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +999,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>52.93</v>
+        <v>53.49</v>
       </c>
       <c r="Z2">
-        <v>16.32</v>
+        <v>15.31</v>
       </c>
       <c r="AA2">
-        <v>8.09</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AB2">
-        <v>8.23</v>
+        <v>5.77</v>
       </c>
       <c r="AC2">
-        <v>69.31999999999999</v>
+        <v>52.51</v>
       </c>
       <c r="AD2">
-        <v>81.01000000000001</v>
+        <v>67.72</v>
       </c>
       <c r="AE2">
-        <v>44.18</v>
+        <v>43.16</v>
       </c>
       <c r="AF2">
-        <v>-23.61</v>
+        <v>183.74</v>
       </c>
       <c r="AG2">
-        <v>1178.52</v>
+        <v>1181.52</v>
       </c>
       <c r="AH2">
-        <v>1012.34</v>
+        <v>1013.52</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1026,7 +1035,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>41.25</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1046,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>898.8</v>
+        <v>894.2</v>
       </c>
       <c r="D3">
-        <v>0.97</v>
+        <v>-0.51</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1058,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-7.96</v>
+        <v>-8.43</v>
       </c>
       <c r="H3">
-        <v>69.75</v>
+        <v>68.88</v>
       </c>
       <c r="I3">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="J3">
-        <v>-0.6899999999999999</v>
+        <v>-2</v>
       </c>
       <c r="K3">
-        <v>9.69</v>
+        <v>4.8</v>
       </c>
       <c r="L3">
-        <v>35.48</v>
+        <v>36.08</v>
       </c>
       <c r="M3">
-        <v>61.75</v>
+        <v>61.74</v>
       </c>
       <c r="N3">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="O3">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>888.9</v>
+        <v>891.54</v>
       </c>
       <c r="Q3">
-        <v>875.01</v>
+        <v>873.98</v>
       </c>
       <c r="R3">
-        <v>907.35</v>
+        <v>907.16</v>
       </c>
       <c r="S3">
-        <v>765.6</v>
+        <v>766.34</v>
       </c>
       <c r="T3">
-        <v>17.4</v>
+        <v>16.68</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,34 +1112,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>53.7</v>
+        <v>52.23</v>
       </c>
       <c r="Z3">
-        <v>-3.21</v>
+        <v>-2.09</v>
       </c>
       <c r="AA3">
-        <v>-8.220000000000001</v>
+        <v>-6.99</v>
       </c>
       <c r="AB3">
-        <v>5.01</v>
+        <v>4.9</v>
       </c>
       <c r="AC3">
-        <v>99.31</v>
+        <v>97.62</v>
       </c>
       <c r="AD3">
-        <v>98.40000000000001</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="AE3">
-        <v>23.4</v>
+        <v>22.51</v>
       </c>
       <c r="AF3">
-        <v>-44.08</v>
+        <v>-57.38</v>
       </c>
       <c r="AG3">
-        <v>925.08</v>
+        <v>921.37</v>
       </c>
       <c r="AH3">
-        <v>824.9400000000001</v>
+        <v>826.59</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1139,7 +1148,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>16.09</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1159,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1894.4</v>
+        <v>1868</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-1.39</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1171,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-2.35</v>
+        <v>-3.71</v>
       </c>
       <c r="H4">
-        <v>39.84</v>
+        <v>37.89</v>
       </c>
       <c r="I4">
-        <v>-1.33</v>
+        <v>-2.42</v>
       </c>
       <c r="J4">
-        <v>4.96</v>
+        <v>4.78</v>
       </c>
       <c r="K4">
-        <v>25.34</v>
+        <v>22.98</v>
       </c>
       <c r="L4">
-        <v>27.84</v>
+        <v>28.86</v>
       </c>
       <c r="M4">
-        <v>30.28</v>
+        <v>30.05</v>
       </c>
       <c r="N4">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="O4">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P4">
-        <v>1909.74</v>
+        <v>1900.46</v>
       </c>
       <c r="Q4">
-        <v>1840.57</v>
+        <v>1846.03</v>
       </c>
       <c r="R4">
-        <v>1769.44</v>
+        <v>1777.68</v>
       </c>
       <c r="S4">
-        <v>1667.27</v>
+        <v>1668.06</v>
       </c>
       <c r="T4">
-        <v>13.62</v>
+        <v>11.99</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,34 +1225,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>57.67</v>
+        <v>53.75</v>
       </c>
       <c r="Z4">
-        <v>43.1</v>
+        <v>38.57</v>
       </c>
       <c r="AA4">
-        <v>42.38</v>
+        <v>41.62</v>
       </c>
       <c r="AB4">
-        <v>0.72</v>
+        <v>-3.05</v>
       </c>
       <c r="AC4">
-        <v>45.4</v>
+        <v>24.13</v>
       </c>
       <c r="AD4">
-        <v>57.6</v>
+        <v>42.66</v>
       </c>
       <c r="AE4">
-        <v>50.82</v>
+        <v>49.18</v>
       </c>
       <c r="AF4">
-        <v>-50.24</v>
+        <v>-67.06999999999999</v>
       </c>
       <c r="AG4">
-        <v>1993.72</v>
+        <v>1994.63</v>
       </c>
       <c r="AH4">
-        <v>1687.42</v>
+        <v>1697.43</v>
       </c>
       <c r="AI4">
         <v>1751.87</v>
@@ -1252,7 +1261,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>31.19</v>
+        <v>28.09</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1272,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2095.3</v>
+        <v>2062.7</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="E5">
         <v>2419.36</v>
@@ -1275,46 +1284,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-13.39</v>
+        <v>-14.74</v>
       </c>
       <c r="H5">
-        <v>20.03</v>
+        <v>18.17</v>
       </c>
       <c r="I5">
-        <v>-0.14</v>
+        <v>-1.08</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2.09</v>
       </c>
       <c r="K5">
-        <v>11.62</v>
+        <v>10.21</v>
       </c>
       <c r="L5">
-        <v>-13.84</v>
+        <v>-13.61</v>
       </c>
       <c r="M5">
-        <v>21.46</v>
+        <v>20.43</v>
       </c>
       <c r="N5">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O5">
         <v>49</v>
       </c>
       <c r="P5">
-        <v>2087.58</v>
+        <v>2083.08</v>
       </c>
       <c r="Q5">
-        <v>2064.96</v>
+        <v>2065.38</v>
       </c>
       <c r="R5">
-        <v>2021.76</v>
+        <v>2028</v>
       </c>
       <c r="S5">
-        <v>2107.49</v>
+        <v>2106.57</v>
       </c>
       <c r="T5">
-        <v>-0.58</v>
+        <v>-2.08</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,34 +1338,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>57.65</v>
+        <v>50.79</v>
       </c>
       <c r="Z5">
-        <v>21.51</v>
+        <v>18.43</v>
       </c>
       <c r="AA5">
-        <v>22.52</v>
+        <v>21.7</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>-3.27</v>
       </c>
       <c r="AC5">
-        <v>45.84</v>
+        <v>28.69</v>
       </c>
       <c r="AD5">
-        <v>48.87</v>
+        <v>40.94</v>
       </c>
       <c r="AE5">
-        <v>46.85</v>
+        <v>47.33</v>
       </c>
       <c r="AF5">
-        <v>-12.38</v>
+        <v>-50.25</v>
       </c>
       <c r="AG5">
-        <v>2138.45</v>
+        <v>2138.71</v>
       </c>
       <c r="AH5">
-        <v>1991.46</v>
+        <v>1992.04</v>
       </c>
       <c r="AI5">
         <v>1954.68</v>
@@ -1365,7 +1374,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>16.95</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1385,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>792.05</v>
+        <v>780.6</v>
       </c>
       <c r="D6">
-        <v>2.17</v>
+        <v>-1.45</v>
       </c>
       <c r="E6">
         <v>1178</v>
@@ -1388,46 +1397,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-32.76</v>
+        <v>-33.74</v>
       </c>
       <c r="H6">
-        <v>12.49</v>
+        <v>10.86</v>
       </c>
       <c r="I6">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="J6">
-        <v>5.47</v>
+        <v>2.41</v>
       </c>
       <c r="K6">
-        <v>0.19</v>
+        <v>-2.19</v>
       </c>
       <c r="L6">
-        <v>-31.03</v>
+        <v>-33.19</v>
       </c>
       <c r="M6">
-        <v>14.89</v>
+        <v>14.65</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P6">
-        <v>781.71</v>
+        <v>780.13</v>
       </c>
       <c r="Q6">
-        <v>780.65</v>
+        <v>781.29</v>
       </c>
       <c r="R6">
-        <v>753.96</v>
+        <v>755.15</v>
       </c>
       <c r="S6">
-        <v>869.33</v>
+        <v>867.79</v>
       </c>
       <c r="T6">
-        <v>-8.890000000000001</v>
+        <v>-10.05</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,34 +1451,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>55.35</v>
+        <v>51.31</v>
       </c>
       <c r="Z6">
-        <v>7.84</v>
+        <v>6.92</v>
       </c>
       <c r="AA6">
-        <v>9.57</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AB6">
-        <v>-1.73</v>
+        <v>-2.12</v>
       </c>
       <c r="AC6">
-        <v>16.85</v>
+        <v>16.12</v>
       </c>
       <c r="AD6">
-        <v>11.62</v>
+        <v>12.95</v>
       </c>
       <c r="AE6">
         <v>22.86</v>
       </c>
       <c r="AF6">
-        <v>-6.12</v>
+        <v>98.02</v>
       </c>
       <c r="AG6">
-        <v>817.6799999999999</v>
+        <v>817.83</v>
       </c>
       <c r="AH6">
-        <v>743.63</v>
+        <v>744.76</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1478,7 +1487,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>21.73</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,13 +1498,13 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3097.2</v>
+        <v>3280.2</v>
       </c>
       <c r="D7">
-        <v>0.28</v>
+        <v>5.91</v>
       </c>
       <c r="E7">
-        <v>3097.2</v>
+        <v>3280.2</v>
       </c>
       <c r="F7">
         <v>1891.45</v>
@@ -1504,43 +1513,43 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>63.75</v>
+        <v>73.42</v>
       </c>
       <c r="I7">
-        <v>15.77</v>
+        <v>25.73</v>
       </c>
       <c r="J7">
-        <v>22.02</v>
+        <v>27.78</v>
       </c>
       <c r="K7">
-        <v>19.71</v>
+        <v>26.73</v>
       </c>
       <c r="L7">
-        <v>13.94</v>
+        <v>25.7</v>
       </c>
       <c r="M7">
-        <v>31.92</v>
+        <v>33.81</v>
       </c>
       <c r="N7">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="P7">
-        <v>2912.14</v>
+        <v>3046.4</v>
       </c>
       <c r="Q7">
-        <v>2679.73</v>
+        <v>2712.43</v>
       </c>
       <c r="R7">
-        <v>2589.92</v>
+        <v>2605.59</v>
       </c>
       <c r="S7">
-        <v>2373.73</v>
+        <v>2377.74</v>
       </c>
       <c r="T7">
-        <v>30.48</v>
+        <v>37.95</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,43 +1564,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>79.23</v>
+        <v>83.55</v>
       </c>
       <c r="Z7">
-        <v>112.16</v>
+        <v>141.62</v>
       </c>
       <c r="AA7">
-        <v>60.69</v>
+        <v>76.88</v>
       </c>
       <c r="AB7">
-        <v>51.47</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="AC7">
         <v>100</v>
       </c>
       <c r="AD7">
-        <v>90.7</v>
+        <v>100</v>
       </c>
       <c r="AE7">
-        <v>132.25</v>
+        <v>142.09</v>
       </c>
       <c r="AF7">
-        <v>74.8</v>
+        <v>212.61</v>
       </c>
       <c r="AG7">
-        <v>3020.63</v>
+        <v>3144.89</v>
       </c>
       <c r="AH7">
-        <v>2338.83</v>
+        <v>2279.97</v>
       </c>
       <c r="AI7">
-        <v>2788.64</v>
+        <v>2798.69</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>57.72</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1611,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7932</v>
+        <v>8055</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1614,46 +1623,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-22.49</v>
+        <v>-21.28</v>
       </c>
       <c r="H8">
-        <v>33.88</v>
+        <v>35.96</v>
       </c>
       <c r="I8">
-        <v>-2.37</v>
+        <v>0.47</v>
       </c>
       <c r="J8">
-        <v>4.6</v>
+        <v>6.28</v>
       </c>
       <c r="K8">
-        <v>14.77</v>
+        <v>15.47</v>
       </c>
       <c r="L8">
-        <v>-17.89</v>
+        <v>-18.48</v>
       </c>
       <c r="M8">
-        <v>14.2</v>
+        <v>14.65</v>
       </c>
       <c r="N8">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O8">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P8">
-        <v>7964.1</v>
+        <v>7971.7</v>
       </c>
       <c r="Q8">
-        <v>8011.78</v>
+        <v>8036.42</v>
       </c>
       <c r="R8">
-        <v>7821.57</v>
+        <v>7849.66</v>
       </c>
       <c r="S8">
-        <v>7416.35</v>
+        <v>7413.27</v>
       </c>
       <c r="T8">
-        <v>6.95</v>
+        <v>8.66</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,34 +1677,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>49.3</v>
+        <v>54.62</v>
       </c>
       <c r="Z8">
-        <v>54.48</v>
+        <v>54.25</v>
       </c>
       <c r="AA8">
-        <v>91.88</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="AB8">
-        <v>-37.4</v>
+        <v>-30.1</v>
       </c>
       <c r="AC8">
-        <v>2.52</v>
+        <v>14.62</v>
       </c>
       <c r="AD8">
-        <v>7.72</v>
+        <v>6.56</v>
       </c>
       <c r="AE8">
-        <v>229.93</v>
+        <v>236.47</v>
       </c>
       <c r="AF8">
-        <v>-42.38</v>
+        <v>-42.58</v>
       </c>
       <c r="AG8">
-        <v>8506.049999999999</v>
+        <v>8483.139999999999</v>
       </c>
       <c r="AH8">
-        <v>7517.5</v>
+        <v>7589.71</v>
       </c>
       <c r="AI8">
         <v>7451.92</v>
@@ -1704,7 +1713,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>17.03</v>
+        <v>17.11</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1903,886 +1912,1093 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>6.11</v>
-      </c>
-      <c r="D7" s="6">
-        <v>5.94</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.17</v>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-3.45</v>
+        <v>6.11</v>
       </c>
       <c r="D8" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E8" s="8">
-        <v>2.76</v>
+        <v>3.57</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>5.89</v>
+        <v>-3.45</v>
       </c>
       <c r="D9" s="6">
-        <v>4.96</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.93</v>
+        <v>-2</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.45</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>3.61</v>
+        <v>5.89</v>
       </c>
       <c r="D10" s="6">
-        <v>3</v>
+        <v>4.78</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.61</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>0.61</v>
+        <v>3.61</v>
       </c>
       <c r="D11" s="6">
-        <v>5.47</v>
-      </c>
-      <c r="E11" s="8">
-        <v>4.86</v>
+        <v>2.09</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>25.87</v>
+        <v>0.61</v>
       </c>
       <c r="D12" s="6">
-        <v>22.02</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.85</v>
+        <v>2.41</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.8</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>1.93</v>
+        <v>25.87</v>
       </c>
       <c r="D13" s="6">
-        <v>4.6</v>
+        <v>27.78</v>
       </c>
       <c r="E13" s="8">
-        <v>2.67</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>4.98</v>
+        <v>1.93</v>
       </c>
       <c r="D14" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-4.83</v>
+        <v>6.28</v>
+      </c>
+      <c r="E14" s="8">
+        <v>4.35</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>1.27</v>
+        <v>4.98</v>
       </c>
       <c r="D15" s="6">
-        <v>2.25</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.98</v>
+        <v>-4.07</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-9.050000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.84</v>
+        <v>1.5</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="D17" s="6">
-        <v>-0.14</v>
+        <v>-2.42</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.4</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.71</v>
+        <v>1.26</v>
       </c>
       <c r="D18" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.81</v>
+        <v>-1.08</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>14.67</v>
+        <v>-3.71</v>
       </c>
       <c r="D19" s="6">
-        <v>15.77</v>
+        <v>-1</v>
       </c>
       <c r="E19" s="8">
-        <v>1.1</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-2.69</v>
+        <v>14.67</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.37</v>
+        <v>25.73</v>
       </c>
       <c r="E20" s="8">
-        <v>0.32</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>37.14</v>
+        <v>-2.69</v>
       </c>
       <c r="D21" s="6">
-        <v>32.45</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-4.69</v>
+        <v>0.47</v>
+      </c>
+      <c r="E21" s="8">
+        <v>3.16</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>33.87</v>
+        <v>37.14</v>
       </c>
       <c r="D22" s="6">
-        <v>35.48</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.61</v>
+        <v>33.12</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-4.02</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>30.65</v>
+        <v>33.87</v>
       </c>
       <c r="D23" s="6">
-        <v>27.84</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.81</v>
+        <v>36.08</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.21</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-13.08</v>
+        <v>30.65</v>
       </c>
       <c r="D24" s="6">
-        <v>-13.84</v>
+        <v>28.86</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.76</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-30.64</v>
+        <v>-13.08</v>
       </c>
       <c r="D25" s="6">
-        <v>-31.03</v>
+        <v>-13.61</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.39</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>4.35</v>
+        <v>-30.64</v>
       </c>
       <c r="D26" s="6">
-        <v>13.94</v>
-      </c>
-      <c r="E26" s="8">
-        <v>9.59</v>
+        <v>-33.19</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.55</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-18.44</v>
+        <v>4.35</v>
       </c>
       <c r="D27" s="6">
-        <v>-17.89</v>
+        <v>25.7</v>
       </c>
       <c r="E27" s="8">
-        <v>0.55</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>4.86</v>
+        <v>-18.44</v>
       </c>
       <c r="D28" s="6">
-        <v>4.32</v>
+        <v>-18.48</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.54</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>10.06</v>
+        <v>4.86</v>
       </c>
       <c r="D29" s="6">
-        <v>9.69</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.37</v>
+        <v>6.31</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.45</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>23.99</v>
+        <v>10.06</v>
       </c>
       <c r="D30" s="6">
-        <v>25.34</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.35</v>
+        <v>4.8</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-5.26</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>14.05</v>
+        <v>23.99</v>
       </c>
       <c r="D31" s="6">
-        <v>11.62</v>
+        <v>22.98</v>
       </c>
       <c r="E31" s="7">
-        <v>-2.43</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-0.76</v>
+        <v>14.05</v>
       </c>
       <c r="D32" s="6">
-        <v>0.19</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.95</v>
+        <v>10.21</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.84</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>20.67</v>
+        <v>-0.76</v>
       </c>
       <c r="D33" s="6">
-        <v>19.71</v>
+        <v>-2.19</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.96</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>16.89</v>
+        <v>20.67</v>
       </c>
       <c r="D34" s="6">
-        <v>14.77</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-2.12</v>
+        <v>26.73</v>
+      </c>
+      <c r="E34" s="8">
+        <v>6.06</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-7.26</v>
+        <v>16.89</v>
       </c>
       <c r="D35" s="6">
-        <v>-9.58</v>
+        <v>15.47</v>
       </c>
       <c r="E35" s="7">
-        <v>-2.32</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-8.84</v>
+        <v>-7.26</v>
       </c>
       <c r="D36" s="6">
-        <v>-7.96</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.88</v>
+        <v>-9.32</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-13.84</v>
+        <v>-8.84</v>
       </c>
       <c r="D37" s="6">
-        <v>-13.39</v>
+        <v>-8.43</v>
       </c>
       <c r="E37" s="8">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-34.19</v>
+        <v>-2.35</v>
       </c>
       <c r="D38" s="6">
-        <v>-32.76</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.43</v>
+        <v>-3.71</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>1151.6</v>
+        <v>-13.84</v>
       </c>
       <c r="D39" s="6">
-        <v>1122.7</v>
+        <v>-14.74</v>
       </c>
       <c r="E39" s="7">
-        <v>-28.9</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>890.15</v>
+        <v>-34.19</v>
       </c>
       <c r="D40" s="6">
-        <v>898.8</v>
+        <v>-33.74</v>
       </c>
       <c r="E40" s="8">
-        <v>8.65</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>775.2</v>
+        <v>-22.49</v>
       </c>
       <c r="D41" s="6">
-        <v>792.05</v>
+        <v>-21.28</v>
       </c>
       <c r="E41" s="8">
-        <v>16.85</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>3088.7</v>
+        <v>1151.6</v>
       </c>
       <c r="D42" s="6">
-        <v>3097.2</v>
-      </c>
-      <c r="E42" s="8">
-        <v>8.5</v>
+        <v>1126</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-25.6</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>85</v>
+        <v>890.15</v>
       </c>
       <c r="D43" s="6">
-        <v>57</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-28</v>
+        <v>894.2</v>
+      </c>
+      <c r="E43" s="8">
+        <v>4.05</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>71</v>
+        <v>1894.4</v>
       </c>
       <c r="D44" s="6">
-        <v>85</v>
-      </c>
-      <c r="E44" s="8">
-        <v>14</v>
+        <v>1868</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-26.4</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>57</v>
+        <v>2095.3</v>
       </c>
       <c r="D45" s="6">
-        <v>71</v>
-      </c>
-      <c r="E45" s="8">
-        <v>14</v>
+        <v>2062.7</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-32.6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>58.64</v>
+        <v>775.2</v>
       </c>
       <c r="D46" s="6">
-        <v>52.93</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-5.71</v>
+        <v>780.6</v>
+      </c>
+      <c r="E46" s="8">
+        <v>5.4</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>51.31</v>
+        <v>3088.7</v>
       </c>
       <c r="D47" s="6">
-        <v>53.7</v>
+        <v>3280.2</v>
       </c>
       <c r="E47" s="8">
-        <v>2.39</v>
+        <v>191.5</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>49.96</v>
+        <v>7932</v>
       </c>
       <c r="D48" s="6">
-        <v>55.35</v>
+        <v>8055</v>
       </c>
       <c r="E48" s="8">
-        <v>5.39</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C49" s="6">
-        <v>78.98999999999999</v>
+        <v>85</v>
       </c>
       <c r="D49" s="6">
-        <v>79.23</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.24</v>
+        <v>71</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-14</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C50" s="6">
-        <v>22.28</v>
+        <v>71</v>
       </c>
       <c r="D50" s="6">
-        <v>-23.61</v>
+        <v>57</v>
       </c>
       <c r="E50" s="7">
-        <v>-45.89</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C51" s="6">
-        <v>-59.36</v>
+        <v>99</v>
       </c>
       <c r="D51" s="6">
-        <v>-44.08</v>
-      </c>
-      <c r="E51" s="8">
-        <v>15.28</v>
+        <v>85</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C52" s="6">
-        <v>-60.72</v>
+        <v>43</v>
       </c>
       <c r="D52" s="6">
-        <v>-50.24</v>
-      </c>
-      <c r="E52" s="8">
-        <v>10.48</v>
+        <v>29</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-14</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C53" s="6">
-        <v>-30.63</v>
+        <v>57</v>
       </c>
       <c r="D53" s="6">
-        <v>-12.38</v>
+        <v>99</v>
       </c>
       <c r="E53" s="8">
-        <v>18.25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C54" s="6">
-        <v>22.78</v>
+        <v>29</v>
       </c>
       <c r="D54" s="6">
-        <v>-6.12</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-28.9</v>
+        <v>43</v>
+      </c>
+      <c r="E54" s="8">
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>2773.38</v>
+        <v>58.64</v>
       </c>
       <c r="D55" s="6">
-        <v>74.8</v>
+        <v>53.49</v>
       </c>
       <c r="E55" s="7">
-        <v>-2698.58</v>
+        <v>-5.15</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>51.31</v>
+      </c>
+      <c r="D56" s="6">
+        <v>52.23</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>57.67</v>
+      </c>
+      <c r="D57" s="6">
+        <v>53.75</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-3.92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>57.65</v>
+      </c>
+      <c r="D58" s="6">
+        <v>50.79</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-6.86</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>49.96</v>
+      </c>
+      <c r="D59" s="6">
+        <v>51.31</v>
+      </c>
+      <c r="E59" s="8">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="D60" s="6">
+        <v>83.55</v>
+      </c>
+      <c r="E60" s="8">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>49.3</v>
+      </c>
+      <c r="D61" s="6">
+        <v>54.62</v>
+      </c>
+      <c r="E61" s="8">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C62" s="6">
+        <v>22.28</v>
+      </c>
+      <c r="D62" s="6">
+        <v>183.74</v>
+      </c>
+      <c r="E62" s="8">
+        <v>161.46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-59.36</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-57.38</v>
+      </c>
+      <c r="E63" s="8">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-60.72</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-67.06999999999999</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-6.35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>-30.63</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-50.25</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-19.62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>22.78</v>
+      </c>
+      <c r="D66" s="6">
+        <v>98.02</v>
+      </c>
+      <c r="E66" s="8">
+        <v>75.23999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>2773.38</v>
+      </c>
+      <c r="D67" s="6">
+        <v>212.61</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-2560.77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
         <v>-71.34</v>
       </c>
-      <c r="D56" s="6">
-        <v>-42.38</v>
-      </c>
-      <c r="E56" s="8">
-        <v>28.96</v>
+      <c r="D68" s="6">
+        <v>-42.58</v>
+      </c>
+      <c r="E68" s="8">
+        <v>28.76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2806,28 +3022,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2841,16 +3057,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>58</v>
+        <v>57.1</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="G2" s="11">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -2981,25 +3197,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.6175</v>
+        <v>0.6174000000000001</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3192</v>
+        <v>0.3381</v>
       </c>
       <c r="C2" s="14">
-        <v>0.3028</v>
+        <v>0.3005</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2146</v>
+        <v>0.2043</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1489</v>
+        <v>0.1465</v>
       </c>
       <c r="F2" s="14">
-        <v>0.142</v>
+        <v>0.1465</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1</v>
+        <v>0.1006</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="84">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,28 +187,52 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>0.0% → -4.7%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-4.7%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.0 → 51.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>51.3</t>
-  </si>
-  <si>
-    <t>49.3 → 54.6</t>
-  </si>
-  <si>
-    <t>49.3</t>
-  </si>
-  <si>
-    <t>54.6</t>
+    <t>53.5 → 46.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.5</t>
+  </si>
+  <si>
+    <t>46.5</t>
+  </si>
+  <si>
+    <t>52.2 → 43.5</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>43.5</t>
+  </si>
+  <si>
+    <t>50.8 → 46.3</t>
+  </si>
+  <si>
+    <t>50.8</t>
+  </si>
+  <si>
+    <t>46.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -260,7 +284,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,7 +318,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -306,8 +330,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,13 +365,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -418,14 +455,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -434,7 +472,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -933,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1126</v>
+        <v>1087.2</v>
       </c>
       <c r="D2">
-        <v>0.29</v>
+        <v>-3.45</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -945,46 +983,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-9.32</v>
+        <v>-12.44</v>
       </c>
       <c r="H2">
-        <v>50.46</v>
+        <v>45.28</v>
       </c>
       <c r="I2">
-        <v>-4.07</v>
+        <v>-5.8</v>
       </c>
       <c r="J2">
-        <v>3.57</v>
+        <v>0.28</v>
       </c>
       <c r="K2">
-        <v>6.31</v>
+        <v>2.33</v>
       </c>
       <c r="L2">
-        <v>33.12</v>
+        <v>28.82</v>
       </c>
       <c r="M2">
-        <v>10.06</v>
+        <v>9.68</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>1147.82</v>
+        <v>1134.42</v>
       </c>
       <c r="Q2">
-        <v>1097.52</v>
+        <v>1098.43</v>
       </c>
       <c r="R2">
-        <v>1106.96</v>
+        <v>1107.9</v>
       </c>
       <c r="S2">
-        <v>934.76</v>
+        <v>935.58</v>
       </c>
       <c r="T2">
-        <v>20.46</v>
+        <v>16.21</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -999,34 +1037,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>53.49</v>
+        <v>46.51</v>
       </c>
       <c r="Z2">
-        <v>15.31</v>
+        <v>11.24</v>
       </c>
       <c r="AA2">
-        <v>9.529999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB2">
-        <v>5.77</v>
+        <v>1.36</v>
       </c>
       <c r="AC2">
-        <v>52.51</v>
+        <v>31.8</v>
       </c>
       <c r="AD2">
-        <v>67.72</v>
+        <v>51.21</v>
       </c>
       <c r="AE2">
-        <v>43.16</v>
+        <v>43.32</v>
       </c>
       <c r="AF2">
-        <v>183.74</v>
+        <v>-18.86</v>
       </c>
       <c r="AG2">
         <v>1181.52</v>
       </c>
       <c r="AH2">
-        <v>1013.52</v>
+        <v>1015.35</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1035,7 +1073,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>40.02</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,10 +1084,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>894.2</v>
+        <v>863.05</v>
       </c>
       <c r="D3">
-        <v>-0.51</v>
+        <v>-3.48</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1058,46 +1096,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.43</v>
+        <v>-11.62</v>
       </c>
       <c r="H3">
-        <v>68.88</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>1.5</v>
+        <v>-2.81</v>
       </c>
       <c r="J3">
-        <v>-2</v>
+        <v>-5.66</v>
       </c>
       <c r="K3">
-        <v>4.8</v>
+        <v>-0.21</v>
       </c>
       <c r="L3">
-        <v>36.08</v>
+        <v>29.01</v>
       </c>
       <c r="M3">
-        <v>61.74</v>
+        <v>60.98</v>
       </c>
       <c r="N3">
         <v>57</v>
       </c>
       <c r="O3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>891.54</v>
+        <v>886.55</v>
       </c>
       <c r="Q3">
-        <v>873.98</v>
+        <v>871.49</v>
       </c>
       <c r="R3">
-        <v>907.16</v>
+        <v>906.2</v>
       </c>
       <c r="S3">
-        <v>766.34</v>
+        <v>766.99</v>
       </c>
       <c r="T3">
-        <v>16.68</v>
+        <v>12.52</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1112,34 +1150,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.23</v>
+        <v>43.55</v>
       </c>
       <c r="Z3">
-        <v>-2.09</v>
+        <v>-3.68</v>
       </c>
       <c r="AA3">
-        <v>-6.99</v>
+        <v>-6.33</v>
       </c>
       <c r="AB3">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="AC3">
-        <v>97.62</v>
+        <v>78.48</v>
       </c>
       <c r="AD3">
-        <v>98.73999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="AE3">
-        <v>22.51</v>
+        <v>23.33</v>
       </c>
       <c r="AF3">
-        <v>-57.38</v>
+        <v>11.23</v>
       </c>
       <c r="AG3">
-        <v>921.37</v>
+        <v>915.39</v>
       </c>
       <c r="AH3">
-        <v>826.59</v>
+        <v>827.59</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1148,7 +1186,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>15.58</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1159,10 +1197,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1868</v>
+        <v>1873.5</v>
       </c>
       <c r="D4">
-        <v>-1.39</v>
+        <v>0.29</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1171,46 +1209,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-3.71</v>
+        <v>-3.43</v>
       </c>
       <c r="H4">
-        <v>37.89</v>
+        <v>38.3</v>
       </c>
       <c r="I4">
-        <v>-2.42</v>
+        <v>-2.3</v>
       </c>
       <c r="J4">
-        <v>4.78</v>
+        <v>6.52</v>
       </c>
       <c r="K4">
-        <v>22.98</v>
+        <v>24.57</v>
       </c>
       <c r="L4">
-        <v>28.86</v>
+        <v>28.37</v>
       </c>
       <c r="M4">
-        <v>30.05</v>
+        <v>31.29</v>
       </c>
       <c r="N4">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="O4">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P4">
-        <v>1900.46</v>
+        <v>1891.64</v>
       </c>
       <c r="Q4">
-        <v>1846.03</v>
+        <v>1853.31</v>
       </c>
       <c r="R4">
-        <v>1777.68</v>
+        <v>1785.25</v>
       </c>
       <c r="S4">
-        <v>1668.06</v>
+        <v>1668.88</v>
       </c>
       <c r="T4">
-        <v>11.99</v>
+        <v>12.26</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1225,34 +1263,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>53.75</v>
+        <v>54.45</v>
       </c>
       <c r="Z4">
-        <v>38.57</v>
+        <v>35.02</v>
       </c>
       <c r="AA4">
-        <v>41.62</v>
+        <v>40.3</v>
       </c>
       <c r="AB4">
-        <v>-3.05</v>
+        <v>-5.28</v>
       </c>
       <c r="AC4">
-        <v>24.13</v>
+        <v>12.99</v>
       </c>
       <c r="AD4">
-        <v>42.66</v>
+        <v>27.51</v>
       </c>
       <c r="AE4">
-        <v>49.18</v>
+        <v>47.12</v>
       </c>
       <c r="AF4">
-        <v>-67.06999999999999</v>
+        <v>-64.66</v>
       </c>
       <c r="AG4">
-        <v>1994.63</v>
+        <v>1991.45</v>
       </c>
       <c r="AH4">
-        <v>1697.43</v>
+        <v>1715.16</v>
       </c>
       <c r="AI4">
         <v>1751.87</v>
@@ -1261,7 +1299,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>28.09</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1272,10 +1310,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2062.7</v>
+        <v>2038.1</v>
       </c>
       <c r="D5">
-        <v>-1.56</v>
+        <v>-1.19</v>
       </c>
       <c r="E5">
         <v>2419.36</v>
@@ -1284,46 +1322,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-14.74</v>
+        <v>-15.76</v>
       </c>
       <c r="H5">
-        <v>18.17</v>
+        <v>16.76</v>
       </c>
       <c r="I5">
-        <v>-1.08</v>
+        <v>-1.7</v>
       </c>
       <c r="J5">
-        <v>2.09</v>
+        <v>-0.79</v>
       </c>
       <c r="K5">
-        <v>10.21</v>
+        <v>8.25</v>
       </c>
       <c r="L5">
-        <v>-13.61</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="M5">
-        <v>20.43</v>
+        <v>20.95</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P5">
-        <v>2083.08</v>
+        <v>2076.04</v>
       </c>
       <c r="Q5">
-        <v>2065.38</v>
+        <v>2065.32</v>
       </c>
       <c r="R5">
-        <v>2028</v>
+        <v>2032.62</v>
       </c>
       <c r="S5">
-        <v>2106.57</v>
+        <v>2105.94</v>
       </c>
       <c r="T5">
-        <v>-2.08</v>
+        <v>-3.22</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1338,34 +1376,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>50.79</v>
+        <v>46.31</v>
       </c>
       <c r="Z5">
-        <v>18.43</v>
+        <v>13.84</v>
       </c>
       <c r="AA5">
-        <v>21.7</v>
+        <v>20.13</v>
       </c>
       <c r="AB5">
-        <v>-3.27</v>
+        <v>-6.29</v>
       </c>
       <c r="AC5">
-        <v>28.69</v>
+        <v>13.02</v>
       </c>
       <c r="AD5">
-        <v>40.94</v>
+        <v>29.18</v>
       </c>
       <c r="AE5">
-        <v>47.33</v>
+        <v>46.59</v>
       </c>
       <c r="AF5">
-        <v>-50.25</v>
+        <v>-58.58</v>
       </c>
       <c r="AG5">
-        <v>2138.71</v>
+        <v>2138.74</v>
       </c>
       <c r="AH5">
-        <v>1992.04</v>
+        <v>1991.89</v>
       </c>
       <c r="AI5">
         <v>1954.68</v>
@@ -1374,7 +1412,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>15.44</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1385,10 +1423,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>780.6</v>
+        <v>787.05</v>
       </c>
       <c r="D6">
-        <v>-1.45</v>
+        <v>0.83</v>
       </c>
       <c r="E6">
         <v>1178</v>
@@ -1397,46 +1435,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-33.74</v>
+        <v>-33.19</v>
       </c>
       <c r="H6">
-        <v>10.86</v>
+        <v>11.78</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>1.88</v>
       </c>
       <c r="J6">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="K6">
-        <v>-2.19</v>
+        <v>-0.31</v>
       </c>
       <c r="L6">
-        <v>-33.19</v>
+        <v>-30.87</v>
       </c>
       <c r="M6">
-        <v>14.65</v>
+        <v>15.54</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P6">
-        <v>780.13</v>
+        <v>783.04</v>
       </c>
       <c r="Q6">
-        <v>781.29</v>
+        <v>782.37</v>
       </c>
       <c r="R6">
-        <v>755.15</v>
+        <v>756.17</v>
       </c>
       <c r="S6">
-        <v>867.79</v>
+        <v>866.34</v>
       </c>
       <c r="T6">
-        <v>-10.05</v>
+        <v>-9.15</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1451,34 +1489,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>51.31</v>
+        <v>53.37</v>
       </c>
       <c r="Z6">
-        <v>6.92</v>
+        <v>6.64</v>
       </c>
       <c r="AA6">
-        <v>9.039999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="AB6">
-        <v>-2.12</v>
+        <v>-1.92</v>
       </c>
       <c r="AC6">
-        <v>16.12</v>
+        <v>22.18</v>
       </c>
       <c r="AD6">
-        <v>12.95</v>
+        <v>18.39</v>
       </c>
       <c r="AE6">
-        <v>22.86</v>
+        <v>23.01</v>
       </c>
       <c r="AF6">
-        <v>98.02</v>
+        <v>95.12</v>
       </c>
       <c r="AG6">
-        <v>817.83</v>
+        <v>818.2</v>
       </c>
       <c r="AH6">
-        <v>744.76</v>
+        <v>746.54</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1487,7 +1525,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>19.26</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1498,10 +1536,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3280.2</v>
+        <v>3127.5</v>
       </c>
       <c r="D7">
-        <v>5.91</v>
+        <v>-4.66</v>
       </c>
       <c r="E7">
         <v>3280.2</v>
@@ -1510,46 +1548,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-4.66</v>
       </c>
       <c r="H7">
-        <v>73.42</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="I7">
-        <v>25.73</v>
+        <v>8.66</v>
       </c>
       <c r="J7">
-        <v>27.78</v>
+        <v>19.09</v>
       </c>
       <c r="K7">
-        <v>26.73</v>
+        <v>20.85</v>
       </c>
       <c r="L7">
-        <v>25.7</v>
+        <v>18.31</v>
       </c>
       <c r="M7">
-        <v>33.81</v>
+        <v>32.96</v>
       </c>
       <c r="N7">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="O7">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P7">
-        <v>3046.4</v>
+        <v>3096.24</v>
       </c>
       <c r="Q7">
-        <v>2712.43</v>
+        <v>2742.31</v>
       </c>
       <c r="R7">
-        <v>2605.59</v>
+        <v>2618.04</v>
       </c>
       <c r="S7">
-        <v>2377.74</v>
+        <v>2381.16</v>
       </c>
       <c r="T7">
-        <v>37.95</v>
+        <v>31.34</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1564,34 +1602,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>83.55</v>
+        <v>70.39</v>
       </c>
       <c r="Z7">
-        <v>141.62</v>
+        <v>150.91</v>
       </c>
       <c r="AA7">
-        <v>76.88</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="AB7">
-        <v>64.73999999999999</v>
+        <v>59.23</v>
       </c>
       <c r="AC7">
-        <v>100</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="AD7">
-        <v>100</v>
+        <v>95.22</v>
       </c>
       <c r="AE7">
-        <v>142.09</v>
+        <v>146.27</v>
       </c>
       <c r="AF7">
-        <v>212.61</v>
+        <v>-11.88</v>
       </c>
       <c r="AG7">
-        <v>3144.89</v>
+        <v>3203.3</v>
       </c>
       <c r="AH7">
-        <v>2279.97</v>
+        <v>2281.33</v>
       </c>
       <c r="AI7">
         <v>2798.69</v>
@@ -1600,7 +1638,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>61.5</v>
+        <v>64.77</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1611,10 +1649,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8055</v>
+        <v>7967.5</v>
       </c>
       <c r="D8">
-        <v>1.55</v>
+        <v>-1.09</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1623,25 +1661,25 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-21.28</v>
+        <v>-22.14</v>
       </c>
       <c r="H8">
-        <v>35.96</v>
+        <v>34.48</v>
       </c>
       <c r="I8">
-        <v>0.47</v>
+        <v>0.16</v>
       </c>
       <c r="J8">
-        <v>6.28</v>
+        <v>5.36</v>
       </c>
       <c r="K8">
-        <v>15.47</v>
+        <v>16.3</v>
       </c>
       <c r="L8">
-        <v>-18.48</v>
+        <v>-20.2</v>
       </c>
       <c r="M8">
-        <v>14.65</v>
+        <v>15.01</v>
       </c>
       <c r="N8">
         <v>43</v>
@@ -1650,19 +1688,19 @@
         <v>51</v>
       </c>
       <c r="P8">
-        <v>7971.7</v>
+        <v>7974.3</v>
       </c>
       <c r="Q8">
-        <v>8036.42</v>
+        <v>8059.25</v>
       </c>
       <c r="R8">
-        <v>7849.66</v>
+        <v>7873.6</v>
       </c>
       <c r="S8">
-        <v>7413.27</v>
+        <v>7409.78</v>
       </c>
       <c r="T8">
-        <v>8.66</v>
+        <v>7.53</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1677,34 +1715,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>54.62</v>
+        <v>50.56</v>
       </c>
       <c r="Z8">
-        <v>54.25</v>
+        <v>46.46</v>
       </c>
       <c r="AA8">
-        <v>84.34999999999999</v>
+        <v>76.77</v>
       </c>
       <c r="AB8">
-        <v>-30.1</v>
+        <v>-30.31</v>
       </c>
       <c r="AC8">
-        <v>14.62</v>
+        <v>18.07</v>
       </c>
       <c r="AD8">
-        <v>6.56</v>
+        <v>11.74</v>
       </c>
       <c r="AE8">
-        <v>236.47</v>
+        <v>234.44</v>
       </c>
       <c r="AF8">
-        <v>-42.58</v>
+        <v>-55.3</v>
       </c>
       <c r="AG8">
-        <v>8483.139999999999</v>
+        <v>8433.73</v>
       </c>
       <c r="AH8">
-        <v>7589.71</v>
+        <v>7684.77</v>
       </c>
       <c r="AI8">
         <v>7451.92</v>
@@ -1713,7 +1751,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>17.11</v>
+        <v>15.13</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1894,7 +1932,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1913,1092 +1951,1081 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3.57</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.28</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-3.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-2</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-5.66</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>4.78</v>
+      </c>
+      <c r="D12" s="7">
+        <v>6.52</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2.09</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-0.79</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>2.41</v>
+      </c>
+      <c r="D14" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>27.78</v>
+      </c>
+      <c r="D15" s="7">
+        <v>19.09</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-8.69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>6.28</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5.36</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-4.07</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-5.8</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-2.81</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-4.31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-2.42</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-2.3</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.08</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-1.7</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1.88</v>
+      </c>
+      <c r="E21" s="9">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>25.73</v>
+      </c>
+      <c r="D22" s="7">
+        <v>8.66</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-17.07</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0.47</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>33.12</v>
+      </c>
+      <c r="D24" s="7">
+        <v>28.82</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>36.08</v>
+      </c>
+      <c r="D25" s="7">
+        <v>29.01</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-7.07</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>28.86</v>
+      </c>
+      <c r="D26" s="7">
+        <v>28.37</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-13.61</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="E27" s="9">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-33.19</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-30.87</v>
+      </c>
+      <c r="E28" s="9">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>25.7</v>
+      </c>
+      <c r="D29" s="7">
+        <v>18.31</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-7.39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-18.48</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-20.2</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>6.31</v>
+      </c>
+      <c r="D31" s="7">
+        <v>2.33</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-3.98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>4.8</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-0.21</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-5.01</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>22.98</v>
+      </c>
+      <c r="D33" s="7">
+        <v>24.57</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>10.21</v>
+      </c>
+      <c r="D34" s="7">
+        <v>8.25</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-2.19</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-0.31</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>26.73</v>
+      </c>
+      <c r="D36" s="7">
+        <v>20.85</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-5.88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>15.47</v>
+      </c>
+      <c r="D37" s="7">
+        <v>16.3</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-9.32</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-12.44</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-8.43</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-11.62</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-3.19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-3.71</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-3.43</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-14.74</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-15.76</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-33.74</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-33.19</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D43" s="7">
+        <v>-4.66</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-4.66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-21.28</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-22.14</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>6.11</v>
-      </c>
-      <c r="D8" s="6">
-        <v>3.57</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1126</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1087.2</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-38.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-3.45</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-2</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>894.2</v>
+      </c>
+      <c r="D46" s="7">
+        <v>863.05</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-31.15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>5.89</v>
-      </c>
-      <c r="D10" s="6">
-        <v>4.78</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1868</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1873.5</v>
+      </c>
+      <c r="E47" s="9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>3.61</v>
-      </c>
-      <c r="D11" s="6">
-        <v>2.09</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>2062.7</v>
+      </c>
+      <c r="D48" s="7">
+        <v>2038.1</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-24.6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.61</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>780.6</v>
+      </c>
+      <c r="D49" s="7">
+        <v>787.05</v>
+      </c>
+      <c r="E49" s="9">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>3280.2</v>
+      </c>
+      <c r="D50" s="7">
+        <v>3127.5</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-152.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>8055</v>
+      </c>
+      <c r="D51" s="7">
+        <v>7967.5</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-87.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7">
+        <v>85</v>
+      </c>
+      <c r="D52" s="7">
+        <v>99</v>
+      </c>
+      <c r="E52" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="7">
+        <v>99</v>
+      </c>
+      <c r="D53" s="7">
+        <v>85</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>53.49</v>
+      </c>
+      <c r="D54" s="7">
+        <v>46.51</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-6.98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>52.23</v>
+      </c>
+      <c r="D55" s="7">
+        <v>43.55</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-8.68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>53.75</v>
+      </c>
+      <c r="D56" s="7">
+        <v>54.45</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>50.79</v>
+      </c>
+      <c r="D57" s="7">
+        <v>46.31</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-4.48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>51.31</v>
+      </c>
+      <c r="D58" s="7">
+        <v>53.37</v>
+      </c>
+      <c r="E58" s="9">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>83.55</v>
+      </c>
+      <c r="D59" s="7">
+        <v>70.39</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-13.16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>54.62</v>
+      </c>
+      <c r="D60" s="7">
+        <v>50.56</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-4.06</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>183.74</v>
+      </c>
+      <c r="D61" s="7">
+        <v>-18.86</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-202.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-57.38</v>
+      </c>
+      <c r="D62" s="7">
+        <v>11.23</v>
+      </c>
+      <c r="E62" s="9">
+        <v>68.61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-67.06999999999999</v>
+      </c>
+      <c r="D63" s="7">
+        <v>-64.66</v>
+      </c>
+      <c r="E63" s="9">
         <v>2.41</v>
       </c>
-      <c r="E12" s="8">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-50.25</v>
+      </c>
+      <c r="D64" s="7">
+        <v>-58.58</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-8.33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>98.02</v>
+      </c>
+      <c r="D65" s="7">
+        <v>95.12</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>25.87</v>
-      </c>
-      <c r="D13" s="6">
-        <v>27.78</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="7">
+        <v>212.61</v>
+      </c>
+      <c r="D66" s="7">
+        <v>-11.88</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-224.49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1.93</v>
-      </c>
-      <c r="D14" s="6">
-        <v>6.28</v>
-      </c>
-      <c r="E14" s="8">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>4.98</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-4.07</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-9.050000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1.27</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1.51</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.42</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>1.26</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.08</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>14.67</v>
-      </c>
-      <c r="D20" s="6">
-        <v>25.73</v>
-      </c>
-      <c r="E20" s="8">
-        <v>11.06</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0.47</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>37.14</v>
-      </c>
-      <c r="D22" s="6">
-        <v>33.12</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-4.02</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>33.87</v>
-      </c>
-      <c r="D23" s="6">
-        <v>36.08</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>30.65</v>
-      </c>
-      <c r="D24" s="6">
-        <v>28.86</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-13.08</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-13.61</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-30.64</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-33.19</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>4.35</v>
-      </c>
-      <c r="D27" s="6">
-        <v>25.7</v>
-      </c>
-      <c r="E27" s="8">
-        <v>21.35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-18.44</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-18.48</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>4.86</v>
-      </c>
-      <c r="D29" s="6">
-        <v>6.31</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>10.06</v>
-      </c>
-      <c r="D30" s="6">
-        <v>4.8</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-5.26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>23.99</v>
-      </c>
-      <c r="D31" s="6">
-        <v>22.98</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>14.05</v>
-      </c>
-      <c r="D32" s="6">
-        <v>10.21</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-0.76</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-2.19</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>20.67</v>
-      </c>
-      <c r="D34" s="6">
-        <v>26.73</v>
-      </c>
-      <c r="E34" s="8">
-        <v>6.06</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>16.89</v>
-      </c>
-      <c r="D35" s="6">
-        <v>15.47</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-7.26</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-9.32</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-8.84</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-8.43</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-2.35</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-13.84</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-14.74</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-34.19</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-33.74</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-22.49</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-21.28</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1151.6</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1126</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-25.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>890.15</v>
-      </c>
-      <c r="D43" s="6">
-        <v>894.2</v>
-      </c>
-      <c r="E43" s="8">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1894.4</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1868</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-26.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>2095.3</v>
-      </c>
-      <c r="D45" s="6">
-        <v>2062.7</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-32.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>775.2</v>
-      </c>
-      <c r="D46" s="6">
-        <v>780.6</v>
-      </c>
-      <c r="E46" s="8">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>3088.7</v>
-      </c>
-      <c r="D47" s="6">
-        <v>3280.2</v>
-      </c>
-      <c r="E47" s="8">
-        <v>191.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>7932</v>
-      </c>
-      <c r="D48" s="6">
-        <v>8055</v>
-      </c>
-      <c r="E48" s="8">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>85</v>
-      </c>
-      <c r="D49" s="6">
-        <v>71</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>71</v>
-      </c>
-      <c r="D50" s="6">
-        <v>57</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
-        <v>99</v>
-      </c>
-      <c r="D51" s="6">
-        <v>85</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="6">
-        <v>43</v>
-      </c>
-      <c r="D52" s="6">
-        <v>29</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="6">
-        <v>57</v>
-      </c>
-      <c r="D53" s="6">
-        <v>99</v>
-      </c>
-      <c r="E53" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="6">
-        <v>29</v>
-      </c>
-      <c r="D54" s="6">
-        <v>43</v>
-      </c>
-      <c r="E54" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>58.64</v>
-      </c>
-      <c r="D55" s="6">
-        <v>53.49</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-5.15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>51.31</v>
-      </c>
-      <c r="D56" s="6">
-        <v>52.23</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>57.67</v>
-      </c>
-      <c r="D57" s="6">
-        <v>53.75</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-3.92</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>57.65</v>
-      </c>
-      <c r="D58" s="6">
-        <v>50.79</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-6.86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>49.96</v>
-      </c>
-      <c r="D59" s="6">
-        <v>51.31</v>
-      </c>
-      <c r="E59" s="8">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>78.98999999999999</v>
-      </c>
-      <c r="D60" s="6">
-        <v>83.55</v>
-      </c>
-      <c r="E60" s="8">
-        <v>4.56</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>49.3</v>
-      </c>
-      <c r="D61" s="6">
-        <v>54.62</v>
-      </c>
-      <c r="E61" s="8">
-        <v>5.32</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="6">
-        <v>22.28</v>
-      </c>
-      <c r="D62" s="6">
-        <v>183.74</v>
-      </c>
-      <c r="E62" s="8">
-        <v>161.46</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-59.36</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-57.38</v>
-      </c>
-      <c r="E63" s="8">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-60.72</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-67.06999999999999</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-6.35</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-30.63</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-50.25</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-19.62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>22.78</v>
-      </c>
-      <c r="D66" s="6">
-        <v>98.02</v>
-      </c>
-      <c r="E66" s="8">
-        <v>75.23999999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>2773.38</v>
-      </c>
-      <c r="D67" s="6">
-        <v>212.61</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-2560.77</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-71.34</v>
-      </c>
-      <c r="D68" s="6">
+      <c r="C67" s="7">
         <v>-42.58</v>
       </c>
-      <c r="E68" s="8">
-        <v>28.76</v>
+      <c r="D67" s="7">
+        <v>-55.3</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-12.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3018,60 +3045,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>52.2</v>
+      </c>
+      <c r="E2" s="12">
         <v>70</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>57.1</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>6.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>12</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>10.3</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -3173,49 +3200,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.6174000000000001</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3381</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.3005</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2043</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1465</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1465</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.1006</v>
+      <c r="A2" s="15">
+        <v>0.6098</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3296</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.3129</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2095</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1554</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1501</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0968</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,52 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>0.0% → -4.7%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-4.7%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>53.5 → 46.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.5</t>
+    <t>46.5 → 54.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>46.5</t>
   </si>
   <si>
-    <t>52.2 → 43.5</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>43.5</t>
-  </si>
-  <si>
-    <t>50.8 → 46.3</t>
-  </si>
-  <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>46.3</t>
+    <t>54.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -284,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,7 +285,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -330,15 +297,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,19 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -455,15 +409,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -472,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -971,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1087.2</v>
+        <v>1137.6</v>
       </c>
       <c r="D2">
-        <v>-3.45</v>
+        <v>4.64</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -983,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-12.44</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="H2">
-        <v>45.28</v>
+        <v>52.01</v>
       </c>
       <c r="I2">
-        <v>-5.8</v>
+        <v>-3.97</v>
       </c>
       <c r="J2">
-        <v>0.28</v>
+        <v>6.43</v>
       </c>
       <c r="K2">
-        <v>2.33</v>
+        <v>7.64</v>
       </c>
       <c r="L2">
-        <v>28.82</v>
+        <v>33.9</v>
       </c>
       <c r="M2">
-        <v>9.68</v>
+        <v>10.68</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>1134.42</v>
+        <v>1125.02</v>
       </c>
       <c r="Q2">
-        <v>1098.43</v>
+        <v>1102.51</v>
       </c>
       <c r="R2">
-        <v>1107.9</v>
+        <v>1110.32</v>
       </c>
       <c r="S2">
-        <v>935.58</v>
+        <v>936.77</v>
       </c>
       <c r="T2">
-        <v>16.21</v>
+        <v>21.44</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1037,34 +990,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>46.51</v>
+        <v>54.76</v>
       </c>
       <c r="Z2">
-        <v>11.24</v>
+        <v>11.95</v>
       </c>
       <c r="AA2">
-        <v>9.880000000000001</v>
+        <v>10.29</v>
       </c>
       <c r="AB2">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="AC2">
-        <v>31.8</v>
+        <v>30.47</v>
       </c>
       <c r="AD2">
-        <v>51.21</v>
+        <v>38.26</v>
       </c>
       <c r="AE2">
-        <v>43.32</v>
+        <v>44.55</v>
       </c>
       <c r="AF2">
-        <v>-18.86</v>
+        <v>33.25</v>
       </c>
       <c r="AG2">
-        <v>1181.52</v>
+        <v>1184.84</v>
       </c>
       <c r="AH2">
-        <v>1015.35</v>
+        <v>1020.18</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1073,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>35.5</v>
+        <v>31.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1084,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>863.05</v>
+        <v>876.3</v>
       </c>
       <c r="D3">
-        <v>-3.48</v>
+        <v>1.54</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1096,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-11.62</v>
+        <v>-10.26</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>65.5</v>
       </c>
       <c r="I3">
-        <v>-2.81</v>
+        <v>-1.16</v>
       </c>
       <c r="J3">
-        <v>-5.66</v>
+        <v>-4</v>
       </c>
       <c r="K3">
-        <v>-0.21</v>
+        <v>1.22</v>
       </c>
       <c r="L3">
-        <v>29.01</v>
+        <v>31.88</v>
       </c>
       <c r="M3">
-        <v>60.98</v>
+        <v>61.43</v>
       </c>
       <c r="N3">
         <v>57</v>
       </c>
       <c r="O3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P3">
-        <v>886.55</v>
+        <v>884.5</v>
       </c>
       <c r="Q3">
-        <v>871.49</v>
+        <v>871.11</v>
       </c>
       <c r="R3">
-        <v>906.2</v>
+        <v>905.5599999999999</v>
       </c>
       <c r="S3">
-        <v>766.99</v>
+        <v>767.6900000000001</v>
       </c>
       <c r="T3">
-        <v>12.52</v>
+        <v>14.15</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1150,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.55</v>
+        <v>47.54</v>
       </c>
       <c r="Z3">
-        <v>-3.68</v>
+        <v>-3.82</v>
       </c>
       <c r="AA3">
-        <v>-6.33</v>
+        <v>-5.83</v>
       </c>
       <c r="AB3">
-        <v>2.65</v>
+        <v>2.01</v>
       </c>
       <c r="AC3">
-        <v>78.48</v>
+        <v>66.87</v>
       </c>
       <c r="AD3">
-        <v>91.8</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="AE3">
-        <v>23.33</v>
+        <v>22.64</v>
       </c>
       <c r="AF3">
-        <v>11.23</v>
+        <v>-40.16</v>
       </c>
       <c r="AG3">
-        <v>915.39</v>
+        <v>914.7</v>
       </c>
       <c r="AH3">
-        <v>827.59</v>
+        <v>827.53</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1186,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>17.44</v>
+        <v>19.06</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1197,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1873.5</v>
+        <v>1888.9</v>
       </c>
       <c r="D4">
-        <v>0.29</v>
+        <v>0.82</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1209,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-3.43</v>
+        <v>-2.63</v>
       </c>
       <c r="H4">
-        <v>38.3</v>
+        <v>39.43</v>
       </c>
       <c r="I4">
-        <v>-2.3</v>
+        <v>-2.02</v>
       </c>
       <c r="J4">
-        <v>6.52</v>
+        <v>9.31</v>
       </c>
       <c r="K4">
-        <v>24.57</v>
+        <v>22.67</v>
       </c>
       <c r="L4">
-        <v>28.37</v>
+        <v>29.34</v>
       </c>
       <c r="M4">
-        <v>31.29</v>
+        <v>31.48</v>
       </c>
       <c r="N4">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="O4">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P4">
-        <v>1891.64</v>
+        <v>1883.84</v>
       </c>
       <c r="Q4">
-        <v>1853.31</v>
+        <v>1861.89</v>
       </c>
       <c r="R4">
-        <v>1785.25</v>
+        <v>1793.57</v>
       </c>
       <c r="S4">
-        <v>1668.88</v>
+        <v>1669.84</v>
       </c>
       <c r="T4">
-        <v>12.26</v>
+        <v>13.12</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1263,43 +1216,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>54.45</v>
+        <v>56.42</v>
       </c>
       <c r="Z4">
-        <v>35.02</v>
+        <v>33.07</v>
       </c>
       <c r="AA4">
-        <v>40.3</v>
+        <v>38.85</v>
       </c>
       <c r="AB4">
-        <v>-5.28</v>
+        <v>-5.79</v>
       </c>
       <c r="AC4">
-        <v>12.99</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AD4">
-        <v>27.51</v>
+        <v>15.42</v>
       </c>
       <c r="AE4">
-        <v>47.12</v>
+        <v>46.15</v>
       </c>
       <c r="AF4">
-        <v>-64.66</v>
+        <v>-59.25</v>
       </c>
       <c r="AG4">
-        <v>1991.45</v>
+        <v>1984.96</v>
       </c>
       <c r="AH4">
-        <v>1715.16</v>
+        <v>1738.81</v>
       </c>
       <c r="AI4">
-        <v>1751.87</v>
+        <v>1753.66</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>24.99</v>
+        <v>24.56</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1310,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2038.1</v>
+        <v>2004.8</v>
       </c>
       <c r="D5">
-        <v>-1.19</v>
+        <v>-1.63</v>
       </c>
       <c r="E5">
         <v>2419.36</v>
@@ -1322,46 +1275,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-15.76</v>
+        <v>-17.14</v>
       </c>
       <c r="H5">
-        <v>16.76</v>
+        <v>14.85</v>
       </c>
       <c r="I5">
-        <v>-1.7</v>
+        <v>-4.02</v>
       </c>
       <c r="J5">
-        <v>-0.79</v>
+        <v>-1.69</v>
       </c>
       <c r="K5">
-        <v>8.25</v>
+        <v>10.19</v>
       </c>
       <c r="L5">
-        <v>-9.369999999999999</v>
+        <v>-14.47</v>
       </c>
       <c r="M5">
-        <v>20.95</v>
+        <v>20.54</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P5">
-        <v>2076.04</v>
+        <v>2059.24</v>
       </c>
       <c r="Q5">
-        <v>2065.32</v>
+        <v>2064.41</v>
       </c>
       <c r="R5">
-        <v>2032.62</v>
+        <v>2035.1</v>
       </c>
       <c r="S5">
-        <v>2105.94</v>
+        <v>2105.38</v>
       </c>
       <c r="T5">
-        <v>-3.22</v>
+        <v>-4.78</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1376,34 +1329,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>46.31</v>
+        <v>41.04</v>
       </c>
       <c r="Z5">
-        <v>13.84</v>
+        <v>7.42</v>
       </c>
       <c r="AA5">
-        <v>20.13</v>
+        <v>17.58</v>
       </c>
       <c r="AB5">
-        <v>-6.29</v>
+        <v>-10.16</v>
       </c>
       <c r="AC5">
-        <v>13.02</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>29.18</v>
+        <v>13.9</v>
       </c>
       <c r="AE5">
-        <v>46.59</v>
+        <v>47.55</v>
       </c>
       <c r="AF5">
-        <v>-58.58</v>
+        <v>-23.79</v>
       </c>
       <c r="AG5">
-        <v>2138.74</v>
+        <v>2140.44</v>
       </c>
       <c r="AH5">
-        <v>1991.89</v>
+        <v>1988.38</v>
       </c>
       <c r="AI5">
         <v>1954.68</v>
@@ -1412,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>16.69</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1423,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>787.05</v>
+        <v>810.25</v>
       </c>
       <c r="D6">
-        <v>0.83</v>
+        <v>2.95</v>
       </c>
       <c r="E6">
         <v>1178</v>
@@ -1435,46 +1388,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-33.19</v>
+        <v>-31.22</v>
       </c>
       <c r="H6">
-        <v>11.78</v>
+        <v>15.08</v>
       </c>
       <c r="I6">
-        <v>1.88</v>
+        <v>3.84</v>
       </c>
       <c r="J6">
-        <v>2.5</v>
+        <v>5.85</v>
       </c>
       <c r="K6">
-        <v>-0.31</v>
+        <v>4.02</v>
       </c>
       <c r="L6">
-        <v>-30.87</v>
+        <v>-30.31</v>
       </c>
       <c r="M6">
-        <v>15.54</v>
+        <v>16.2</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P6">
-        <v>783.04</v>
+        <v>789.03</v>
       </c>
       <c r="Q6">
-        <v>782.37</v>
+        <v>784.9299999999999</v>
       </c>
       <c r="R6">
-        <v>756.17</v>
+        <v>757.91</v>
       </c>
       <c r="S6">
-        <v>866.34</v>
+        <v>865.03</v>
       </c>
       <c r="T6">
-        <v>-9.15</v>
+        <v>-6.33</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1489,34 +1442,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>53.37</v>
+        <v>59.96</v>
       </c>
       <c r="Z6">
-        <v>6.64</v>
+        <v>8.19</v>
       </c>
       <c r="AA6">
-        <v>8.56</v>
+        <v>8.49</v>
       </c>
       <c r="AB6">
-        <v>-1.92</v>
+        <v>-0.29</v>
       </c>
       <c r="AC6">
-        <v>22.18</v>
+        <v>30.37</v>
       </c>
       <c r="AD6">
-        <v>18.39</v>
+        <v>22.89</v>
       </c>
       <c r="AE6">
-        <v>23.01</v>
+        <v>23.35</v>
       </c>
       <c r="AF6">
-        <v>95.12</v>
+        <v>445.76</v>
       </c>
       <c r="AG6">
-        <v>818.2</v>
+        <v>821.0700000000001</v>
       </c>
       <c r="AH6">
-        <v>746.54</v>
+        <v>748.78</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1525,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>18.21</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1536,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3127.5</v>
+        <v>3200.2</v>
       </c>
       <c r="D7">
-        <v>-4.66</v>
+        <v>2.32</v>
       </c>
       <c r="E7">
         <v>3280.2</v>
@@ -1548,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-4.66</v>
+        <v>-2.44</v>
       </c>
       <c r="H7">
-        <v>65.34999999999999</v>
+        <v>69.19</v>
       </c>
       <c r="I7">
-        <v>8.66</v>
+        <v>10.83</v>
       </c>
       <c r="J7">
-        <v>19.09</v>
+        <v>26.5</v>
       </c>
       <c r="K7">
-        <v>20.85</v>
+        <v>23.77</v>
       </c>
       <c r="L7">
-        <v>18.31</v>
+        <v>20.76</v>
       </c>
       <c r="M7">
-        <v>32.96</v>
+        <v>33.55</v>
       </c>
       <c r="N7">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P7">
-        <v>3096.24</v>
+        <v>3158.76</v>
       </c>
       <c r="Q7">
-        <v>2742.31</v>
+        <v>2774.03</v>
       </c>
       <c r="R7">
-        <v>2618.04</v>
+        <v>2632.36</v>
       </c>
       <c r="S7">
-        <v>2381.16</v>
+        <v>2385.1</v>
       </c>
       <c r="T7">
-        <v>31.34</v>
+        <v>34.17</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1602,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>70.39</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Z7">
-        <v>150.91</v>
+        <v>162.26</v>
       </c>
       <c r="AA7">
-        <v>91.68000000000001</v>
+        <v>105.8</v>
       </c>
       <c r="AB7">
-        <v>59.23</v>
+        <v>56.46</v>
       </c>
       <c r="AC7">
-        <v>85.65000000000001</v>
+        <v>73.72</v>
       </c>
       <c r="AD7">
-        <v>95.22</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="AE7">
-        <v>146.27</v>
+        <v>146.96</v>
       </c>
       <c r="AF7">
-        <v>-11.88</v>
+        <v>-39.22</v>
       </c>
       <c r="AG7">
-        <v>3203.3</v>
+        <v>3269.87</v>
       </c>
       <c r="AH7">
-        <v>2281.33</v>
+        <v>2278.19</v>
       </c>
       <c r="AI7">
         <v>2798.69</v>
@@ -1638,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>64.77</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1649,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7967.5</v>
+        <v>8109.5</v>
       </c>
       <c r="D8">
-        <v>-1.09</v>
+        <v>1.78</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1661,46 +1614,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-22.14</v>
+        <v>-20.75</v>
       </c>
       <c r="H8">
-        <v>34.48</v>
+        <v>36.88</v>
       </c>
       <c r="I8">
-        <v>0.16</v>
+        <v>1.56</v>
       </c>
       <c r="J8">
-        <v>5.36</v>
+        <v>7.97</v>
       </c>
       <c r="K8">
-        <v>16.3</v>
+        <v>16.19</v>
       </c>
       <c r="L8">
-        <v>-20.2</v>
+        <v>-17.46</v>
       </c>
       <c r="M8">
-        <v>15.01</v>
+        <v>15.4</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P8">
-        <v>7974.3</v>
+        <v>7999.2</v>
       </c>
       <c r="Q8">
-        <v>8059.25</v>
+        <v>8093.42</v>
       </c>
       <c r="R8">
-        <v>7873.6</v>
+        <v>7900.44</v>
       </c>
       <c r="S8">
-        <v>7409.78</v>
+        <v>7407.24</v>
       </c>
       <c r="T8">
-        <v>7.53</v>
+        <v>9.48</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1715,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>50.56</v>
+        <v>56.24</v>
       </c>
       <c r="Z8">
-        <v>46.46</v>
+        <v>51.16</v>
       </c>
       <c r="AA8">
-        <v>76.77</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="AB8">
-        <v>-30.31</v>
+        <v>-20.49</v>
       </c>
       <c r="AC8">
-        <v>18.07</v>
+        <v>37.25</v>
       </c>
       <c r="AD8">
-        <v>11.74</v>
+        <v>23.32</v>
       </c>
       <c r="AE8">
-        <v>234.44</v>
+        <v>232.58</v>
       </c>
       <c r="AF8">
-        <v>-55.3</v>
+        <v>-55.01</v>
       </c>
       <c r="AG8">
-        <v>8433.73</v>
+        <v>8320.200000000001</v>
       </c>
       <c r="AH8">
-        <v>7684.77</v>
+        <v>7866.65</v>
       </c>
       <c r="AI8">
         <v>7451.92</v>
@@ -1751,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>15.13</v>
+        <v>14.68</v>
       </c>
     </row>
   </sheetData>
@@ -1892,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1932,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1950,1082 +1903,1022 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.28</v>
+      </c>
+      <c r="D7" s="6">
+        <v>6.43</v>
+      </c>
+      <c r="E7" s="7">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-5.66</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-4</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>6.52</v>
+      </c>
+      <c r="D9" s="6">
+        <v>9.31</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-0.79</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-1.69</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D11" s="6">
+        <v>5.85</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>19.09</v>
+      </c>
+      <c r="D12" s="6">
+        <v>26.5</v>
+      </c>
+      <c r="E12" s="7">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>5.36</v>
+      </c>
+      <c r="D13" s="6">
+        <v>7.97</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>3.57</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-5.8</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-3.97</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.81</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-1.16</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-2.3</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-2.02</v>
+      </c>
+      <c r="E16" s="7">
         <v>0.28</v>
       </c>
-      <c r="E10" s="8">
-        <v>-3.29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.7</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-4.02</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1.88</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3.84</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>8.66</v>
+      </c>
+      <c r="D19" s="6">
+        <v>10.83</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>28.82</v>
+      </c>
+      <c r="D21" s="6">
+        <v>33.9</v>
+      </c>
+      <c r="E21" s="7">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-2</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-5.66</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>29.01</v>
+      </c>
+      <c r="D22" s="6">
+        <v>31.88</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>4.78</v>
-      </c>
-      <c r="D12" s="7">
-        <v>6.52</v>
-      </c>
-      <c r="E12" s="9">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>28.37</v>
+      </c>
+      <c r="D23" s="6">
+        <v>29.34</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>2.09</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-0.79</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-14.47</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>2.41</v>
-      </c>
-      <c r="D14" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-30.87</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-30.31</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>27.78</v>
-      </c>
-      <c r="D15" s="7">
-        <v>19.09</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-8.69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>18.31</v>
+      </c>
+      <c r="D26" s="6">
+        <v>20.76</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>6.28</v>
-      </c>
-      <c r="D16" s="7">
-        <v>5.36</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-20.2</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-17.46</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-4.07</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-5.8</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="D28" s="6">
+        <v>7.64</v>
+      </c>
+      <c r="E28" s="7">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-2.81</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-4.31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-0.21</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1.22</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-2.42</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-2.3</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>24.57</v>
+      </c>
+      <c r="D30" s="6">
+        <v>22.67</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.08</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-1.7</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>8.25</v>
+      </c>
+      <c r="D31" s="6">
+        <v>10.19</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1</v>
-      </c>
-      <c r="D21" s="7">
-        <v>1.88</v>
-      </c>
-      <c r="E21" s="9">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-0.31</v>
+      </c>
+      <c r="D32" s="6">
+        <v>4.02</v>
+      </c>
+      <c r="E32" s="7">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>25.73</v>
-      </c>
-      <c r="D22" s="7">
-        <v>8.66</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-17.07</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>20.85</v>
+      </c>
+      <c r="D33" s="6">
+        <v>23.77</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0.47</v>
-      </c>
-      <c r="D23" s="7">
-        <v>0.16</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>16.3</v>
+      </c>
+      <c r="D34" s="6">
+        <v>16.19</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>33.12</v>
-      </c>
-      <c r="D24" s="7">
-        <v>28.82</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-12.44</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="E35" s="7">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>36.08</v>
-      </c>
-      <c r="D25" s="7">
-        <v>29.01</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-7.07</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-11.62</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-10.26</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>28.86</v>
-      </c>
-      <c r="D26" s="7">
-        <v>28.37</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-3.43</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-2.63</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-13.61</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="E27" s="9">
-        <v>4.24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-15.76</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-17.14</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
         <v>-33.19</v>
       </c>
-      <c r="D28" s="7">
-        <v>-30.87</v>
-      </c>
-      <c r="E28" s="9">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="D39" s="6">
+        <v>-31.22</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>25.7</v>
-      </c>
-      <c r="D29" s="7">
-        <v>18.31</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-7.39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-4.66</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-2.44</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-18.48</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-20.2</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-22.14</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-20.75</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>6.31</v>
-      </c>
-      <c r="D31" s="7">
-        <v>2.33</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-3.98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1087.2</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1137.6</v>
+      </c>
+      <c r="E42" s="7">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>4.8</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-0.21</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>863.05</v>
+      </c>
+      <c r="D43" s="6">
+        <v>876.3</v>
+      </c>
+      <c r="E43" s="7">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>22.98</v>
-      </c>
-      <c r="D33" s="7">
-        <v>24.57</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1873.5</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1888.9</v>
+      </c>
+      <c r="E44" s="7">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>10.21</v>
-      </c>
-      <c r="D34" s="7">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2038.1</v>
+      </c>
+      <c r="D45" s="6">
+        <v>2004.8</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-33.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>787.05</v>
+      </c>
+      <c r="D46" s="6">
+        <v>810.25</v>
+      </c>
+      <c r="E46" s="7">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>3127.5</v>
+      </c>
+      <c r="D47" s="6">
+        <v>3200.2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>7967.5</v>
+      </c>
+      <c r="D48" s="6">
+        <v>8109.5</v>
+      </c>
+      <c r="E48" s="7">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>99</v>
+      </c>
+      <c r="D49" s="6">
+        <v>85</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>85</v>
+      </c>
+      <c r="D50" s="6">
+        <v>99</v>
+      </c>
+      <c r="E50" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>46.51</v>
+      </c>
+      <c r="D51" s="6">
+        <v>54.76</v>
+      </c>
+      <c r="E51" s="7">
         <v>8.25</v>
       </c>
-      <c r="E34" s="8">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>43.55</v>
+      </c>
+      <c r="D52" s="6">
+        <v>47.54</v>
+      </c>
+      <c r="E52" s="7">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>54.45</v>
+      </c>
+      <c r="D53" s="6">
+        <v>56.42</v>
+      </c>
+      <c r="E53" s="7">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>46.31</v>
+      </c>
+      <c r="D54" s="6">
+        <v>41.04</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-5.27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-2.19</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-0.31</v>
-      </c>
-      <c r="E35" s="9">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>53.37</v>
+      </c>
+      <c r="D55" s="6">
+        <v>59.96</v>
+      </c>
+      <c r="E55" s="7">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>26.73</v>
-      </c>
-      <c r="D36" s="7">
-        <v>20.85</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-5.88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>70.39</v>
+      </c>
+      <c r="D56" s="6">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="E56" s="7">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>15.47</v>
-      </c>
-      <c r="D37" s="7">
-        <v>16.3</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>50.56</v>
+      </c>
+      <c r="D57" s="6">
+        <v>56.24</v>
+      </c>
+      <c r="E57" s="7">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-9.32</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-12.44</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-3.12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-18.86</v>
+      </c>
+      <c r="D58" s="6">
+        <v>33.25</v>
+      </c>
+      <c r="E58" s="7">
+        <v>52.11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-8.43</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-11.62</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-3.19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>11.23</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-40.16</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-51.39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-3.71</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-3.43</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-64.66</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-59.25</v>
+      </c>
+      <c r="E60" s="7">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-14.74</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-15.76</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-58.58</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-23.79</v>
+      </c>
+      <c r="E61" s="7">
+        <v>34.79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-33.74</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-33.19</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>95.12</v>
+      </c>
+      <c r="D62" s="6">
+        <v>445.76</v>
+      </c>
+      <c r="E62" s="7">
+        <v>350.64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>0</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-4.66</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-4.66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-11.88</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-39.22</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-27.34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-21.28</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-22.14</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>1126</v>
-      </c>
-      <c r="D45" s="7">
-        <v>1087.2</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-38.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>894.2</v>
-      </c>
-      <c r="D46" s="7">
-        <v>863.05</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-31.15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>1868</v>
-      </c>
-      <c r="D47" s="7">
-        <v>1873.5</v>
-      </c>
-      <c r="E47" s="9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>2062.7</v>
-      </c>
-      <c r="D48" s="7">
-        <v>2038.1</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-24.6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>780.6</v>
-      </c>
-      <c r="D49" s="7">
-        <v>787.05</v>
-      </c>
-      <c r="E49" s="9">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>3280.2</v>
-      </c>
-      <c r="D50" s="7">
-        <v>3127.5</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-152.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>8055</v>
-      </c>
-      <c r="D51" s="7">
-        <v>7967.5</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-87.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="7">
-        <v>85</v>
-      </c>
-      <c r="D52" s="7">
-        <v>99</v>
-      </c>
-      <c r="E52" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="7">
-        <v>99</v>
-      </c>
-      <c r="D53" s="7">
-        <v>85</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>53.49</v>
-      </c>
-      <c r="D54" s="7">
-        <v>46.51</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-6.98</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>52.23</v>
-      </c>
-      <c r="D55" s="7">
-        <v>43.55</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-8.68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>53.75</v>
-      </c>
-      <c r="D56" s="7">
-        <v>54.45</v>
-      </c>
-      <c r="E56" s="9">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>50.79</v>
-      </c>
-      <c r="D57" s="7">
-        <v>46.31</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-4.48</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>51.31</v>
-      </c>
-      <c r="D58" s="7">
-        <v>53.37</v>
-      </c>
-      <c r="E58" s="9">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>83.55</v>
-      </c>
-      <c r="D59" s="7">
-        <v>70.39</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-13.16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>54.62</v>
-      </c>
-      <c r="D60" s="7">
-        <v>50.56</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-4.06</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="7">
-        <v>183.74</v>
-      </c>
-      <c r="D61" s="7">
-        <v>-18.86</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-202.6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-57.38</v>
-      </c>
-      <c r="D62" s="7">
-        <v>11.23</v>
-      </c>
-      <c r="E62" s="9">
-        <v>68.61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-67.06999999999999</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-64.66</v>
-      </c>
-      <c r="E63" s="9">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-50.25</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-58.58</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-8.33</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>98.02</v>
-      </c>
-      <c r="D65" s="7">
-        <v>95.12</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>212.61</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-11.88</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-224.49</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>-42.58</v>
-      </c>
-      <c r="D67" s="7">
+      <c r="C64" s="6">
         <v>-55.3</v>
       </c>
-      <c r="E67" s="8">
-        <v>-12.72</v>
+      <c r="D64" s="6">
+        <v>-55.01</v>
+      </c>
+      <c r="E64" s="7">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3045,60 +2938,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>83</v>
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>60.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>52.2</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>55.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="12">
-        <v>3.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>10.3</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3200,49 +3093,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.6098</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3296</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.3129</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2095</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1554</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1501</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0968</v>
+      <c r="A2" s="14">
+        <v>0.6143</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3355</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.3148</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2054</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.162</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.154</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.1068</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,16 +190,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>46.5 → 54.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>46.5</t>
-  </si>
-  <si>
-    <t>54.8</t>
+    <t>52.3 → 49.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.3</t>
+  </si>
+  <si>
+    <t>49.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -924,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1137.6</v>
+        <v>1122.2</v>
       </c>
       <c r="D2">
-        <v>4.64</v>
+        <v>-4.07</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -936,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-8.380000000000001</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="H2">
-        <v>52.01</v>
+        <v>49.96</v>
       </c>
       <c r="I2">
-        <v>-3.97</v>
+        <v>-0.04</v>
       </c>
       <c r="J2">
-        <v>6.43</v>
+        <v>5.44</v>
       </c>
       <c r="K2">
-        <v>7.64</v>
+        <v>7.56</v>
       </c>
       <c r="L2">
-        <v>33.9</v>
+        <v>29.22</v>
       </c>
       <c r="M2">
-        <v>10.68</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>1125.02</v>
+        <v>1128.56</v>
       </c>
       <c r="Q2">
-        <v>1102.51</v>
+        <v>1110.24</v>
       </c>
       <c r="R2">
-        <v>1110.32</v>
+        <v>1115.14</v>
       </c>
       <c r="S2">
-        <v>936.77</v>
+        <v>939.22</v>
       </c>
       <c r="T2">
-        <v>21.44</v>
+        <v>19.48</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +990,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>54.76</v>
+        <v>51.27</v>
       </c>
       <c r="Z2">
-        <v>11.95</v>
+        <v>13.3</v>
       </c>
       <c r="AA2">
-        <v>10.29</v>
+        <v>11.64</v>
       </c>
       <c r="AB2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC2">
-        <v>30.47</v>
+        <v>41.63</v>
       </c>
       <c r="AD2">
-        <v>38.26</v>
+        <v>35.85</v>
       </c>
       <c r="AE2">
-        <v>44.55</v>
+        <v>47.8</v>
       </c>
       <c r="AF2">
-        <v>33.25</v>
+        <v>-2.48</v>
       </c>
       <c r="AG2">
-        <v>1184.84</v>
+        <v>1194.34</v>
       </c>
       <c r="AH2">
-        <v>1020.18</v>
+        <v>1026.14</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1026,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>31.44</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>876.3</v>
+        <v>877.5</v>
       </c>
       <c r="D3">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-10.26</v>
+        <v>-10.14</v>
       </c>
       <c r="H3">
-        <v>65.5</v>
+        <v>65.73</v>
       </c>
       <c r="I3">
-        <v>-1.16</v>
+        <v>-2.37</v>
       </c>
       <c r="J3">
-        <v>-4</v>
+        <v>1.13</v>
       </c>
       <c r="K3">
-        <v>1.22</v>
+        <v>-0.19</v>
       </c>
       <c r="L3">
-        <v>31.88</v>
+        <v>29.94</v>
       </c>
       <c r="M3">
-        <v>61.43</v>
+        <v>60.49</v>
       </c>
       <c r="N3">
         <v>57</v>
       </c>
       <c r="O3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P3">
-        <v>884.5</v>
+        <v>875.61</v>
       </c>
       <c r="Q3">
-        <v>871.11</v>
+        <v>871.09</v>
       </c>
       <c r="R3">
-        <v>905.5599999999999</v>
+        <v>904.14</v>
       </c>
       <c r="S3">
-        <v>767.6900000000001</v>
+        <v>768.97</v>
       </c>
       <c r="T3">
-        <v>14.15</v>
+        <v>14.11</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>47.54</v>
+        <v>48.32</v>
       </c>
       <c r="Z3">
-        <v>-3.82</v>
+        <v>-4.38</v>
       </c>
       <c r="AA3">
-        <v>-5.83</v>
+        <v>-5.35</v>
       </c>
       <c r="AB3">
-        <v>2.01</v>
+        <v>0.97</v>
       </c>
       <c r="AC3">
-        <v>66.87</v>
+        <v>42.58</v>
       </c>
       <c r="AD3">
-        <v>80.98999999999999</v>
+        <v>50.19</v>
       </c>
       <c r="AE3">
-        <v>22.64</v>
+        <v>21.45</v>
       </c>
       <c r="AF3">
-        <v>-40.16</v>
+        <v>-63.5</v>
       </c>
       <c r="AG3">
-        <v>914.7</v>
+        <v>914.6900000000001</v>
       </c>
       <c r="AH3">
-        <v>827.53</v>
+        <v>827.49</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1139,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>19.06</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1888.9</v>
+        <v>1846.7</v>
       </c>
       <c r="D4">
-        <v>0.82</v>
+        <v>-0.87</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-2.63</v>
+        <v>-4.81</v>
       </c>
       <c r="H4">
-        <v>39.43</v>
+        <v>36.32</v>
       </c>
       <c r="I4">
-        <v>-2.02</v>
+        <v>-2.52</v>
       </c>
       <c r="J4">
-        <v>9.31</v>
+        <v>7.09</v>
       </c>
       <c r="K4">
-        <v>22.67</v>
+        <v>17.83</v>
       </c>
       <c r="L4">
-        <v>29.34</v>
+        <v>20.96</v>
       </c>
       <c r="M4">
-        <v>31.48</v>
+        <v>29.58</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P4">
-        <v>1883.84</v>
+        <v>1868</v>
       </c>
       <c r="Q4">
-        <v>1861.89</v>
+        <v>1871.89</v>
       </c>
       <c r="R4">
-        <v>1793.57</v>
+        <v>1807.3</v>
       </c>
       <c r="S4">
-        <v>1669.84</v>
+        <v>1671.08</v>
       </c>
       <c r="T4">
-        <v>13.12</v>
+        <v>10.51</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,34 +1216,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>56.42</v>
+        <v>49.86</v>
       </c>
       <c r="Z4">
-        <v>33.07</v>
+        <v>24.35</v>
       </c>
       <c r="AA4">
-        <v>38.85</v>
+        <v>34.39</v>
       </c>
       <c r="AB4">
-        <v>-5.79</v>
+        <v>-10.04</v>
       </c>
       <c r="AC4">
-        <v>9.130000000000001</v>
+        <v>6.19</v>
       </c>
       <c r="AD4">
-        <v>15.42</v>
+        <v>7.71</v>
       </c>
       <c r="AE4">
-        <v>46.15</v>
+        <v>44.66</v>
       </c>
       <c r="AF4">
-        <v>-59.25</v>
+        <v>-43.86</v>
       </c>
       <c r="AG4">
-        <v>1984.96</v>
+        <v>1969.65</v>
       </c>
       <c r="AH4">
-        <v>1738.81</v>
+        <v>1774.12</v>
       </c>
       <c r="AI4">
         <v>1753.66</v>
@@ -1252,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>24.56</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>2004.8</v>
+        <v>1926.6</v>
       </c>
       <c r="D5">
-        <v>-1.63</v>
+        <v>-3.48</v>
       </c>
       <c r="E5">
         <v>2419.36</v>
@@ -1275,46 +1275,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-17.14</v>
+        <v>-20.37</v>
       </c>
       <c r="H5">
-        <v>14.85</v>
+        <v>10.37</v>
       </c>
       <c r="I5">
-        <v>-4.02</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="J5">
-        <v>-1.69</v>
+        <v>-2.74</v>
       </c>
       <c r="K5">
-        <v>10.19</v>
+        <v>4.32</v>
       </c>
       <c r="L5">
-        <v>-14.47</v>
+        <v>-18.81</v>
       </c>
       <c r="M5">
-        <v>20.54</v>
+        <v>20.7</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="P5">
-        <v>2059.24</v>
+        <v>2005.66</v>
       </c>
       <c r="Q5">
-        <v>2064.41</v>
+        <v>2061.32</v>
       </c>
       <c r="R5">
-        <v>2035.1</v>
+        <v>2037.91</v>
       </c>
       <c r="S5">
-        <v>2105.38</v>
+        <v>2103.51</v>
       </c>
       <c r="T5">
-        <v>-4.78</v>
+        <v>-8.41</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,43 +1329,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>41.04</v>
+        <v>31.38</v>
       </c>
       <c r="Z5">
-        <v>7.42</v>
+        <v>-8.49</v>
       </c>
       <c r="AA5">
-        <v>17.58</v>
+        <v>9.82</v>
       </c>
       <c r="AB5">
-        <v>-10.16</v>
+        <v>-18.3</v>
       </c>
       <c r="AC5">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>47.55</v>
+        <v>49.85</v>
       </c>
       <c r="AF5">
-        <v>-23.79</v>
+        <v>203.78</v>
       </c>
       <c r="AG5">
-        <v>2140.44</v>
+        <v>2153.38</v>
       </c>
       <c r="AH5">
-        <v>1988.38</v>
+        <v>1969.25</v>
       </c>
       <c r="AI5">
-        <v>1954.68</v>
+        <v>2114.4</v>
       </c>
       <c r="AJ5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK5">
-        <v>19.97</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>810.25</v>
+        <v>823.95</v>
       </c>
       <c r="D6">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="E6">
         <v>1178</v>
@@ -1388,46 +1388,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-31.22</v>
+        <v>-30.06</v>
       </c>
       <c r="H6">
-        <v>15.08</v>
+        <v>17.02</v>
       </c>
       <c r="I6">
-        <v>3.84</v>
+        <v>4.03</v>
       </c>
       <c r="J6">
-        <v>5.85</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K6">
-        <v>4.02</v>
+        <v>7.77</v>
       </c>
       <c r="L6">
-        <v>-30.31</v>
+        <v>-28.09</v>
       </c>
       <c r="M6">
-        <v>16.2</v>
+        <v>17.24</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P6">
-        <v>789.03</v>
+        <v>799.83</v>
       </c>
       <c r="Q6">
-        <v>784.9299999999999</v>
+        <v>789.53</v>
       </c>
       <c r="R6">
-        <v>757.91</v>
+        <v>761.54</v>
       </c>
       <c r="S6">
-        <v>865.03</v>
+        <v>862.59</v>
       </c>
       <c r="T6">
-        <v>-6.33</v>
+        <v>-4.48</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,34 +1442,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>59.96</v>
+        <v>61.88</v>
       </c>
       <c r="Z6">
-        <v>8.19</v>
+        <v>10.39</v>
       </c>
       <c r="AA6">
-        <v>8.49</v>
+        <v>8.83</v>
       </c>
       <c r="AB6">
-        <v>-0.29</v>
+        <v>1.55</v>
       </c>
       <c r="AC6">
-        <v>30.37</v>
+        <v>52.5</v>
       </c>
       <c r="AD6">
-        <v>22.89</v>
+        <v>40.09</v>
       </c>
       <c r="AE6">
-        <v>23.35</v>
+        <v>27.14</v>
       </c>
       <c r="AF6">
-        <v>445.76</v>
+        <v>973.67</v>
       </c>
       <c r="AG6">
-        <v>821.0700000000001</v>
+        <v>826.65</v>
       </c>
       <c r="AH6">
-        <v>748.78</v>
+        <v>752.42</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1478,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>19.96</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,58 +1489,58 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3200.2</v>
+        <v>3441.3</v>
       </c>
       <c r="D7">
-        <v>2.32</v>
+        <v>3.69</v>
       </c>
       <c r="E7">
-        <v>3280.2</v>
+        <v>3441.3</v>
       </c>
       <c r="F7">
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-2.44</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>69.19</v>
+        <v>81.94</v>
       </c>
       <c r="I7">
-        <v>10.83</v>
+        <v>11.11</v>
       </c>
       <c r="J7">
-        <v>26.5</v>
+        <v>34.09</v>
       </c>
       <c r="K7">
-        <v>23.77</v>
+        <v>32.02</v>
       </c>
       <c r="L7">
-        <v>20.76</v>
+        <v>26.13</v>
       </c>
       <c r="M7">
-        <v>33.55</v>
+        <v>34.36</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P7">
-        <v>3158.76</v>
+        <v>3273.6</v>
       </c>
       <c r="Q7">
-        <v>2774.03</v>
+        <v>2854.06</v>
       </c>
       <c r="R7">
-        <v>2632.36</v>
+        <v>2667.08</v>
       </c>
       <c r="S7">
-        <v>2385.1</v>
+        <v>2394.73</v>
       </c>
       <c r="T7">
-        <v>34.17</v>
+        <v>43.7</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,43 +1555,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>72.59999999999999</v>
+        <v>78.55</v>
       </c>
       <c r="Z7">
-        <v>162.26</v>
+        <v>199.44</v>
       </c>
       <c r="AA7">
-        <v>105.8</v>
+        <v>136.2</v>
       </c>
       <c r="AB7">
-        <v>56.46</v>
+        <v>63.24</v>
       </c>
       <c r="AC7">
-        <v>73.72</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="AD7">
-        <v>86.45999999999999</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="AE7">
-        <v>146.96</v>
+        <v>147.73</v>
       </c>
       <c r="AF7">
-        <v>-39.22</v>
+        <v>-10.72</v>
       </c>
       <c r="AG7">
-        <v>3269.87</v>
+        <v>3453.34</v>
       </c>
       <c r="AH7">
-        <v>2278.19</v>
+        <v>2254.78</v>
       </c>
       <c r="AI7">
-        <v>2798.69</v>
+        <v>2938.47</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>65.7</v>
+        <v>69.15000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8109.5</v>
+        <v>8286</v>
       </c>
       <c r="D8">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1614,46 +1614,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-20.75</v>
+        <v>-19.03</v>
       </c>
       <c r="H8">
-        <v>36.88</v>
+        <v>39.86</v>
       </c>
       <c r="I8">
-        <v>1.56</v>
+        <v>4.46</v>
       </c>
       <c r="J8">
-        <v>7.97</v>
+        <v>2.62</v>
       </c>
       <c r="K8">
-        <v>16.19</v>
+        <v>18.04</v>
       </c>
       <c r="L8">
-        <v>-17.46</v>
+        <v>-17.06</v>
       </c>
       <c r="M8">
-        <v>15.4</v>
+        <v>15.18</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P8">
-        <v>7999.2</v>
+        <v>8120.1</v>
       </c>
       <c r="Q8">
-        <v>8093.42</v>
+        <v>8098</v>
       </c>
       <c r="R8">
-        <v>7900.44</v>
+        <v>7940.52</v>
       </c>
       <c r="S8">
-        <v>7407.24</v>
+        <v>7404.36</v>
       </c>
       <c r="T8">
-        <v>9.48</v>
+        <v>11.91</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,43 +1668,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>56.24</v>
+        <v>62.3</v>
       </c>
       <c r="Z8">
-        <v>51.16</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="AA8">
-        <v>71.65000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AB8">
-        <v>-20.49</v>
+        <v>4.25</v>
       </c>
       <c r="AC8">
-        <v>37.25</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="AD8">
-        <v>23.32</v>
+        <v>59.69</v>
       </c>
       <c r="AE8">
-        <v>232.58</v>
+        <v>247.53</v>
       </c>
       <c r="AF8">
-        <v>-55.01</v>
+        <v>356.6</v>
       </c>
       <c r="AG8">
-        <v>8320.200000000001</v>
+        <v>8325.030000000001</v>
       </c>
       <c r="AH8">
-        <v>7866.65</v>
+        <v>7870.97</v>
       </c>
       <c r="AI8">
-        <v>7451.92</v>
+        <v>7724.65</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>14.68</v>
+        <v>22.68</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1937,13 +1937,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>0.28</v>
+        <v>10.77</v>
       </c>
       <c r="D7" s="6">
-        <v>6.43</v>
+        <v>5.44</v>
       </c>
       <c r="E7" s="7">
-        <v>6.15</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1954,13 +1954,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-5.66</v>
+        <v>-1.9</v>
       </c>
       <c r="D8" s="6">
-        <v>-4</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.66</v>
+        <v>1.13</v>
+      </c>
+      <c r="E8" s="8">
+        <v>3.03</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1971,13 +1971,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>6.52</v>
+        <v>8.48</v>
       </c>
       <c r="D9" s="6">
-        <v>9.31</v>
+        <v>7.09</v>
       </c>
       <c r="E9" s="7">
-        <v>2.79</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1988,13 +1988,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-0.79</v>
+        <v>-1.32</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.9</v>
+        <v>-2.74</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2005,13 +2005,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>2.5</v>
+        <v>5.03</v>
       </c>
       <c r="D11" s="6">
-        <v>5.85</v>
-      </c>
-      <c r="E11" s="7">
-        <v>3.35</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3.67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2022,13 +2022,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>19.09</v>
+        <v>29.34</v>
       </c>
       <c r="D12" s="6">
-        <v>26.5</v>
-      </c>
-      <c r="E12" s="7">
-        <v>7.41</v>
+        <v>34.09</v>
+      </c>
+      <c r="E12" s="8">
+        <v>4.75</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2039,13 +2039,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>5.36</v>
+        <v>10.19</v>
       </c>
       <c r="D13" s="6">
-        <v>7.97</v>
+        <v>2.62</v>
       </c>
       <c r="E13" s="7">
-        <v>2.61</v>
+        <v>-7.57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2056,13 +2056,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-5.8</v>
+        <v>1.58</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.97</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" s="7">
-        <v>1.83</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2073,13 +2073,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.81</v>
+        <v>-2.6</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.65</v>
+        <v>-2.37</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2090,13 +2090,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.3</v>
+        <v>-1.66</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.02</v>
+        <v>-2.52</v>
       </c>
       <c r="E16" s="7">
-        <v>0.28</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2107,13 +2107,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.7</v>
+        <v>-4.73</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.02</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.32</v>
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2124,13 +2124,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>1.88</v>
+        <v>2.85</v>
       </c>
       <c r="D18" s="6">
-        <v>3.84</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.96</v>
+        <v>4.03</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.18</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2141,13 +2141,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>8.66</v>
+        <v>7.45</v>
       </c>
       <c r="D19" s="6">
-        <v>10.83</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2.17</v>
+        <v>11.11</v>
+      </c>
+      <c r="E19" s="8">
+        <v>3.66</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2158,13 +2158,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>0.16</v>
+        <v>3.16</v>
       </c>
       <c r="D20" s="6">
-        <v>1.56</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.4</v>
+        <v>4.46</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.3</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2175,13 +2175,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>28.82</v>
+        <v>33.96</v>
       </c>
       <c r="D21" s="6">
-        <v>33.9</v>
+        <v>29.22</v>
       </c>
       <c r="E21" s="7">
-        <v>5.08</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2192,13 +2192,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>29.01</v>
+        <v>29.85</v>
       </c>
       <c r="D22" s="6">
-        <v>31.88</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.87</v>
+        <v>29.94</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2209,13 +2209,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>28.37</v>
+        <v>22.44</v>
       </c>
       <c r="D23" s="6">
-        <v>29.34</v>
+        <v>20.96</v>
       </c>
       <c r="E23" s="7">
-        <v>0.97</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2226,13 +2226,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-9.369999999999999</v>
+        <v>-16.81</v>
       </c>
       <c r="D24" s="6">
-        <v>-14.47</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-5.1</v>
+        <v>-18.81</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2243,13 +2243,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-30.87</v>
+        <v>-32.26</v>
       </c>
       <c r="D25" s="6">
-        <v>-30.31</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.5600000000000001</v>
+        <v>-28.09</v>
+      </c>
+      <c r="E25" s="8">
+        <v>4.17</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2260,13 +2260,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>18.31</v>
+        <v>24.24</v>
       </c>
       <c r="D26" s="6">
-        <v>20.76</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.45</v>
+        <v>26.13</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2277,13 +2277,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-20.2</v>
+        <v>-17.36</v>
       </c>
       <c r="D27" s="6">
-        <v>-17.46</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.74</v>
+        <v>-17.06</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2294,13 +2294,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>2.33</v>
+        <v>10.63</v>
       </c>
       <c r="D28" s="6">
-        <v>7.64</v>
+        <v>7.56</v>
       </c>
       <c r="E28" s="7">
-        <v>5.31</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2311,13 +2311,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-0.21</v>
+        <v>-0.1</v>
       </c>
       <c r="D29" s="6">
-        <v>1.22</v>
+        <v>-0.19</v>
       </c>
       <c r="E29" s="7">
-        <v>1.43</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2328,13 +2328,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>24.57</v>
+        <v>17.09</v>
       </c>
       <c r="D30" s="6">
-        <v>22.67</v>
+        <v>17.83</v>
       </c>
       <c r="E30" s="8">
-        <v>-1.9</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2345,13 +2345,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>8.25</v>
+        <v>8.4</v>
       </c>
       <c r="D31" s="6">
-        <v>10.19</v>
+        <v>4.32</v>
       </c>
       <c r="E31" s="7">
-        <v>1.94</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2362,13 +2362,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-0.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D32" s="6">
-        <v>4.02</v>
-      </c>
-      <c r="E32" s="7">
-        <v>4.33</v>
+        <v>7.77</v>
+      </c>
+      <c r="E32" s="8">
+        <v>6.83</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2379,13 +2379,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>20.85</v>
+        <v>27.28</v>
       </c>
       <c r="D33" s="6">
-        <v>23.77</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.92</v>
+        <v>32.02</v>
+      </c>
+      <c r="E33" s="8">
+        <v>4.74</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2396,13 +2396,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>16.3</v>
+        <v>17.05</v>
       </c>
       <c r="D34" s="6">
-        <v>16.19</v>
+        <v>18.04</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.11</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2413,13 +2413,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-12.44</v>
+        <v>-5.79</v>
       </c>
       <c r="D35" s="6">
-        <v>-8.380000000000001</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="E35" s="7">
-        <v>4.06</v>
+        <v>-3.83</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2430,13 +2430,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-11.62</v>
+        <v>-11.21</v>
       </c>
       <c r="D36" s="6">
-        <v>-10.26</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.36</v>
+        <v>-10.14</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.07</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2447,13 +2447,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-3.43</v>
+        <v>-3.97</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.63</v>
+        <v>-4.81</v>
       </c>
       <c r="E37" s="7">
-        <v>0.8</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2464,13 +2464,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-15.76</v>
+        <v>-17.49</v>
       </c>
       <c r="D38" s="6">
-        <v>-17.14</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.38</v>
+        <v>-20.37</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.88</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2481,166 +2481,166 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-33.19</v>
+        <v>-32.32</v>
       </c>
       <c r="D39" s="6">
-        <v>-31.22</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.97</v>
+        <v>-30.06</v>
+      </c>
+      <c r="E39" s="8">
+        <v>2.26</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-4.66</v>
+        <v>-20.04</v>
       </c>
       <c r="D40" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.22</v>
+        <v>-19.03</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.01</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>-22.14</v>
+        <v>1169.8</v>
       </c>
       <c r="D41" s="6">
-        <v>-20.75</v>
+        <v>1122.2</v>
       </c>
       <c r="E41" s="7">
-        <v>1.39</v>
+        <v>-47.6</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1087.2</v>
+        <v>867</v>
       </c>
       <c r="D42" s="6">
-        <v>1137.6</v>
-      </c>
-      <c r="E42" s="7">
-        <v>50.4</v>
+        <v>877.5</v>
+      </c>
+      <c r="E42" s="8">
+        <v>10.5</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>863.05</v>
+        <v>1862.9</v>
       </c>
       <c r="D43" s="6">
-        <v>876.3</v>
+        <v>1846.7</v>
       </c>
       <c r="E43" s="7">
-        <v>13.25</v>
+        <v>-16.2</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>1873.5</v>
+        <v>1996.1</v>
       </c>
       <c r="D44" s="6">
-        <v>1888.9</v>
+        <v>1926.6</v>
       </c>
       <c r="E44" s="7">
-        <v>15.4</v>
+        <v>-69.5</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>2038.1</v>
+        <v>797.3</v>
       </c>
       <c r="D45" s="6">
-        <v>2004.8</v>
+        <v>823.95</v>
       </c>
       <c r="E45" s="8">
-        <v>-33.3</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>787.05</v>
+        <v>3318.8</v>
       </c>
       <c r="D46" s="6">
-        <v>810.25</v>
-      </c>
-      <c r="E46" s="7">
-        <v>23.2</v>
+        <v>3441.3</v>
+      </c>
+      <c r="E46" s="8">
+        <v>122.5</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>3127.5</v>
+        <v>8182.5</v>
       </c>
       <c r="D47" s="6">
-        <v>3200.2</v>
-      </c>
-      <c r="E47" s="7">
-        <v>72.7</v>
+        <v>8286</v>
+      </c>
+      <c r="E47" s="8">
+        <v>103.5</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C48" s="6">
-        <v>7967.5</v>
+        <v>85</v>
       </c>
       <c r="D48" s="6">
-        <v>8109.5</v>
+        <v>71</v>
       </c>
       <c r="E48" s="7">
-        <v>142</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2651,268 +2651,251 @@
         <v>13</v>
       </c>
       <c r="C49" s="6">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="D49" s="6">
         <v>85</v>
       </c>
       <c r="E49" s="8">
-        <v>-14</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>85</v>
+        <v>59.1</v>
       </c>
       <c r="D50" s="6">
-        <v>99</v>
+        <v>51.27</v>
       </c>
       <c r="E50" s="7">
-        <v>14</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="6">
-        <v>46.51</v>
+        <v>45.13</v>
       </c>
       <c r="D51" s="6">
-        <v>54.76</v>
-      </c>
-      <c r="E51" s="7">
-        <v>8.25</v>
+        <v>48.32</v>
+      </c>
+      <c r="E51" s="8">
+        <v>3.19</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>43.55</v>
+        <v>52.3</v>
       </c>
       <c r="D52" s="6">
-        <v>47.54</v>
+        <v>49.86</v>
       </c>
       <c r="E52" s="7">
-        <v>3.99</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>54.45</v>
+        <v>39.76</v>
       </c>
       <c r="D53" s="6">
-        <v>56.42</v>
+        <v>31.38</v>
       </c>
       <c r="E53" s="7">
-        <v>1.97</v>
+        <v>-8.380000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>46.31</v>
+        <v>55.27</v>
       </c>
       <c r="D54" s="6">
-        <v>41.04</v>
+        <v>61.88</v>
       </c>
       <c r="E54" s="8">
-        <v>-5.27</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>53.37</v>
+        <v>75.78</v>
       </c>
       <c r="D55" s="6">
-        <v>59.96</v>
-      </c>
-      <c r="E55" s="7">
-        <v>6.59</v>
+        <v>78.55</v>
+      </c>
+      <c r="E55" s="8">
+        <v>2.77</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>70.39</v>
+        <v>58.86</v>
       </c>
       <c r="D56" s="6">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="E56" s="7">
-        <v>2.21</v>
+        <v>62.3</v>
+      </c>
+      <c r="E56" s="8">
+        <v>3.44</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C57" s="6">
-        <v>50.56</v>
+        <v>260.52</v>
       </c>
       <c r="D57" s="6">
-        <v>56.24</v>
+        <v>-2.48</v>
       </c>
       <c r="E57" s="7">
-        <v>5.68</v>
+        <v>-263</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="6">
-        <v>-18.86</v>
+        <v>-64.41</v>
       </c>
       <c r="D58" s="6">
-        <v>33.25</v>
-      </c>
-      <c r="E58" s="7">
-        <v>52.11</v>
+        <v>-63.5</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.91</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>11.23</v>
+        <v>-40.61</v>
       </c>
       <c r="D59" s="6">
-        <v>-40.16</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-51.39</v>
+        <v>-43.86</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>-64.66</v>
+        <v>-69.14</v>
       </c>
       <c r="D60" s="6">
-        <v>-59.25</v>
-      </c>
-      <c r="E60" s="7">
-        <v>5.41</v>
+        <v>203.78</v>
+      </c>
+      <c r="E60" s="8">
+        <v>272.92</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-58.58</v>
+        <v>57.24</v>
       </c>
       <c r="D61" s="6">
-        <v>-23.79</v>
-      </c>
-      <c r="E61" s="7">
-        <v>34.79</v>
+        <v>973.67</v>
+      </c>
+      <c r="E61" s="8">
+        <v>916.4299999999999</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>95.12</v>
+        <v>-30.78</v>
       </c>
       <c r="D62" s="6">
-        <v>445.76</v>
-      </c>
-      <c r="E62" s="7">
-        <v>350.64</v>
+        <v>-10.72</v>
+      </c>
+      <c r="E62" s="8">
+        <v>20.06</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>-11.88</v>
+        <v>-19.51</v>
       </c>
       <c r="D63" s="6">
-        <v>-39.22</v>
+        <v>356.6</v>
       </c>
       <c r="E63" s="8">
-        <v>-27.34</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-55.3</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-55.01</v>
-      </c>
-      <c r="E64" s="7">
-        <v>0.29</v>
+        <v>376.11</v>
       </c>
     </row>
   </sheetData>
@@ -2977,16 +2960,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>55.5</v>
+        <v>54.8</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="G2" s="11">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3117,25 +3100,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.6143</v>
+        <v>0.6049</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3355</v>
+        <v>0.3436</v>
       </c>
       <c r="C2" s="14">
-        <v>0.3148</v>
+        <v>0.2958</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2054</v>
+        <v>0.207</v>
       </c>
       <c r="E2" s="14">
-        <v>0.162</v>
+        <v>0.1724</v>
       </c>
       <c r="F2" s="14">
-        <v>0.154</v>
+        <v>0.1518</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1068</v>
+        <v>0.09130000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,16 +190,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.3 → 49.9</t>
+    <t>49.9 → 53.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>49.9</t>
+  </si>
+  <si>
+    <t>53.6</t>
+  </si>
+  <si>
+    <t>51.3 → 49.0</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.3</t>
-  </si>
-  <si>
-    <t>49.9</t>
+    <t>51.3</t>
+  </si>
+  <si>
+    <t>49.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +297,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +337,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -409,10 +421,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -924,10 +937,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1122.2</v>
+        <v>1106.7</v>
       </c>
       <c r="D2">
-        <v>-4.07</v>
+        <v>-1.38</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -936,46 +949,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-9.619999999999999</v>
+        <v>-10.87</v>
       </c>
       <c r="H2">
-        <v>49.96</v>
+        <v>47.89</v>
       </c>
       <c r="I2">
-        <v>-0.04</v>
+        <v>-1.71</v>
       </c>
       <c r="J2">
-        <v>5.44</v>
+        <v>3.13</v>
       </c>
       <c r="K2">
-        <v>7.56</v>
+        <v>6.93</v>
       </c>
       <c r="L2">
-        <v>29.22</v>
+        <v>11.97</v>
       </c>
       <c r="M2">
-        <v>9.130000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="N2">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>1128.56</v>
+        <v>1124.7</v>
       </c>
       <c r="Q2">
-        <v>1110.24</v>
+        <v>1112.5</v>
       </c>
       <c r="R2">
-        <v>1115.14</v>
+        <v>1115.96</v>
       </c>
       <c r="S2">
-        <v>939.22</v>
+        <v>940.33</v>
       </c>
       <c r="T2">
-        <v>19.48</v>
+        <v>17.69</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +1003,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>51.27</v>
+        <v>49</v>
       </c>
       <c r="Z2">
-        <v>13.3</v>
+        <v>10.64</v>
       </c>
       <c r="AA2">
-        <v>11.64</v>
+        <v>11.44</v>
       </c>
       <c r="AB2">
-        <v>1.67</v>
+        <v>-0.8</v>
       </c>
       <c r="AC2">
-        <v>41.63</v>
+        <v>32.25</v>
       </c>
       <c r="AD2">
-        <v>35.85</v>
+        <v>36.45</v>
       </c>
       <c r="AE2">
-        <v>47.8</v>
+        <v>46.43</v>
       </c>
       <c r="AF2">
-        <v>-2.48</v>
+        <v>-11.21</v>
       </c>
       <c r="AG2">
-        <v>1194.34</v>
+        <v>1193.45</v>
       </c>
       <c r="AH2">
-        <v>1026.14</v>
+        <v>1031.55</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1026,7 +1039,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>33.03</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1050,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>877.5</v>
+        <v>878.5</v>
       </c>
       <c r="D3">
-        <v>1.21</v>
+        <v>0.11</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1062,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-10.14</v>
+        <v>-10.04</v>
       </c>
       <c r="H3">
-        <v>65.73</v>
+        <v>65.92</v>
       </c>
       <c r="I3">
-        <v>-2.37</v>
+        <v>-1.76</v>
       </c>
       <c r="J3">
-        <v>1.13</v>
+        <v>0.14</v>
       </c>
       <c r="K3">
-        <v>-0.19</v>
+        <v>-6.02</v>
       </c>
       <c r="L3">
-        <v>29.94</v>
+        <v>30.58</v>
       </c>
       <c r="M3">
-        <v>60.49</v>
+        <v>60.2</v>
       </c>
       <c r="N3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O3">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P3">
-        <v>875.61</v>
+        <v>872.47</v>
       </c>
       <c r="Q3">
-        <v>871.09</v>
+        <v>872.8099999999999</v>
       </c>
       <c r="R3">
-        <v>904.14</v>
+        <v>903</v>
       </c>
       <c r="S3">
-        <v>768.97</v>
+        <v>769.71</v>
       </c>
       <c r="T3">
-        <v>14.11</v>
+        <v>14.13</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,34 +1116,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.32</v>
+        <v>48.63</v>
       </c>
       <c r="Z3">
-        <v>-4.38</v>
+        <v>-4.05</v>
       </c>
       <c r="AA3">
-        <v>-5.35</v>
+        <v>-5.09</v>
       </c>
       <c r="AB3">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="AC3">
-        <v>42.58</v>
+        <v>37.53</v>
       </c>
       <c r="AD3">
-        <v>50.19</v>
+        <v>40.41</v>
       </c>
       <c r="AE3">
-        <v>21.45</v>
+        <v>21.02</v>
       </c>
       <c r="AF3">
-        <v>-63.5</v>
+        <v>-48.35</v>
       </c>
       <c r="AG3">
-        <v>914.6900000000001</v>
+        <v>914.6</v>
       </c>
       <c r="AH3">
-        <v>827.49</v>
+        <v>831.02</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1139,7 +1152,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>19.28</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1163,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1846.7</v>
+        <v>1873</v>
       </c>
       <c r="D4">
-        <v>-0.87</v>
+        <v>1.42</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1175,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-4.81</v>
+        <v>-3.45</v>
       </c>
       <c r="H4">
-        <v>36.32</v>
+        <v>38.26</v>
       </c>
       <c r="I4">
-        <v>-2.52</v>
+        <v>0.27</v>
       </c>
       <c r="J4">
-        <v>7.09</v>
+        <v>4.92</v>
       </c>
       <c r="K4">
-        <v>17.83</v>
+        <v>18.6</v>
       </c>
       <c r="L4">
-        <v>20.96</v>
+        <v>23.08</v>
       </c>
       <c r="M4">
-        <v>29.58</v>
+        <v>29.9</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P4">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="Q4">
-        <v>1871.89</v>
+        <v>1877.89</v>
       </c>
       <c r="R4">
-        <v>1807.3</v>
+        <v>1811.69</v>
       </c>
       <c r="S4">
-        <v>1671.08</v>
+        <v>1672.04</v>
       </c>
       <c r="T4">
-        <v>10.51</v>
+        <v>12.02</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,34 +1229,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>49.86</v>
+        <v>53.65</v>
       </c>
       <c r="Z4">
-        <v>24.35</v>
+        <v>22.45</v>
       </c>
       <c r="AA4">
-        <v>34.39</v>
+        <v>32</v>
       </c>
       <c r="AB4">
-        <v>-10.04</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="AC4">
-        <v>6.19</v>
+        <v>6.91</v>
       </c>
       <c r="AD4">
-        <v>7.71</v>
+        <v>6.97</v>
       </c>
       <c r="AE4">
-        <v>44.66</v>
+        <v>45.18</v>
       </c>
       <c r="AF4">
-        <v>-43.86</v>
+        <v>-70.55</v>
       </c>
       <c r="AG4">
-        <v>1969.65</v>
+        <v>1958.07</v>
       </c>
       <c r="AH4">
-        <v>1774.12</v>
+        <v>1797.7</v>
       </c>
       <c r="AI4">
         <v>1753.66</v>
@@ -1252,7 +1265,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>20.54</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1276,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1926.6</v>
+        <v>1913.6</v>
       </c>
       <c r="D5">
-        <v>-3.48</v>
+        <v>-0.67</v>
       </c>
       <c r="E5">
         <v>2419.36</v>
@@ -1275,46 +1288,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-20.37</v>
+        <v>-20.9</v>
       </c>
       <c r="H5">
-        <v>10.37</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="I5">
-        <v>-8.050000000000001</v>
+        <v>-7.23</v>
       </c>
       <c r="J5">
-        <v>-2.74</v>
+        <v>-4.5</v>
       </c>
       <c r="K5">
-        <v>4.32</v>
+        <v>4.47</v>
       </c>
       <c r="L5">
-        <v>-18.81</v>
+        <v>-20.59</v>
       </c>
       <c r="M5">
-        <v>20.7</v>
+        <v>20.88</v>
       </c>
       <c r="N5">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="O5">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P5">
-        <v>2005.66</v>
+        <v>1975.84</v>
       </c>
       <c r="Q5">
-        <v>2061.32</v>
+        <v>2055.66</v>
       </c>
       <c r="R5">
-        <v>2037.91</v>
+        <v>2036.45</v>
       </c>
       <c r="S5">
-        <v>2103.51</v>
+        <v>2102.37</v>
       </c>
       <c r="T5">
-        <v>-8.41</v>
+        <v>-8.98</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,16 +1342,16 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>31.38</v>
+        <v>30.1</v>
       </c>
       <c r="Z5">
-        <v>-8.49</v>
+        <v>-17.35</v>
       </c>
       <c r="AA5">
-        <v>9.82</v>
+        <v>4.38</v>
       </c>
       <c r="AB5">
-        <v>-18.3</v>
+        <v>-21.73</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1347,25 +1360,25 @@
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>49.85</v>
+        <v>48.83</v>
       </c>
       <c r="AF5">
-        <v>203.78</v>
+        <v>335.97</v>
       </c>
       <c r="AG5">
-        <v>2153.38</v>
+        <v>2168.27</v>
       </c>
       <c r="AH5">
-        <v>1969.25</v>
+        <v>1943.04</v>
       </c>
       <c r="AI5">
-        <v>2114.4</v>
+        <v>2060.59</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>28.7</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1389,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>823.95</v>
+        <v>810.4</v>
       </c>
       <c r="D6">
-        <v>3.34</v>
+        <v>-1.64</v>
       </c>
       <c r="E6">
         <v>1178</v>
@@ -1388,46 +1401,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-30.06</v>
+        <v>-31.21</v>
       </c>
       <c r="H6">
-        <v>17.02</v>
+        <v>15.1</v>
       </c>
       <c r="I6">
-        <v>4.03</v>
+        <v>3.82</v>
       </c>
       <c r="J6">
-        <v>8.699999999999999</v>
+        <v>5.09</v>
       </c>
       <c r="K6">
-        <v>7.77</v>
+        <v>9.01</v>
       </c>
       <c r="L6">
-        <v>-28.09</v>
+        <v>-29.88</v>
       </c>
       <c r="M6">
-        <v>17.24</v>
+        <v>15.26</v>
       </c>
       <c r="N6">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="O6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P6">
-        <v>799.83</v>
+        <v>805.79</v>
       </c>
       <c r="Q6">
-        <v>789.53</v>
+        <v>791.65</v>
       </c>
       <c r="R6">
-        <v>761.54</v>
+        <v>763.24</v>
       </c>
       <c r="S6">
-        <v>862.59</v>
+        <v>861.4400000000001</v>
       </c>
       <c r="T6">
-        <v>-4.48</v>
+        <v>-5.93</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,34 +1455,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>61.88</v>
+        <v>57.25</v>
       </c>
       <c r="Z6">
-        <v>10.39</v>
+        <v>10.83</v>
       </c>
       <c r="AA6">
-        <v>8.83</v>
+        <v>9.23</v>
       </c>
       <c r="AB6">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC6">
-        <v>52.5</v>
+        <v>53.39</v>
       </c>
       <c r="AD6">
-        <v>40.09</v>
+        <v>47.76</v>
       </c>
       <c r="AE6">
-        <v>27.14</v>
+        <v>26.55</v>
       </c>
       <c r="AF6">
-        <v>973.67</v>
+        <v>33.3</v>
       </c>
       <c r="AG6">
-        <v>826.65</v>
+        <v>828.4299999999999</v>
       </c>
       <c r="AH6">
-        <v>752.42</v>
+        <v>754.87</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1478,7 +1491,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>27.27</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,13 +1502,13 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3441.3</v>
+        <v>3454.9</v>
       </c>
       <c r="D7">
-        <v>3.69</v>
+        <v>0.4</v>
       </c>
       <c r="E7">
-        <v>3441.3</v>
+        <v>3454.9</v>
       </c>
       <c r="F7">
         <v>1891.45</v>
@@ -1504,22 +1517,22 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>81.94</v>
+        <v>82.66</v>
       </c>
       <c r="I7">
-        <v>11.11</v>
+        <v>5.33</v>
       </c>
       <c r="J7">
-        <v>34.09</v>
+        <v>33.24</v>
       </c>
       <c r="K7">
-        <v>32.02</v>
+        <v>32.2</v>
       </c>
       <c r="L7">
-        <v>26.13</v>
+        <v>23.93</v>
       </c>
       <c r="M7">
-        <v>34.36</v>
+        <v>34.56</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1528,19 +1541,19 @@
         <v>87</v>
       </c>
       <c r="P7">
-        <v>3273.6</v>
+        <v>3308.54</v>
       </c>
       <c r="Q7">
-        <v>2854.06</v>
+        <v>2898.19</v>
       </c>
       <c r="R7">
-        <v>2667.08</v>
+        <v>2685.55</v>
       </c>
       <c r="S7">
-        <v>2394.73</v>
+        <v>2400.34</v>
       </c>
       <c r="T7">
-        <v>43.7</v>
+        <v>43.93</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,43 +1568,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>78.55</v>
+        <v>78.84</v>
       </c>
       <c r="Z7">
-        <v>199.44</v>
+        <v>214.45</v>
       </c>
       <c r="AA7">
-        <v>136.2</v>
+        <v>151.85</v>
       </c>
       <c r="AB7">
-        <v>63.24</v>
+        <v>62.6</v>
       </c>
       <c r="AC7">
-        <v>74.15000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="AD7">
-        <v>71.04000000000001</v>
+        <v>73.45</v>
       </c>
       <c r="AE7">
-        <v>147.73</v>
+        <v>148.81</v>
       </c>
       <c r="AF7">
-        <v>-10.72</v>
+        <v>14.9</v>
       </c>
       <c r="AG7">
-        <v>3453.34</v>
+        <v>3538.67</v>
       </c>
       <c r="AH7">
-        <v>2254.78</v>
+        <v>2257.72</v>
       </c>
       <c r="AI7">
-        <v>2938.47</v>
+        <v>3037.42</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>69.15000000000001</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1615,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8286</v>
+        <v>8189</v>
       </c>
       <c r="D8">
-        <v>1.26</v>
+        <v>-1.17</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1614,46 +1627,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-19.03</v>
+        <v>-19.97</v>
       </c>
       <c r="H8">
-        <v>39.86</v>
+        <v>38.22</v>
       </c>
       <c r="I8">
-        <v>4.46</v>
+        <v>1.66</v>
       </c>
       <c r="J8">
-        <v>2.62</v>
+        <v>-1.37</v>
       </c>
       <c r="K8">
-        <v>18.04</v>
+        <v>17.47</v>
       </c>
       <c r="L8">
-        <v>-17.06</v>
+        <v>-19.05</v>
       </c>
       <c r="M8">
-        <v>15.18</v>
+        <v>14.79</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P8">
-        <v>8120.1</v>
+        <v>8146.9</v>
       </c>
       <c r="Q8">
-        <v>8098</v>
+        <v>8092.48</v>
       </c>
       <c r="R8">
-        <v>7940.52</v>
+        <v>7945.12</v>
       </c>
       <c r="S8">
-        <v>7404.36</v>
+        <v>7403.51</v>
       </c>
       <c r="T8">
-        <v>11.91</v>
+        <v>10.61</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,34 +1681,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>62.3</v>
+        <v>57.45</v>
       </c>
       <c r="Z8">
-        <v>74.65000000000001</v>
+        <v>77.47</v>
       </c>
       <c r="AA8">
-        <v>70.40000000000001</v>
+        <v>71.81</v>
       </c>
       <c r="AB8">
-        <v>4.25</v>
+        <v>5.66</v>
       </c>
       <c r="AC8">
-        <v>85.84999999999999</v>
+        <v>87.55</v>
       </c>
       <c r="AD8">
-        <v>59.69</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="AE8">
-        <v>247.53</v>
+        <v>243.64</v>
       </c>
       <c r="AF8">
-        <v>356.6</v>
+        <v>-32.43</v>
       </c>
       <c r="AG8">
-        <v>8325.030000000001</v>
+        <v>8303.68</v>
       </c>
       <c r="AH8">
-        <v>7870.97</v>
+        <v>7881.27</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1704,7 +1717,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>22.68</v>
+        <v>25.42</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1903,1005 +1916,1059 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>10.77</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>5.44</v>
       </c>
-      <c r="E7" s="7">
-        <v>-5.33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>3.13</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-1.9</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="7">
         <v>1.13</v>
       </c>
-      <c r="E8" s="8">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>0.14</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>8.48</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="7">
         <v>7.09</v>
       </c>
-      <c r="E9" s="7">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>4.92</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-1.32</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C11" s="7">
         <v>-2.74</v>
       </c>
-      <c r="E10" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="7">
+        <v>-4.5</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>5.03</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C12" s="7">
         <v>8.699999999999999</v>
       </c>
-      <c r="E11" s="8">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D12" s="7">
+        <v>5.09</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-3.61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>29.34</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C13" s="7">
         <v>34.09</v>
       </c>
-      <c r="E12" s="8">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D13" s="7">
+        <v>33.24</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>10.19</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C14" s="7">
         <v>2.62</v>
       </c>
-      <c r="E13" s="7">
-        <v>-7.57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-1.37</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-3.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>1.58</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C15" s="7">
         <v>-0.04</v>
       </c>
-      <c r="E14" s="7">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D15" s="7">
+        <v>-1.71</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-2.6</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C16" s="7">
         <v>-2.37</v>
       </c>
-      <c r="E15" s="8">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D16" s="7">
+        <v>-1.76</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-1.66</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C17" s="7">
         <v>-2.52</v>
       </c>
-      <c r="E16" s="7">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D17" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="E17" s="9">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-4.73</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C18" s="7">
         <v>-8.050000000000001</v>
       </c>
-      <c r="E17" s="7">
-        <v>-3.32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D18" s="7">
+        <v>-7.23</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C19" s="7">
         <v>4.03</v>
       </c>
-      <c r="E18" s="8">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="D19" s="7">
+        <v>3.82</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>7.45</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C20" s="7">
         <v>11.11</v>
       </c>
-      <c r="E19" s="8">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="D20" s="7">
+        <v>5.33</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-5.78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>3.16</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C21" s="7">
         <v>4.46</v>
       </c>
-      <c r="E20" s="8">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="D21" s="7">
+        <v>1.66</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>33.96</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="7">
         <v>29.22</v>
       </c>
-      <c r="E21" s="7">
-        <v>-4.74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="D22" s="7">
+        <v>11.97</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-17.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>29.85</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="7">
         <v>29.94</v>
       </c>
-      <c r="E22" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="D23" s="7">
+        <v>30.58</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>22.44</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C24" s="7">
         <v>20.96</v>
       </c>
-      <c r="E23" s="7">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="7">
+        <v>23.08</v>
+      </c>
+      <c r="E24" s="9">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>-16.81</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C25" s="7">
         <v>-18.81</v>
       </c>
-      <c r="E24" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="D25" s="7">
+        <v>-20.59</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-32.26</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C26" s="7">
         <v>-28.09</v>
       </c>
-      <c r="E25" s="8">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D26" s="7">
+        <v>-29.88</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>24.24</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C27" s="7">
         <v>26.13</v>
       </c>
-      <c r="E26" s="8">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D27" s="7">
+        <v>23.93</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>-17.36</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C28" s="7">
         <v>-17.06</v>
       </c>
-      <c r="E27" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="D28" s="7">
+        <v>-19.05</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="6">
-        <v>10.63</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C29" s="7">
         <v>7.56</v>
       </c>
-      <c r="E28" s="7">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="D29" s="7">
+        <v>6.93</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C30" s="7">
         <v>-0.19</v>
       </c>
-      <c r="E29" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="D30" s="7">
+        <v>-6.02</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-5.83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6">
-        <v>17.09</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C31" s="7">
         <v>17.83</v>
       </c>
-      <c r="E30" s="8">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="D31" s="7">
+        <v>18.6</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6">
-        <v>8.4</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C32" s="7">
         <v>4.32</v>
       </c>
-      <c r="E31" s="7">
-        <v>-4.08</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="D32" s="7">
+        <v>4.47</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C33" s="7">
         <v>7.77</v>
       </c>
-      <c r="E32" s="8">
-        <v>6.83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="D33" s="7">
+        <v>9.01</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="6">
-        <v>27.28</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C34" s="7">
         <v>32.02</v>
       </c>
-      <c r="E33" s="8">
-        <v>4.74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="D34" s="7">
+        <v>32.2</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6">
-        <v>17.05</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="C35" s="7">
         <v>18.04</v>
       </c>
-      <c r="E34" s="8">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="D35" s="7">
+        <v>17.47</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="6">
-        <v>-5.79</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C36" s="7">
         <v>-9.619999999999999</v>
       </c>
-      <c r="E35" s="7">
-        <v>-3.83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="D36" s="7">
+        <v>-10.87</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C37" s="7">
+        <v>-10.14</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-10.04</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-4.81</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-3.45</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-20.37</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-20.9</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-30.06</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-31.21</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-19.03</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-19.97</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7">
+        <v>1122.2</v>
+      </c>
+      <c r="D42" s="7">
+        <v>1106.7</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-15.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>877.5</v>
+      </c>
+      <c r="D43" s="7">
+        <v>878.5</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>1846.7</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1873</v>
+      </c>
+      <c r="E44" s="9">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1926.6</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1913.6</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>823.95</v>
+      </c>
+      <c r="D46" s="7">
+        <v>810.4</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-13.55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>3441.3</v>
+      </c>
+      <c r="D47" s="7">
+        <v>3454.9</v>
+      </c>
+      <c r="E47" s="9">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>8286</v>
+      </c>
+      <c r="D48" s="7">
+        <v>8189</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="7">
+        <v>71</v>
+      </c>
+      <c r="D49" s="7">
+        <v>57</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="7">
+        <v>57</v>
+      </c>
+      <c r="D50" s="7">
+        <v>71</v>
+      </c>
+      <c r="E50" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="7">
+        <v>29</v>
+      </c>
+      <c r="D51" s="7">
+        <v>15</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7">
+        <v>15</v>
+      </c>
+      <c r="D52" s="7">
+        <v>29</v>
+      </c>
+      <c r="E52" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>51.27</v>
+      </c>
+      <c r="D53" s="7">
+        <v>49</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>48.32</v>
+      </c>
+      <c r="D54" s="7">
+        <v>48.63</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>49.86</v>
+      </c>
+      <c r="D55" s="7">
+        <v>53.65</v>
+      </c>
+      <c r="E55" s="9">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>31.38</v>
+      </c>
+      <c r="D56" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>61.88</v>
+      </c>
+      <c r="D57" s="7">
+        <v>57.25</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>78.55</v>
+      </c>
+      <c r="D58" s="7">
+        <v>78.84</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>62.3</v>
+      </c>
+      <c r="D59" s="7">
+        <v>57.45</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-4.85</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>-2.48</v>
+      </c>
+      <c r="D60" s="7">
         <v>-11.21</v>
       </c>
-      <c r="D36" s="6">
-        <v>-10.14</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="E60" s="8">
+        <v>-8.73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-63.5</v>
+      </c>
+      <c r="D61" s="7">
+        <v>-48.35</v>
+      </c>
+      <c r="E61" s="9">
+        <v>15.15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-3.97</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-4.81</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-43.86</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-70.55</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-26.69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-17.49</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-20.37</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>203.78</v>
+      </c>
+      <c r="D63" s="7">
+        <v>335.97</v>
+      </c>
+      <c r="E63" s="9">
+        <v>132.19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-32.32</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-30.06</v>
-      </c>
-      <c r="E39" s="8">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>973.67</v>
+      </c>
+      <c r="D64" s="7">
+        <v>33.3</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-940.37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-10.72</v>
+      </c>
+      <c r="D65" s="7">
+        <v>14.9</v>
+      </c>
+      <c r="E65" s="9">
+        <v>25.62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-20.04</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-19.03</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>1169.8</v>
-      </c>
-      <c r="D41" s="6">
-        <v>1122.2</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-47.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>867</v>
-      </c>
-      <c r="D42" s="6">
-        <v>877.5</v>
-      </c>
-      <c r="E42" s="8">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>1862.9</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1846.7</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-16.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1996.1</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1926.6</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-69.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>797.3</v>
-      </c>
-      <c r="D45" s="6">
-        <v>823.95</v>
-      </c>
-      <c r="E45" s="8">
-        <v>26.65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>3318.8</v>
-      </c>
-      <c r="D46" s="6">
-        <v>3441.3</v>
-      </c>
-      <c r="E46" s="8">
-        <v>122.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>8182.5</v>
-      </c>
-      <c r="D47" s="6">
-        <v>8286</v>
-      </c>
-      <c r="E47" s="8">
-        <v>103.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="6">
-        <v>85</v>
-      </c>
-      <c r="D48" s="6">
-        <v>71</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>71</v>
-      </c>
-      <c r="D49" s="6">
-        <v>85</v>
-      </c>
-      <c r="E49" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>59.1</v>
-      </c>
-      <c r="D50" s="6">
-        <v>51.27</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-7.83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>45.13</v>
-      </c>
-      <c r="D51" s="6">
-        <v>48.32</v>
-      </c>
-      <c r="E51" s="8">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>52.3</v>
-      </c>
-      <c r="D52" s="6">
-        <v>49.86</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>39.76</v>
-      </c>
-      <c r="D53" s="6">
-        <v>31.38</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-8.380000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>55.27</v>
-      </c>
-      <c r="D54" s="6">
-        <v>61.88</v>
-      </c>
-      <c r="E54" s="8">
-        <v>6.61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>75.78</v>
-      </c>
-      <c r="D55" s="6">
-        <v>78.55</v>
-      </c>
-      <c r="E55" s="8">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>58.86</v>
-      </c>
-      <c r="D56" s="6">
-        <v>62.3</v>
-      </c>
-      <c r="E56" s="8">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="6">
-        <v>260.52</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-2.48</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-263</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-64.41</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-63.5</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>-40.61</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-43.86</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-69.14</v>
-      </c>
-      <c r="D60" s="6">
-        <v>203.78</v>
-      </c>
-      <c r="E60" s="8">
-        <v>272.92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>57.24</v>
-      </c>
-      <c r="D61" s="6">
-        <v>973.67</v>
-      </c>
-      <c r="E61" s="8">
-        <v>916.4299999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-30.78</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-10.72</v>
-      </c>
-      <c r="E62" s="8">
-        <v>20.06</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-19.51</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="C66" s="7">
         <v>356.6</v>
       </c>
-      <c r="E63" s="8">
-        <v>376.11</v>
+      <c r="D66" s="7">
+        <v>-32.43</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-389.03</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2921,60 +2988,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>72</v>
       </c>
+      <c r="F1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>60.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>54.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>53.6</v>
+      </c>
+      <c r="E2" s="12">
         <v>70</v>
       </c>
-      <c r="F2" s="11">
-        <v>8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>12.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>5.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>11.8</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -3076,49 +3143,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.6049</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3436</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2958</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.207</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1724</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1518</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.09130000000000001</v>
+      <c r="A2" s="15">
+        <v>0.602</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3456</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.299</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2088</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1526</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1479</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0877</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,46 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>49.9 → 53.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.9</t>
-  </si>
-  <si>
-    <t>53.6</t>
-  </si>
-  <si>
-    <t>51.3 → 49.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.3</t>
-  </si>
-  <si>
-    <t>49.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -413,19 +374,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -937,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1106.7</v>
+        <v>1105.7</v>
       </c>
       <c r="D2">
-        <v>-1.38</v>
+        <v>-0.09</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -949,46 +908,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-10.87</v>
+        <v>-10.95</v>
       </c>
       <c r="H2">
-        <v>47.89</v>
+        <v>47.75</v>
       </c>
       <c r="I2">
-        <v>-1.71</v>
+        <v>1.7</v>
       </c>
       <c r="J2">
-        <v>3.13</v>
+        <v>4.16</v>
       </c>
       <c r="K2">
-        <v>6.93</v>
+        <v>6.83</v>
       </c>
       <c r="L2">
-        <v>11.97</v>
+        <v>17.17</v>
       </c>
       <c r="M2">
-        <v>8.77</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N2">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>1124.7</v>
+        <v>1128.4</v>
       </c>
       <c r="Q2">
-        <v>1112.5</v>
+        <v>1114.98</v>
       </c>
       <c r="R2">
-        <v>1115.96</v>
+        <v>1116.76</v>
       </c>
       <c r="S2">
-        <v>940.33</v>
+        <v>941.28</v>
       </c>
       <c r="T2">
-        <v>17.69</v>
+        <v>17.47</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1003,34 +962,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>49</v>
+        <v>48.85</v>
       </c>
       <c r="Z2">
-        <v>10.64</v>
+        <v>8.35</v>
       </c>
       <c r="AA2">
-        <v>11.44</v>
+        <v>10.82</v>
       </c>
       <c r="AB2">
-        <v>-0.8</v>
+        <v>-2.47</v>
       </c>
       <c r="AC2">
-        <v>32.25</v>
+        <v>15.57</v>
       </c>
       <c r="AD2">
-        <v>36.45</v>
+        <v>29.81</v>
       </c>
       <c r="AE2">
-        <v>46.43</v>
+        <v>44.88</v>
       </c>
       <c r="AF2">
-        <v>-11.21</v>
+        <v>-56.06</v>
       </c>
       <c r="AG2">
-        <v>1193.45</v>
+        <v>1191.57</v>
       </c>
       <c r="AH2">
-        <v>1031.55</v>
+        <v>1038.4</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1039,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>31.13</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1050,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>878.5</v>
+        <v>865.05</v>
       </c>
       <c r="D3">
-        <v>0.11</v>
+        <v>-1.53</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1062,46 +1021,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-10.04</v>
+        <v>-11.41</v>
       </c>
       <c r="H3">
-        <v>65.92</v>
+        <v>63.38</v>
       </c>
       <c r="I3">
-        <v>-1.76</v>
+        <v>0.23</v>
       </c>
       <c r="J3">
-        <v>0.14</v>
+        <v>2.48</v>
       </c>
       <c r="K3">
-        <v>-6.02</v>
+        <v>-7.46</v>
       </c>
       <c r="L3">
-        <v>30.58</v>
+        <v>27.95</v>
       </c>
       <c r="M3">
-        <v>60.2</v>
+        <v>59.94</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O3">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P3">
-        <v>872.47</v>
+        <v>872.87</v>
       </c>
       <c r="Q3">
-        <v>872.8099999999999</v>
+        <v>874.59</v>
       </c>
       <c r="R3">
-        <v>903</v>
+        <v>901.48</v>
       </c>
       <c r="S3">
-        <v>769.71</v>
+        <v>770.37</v>
       </c>
       <c r="T3">
-        <v>14.13</v>
+        <v>12.29</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1116,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.63</v>
+        <v>44.78</v>
       </c>
       <c r="Z3">
-        <v>-4.05</v>
+        <v>-4.81</v>
       </c>
       <c r="AA3">
-        <v>-5.09</v>
+        <v>-5.03</v>
       </c>
       <c r="AB3">
-        <v>1.04</v>
+        <v>0.22</v>
       </c>
       <c r="AC3">
-        <v>37.53</v>
+        <v>36.38</v>
       </c>
       <c r="AD3">
-        <v>40.41</v>
+        <v>38.83</v>
       </c>
       <c r="AE3">
-        <v>21.02</v>
+        <v>20.77</v>
       </c>
       <c r="AF3">
-        <v>-48.35</v>
+        <v>-69.25</v>
       </c>
       <c r="AG3">
-        <v>914.6</v>
+        <v>911.35</v>
       </c>
       <c r="AH3">
-        <v>831.02</v>
+        <v>837.83</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1152,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>17.83</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1163,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1873</v>
+        <v>1868.1</v>
       </c>
       <c r="D4">
-        <v>1.42</v>
+        <v>-0.26</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1175,46 +1134,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-3.45</v>
+        <v>-3.71</v>
       </c>
       <c r="H4">
-        <v>38.26</v>
+        <v>37.9</v>
       </c>
       <c r="I4">
-        <v>0.27</v>
+        <v>-0.29</v>
       </c>
       <c r="J4">
-        <v>4.92</v>
+        <v>6.57</v>
       </c>
       <c r="K4">
-        <v>18.6</v>
+        <v>18.29</v>
       </c>
       <c r="L4">
-        <v>23.08</v>
+        <v>23.13</v>
       </c>
       <c r="M4">
-        <v>29.9</v>
+        <v>28.85</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P4">
-        <v>1869</v>
+        <v>1867.92</v>
       </c>
       <c r="Q4">
-        <v>1877.89</v>
+        <v>1881.15</v>
       </c>
       <c r="R4">
-        <v>1811.69</v>
+        <v>1815.45</v>
       </c>
       <c r="S4">
-        <v>1672.04</v>
+        <v>1672.87</v>
       </c>
       <c r="T4">
-        <v>12.02</v>
+        <v>11.67</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1229,43 +1188,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>53.65</v>
+        <v>52.85</v>
       </c>
       <c r="Z4">
-        <v>22.45</v>
+        <v>20.32</v>
       </c>
       <c r="AA4">
-        <v>32</v>
+        <v>29.67</v>
       </c>
       <c r="AB4">
-        <v>-9.550000000000001</v>
+        <v>-9.35</v>
       </c>
       <c r="AC4">
-        <v>6.91</v>
+        <v>14.68</v>
       </c>
       <c r="AD4">
-        <v>6.97</v>
+        <v>9.26</v>
       </c>
       <c r="AE4">
-        <v>45.18</v>
+        <v>46.02</v>
       </c>
       <c r="AF4">
-        <v>-70.55</v>
+        <v>-1.36</v>
       </c>
       <c r="AG4">
-        <v>1958.07</v>
+        <v>1953.41</v>
       </c>
       <c r="AH4">
-        <v>1797.7</v>
+        <v>1808.88</v>
       </c>
       <c r="AI4">
-        <v>1753.66</v>
+        <v>1758.5</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>20.69</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1276,58 +1235,58 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1913.6</v>
+        <v>1949.7</v>
       </c>
       <c r="D5">
-        <v>-0.67</v>
+        <v>1.89</v>
       </c>
       <c r="E5">
-        <v>2419.36</v>
+        <v>2413.39</v>
       </c>
       <c r="F5">
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-20.9</v>
+        <v>-19.21</v>
       </c>
       <c r="H5">
-        <v>9.619999999999999</v>
+        <v>11.69</v>
       </c>
       <c r="I5">
-        <v>-7.23</v>
+        <v>-4.34</v>
       </c>
       <c r="J5">
-        <v>-4.5</v>
+        <v>-3.8</v>
       </c>
       <c r="K5">
-        <v>4.47</v>
+        <v>6.44</v>
       </c>
       <c r="L5">
-        <v>-20.59</v>
+        <v>-19.41</v>
       </c>
       <c r="M5">
-        <v>20.88</v>
+        <v>21.49</v>
       </c>
       <c r="N5">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="O5">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P5">
-        <v>1975.84</v>
+        <v>1958.16</v>
       </c>
       <c r="Q5">
-        <v>2055.66</v>
+        <v>2051.26</v>
       </c>
       <c r="R5">
-        <v>2036.45</v>
+        <v>2034.25</v>
       </c>
       <c r="S5">
-        <v>2102.37</v>
+        <v>2101.43</v>
       </c>
       <c r="T5">
-        <v>-8.98</v>
+        <v>-7.22</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1342,34 +1301,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.1</v>
+        <v>37.69</v>
       </c>
       <c r="Z5">
-        <v>-17.35</v>
+        <v>-21.21</v>
       </c>
       <c r="AA5">
-        <v>4.38</v>
+        <v>-0.73</v>
       </c>
       <c r="AB5">
-        <v>-21.73</v>
+        <v>-20.48</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>8.77</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE5">
-        <v>48.83</v>
+        <v>51.34</v>
       </c>
       <c r="AF5">
-        <v>335.97</v>
+        <v>131.47</v>
       </c>
       <c r="AG5">
-        <v>2168.27</v>
+        <v>2173.31</v>
       </c>
       <c r="AH5">
-        <v>1943.04</v>
+        <v>1929.21</v>
       </c>
       <c r="AI5">
         <v>2060.59</v>
@@ -1378,7 +1337,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>34.24</v>
+        <v>33.73</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1389,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>810.4</v>
+        <v>796.35</v>
       </c>
       <c r="D6">
-        <v>-1.64</v>
+        <v>-1.73</v>
       </c>
       <c r="E6">
         <v>1178</v>
@@ -1401,46 +1360,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-31.21</v>
+        <v>-32.4</v>
       </c>
       <c r="H6">
-        <v>15.1</v>
+        <v>13.1</v>
       </c>
       <c r="I6">
-        <v>3.82</v>
+        <v>1.18</v>
       </c>
       <c r="J6">
-        <v>5.09</v>
+        <v>3.68</v>
       </c>
       <c r="K6">
-        <v>9.01</v>
+        <v>7.12</v>
       </c>
       <c r="L6">
-        <v>-29.88</v>
+        <v>-31.96</v>
       </c>
       <c r="M6">
-        <v>15.26</v>
+        <v>15.09</v>
       </c>
       <c r="N6">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="O6">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="P6">
-        <v>805.79</v>
+        <v>807.65</v>
       </c>
       <c r="Q6">
-        <v>791.65</v>
+        <v>792.52</v>
       </c>
       <c r="R6">
-        <v>763.24</v>
+        <v>764.47</v>
       </c>
       <c r="S6">
-        <v>861.4400000000001</v>
+        <v>860.3</v>
       </c>
       <c r="T6">
-        <v>-5.93</v>
+        <v>-7.43</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1455,34 +1414,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>57.25</v>
+        <v>52.83</v>
       </c>
       <c r="Z6">
-        <v>10.83</v>
+        <v>9.94</v>
       </c>
       <c r="AA6">
-        <v>9.23</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB6">
-        <v>1.6</v>
+        <v>0.57</v>
       </c>
       <c r="AC6">
-        <v>53.39</v>
+        <v>52.16</v>
       </c>
       <c r="AD6">
-        <v>47.76</v>
+        <v>52.68</v>
       </c>
       <c r="AE6">
-        <v>26.55</v>
+        <v>26.21</v>
       </c>
       <c r="AF6">
-        <v>33.3</v>
+        <v>-41.67</v>
       </c>
       <c r="AG6">
-        <v>828.4299999999999</v>
+        <v>828.86</v>
       </c>
       <c r="AH6">
-        <v>754.87</v>
+        <v>756.1900000000001</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1491,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>32.5</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1502,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3454.9</v>
+        <v>3386.6</v>
       </c>
       <c r="D7">
-        <v>0.4</v>
+        <v>-1.98</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1514,25 +1473,25 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-1.98</v>
       </c>
       <c r="H7">
-        <v>82.66</v>
+        <v>79.05</v>
       </c>
       <c r="I7">
-        <v>5.33</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="J7">
-        <v>33.24</v>
+        <v>31.66</v>
       </c>
       <c r="K7">
-        <v>32.2</v>
+        <v>29.59</v>
       </c>
       <c r="L7">
-        <v>23.93</v>
+        <v>21.77</v>
       </c>
       <c r="M7">
-        <v>34.56</v>
+        <v>34.52</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1541,19 +1500,19 @@
         <v>87</v>
       </c>
       <c r="P7">
-        <v>3308.54</v>
+        <v>3360.36</v>
       </c>
       <c r="Q7">
-        <v>2898.19</v>
+        <v>2940.31</v>
       </c>
       <c r="R7">
-        <v>2685.55</v>
+        <v>2702.18</v>
       </c>
       <c r="S7">
-        <v>2400.34</v>
+        <v>2405.6</v>
       </c>
       <c r="T7">
-        <v>43.93</v>
+        <v>40.78</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1568,34 +1527,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>78.84</v>
+        <v>73.48</v>
       </c>
       <c r="Z7">
-        <v>214.45</v>
+        <v>218.31</v>
       </c>
       <c r="AA7">
-        <v>151.85</v>
+        <v>165.14</v>
       </c>
       <c r="AB7">
-        <v>62.6</v>
+        <v>53.17</v>
       </c>
       <c r="AC7">
-        <v>80.95</v>
+        <v>78.44</v>
       </c>
       <c r="AD7">
-        <v>73.45</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="AE7">
-        <v>148.81</v>
+        <v>147.47</v>
       </c>
       <c r="AF7">
-        <v>14.9</v>
+        <v>-54.87</v>
       </c>
       <c r="AG7">
-        <v>3538.67</v>
+        <v>3593.45</v>
       </c>
       <c r="AH7">
-        <v>2257.72</v>
+        <v>2287.18</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1604,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>71.25</v>
+        <v>71.15000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1615,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8189</v>
+        <v>8148.5</v>
       </c>
       <c r="D8">
-        <v>-1.17</v>
+        <v>-0.49</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1627,22 +1586,22 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-19.97</v>
+        <v>-20.37</v>
       </c>
       <c r="H8">
-        <v>38.22</v>
+        <v>37.54</v>
       </c>
       <c r="I8">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="J8">
-        <v>-1.37</v>
+        <v>-1.82</v>
       </c>
       <c r="K8">
-        <v>17.47</v>
+        <v>16.89</v>
       </c>
       <c r="L8">
-        <v>-19.05</v>
+        <v>-20.37</v>
       </c>
       <c r="M8">
         <v>14.79</v>
@@ -1651,22 +1610,22 @@
         <v>43</v>
       </c>
       <c r="O8">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P8">
-        <v>8146.9</v>
+        <v>8183.1</v>
       </c>
       <c r="Q8">
-        <v>8092.48</v>
+        <v>8088.45</v>
       </c>
       <c r="R8">
-        <v>7945.12</v>
+        <v>7952.03</v>
       </c>
       <c r="S8">
-        <v>7403.51</v>
+        <v>7402.5</v>
       </c>
       <c r="T8">
-        <v>10.61</v>
+        <v>10.08</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1681,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.45</v>
+        <v>55.51</v>
       </c>
       <c r="Z8">
-        <v>77.47</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="AA8">
-        <v>71.81</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="AB8">
-        <v>5.66</v>
+        <v>3</v>
       </c>
       <c r="AC8">
-        <v>87.55</v>
+        <v>70.12</v>
       </c>
       <c r="AD8">
-        <v>76.45999999999999</v>
+        <v>81.17</v>
       </c>
       <c r="AE8">
-        <v>243.64</v>
+        <v>237.95</v>
       </c>
       <c r="AF8">
-        <v>-32.43</v>
+        <v>-15.67</v>
       </c>
       <c r="AG8">
-        <v>8303.68</v>
+        <v>8291.610000000001</v>
       </c>
       <c r="AH8">
-        <v>7881.27</v>
+        <v>7885.29</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1717,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>25.42</v>
+        <v>25.51</v>
       </c>
     </row>
   </sheetData>
@@ -1878,1097 +1837,1059 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3.13</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4.16</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.14</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4.92</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6.57</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-4.5</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-3.8</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5.09</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3.68</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>33.24</v>
+      </c>
+      <c r="D12" s="5">
+        <v>31.66</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.37</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-1.82</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.71</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1.7</v>
+      </c>
+      <c r="E14" s="6">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-1.76</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.29</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-7.23</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-4.34</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>5.33</v>
+      </c>
+      <c r="D19" s="5">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="D20" s="5">
+        <v>2.27</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>11.97</v>
+      </c>
+      <c r="D21" s="5">
+        <v>17.17</v>
+      </c>
+      <c r="E21" s="6">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>30.58</v>
+      </c>
+      <c r="D22" s="5">
+        <v>27.95</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>23.08</v>
+      </c>
+      <c r="D23" s="5">
+        <v>23.13</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-20.59</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-19.41</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-29.88</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-31.96</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>23.93</v>
+      </c>
+      <c r="D26" s="5">
+        <v>21.77</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-19.05</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-20.37</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>6.93</v>
+      </c>
+      <c r="D28" s="5">
+        <v>6.83</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-6.02</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-7.46</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>18.6</v>
+      </c>
+      <c r="D30" s="5">
+        <v>18.29</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>4.47</v>
+      </c>
+      <c r="D31" s="5">
+        <v>6.44</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>9.01</v>
+      </c>
+      <c r="D32" s="5">
+        <v>7.12</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>32.2</v>
+      </c>
+      <c r="D33" s="5">
+        <v>29.59</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>17.47</v>
+      </c>
+      <c r="D34" s="5">
+        <v>16.89</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-10.87</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-10.95</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-10.04</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-11.41</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-3.45</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-3.71</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-20.9</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-19.21</v>
+      </c>
+      <c r="E38" s="6">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-31.21</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-32.4</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="D40" s="5">
+        <v>-1.98</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-19.97</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-20.37</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>5.44</v>
-      </c>
-      <c r="D8" s="7">
-        <v>3.13</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1106.7</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1105.7</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1.13</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0.14</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>878.5</v>
+      </c>
+      <c r="D43" s="5">
+        <v>865.05</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-13.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>7.09</v>
-      </c>
-      <c r="D10" s="7">
-        <v>4.92</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1873</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1868.1</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-2.74</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1913.6</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1949.7</v>
+      </c>
+      <c r="E45" s="6">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="D12" s="7">
-        <v>5.09</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-3.61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>810.4</v>
+      </c>
+      <c r="D46" s="5">
+        <v>796.35</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-14.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>34.09</v>
-      </c>
-      <c r="D13" s="7">
-        <v>33.24</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>3454.9</v>
+      </c>
+      <c r="D47" s="5">
+        <v>3386.6</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-68.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>2.62</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-1.37</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-3.99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>8189</v>
+      </c>
+      <c r="D48" s="5">
+        <v>8148.5</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-40.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-0.04</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-1.71</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>57</v>
+      </c>
+      <c r="D49" s="5">
+        <v>71</v>
+      </c>
+      <c r="E49" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-2.37</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-1.76</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5">
+        <v>71</v>
+      </c>
+      <c r="D50" s="5">
+        <v>57</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="5">
+        <v>15</v>
+      </c>
+      <c r="D51" s="5">
+        <v>29</v>
+      </c>
+      <c r="E51" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="5">
+        <v>29</v>
+      </c>
+      <c r="D52" s="5">
+        <v>15</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>49</v>
+      </c>
+      <c r="D53" s="5">
+        <v>48.85</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>48.63</v>
+      </c>
+      <c r="D54" s="5">
+        <v>44.78</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-2.52</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0.27</v>
-      </c>
-      <c r="E17" s="9">
-        <v>2.79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>53.65</v>
+      </c>
+      <c r="D55" s="5">
+        <v>52.85</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-7.23</v>
-      </c>
-      <c r="E18" s="9">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>30.1</v>
+      </c>
+      <c r="D56" s="5">
+        <v>37.69</v>
+      </c>
+      <c r="E56" s="6">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>4.03</v>
-      </c>
-      <c r="D19" s="7">
-        <v>3.82</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>57.25</v>
+      </c>
+      <c r="D57" s="5">
+        <v>52.83</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-4.42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>11.11</v>
-      </c>
-      <c r="D20" s="7">
-        <v>5.33</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-5.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>78.84</v>
+      </c>
+      <c r="D58" s="5">
+        <v>73.48</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-5.36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>4.46</v>
-      </c>
-      <c r="D21" s="7">
-        <v>1.66</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>57.45</v>
+      </c>
+      <c r="D59" s="5">
+        <v>55.51</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>29.22</v>
-      </c>
-      <c r="D22" s="7">
-        <v>11.97</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-17.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-11.21</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-56.06</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-44.85</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>29.94</v>
-      </c>
-      <c r="D23" s="7">
-        <v>30.58</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-48.35</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-69.25</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-20.9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>20.96</v>
-      </c>
-      <c r="D24" s="7">
-        <v>23.08</v>
-      </c>
-      <c r="E24" s="9">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
+        <v>-70.55</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-1.36</v>
+      </c>
+      <c r="E62" s="6">
+        <v>69.19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-18.81</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-20.59</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>335.97</v>
+      </c>
+      <c r="D63" s="5">
+        <v>131.47</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-204.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-28.09</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-29.88</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>33.3</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-41.67</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-74.97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>26.13</v>
-      </c>
-      <c r="D27" s="7">
-        <v>23.93</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>14.9</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-54.87</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-69.77</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-17.06</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-19.05</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>7.56</v>
-      </c>
-      <c r="D29" s="7">
-        <v>6.93</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-0.19</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-6.02</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-5.83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>17.83</v>
-      </c>
-      <c r="D31" s="7">
-        <v>18.6</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>4.32</v>
-      </c>
-      <c r="D32" s="7">
-        <v>4.47</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>7.77</v>
-      </c>
-      <c r="D33" s="7">
-        <v>9.01</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>32.02</v>
-      </c>
-      <c r="D34" s="7">
-        <v>32.2</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>18.04</v>
-      </c>
-      <c r="D35" s="7">
-        <v>17.47</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-9.619999999999999</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-10.87</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-10.14</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-10.04</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-4.81</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-3.45</v>
-      </c>
-      <c r="E38" s="9">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-20.37</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-20.9</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-30.06</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-31.21</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-19.03</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-19.97</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="7">
-        <v>1122.2</v>
-      </c>
-      <c r="D42" s="7">
-        <v>1106.7</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-15.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>877.5</v>
-      </c>
-      <c r="D43" s="7">
-        <v>878.5</v>
-      </c>
-      <c r="E43" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>1846.7</v>
-      </c>
-      <c r="D44" s="7">
-        <v>1873</v>
-      </c>
-      <c r="E44" s="9">
-        <v>26.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>1926.6</v>
-      </c>
-      <c r="D45" s="7">
-        <v>1913.6</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>823.95</v>
-      </c>
-      <c r="D46" s="7">
-        <v>810.4</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-13.55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>3441.3</v>
-      </c>
-      <c r="D47" s="7">
-        <v>3454.9</v>
-      </c>
-      <c r="E47" s="9">
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>8286</v>
-      </c>
-      <c r="D48" s="7">
-        <v>8189</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="7">
-        <v>71</v>
-      </c>
-      <c r="D49" s="7">
-        <v>57</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="7">
-        <v>57</v>
-      </c>
-      <c r="D50" s="7">
-        <v>71</v>
-      </c>
-      <c r="E50" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="7">
-        <v>29</v>
-      </c>
-      <c r="D51" s="7">
-        <v>15</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="7">
-        <v>15</v>
-      </c>
-      <c r="D52" s="7">
-        <v>29</v>
-      </c>
-      <c r="E52" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>51.27</v>
-      </c>
-      <c r="D53" s="7">
-        <v>49</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>48.32</v>
-      </c>
-      <c r="D54" s="7">
-        <v>48.63</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>49.86</v>
-      </c>
-      <c r="D55" s="7">
-        <v>53.65</v>
-      </c>
-      <c r="E55" s="9">
-        <v>3.79</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>31.38</v>
-      </c>
-      <c r="D56" s="7">
-        <v>30.1</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>61.88</v>
-      </c>
-      <c r="D57" s="7">
-        <v>57.25</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-4.63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>78.55</v>
-      </c>
-      <c r="D58" s="7">
-        <v>78.84</v>
-      </c>
-      <c r="E58" s="9">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>62.3</v>
-      </c>
-      <c r="D59" s="7">
-        <v>57.45</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-4.85</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="B66" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="7">
-        <v>-2.48</v>
-      </c>
-      <c r="D60" s="7">
-        <v>-11.21</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-8.73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-63.5</v>
-      </c>
-      <c r="D61" s="7">
-        <v>-48.35</v>
-      </c>
-      <c r="E61" s="9">
-        <v>15.15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-43.86</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-70.55</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-26.69</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>203.78</v>
-      </c>
-      <c r="D63" s="7">
-        <v>335.97</v>
-      </c>
-      <c r="E63" s="9">
-        <v>132.19</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>973.67</v>
-      </c>
-      <c r="D64" s="7">
-        <v>33.3</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-940.37</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-10.72</v>
-      </c>
-      <c r="D65" s="7">
-        <v>14.9</v>
-      </c>
-      <c r="E65" s="9">
-        <v>25.62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>356.6</v>
-      </c>
-      <c r="D66" s="7">
+      <c r="C66" s="5">
         <v>-32.43</v>
       </c>
-      <c r="E66" s="8">
-        <v>-389.03</v>
+      <c r="D66" s="5">
+        <v>-15.67</v>
+      </c>
+      <c r="E66" s="6">
+        <v>16.76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2988,60 +2909,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="11">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>52.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="12">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="13">
-        <v>7</v>
-      </c>
-      <c r="D2" s="12">
-        <v>53.6</v>
-      </c>
-      <c r="E2" s="12">
-        <v>70</v>
-      </c>
-      <c r="F2" s="12">
-        <v>5.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>11.8</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>6.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>11.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -3143,49 +3064,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.602</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3456</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.299</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2088</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1526</v>
-      </c>
-      <c r="F2" s="15">
+      <c r="A2" s="13">
+        <v>0.5993999999999999</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3452</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2885</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.2149</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1509</v>
+      </c>
+      <c r="F2" s="13">
         <v>0.1479</v>
       </c>
-      <c r="G2" s="15">
-        <v>0.0877</v>
+      <c r="G2" s="13">
+        <v>0.0814</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="85">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,12 +157,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -172,7 +172,70 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>44.8 → 54.3</t>
+  </si>
+  <si>
+    <t>44.8</t>
+  </si>
+  <si>
+    <t>54.3</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>73.5 → 69.2</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>73.5</t>
+  </si>
+  <si>
+    <t>69.2</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-2.0% → -3.7%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-2.0%</t>
+  </si>
+  <si>
+    <t>-3.7%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -224,7 +287,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -265,13 +328,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,6 +369,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,21 +450,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -397,7 +475,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -896,10 +974,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1105.7</v>
+        <v>1103.2</v>
       </c>
       <c r="D2">
-        <v>-0.09</v>
+        <v>-0.23</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -908,88 +986,88 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-10.95</v>
+        <v>-11.15</v>
       </c>
       <c r="H2">
-        <v>47.75</v>
+        <v>47.42</v>
       </c>
       <c r="I2">
-        <v>1.7</v>
+        <v>-3.02</v>
       </c>
       <c r="J2">
-        <v>4.16</v>
+        <v>4.47</v>
       </c>
       <c r="K2">
-        <v>6.83</v>
+        <v>7.21</v>
       </c>
       <c r="L2">
-        <v>17.17</v>
+        <v>19.28</v>
       </c>
       <c r="M2">
-        <v>8.140000000000001</v>
+        <v>7.44</v>
       </c>
       <c r="N2">
+        <v>57</v>
+      </c>
+      <c r="O2">
         <v>71</v>
       </c>
-      <c r="O2">
-        <v>69</v>
-      </c>
       <c r="P2">
-        <v>1128.4</v>
+        <v>1121.52</v>
       </c>
       <c r="Q2">
-        <v>1114.98</v>
+        <v>1117.59</v>
       </c>
       <c r="R2">
-        <v>1116.76</v>
+        <v>1116.22</v>
       </c>
       <c r="S2">
-        <v>941.28</v>
+        <v>942.25</v>
       </c>
       <c r="T2">
-        <v>17.47</v>
+        <v>17.08</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
       </c>
       <c r="V2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
         <v>45</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.85</v>
+        <v>48.44</v>
       </c>
       <c r="Z2">
-        <v>8.35</v>
+        <v>6.27</v>
       </c>
       <c r="AA2">
-        <v>10.82</v>
+        <v>9.91</v>
       </c>
       <c r="AB2">
-        <v>-2.47</v>
+        <v>-3.64</v>
       </c>
       <c r="AC2">
-        <v>15.57</v>
+        <v>10.97</v>
       </c>
       <c r="AD2">
-        <v>29.81</v>
+        <v>19.59</v>
       </c>
       <c r="AE2">
-        <v>44.88</v>
+        <v>43.05</v>
       </c>
       <c r="AF2">
-        <v>-56.06</v>
+        <v>-43.2</v>
       </c>
       <c r="AG2">
-        <v>1191.57</v>
+        <v>1188.33</v>
       </c>
       <c r="AH2">
-        <v>1038.4</v>
+        <v>1046.86</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -998,7 +1076,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>29.48</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1087,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>865.05</v>
+        <v>897.9</v>
       </c>
       <c r="D3">
-        <v>-1.53</v>
+        <v>3.8</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1021,88 +1099,88 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-11.41</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="H3">
-        <v>63.38</v>
+        <v>69.58</v>
       </c>
       <c r="I3">
-        <v>0.23</v>
+        <v>2.46</v>
       </c>
       <c r="J3">
-        <v>2.48</v>
+        <v>8.25</v>
       </c>
       <c r="K3">
-        <v>-7.46</v>
+        <v>-2.13</v>
       </c>
       <c r="L3">
-        <v>27.95</v>
+        <v>32.37</v>
       </c>
       <c r="M3">
-        <v>59.94</v>
+        <v>61</v>
       </c>
       <c r="N3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O3">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>872.87</v>
+        <v>877.1900000000001</v>
       </c>
       <c r="Q3">
-        <v>874.59</v>
+        <v>877.85</v>
       </c>
       <c r="R3">
-        <v>901.48</v>
+        <v>900.17</v>
       </c>
       <c r="S3">
-        <v>770.37</v>
+        <v>771.1799999999999</v>
       </c>
       <c r="T3">
-        <v>12.29</v>
+        <v>16.43</v>
       </c>
       <c r="U3" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" t="s">
         <v>45</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>46</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
       </c>
       <c r="X3">
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.78</v>
+        <v>54.29</v>
       </c>
       <c r="Z3">
-        <v>-4.81</v>
+        <v>-2.74</v>
       </c>
       <c r="AA3">
-        <v>-5.03</v>
+        <v>-4.57</v>
       </c>
       <c r="AB3">
-        <v>0.22</v>
+        <v>1.83</v>
       </c>
       <c r="AC3">
-        <v>36.38</v>
+        <v>54.05</v>
       </c>
       <c r="AD3">
-        <v>38.83</v>
+        <v>42.66</v>
       </c>
       <c r="AE3">
-        <v>20.77</v>
+        <v>21.69</v>
       </c>
       <c r="AF3">
-        <v>-69.25</v>
+        <v>102.83</v>
       </c>
       <c r="AG3">
-        <v>911.35</v>
+        <v>910.25</v>
       </c>
       <c r="AH3">
-        <v>837.83</v>
+        <v>845.46</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1111,7 +1189,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>17.09</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1200,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1868.1</v>
+        <v>1875.4</v>
       </c>
       <c r="D4">
-        <v>-0.26</v>
+        <v>0.39</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1134,88 +1212,88 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-3.71</v>
+        <v>-3.33</v>
       </c>
       <c r="H4">
-        <v>37.9</v>
+        <v>38.44</v>
       </c>
       <c r="I4">
-        <v>-0.29</v>
+        <v>-0.71</v>
       </c>
       <c r="J4">
-        <v>6.57</v>
+        <v>4.02</v>
       </c>
       <c r="K4">
-        <v>18.29</v>
+        <v>21.96</v>
       </c>
       <c r="L4">
-        <v>23.13</v>
+        <v>23.14</v>
       </c>
       <c r="M4">
-        <v>28.85</v>
+        <v>29.24</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P4">
-        <v>1867.92</v>
+        <v>1865.22</v>
       </c>
       <c r="Q4">
-        <v>1881.15</v>
+        <v>1886.22</v>
       </c>
       <c r="R4">
-        <v>1815.45</v>
+        <v>1819.37</v>
       </c>
       <c r="S4">
-        <v>1672.87</v>
+        <v>1673.48</v>
       </c>
       <c r="T4">
-        <v>11.67</v>
+        <v>12.07</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X4">
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>52.85</v>
+        <v>53.95</v>
       </c>
       <c r="Z4">
-        <v>20.32</v>
+        <v>19</v>
       </c>
       <c r="AA4">
-        <v>29.67</v>
+        <v>27.53</v>
       </c>
       <c r="AB4">
-        <v>-9.35</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="AC4">
-        <v>14.68</v>
+        <v>25.31</v>
       </c>
       <c r="AD4">
-        <v>9.26</v>
+        <v>15.63</v>
       </c>
       <c r="AE4">
-        <v>46.02</v>
+        <v>44.94</v>
       </c>
       <c r="AF4">
-        <v>-1.36</v>
+        <v>-26.01</v>
       </c>
       <c r="AG4">
-        <v>1953.41</v>
+        <v>1938.13</v>
       </c>
       <c r="AH4">
-        <v>1808.88</v>
+        <v>1834.32</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1224,7 +1302,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>20.07</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,100 +1313,100 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1949.7</v>
+        <v>1928.4</v>
       </c>
       <c r="D5">
-        <v>1.89</v>
+        <v>-1.09</v>
       </c>
       <c r="E5">
-        <v>2413.39</v>
+        <v>2398.74</v>
       </c>
       <c r="F5">
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.21</v>
+        <v>-19.61</v>
       </c>
       <c r="H5">
-        <v>11.69</v>
+        <v>10.47</v>
       </c>
       <c r="I5">
-        <v>-4.34</v>
+        <v>-3.81</v>
       </c>
       <c r="J5">
-        <v>-3.8</v>
+        <v>-5.36</v>
       </c>
       <c r="K5">
-        <v>6.44</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L5">
-        <v>-19.41</v>
+        <v>-20.1</v>
       </c>
       <c r="M5">
-        <v>21.49</v>
+        <v>21.26</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>1958.16</v>
+        <v>1942.88</v>
       </c>
       <c r="Q5">
-        <v>2051.26</v>
+        <v>2044.97</v>
       </c>
       <c r="R5">
-        <v>2034.25</v>
+        <v>2032.1</v>
       </c>
       <c r="S5">
-        <v>2101.43</v>
+        <v>2100.28</v>
       </c>
       <c r="T5">
-        <v>-7.22</v>
+        <v>-8.18</v>
       </c>
       <c r="U5" t="s">
+        <v>45</v>
+      </c>
+      <c r="V5" t="s">
         <v>46</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
       <c r="W5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>37.69</v>
+        <v>35.26</v>
       </c>
       <c r="Z5">
-        <v>-21.21</v>
+        <v>-25.69</v>
       </c>
       <c r="AA5">
-        <v>-0.73</v>
+        <v>-5.73</v>
       </c>
       <c r="AB5">
-        <v>-20.48</v>
+        <v>-19.97</v>
       </c>
       <c r="AC5">
-        <v>8.77</v>
+        <v>14.73</v>
       </c>
       <c r="AD5">
-        <v>2.92</v>
+        <v>7.83</v>
       </c>
       <c r="AE5">
-        <v>51.34</v>
+        <v>50.55</v>
       </c>
       <c r="AF5">
-        <v>131.47</v>
+        <v>-10.9</v>
       </c>
       <c r="AG5">
-        <v>2173.31</v>
+        <v>2178.78</v>
       </c>
       <c r="AH5">
-        <v>1929.21</v>
+        <v>1911.16</v>
       </c>
       <c r="AI5">
         <v>2060.59</v>
@@ -1337,7 +1415,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>33.73</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,100 +1426,100 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>796.35</v>
+        <v>795.3</v>
       </c>
       <c r="D6">
-        <v>-1.73</v>
+        <v>-0.13</v>
       </c>
       <c r="E6">
-        <v>1178</v>
+        <v>1175.4</v>
       </c>
       <c r="F6">
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-32.4</v>
+        <v>-32.34</v>
       </c>
       <c r="H6">
-        <v>13.1</v>
+        <v>12.95</v>
       </c>
       <c r="I6">
-        <v>1.18</v>
+        <v>-1.85</v>
       </c>
       <c r="J6">
-        <v>3.68</v>
+        <v>2.11</v>
       </c>
       <c r="K6">
-        <v>7.12</v>
+        <v>5.28</v>
       </c>
       <c r="L6">
-        <v>-31.96</v>
+        <v>-32.49</v>
       </c>
       <c r="M6">
-        <v>15.09</v>
+        <v>15.41</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P6">
-        <v>807.65</v>
+        <v>804.66</v>
       </c>
       <c r="Q6">
-        <v>792.52</v>
+        <v>794.13</v>
       </c>
       <c r="R6">
-        <v>764.47</v>
+        <v>765.72</v>
       </c>
       <c r="S6">
-        <v>860.3</v>
+        <v>859.15</v>
       </c>
       <c r="T6">
         <v>-7.43</v>
       </c>
       <c r="U6" t="s">
+        <v>45</v>
+      </c>
+      <c r="V6" t="s">
         <v>46</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
       <c r="W6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>52.83</v>
+        <v>52.5</v>
       </c>
       <c r="Z6">
-        <v>9.94</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AA6">
-        <v>9.380000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="AB6">
-        <v>0.57</v>
+        <v>-0.26</v>
       </c>
       <c r="AC6">
-        <v>52.16</v>
+        <v>38.33</v>
       </c>
       <c r="AD6">
-        <v>52.68</v>
+        <v>47.96</v>
       </c>
       <c r="AE6">
-        <v>26.21</v>
+        <v>25.72</v>
       </c>
       <c r="AF6">
-        <v>-41.67</v>
+        <v>-57.6</v>
       </c>
       <c r="AG6">
-        <v>828.86</v>
+        <v>827.74</v>
       </c>
       <c r="AH6">
-        <v>756.1900000000001</v>
+        <v>760.51</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1450,7 +1528,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>34.52</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1539,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3386.6</v>
+        <v>3328.1</v>
       </c>
       <c r="D7">
-        <v>-1.98</v>
+        <v>-1.73</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1473,88 +1551,88 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-1.98</v>
+        <v>-3.67</v>
       </c>
       <c r="H7">
-        <v>79.05</v>
+        <v>75.95</v>
       </c>
       <c r="I7">
-        <v>8.279999999999999</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>31.66</v>
+        <v>30.81</v>
       </c>
       <c r="K7">
-        <v>29.59</v>
+        <v>36.09</v>
       </c>
       <c r="L7">
-        <v>21.77</v>
+        <v>21.42</v>
       </c>
       <c r="M7">
-        <v>34.52</v>
+        <v>33.22</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P7">
-        <v>3360.36</v>
+        <v>3385.94</v>
       </c>
       <c r="Q7">
-        <v>2940.31</v>
+        <v>2978.9</v>
       </c>
       <c r="R7">
-        <v>2702.18</v>
+        <v>2718.6</v>
       </c>
       <c r="S7">
-        <v>2405.6</v>
+        <v>2410.6</v>
       </c>
       <c r="T7">
-        <v>40.78</v>
+        <v>38.06</v>
       </c>
       <c r="U7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X7">
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>73.48</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="Z7">
-        <v>218.31</v>
+        <v>214.18</v>
       </c>
       <c r="AA7">
-        <v>165.14</v>
+        <v>174.95</v>
       </c>
       <c r="AB7">
-        <v>53.17</v>
+        <v>39.23</v>
       </c>
       <c r="AC7">
-        <v>78.44</v>
+        <v>68.19</v>
       </c>
       <c r="AD7">
-        <v>77.84999999999999</v>
+        <v>75.86</v>
       </c>
       <c r="AE7">
-        <v>147.47</v>
+        <v>145.83</v>
       </c>
       <c r="AF7">
-        <v>-54.87</v>
+        <v>-69.88</v>
       </c>
       <c r="AG7">
-        <v>3593.45</v>
+        <v>3627.69</v>
       </c>
       <c r="AH7">
-        <v>2287.18</v>
+        <v>2330.12</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1563,7 +1641,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>71.15000000000001</v>
+        <v>69.25</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1652,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8148.5</v>
+        <v>8376</v>
       </c>
       <c r="D8">
-        <v>-0.49</v>
+        <v>2.79</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1586,88 +1664,88 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-20.37</v>
+        <v>-18.15</v>
       </c>
       <c r="H8">
-        <v>37.54</v>
+        <v>41.38</v>
       </c>
       <c r="I8">
-        <v>2.27</v>
+        <v>3.29</v>
       </c>
       <c r="J8">
-        <v>-1.82</v>
+        <v>1.79</v>
       </c>
       <c r="K8">
-        <v>16.89</v>
+        <v>21.78</v>
       </c>
       <c r="L8">
-        <v>-20.37</v>
+        <v>-16.84</v>
       </c>
       <c r="M8">
-        <v>14.79</v>
+        <v>15.1</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="P8">
-        <v>8183.1</v>
+        <v>8236.4</v>
       </c>
       <c r="Q8">
-        <v>8088.45</v>
+        <v>8102.05</v>
       </c>
       <c r="R8">
-        <v>7952.03</v>
+        <v>7961.96</v>
       </c>
       <c r="S8">
-        <v>7402.5</v>
+        <v>7402.61</v>
       </c>
       <c r="T8">
-        <v>10.08</v>
+        <v>13.15</v>
       </c>
       <c r="U8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X8">
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>55.51</v>
+        <v>63.07</v>
       </c>
       <c r="Z8">
-        <v>75.56999999999999</v>
+        <v>91.36</v>
       </c>
       <c r="AA8">
-        <v>72.56999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="AB8">
-        <v>3</v>
+        <v>15.04</v>
       </c>
       <c r="AC8">
         <v>70.12</v>
       </c>
       <c r="AD8">
-        <v>81.17</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="AE8">
-        <v>237.95</v>
+        <v>248.85</v>
       </c>
       <c r="AF8">
-        <v>-15.67</v>
+        <v>120.49</v>
       </c>
       <c r="AG8">
-        <v>8291.610000000001</v>
+        <v>8342.58</v>
       </c>
       <c r="AH8">
-        <v>7885.29</v>
+        <v>7861.52</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1676,7 +1754,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>25.51</v>
+        <v>28.5</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,1059 +1915,1140 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>3.13</v>
-      </c>
-      <c r="D7" s="5">
-        <v>4.16</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.14</v>
-      </c>
-      <c r="D8" s="5">
-        <v>2.48</v>
-      </c>
-      <c r="E8" s="6">
-        <v>2.34</v>
+      <c r="A7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>4.92</v>
-      </c>
-      <c r="D9" s="5">
-        <v>6.57</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1.65</v>
-      </c>
+      <c r="A9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>4.16</v>
+      </c>
+      <c r="D11" s="7">
+        <v>4.47</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2.48</v>
+      </c>
+      <c r="D12" s="7">
+        <v>8.25</v>
+      </c>
+      <c r="E12" s="8">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>6.57</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4.02</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-4.5</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C14" s="7">
         <v>-3.8</v>
       </c>
-      <c r="E10" s="6">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D14" s="7">
+        <v>-5.36</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>5.09</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C15" s="7">
         <v>3.68</v>
       </c>
-      <c r="E11" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D15" s="7">
+        <v>2.11</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>33.24</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C16" s="7">
         <v>31.66</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D16" s="7">
+        <v>30.81</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-1.37</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C17" s="7">
         <v>-1.82</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D17" s="7">
+        <v>1.79</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-1.71</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C18" s="7">
         <v>1.7</v>
       </c>
-      <c r="E14" s="6">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D18" s="7">
+        <v>-3.02</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-4.72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-1.76</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C19" s="7">
         <v>0.23</v>
       </c>
-      <c r="E15" s="6">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D19" s="7">
+        <v>2.46</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>0.27</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C20" s="7">
         <v>-0.29</v>
       </c>
-      <c r="E16" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D20" s="7">
+        <v>-0.71</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-7.23</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C21" s="7">
         <v>-4.34</v>
       </c>
-      <c r="E17" s="6">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D21" s="7">
+        <v>-3.81</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C22" s="7">
         <v>1.18</v>
       </c>
-      <c r="E18" s="7">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D22" s="7">
+        <v>-1.85</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C23" s="7">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="D23" s="7">
+        <v>4</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-4.28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2.27</v>
+      </c>
+      <c r="D24" s="7">
+        <v>3.29</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>17.17</v>
+      </c>
+      <c r="D25" s="7">
+        <v>19.28</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>27.95</v>
+      </c>
+      <c r="D26" s="7">
+        <v>32.37</v>
+      </c>
+      <c r="E26" s="8">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>23.13</v>
+      </c>
+      <c r="D27" s="7">
+        <v>23.14</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-19.41</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-20.1</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-31.96</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-32.49</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>21.77</v>
+      </c>
+      <c r="D30" s="7">
+        <v>21.42</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-20.37</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-16.84</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>6.83</v>
+      </c>
+      <c r="D32" s="7">
+        <v>7.21</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-7.46</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-2.13</v>
+      </c>
+      <c r="E33" s="8">
         <v>5.33</v>
       </c>
-      <c r="D19" s="5">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="E19" s="6">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>18.29</v>
+      </c>
+      <c r="D34" s="7">
+        <v>21.96</v>
+      </c>
+      <c r="E34" s="8">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>6.44</v>
+      </c>
+      <c r="D35" s="7">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E35" s="8">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>7.12</v>
+      </c>
+      <c r="D36" s="7">
+        <v>5.28</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>29.59</v>
+      </c>
+      <c r="D37" s="7">
+        <v>36.09</v>
+      </c>
+      <c r="E37" s="8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1.66</v>
-      </c>
-      <c r="D20" s="5">
-        <v>2.27</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>16.89</v>
+      </c>
+      <c r="D38" s="7">
+        <v>21.78</v>
+      </c>
+      <c r="E38" s="8">
+        <v>4.89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>11.97</v>
-      </c>
-      <c r="D21" s="5">
-        <v>17.17</v>
-      </c>
-      <c r="E21" s="6">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-10.95</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-11.15</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>30.58</v>
-      </c>
-      <c r="D22" s="5">
-        <v>27.95</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-11.41</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="E40" s="8">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>23.08</v>
-      </c>
-      <c r="D23" s="5">
-        <v>23.13</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-3.71</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-3.33</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-20.59</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-19.41</v>
-      </c>
-      <c r="E24" s="6">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-19.21</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-19.61</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-29.88</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-31.96</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-32.4</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-32.34</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>23.93</v>
-      </c>
-      <c r="D26" s="5">
-        <v>21.77</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-1.98</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-3.67</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-19.05</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
         <v>-20.37</v>
       </c>
-      <c r="E27" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D45" s="7">
+        <v>-18.15</v>
+      </c>
+      <c r="E45" s="8">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>6.93</v>
-      </c>
-      <c r="D28" s="5">
-        <v>6.83</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1105.7</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1103.2</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-7.46</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>865.05</v>
+      </c>
+      <c r="D47" s="7">
+        <v>897.9</v>
+      </c>
+      <c r="E47" s="8">
+        <v>32.85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>18.6</v>
-      </c>
-      <c r="D30" s="5">
-        <v>18.29</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>1868.1</v>
+      </c>
+      <c r="D48" s="7">
+        <v>1875.4</v>
+      </c>
+      <c r="E48" s="8">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>4.47</v>
-      </c>
-      <c r="D31" s="5">
-        <v>6.44</v>
-      </c>
-      <c r="E31" s="6">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>1949.7</v>
+      </c>
+      <c r="D49" s="7">
+        <v>1928.4</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-21.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>9.01</v>
-      </c>
-      <c r="D32" s="5">
-        <v>7.12</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>796.35</v>
+      </c>
+      <c r="D50" s="7">
+        <v>795.3</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>32.2</v>
-      </c>
-      <c r="D33" s="5">
-        <v>29.59</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>3386.6</v>
+      </c>
+      <c r="D51" s="7">
+        <v>3328.1</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-58.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>17.47</v>
-      </c>
-      <c r="D34" s="5">
-        <v>16.89</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7">
+        <v>8148.5</v>
+      </c>
+      <c r="D52" s="7">
+        <v>8376</v>
+      </c>
+      <c r="E52" s="8">
+        <v>227.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-10.87</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-10.95</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="7">
+        <v>71</v>
+      </c>
+      <c r="D53" s="7">
+        <v>57</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-10.04</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-11.41</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="7">
+        <v>57</v>
+      </c>
+      <c r="D54" s="7">
+        <v>71</v>
+      </c>
+      <c r="E54" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>48.85</v>
+      </c>
+      <c r="D55" s="7">
+        <v>48.44</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>44.78</v>
+      </c>
+      <c r="D56" s="7">
+        <v>54.29</v>
+      </c>
+      <c r="E56" s="8">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-3.45</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-3.71</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>52.85</v>
+      </c>
+      <c r="D57" s="7">
+        <v>53.95</v>
+      </c>
+      <c r="E57" s="8">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-20.9</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-19.21</v>
-      </c>
-      <c r="E38" s="6">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>37.69</v>
+      </c>
+      <c r="D58" s="7">
+        <v>35.26</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-31.21</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-32.4</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>52.83</v>
+      </c>
+      <c r="D59" s="7">
+        <v>52.5</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>0</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-1.98</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>73.48</v>
+      </c>
+      <c r="D60" s="7">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-4.33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-19.97</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-20.37</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="7">
+        <v>55.51</v>
+      </c>
+      <c r="D61" s="7">
+        <v>63.07</v>
+      </c>
+      <c r="E61" s="8">
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1106.7</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1105.7</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-56.06</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-43.2</v>
+      </c>
+      <c r="E62" s="8">
+        <v>12.86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>878.5</v>
-      </c>
-      <c r="D43" s="5">
-        <v>865.05</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-13.45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-69.25</v>
+      </c>
+      <c r="D63" s="7">
+        <v>102.83</v>
+      </c>
+      <c r="E63" s="8">
+        <v>172.08</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1873</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1868.1</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-1.36</v>
+      </c>
+      <c r="D64" s="7">
+        <v>-26.01</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-24.65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1913.6</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1949.7</v>
-      </c>
-      <c r="E45" s="6">
-        <v>36.1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>131.47</v>
+      </c>
+      <c r="D65" s="7">
+        <v>-10.9</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-142.37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>810.4</v>
-      </c>
-      <c r="D46" s="5">
-        <v>796.35</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-14.05</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="7">
+        <v>-41.67</v>
+      </c>
+      <c r="D66" s="7">
+        <v>-57.6</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-15.93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>3454.9</v>
-      </c>
-      <c r="D47" s="5">
-        <v>3386.6</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-68.3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="7">
+        <v>-54.87</v>
+      </c>
+      <c r="D67" s="7">
+        <v>-69.88</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-15.01</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>8189</v>
-      </c>
-      <c r="D48" s="5">
-        <v>8148.5</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-40.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5">
-        <v>57</v>
-      </c>
-      <c r="D49" s="5">
-        <v>71</v>
-      </c>
-      <c r="E49" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5">
-        <v>71</v>
-      </c>
-      <c r="D50" s="5">
-        <v>57</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="5">
-        <v>15</v>
-      </c>
-      <c r="D51" s="5">
-        <v>29</v>
-      </c>
-      <c r="E51" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="5">
-        <v>29</v>
-      </c>
-      <c r="D52" s="5">
-        <v>15</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>49</v>
-      </c>
-      <c r="D53" s="5">
-        <v>48.85</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>48.63</v>
-      </c>
-      <c r="D54" s="5">
-        <v>44.78</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>53.65</v>
-      </c>
-      <c r="D55" s="5">
-        <v>52.85</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>30.1</v>
-      </c>
-      <c r="D56" s="5">
-        <v>37.69</v>
-      </c>
-      <c r="E56" s="6">
-        <v>7.59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>57.25</v>
-      </c>
-      <c r="D57" s="5">
-        <v>52.83</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-4.42</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>78.84</v>
-      </c>
-      <c r="D58" s="5">
-        <v>73.48</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-5.36</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>57.45</v>
-      </c>
-      <c r="D59" s="5">
-        <v>55.51</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="3" t="s">
+      <c r="B68" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="5">
-        <v>-11.21</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-56.06</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-44.85</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-48.35</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-69.25</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-20.9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-70.55</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-1.36</v>
-      </c>
-      <c r="E62" s="6">
-        <v>69.19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>335.97</v>
-      </c>
-      <c r="D63" s="5">
-        <v>131.47</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-204.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>33.3</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-41.67</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-74.97</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>14.9</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-54.87</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-69.77</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-32.43</v>
-      </c>
-      <c r="D66" s="5">
+      <c r="C68" s="7">
         <v>-15.67</v>
       </c>
-      <c r="E66" s="6">
-        <v>16.76</v>
+      <c r="D68" s="7">
+        <v>120.49</v>
+      </c>
+      <c r="E68" s="8">
+        <v>136.16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2909,61 +3068,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>53.8</v>
+      </c>
+      <c r="E2" s="12">
+        <v>70</v>
+      </c>
+      <c r="F2" s="12">
+        <v>6.6</v>
+      </c>
+      <c r="G2" s="12">
+        <v>14.3</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="I2" s="12">
         <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>52.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>70</v>
-      </c>
-      <c r="F2" s="10">
-        <v>6.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>11.1</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3064,49 +3223,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.5993999999999999</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3452</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2885</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.2149</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1509</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1479</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0814</v>
+      <c r="A2" s="15">
+        <v>0.61</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3322</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2924</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2126</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1541</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.151</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.07440000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,55 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>No → Yes</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.4 → 50.8</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>44.8 → 54.3</t>
-  </si>
-  <si>
-    <t>44.8</t>
-  </si>
-  <si>
-    <t>54.3</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>73.5 → 69.2</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>73.5</t>
-  </si>
-  <si>
-    <t>69.2</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-2.0% → -3.7%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-2.0%</t>
-  </si>
-  <si>
-    <t>-3.7%</t>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>50.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -287,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,20 +292,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,12 +326,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -458,15 +409,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -475,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -974,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1103.2</v>
+        <v>1116.8</v>
       </c>
       <c r="D2">
-        <v>-0.23</v>
+        <v>1.23</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -986,25 +936,25 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-11.15</v>
+        <v>-10.06</v>
       </c>
       <c r="H2">
-        <v>47.42</v>
+        <v>49.23</v>
       </c>
       <c r="I2">
-        <v>-3.02</v>
+        <v>-4.53</v>
       </c>
       <c r="J2">
-        <v>4.47</v>
+        <v>6.26</v>
       </c>
       <c r="K2">
-        <v>7.21</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L2">
-        <v>19.28</v>
+        <v>20.39</v>
       </c>
       <c r="M2">
-        <v>7.44</v>
+        <v>7.22</v>
       </c>
       <c r="N2">
         <v>57</v>
@@ -1013,19 +963,19 @@
         <v>71</v>
       </c>
       <c r="P2">
-        <v>1121.52</v>
+        <v>1110.92</v>
       </c>
       <c r="Q2">
-        <v>1117.59</v>
+        <v>1120.24</v>
       </c>
       <c r="R2">
-        <v>1116.22</v>
+        <v>1114.71</v>
       </c>
       <c r="S2">
-        <v>942.25</v>
+        <v>943.38</v>
       </c>
       <c r="T2">
-        <v>17.08</v>
+        <v>18.38</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1040,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.44</v>
+        <v>50.81</v>
       </c>
       <c r="Z2">
-        <v>6.27</v>
+        <v>5.64</v>
       </c>
       <c r="AA2">
-        <v>9.91</v>
+        <v>9.06</v>
       </c>
       <c r="AB2">
-        <v>-3.64</v>
+        <v>-3.41</v>
       </c>
       <c r="AC2">
-        <v>10.97</v>
+        <v>13.92</v>
       </c>
       <c r="AD2">
-        <v>19.59</v>
+        <v>13.48</v>
       </c>
       <c r="AE2">
-        <v>43.05</v>
+        <v>42.69</v>
       </c>
       <c r="AF2">
-        <v>-43.2</v>
+        <v>-65.68000000000001</v>
       </c>
       <c r="AG2">
-        <v>1188.33</v>
+        <v>1186.31</v>
       </c>
       <c r="AH2">
-        <v>1046.86</v>
+        <v>1054.18</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1076,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>27.9</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1087,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>897.9</v>
+        <v>889</v>
       </c>
       <c r="D3">
-        <v>3.8</v>
+        <v>-0.99</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1099,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.050000000000001</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="H3">
-        <v>69.58</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I3">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="J3">
-        <v>8.25</v>
+        <v>6.77</v>
       </c>
       <c r="K3">
-        <v>-2.13</v>
+        <v>-0.6</v>
       </c>
       <c r="L3">
-        <v>32.37</v>
+        <v>31.57</v>
       </c>
       <c r="M3">
-        <v>61</v>
+        <v>60.31</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P3">
-        <v>877.1900000000001</v>
+        <v>881.59</v>
       </c>
       <c r="Q3">
-        <v>877.85</v>
+        <v>879.13</v>
       </c>
       <c r="R3">
-        <v>900.17</v>
+        <v>898.86</v>
       </c>
       <c r="S3">
-        <v>771.1799999999999</v>
+        <v>771.97</v>
       </c>
       <c r="T3">
-        <v>16.43</v>
+        <v>15.16</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1153,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>54.29</v>
+        <v>51.69</v>
       </c>
       <c r="Z3">
-        <v>-2.74</v>
+        <v>-1.8</v>
       </c>
       <c r="AA3">
-        <v>-4.57</v>
+        <v>-4.02</v>
       </c>
       <c r="AB3">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="AC3">
-        <v>54.05</v>
+        <v>62.66</v>
       </c>
       <c r="AD3">
-        <v>42.66</v>
+        <v>51.03</v>
       </c>
       <c r="AE3">
-        <v>21.69</v>
+        <v>21.55</v>
       </c>
       <c r="AF3">
-        <v>102.83</v>
+        <v>-17.02</v>
       </c>
       <c r="AG3">
-        <v>910.25</v>
+        <v>911.15</v>
       </c>
       <c r="AH3">
-        <v>845.46</v>
+        <v>847.12</v>
       </c>
       <c r="AI3">
         <v>909.1900000000001</v>
@@ -1189,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>17.44</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1200,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1875.4</v>
+        <v>1862.9</v>
       </c>
       <c r="D4">
-        <v>0.39</v>
+        <v>-0.67</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1212,25 +1162,25 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-3.33</v>
+        <v>-3.97</v>
       </c>
       <c r="H4">
-        <v>38.44</v>
+        <v>37.51</v>
       </c>
       <c r="I4">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>4.02</v>
+        <v>5.02</v>
       </c>
       <c r="K4">
-        <v>21.96</v>
+        <v>24.78</v>
       </c>
       <c r="L4">
-        <v>23.14</v>
+        <v>23.51</v>
       </c>
       <c r="M4">
-        <v>29.24</v>
+        <v>27.98</v>
       </c>
       <c r="N4">
         <v>85</v>
@@ -1242,16 +1192,16 @@
         <v>1865.22</v>
       </c>
       <c r="Q4">
-        <v>1886.22</v>
+        <v>1886.88</v>
       </c>
       <c r="R4">
-        <v>1819.37</v>
+        <v>1822.85</v>
       </c>
       <c r="S4">
-        <v>1673.48</v>
+        <v>1674.09</v>
       </c>
       <c r="T4">
-        <v>12.07</v>
+        <v>11.28</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1266,34 +1216,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>53.95</v>
+        <v>51.72</v>
       </c>
       <c r="Z4">
-        <v>19</v>
+        <v>16.76</v>
       </c>
       <c r="AA4">
-        <v>27.53</v>
+        <v>25.38</v>
       </c>
       <c r="AB4">
-        <v>-8.529999999999999</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="AC4">
-        <v>25.31</v>
+        <v>23.23</v>
       </c>
       <c r="AD4">
-        <v>15.63</v>
+        <v>21.07</v>
       </c>
       <c r="AE4">
-        <v>44.94</v>
+        <v>44.08</v>
       </c>
       <c r="AF4">
-        <v>-26.01</v>
+        <v>-32.49</v>
       </c>
       <c r="AG4">
-        <v>1938.13</v>
+        <v>1937.17</v>
       </c>
       <c r="AH4">
-        <v>1834.32</v>
+        <v>1836.58</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1302,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>18.79</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1313,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1928.4</v>
+        <v>1913.7</v>
       </c>
       <c r="D5">
-        <v>-1.09</v>
+        <v>-0.76</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1325,46 +1275,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
+        <v>-20.22</v>
+      </c>
+      <c r="H5">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="I5">
+        <v>-4.13</v>
+      </c>
+      <c r="J5">
+        <v>-6.84</v>
+      </c>
+      <c r="K5">
+        <v>7.05</v>
+      </c>
+      <c r="L5">
         <v>-19.61</v>
       </c>
-      <c r="H5">
-        <v>10.47</v>
-      </c>
-      <c r="I5">
-        <v>-3.81</v>
-      </c>
-      <c r="J5">
-        <v>-5.36</v>
-      </c>
-      <c r="K5">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="L5">
-        <v>-20.1</v>
-      </c>
       <c r="M5">
-        <v>21.26</v>
+        <v>20.47</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="P5">
-        <v>1942.88</v>
+        <v>1926.4</v>
       </c>
       <c r="Q5">
-        <v>2044.97</v>
+        <v>2036.98</v>
       </c>
       <c r="R5">
-        <v>2032.1</v>
+        <v>2029.01</v>
       </c>
       <c r="S5">
-        <v>2100.28</v>
+        <v>2099.01</v>
       </c>
       <c r="T5">
-        <v>-8.18</v>
+        <v>-8.83</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1379,34 +1329,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.26</v>
+        <v>33.65</v>
       </c>
       <c r="Z5">
-        <v>-25.69</v>
+        <v>-30.09</v>
       </c>
       <c r="AA5">
-        <v>-5.73</v>
+        <v>-10.6</v>
       </c>
       <c r="AB5">
-        <v>-19.97</v>
+        <v>-19.49</v>
       </c>
       <c r="AC5">
-        <v>14.73</v>
+        <v>19.01</v>
       </c>
       <c r="AD5">
-        <v>7.83</v>
+        <v>14.17</v>
       </c>
       <c r="AE5">
-        <v>50.55</v>
+        <v>50.36</v>
       </c>
       <c r="AF5">
-        <v>-10.9</v>
+        <v>-14.01</v>
       </c>
       <c r="AG5">
-        <v>2178.78</v>
+        <v>2182.21</v>
       </c>
       <c r="AH5">
-        <v>1911.16</v>
+        <v>1891.74</v>
       </c>
       <c r="AI5">
         <v>2060.59</v>
@@ -1415,7 +1365,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>33.28</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1426,58 +1376,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>795.3</v>
+        <v>805.3</v>
       </c>
       <c r="D6">
-        <v>-0.13</v>
+        <v>1.26</v>
       </c>
       <c r="E6">
-        <v>1175.4</v>
+        <v>1131.2</v>
       </c>
       <c r="F6">
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-32.34</v>
+        <v>-28.81</v>
       </c>
       <c r="H6">
-        <v>12.95</v>
+        <v>14.37</v>
       </c>
       <c r="I6">
-        <v>-1.85</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>2.11</v>
+        <v>5.52</v>
       </c>
       <c r="K6">
-        <v>5.28</v>
+        <v>8.65</v>
       </c>
       <c r="L6">
-        <v>-32.49</v>
+        <v>-31.49</v>
       </c>
       <c r="M6">
-        <v>15.41</v>
+        <v>15.87</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P6">
-        <v>804.66</v>
+        <v>806.26</v>
       </c>
       <c r="Q6">
-        <v>794.13</v>
+        <v>796.39</v>
       </c>
       <c r="R6">
-        <v>765.72</v>
+        <v>767.4</v>
       </c>
       <c r="S6">
-        <v>859.15</v>
+        <v>858.09</v>
       </c>
       <c r="T6">
-        <v>-7.43</v>
+        <v>-6.15</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1492,34 +1442,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>52.5</v>
+        <v>55.33</v>
       </c>
       <c r="Z6">
         <v>9.039999999999999</v>
       </c>
       <c r="AA6">
-        <v>9.31</v>
+        <v>9.25</v>
       </c>
       <c r="AB6">
-        <v>-0.26</v>
+        <v>-0.22</v>
       </c>
       <c r="AC6">
-        <v>38.33</v>
+        <v>34.45</v>
       </c>
       <c r="AD6">
-        <v>47.96</v>
+        <v>41.64</v>
       </c>
       <c r="AE6">
-        <v>25.72</v>
+        <v>25.52</v>
       </c>
       <c r="AF6">
-        <v>-57.6</v>
+        <v>-33.17</v>
       </c>
       <c r="AG6">
-        <v>827.74</v>
+        <v>826.23</v>
       </c>
       <c r="AH6">
-        <v>760.51</v>
+        <v>766.55</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1528,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>34.34</v>
+        <v>35.45</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1539,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3328.1</v>
+        <v>3292.6</v>
       </c>
       <c r="D7">
-        <v>-1.73</v>
+        <v>-1.07</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1551,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-3.67</v>
+        <v>-4.7</v>
       </c>
       <c r="H7">
-        <v>75.95</v>
+        <v>74.08</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>-0.79</v>
       </c>
       <c r="J7">
-        <v>30.81</v>
+        <v>28.8</v>
       </c>
       <c r="K7">
-        <v>36.09</v>
+        <v>38.03</v>
       </c>
       <c r="L7">
-        <v>21.42</v>
+        <v>26.4</v>
       </c>
       <c r="M7">
-        <v>33.22</v>
+        <v>32.87</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P7">
-        <v>3385.94</v>
+        <v>3380.7</v>
       </c>
       <c r="Q7">
-        <v>2978.9</v>
+        <v>3014.51</v>
       </c>
       <c r="R7">
-        <v>2718.6</v>
+        <v>2734.21</v>
       </c>
       <c r="S7">
-        <v>2410.6</v>
+        <v>2415.2</v>
       </c>
       <c r="T7">
-        <v>38.06</v>
+        <v>36.33</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1605,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>69.15000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="Z7">
-        <v>214.18</v>
+        <v>205.68</v>
       </c>
       <c r="AA7">
-        <v>174.95</v>
+        <v>181.1</v>
       </c>
       <c r="AB7">
-        <v>39.23</v>
+        <v>24.58</v>
       </c>
       <c r="AC7">
-        <v>68.19</v>
+        <v>54.82</v>
       </c>
       <c r="AD7">
-        <v>75.86</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="AE7">
-        <v>145.83</v>
+        <v>146.86</v>
       </c>
       <c r="AF7">
-        <v>-69.88</v>
+        <v>-56.54</v>
       </c>
       <c r="AG7">
-        <v>3627.69</v>
+        <v>3649.24</v>
       </c>
       <c r="AH7">
-        <v>2330.12</v>
+        <v>2379.78</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1641,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>69.25</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1652,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8376</v>
+        <v>8243.5</v>
       </c>
       <c r="D8">
-        <v>2.79</v>
+        <v>-1.58</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1664,46 +1614,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-18.15</v>
+        <v>-19.44</v>
       </c>
       <c r="H8">
-        <v>41.38</v>
+        <v>39.14</v>
       </c>
       <c r="I8">
-        <v>3.29</v>
+        <v>0.75</v>
       </c>
       <c r="J8">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="K8">
-        <v>21.78</v>
+        <v>19.64</v>
       </c>
       <c r="L8">
-        <v>-16.84</v>
+        <v>-17.03</v>
       </c>
       <c r="M8">
-        <v>15.1</v>
+        <v>14.43</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="P8">
-        <v>8236.4</v>
+        <v>8248.6</v>
       </c>
       <c r="Q8">
-        <v>8102.05</v>
+        <v>8103.85</v>
       </c>
       <c r="R8">
-        <v>7961.96</v>
+        <v>7969.33</v>
       </c>
       <c r="S8">
-        <v>7402.61</v>
+        <v>7402.58</v>
       </c>
       <c r="T8">
-        <v>13.15</v>
+        <v>11.36</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1718,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>63.07</v>
+        <v>56.99</v>
       </c>
       <c r="Z8">
-        <v>91.36</v>
+        <v>92.13</v>
       </c>
       <c r="AA8">
-        <v>76.31999999999999</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="AB8">
-        <v>15.04</v>
+        <v>12.64</v>
       </c>
       <c r="AC8">
-        <v>70.12</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="AD8">
-        <v>75.93000000000001</v>
+        <v>69.37</v>
       </c>
       <c r="AE8">
-        <v>248.85</v>
+        <v>249.32</v>
       </c>
       <c r="AF8">
-        <v>120.49</v>
+        <v>-1.44</v>
       </c>
       <c r="AG8">
-        <v>8342.58</v>
+        <v>8348.209999999999</v>
       </c>
       <c r="AH8">
-        <v>7861.52</v>
+        <v>7859.49</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1754,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>28.5</v>
+        <v>31.09</v>
       </c>
     </row>
   </sheetData>
@@ -1895,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1938,1117 +1888,1003 @@
         <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>4.47</v>
+      </c>
+      <c r="D7" s="6">
+        <v>6.26</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>8.25</v>
+      </c>
+      <c r="D8" s="6">
+        <v>6.77</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>4.02</v>
+      </c>
+      <c r="D9" s="6">
+        <v>5.02</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-5.36</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-6.84</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2.11</v>
+      </c>
+      <c r="D11" s="6">
+        <v>5.52</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>30.81</v>
+      </c>
+      <c r="D12" s="6">
+        <v>28.8</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.79</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.72</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-3.02</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-4.53</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2.46</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2.54</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.71</v>
+      </c>
+      <c r="D16" s="6">
         <v>0</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="E16" s="7">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.81</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-4.13</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.79</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-4.79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>3.29</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>4.16</v>
-      </c>
-      <c r="D11" s="7">
-        <v>4.47</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>19.28</v>
+      </c>
+      <c r="D21" s="6">
+        <v>20.39</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2.48</v>
-      </c>
-      <c r="D12" s="7">
-        <v>8.25</v>
-      </c>
-      <c r="E12" s="8">
-        <v>5.77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>32.37</v>
+      </c>
+      <c r="D22" s="6">
+        <v>31.57</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>6.57</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4.02</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>23.14</v>
+      </c>
+      <c r="D23" s="6">
+        <v>23.51</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-3.8</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-5.36</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-20.1</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-19.61</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>3.68</v>
-      </c>
-      <c r="D15" s="7">
-        <v>2.11</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-32.49</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-31.49</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>31.66</v>
-      </c>
-      <c r="D16" s="7">
-        <v>30.81</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>21.42</v>
+      </c>
+      <c r="D26" s="6">
+        <v>26.4</v>
+      </c>
+      <c r="E26" s="7">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.82</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.79</v>
-      </c>
-      <c r="E17" s="8">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-16.84</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-17.03</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>1.7</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-3.02</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-4.72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>7.21</v>
+      </c>
+      <c r="D28" s="6">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0.23</v>
-      </c>
-      <c r="D19" s="7">
-        <v>2.46</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-2.13</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-0.29</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-0.71</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>21.96</v>
+      </c>
+      <c r="D30" s="6">
+        <v>24.78</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-4.34</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-3.81</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="D31" s="6">
+        <v>7.05</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>1.18</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-1.85</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>5.28</v>
+      </c>
+      <c r="D32" s="6">
+        <v>8.65</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="D23" s="7">
-        <v>4</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-4.28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>36.09</v>
+      </c>
+      <c r="D33" s="6">
+        <v>38.03</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>2.27</v>
-      </c>
-      <c r="D24" s="7">
-        <v>3.29</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>21.78</v>
+      </c>
+      <c r="D34" s="6">
+        <v>19.64</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>17.17</v>
-      </c>
-      <c r="D25" s="7">
-        <v>19.28</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-11.15</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-10.06</v>
+      </c>
+      <c r="E35" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>27.95</v>
-      </c>
-      <c r="D26" s="7">
-        <v>32.37</v>
-      </c>
-      <c r="E26" s="8">
-        <v>4.42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>23.13</v>
-      </c>
-      <c r="D27" s="7">
-        <v>23.14</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-3.33</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-3.97</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-19.41</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-20.1</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-19.61</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-20.22</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-31.96</v>
-      </c>
-      <c r="D29" s="7">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-32.34</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-28.81</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-3.67</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-4.7</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-18.15</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-19.44</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1103.2</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1116.8</v>
+      </c>
+      <c r="E42" s="7">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>897.9</v>
+      </c>
+      <c r="D43" s="6">
+        <v>889</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-8.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1875.4</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1862.9</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-12.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1928.4</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1913.7</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-14.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>795.3</v>
+      </c>
+      <c r="D46" s="6">
+        <v>805.3</v>
+      </c>
+      <c r="E46" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>3328.1</v>
+      </c>
+      <c r="D47" s="6">
+        <v>3292.6</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-35.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>8376</v>
+      </c>
+      <c r="D48" s="6">
+        <v>8243.5</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-132.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>48.44</v>
+      </c>
+      <c r="D49" s="6">
+        <v>50.81</v>
+      </c>
+      <c r="E49" s="7">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>54.29</v>
+      </c>
+      <c r="D50" s="6">
+        <v>51.69</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>53.95</v>
+      </c>
+      <c r="D51" s="6">
+        <v>51.72</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>35.26</v>
+      </c>
+      <c r="D52" s="6">
+        <v>33.65</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>52.5</v>
+      </c>
+      <c r="D53" s="6">
+        <v>55.33</v>
+      </c>
+      <c r="E53" s="7">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="D54" s="6">
+        <v>66.58</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>63.07</v>
+      </c>
+      <c r="D55" s="6">
+        <v>56.99</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-6.08</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-43.2</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-65.68000000000001</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-22.48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>102.83</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-17.02</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-119.85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-26.01</v>
+      </c>
+      <c r="D58" s="6">
         <v>-32.49</v>
       </c>
-      <c r="E29" s="9">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="E58" s="8">
+        <v>-6.48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-10.9</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-14.01</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-57.6</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-33.17</v>
+      </c>
+      <c r="E60" s="7">
+        <v>24.43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>21.77</v>
-      </c>
-      <c r="D30" s="7">
-        <v>21.42</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-69.88</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-56.54</v>
+      </c>
+      <c r="E61" s="7">
+        <v>13.34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-20.37</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-16.84</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>6.83</v>
-      </c>
-      <c r="D32" s="7">
-        <v>7.21</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-7.46</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-2.13</v>
-      </c>
-      <c r="E33" s="8">
-        <v>5.33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>18.29</v>
-      </c>
-      <c r="D34" s="7">
-        <v>21.96</v>
-      </c>
-      <c r="E34" s="8">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>6.44</v>
-      </c>
-      <c r="D35" s="7">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E35" s="8">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>7.12</v>
-      </c>
-      <c r="D36" s="7">
-        <v>5.28</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>29.59</v>
-      </c>
-      <c r="D37" s="7">
-        <v>36.09</v>
-      </c>
-      <c r="E37" s="8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>16.89</v>
-      </c>
-      <c r="D38" s="7">
-        <v>21.78</v>
-      </c>
-      <c r="E38" s="8">
-        <v>4.89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-10.95</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-11.15</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-11.41</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="E40" s="8">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-3.71</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-3.33</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-19.21</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-19.61</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-32.4</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-32.34</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-1.98</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-3.67</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-20.37</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-18.15</v>
-      </c>
-      <c r="E45" s="8">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1105.7</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1103.2</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>865.05</v>
-      </c>
-      <c r="D47" s="7">
-        <v>897.9</v>
-      </c>
-      <c r="E47" s="8">
-        <v>32.85</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>1868.1</v>
-      </c>
-      <c r="D48" s="7">
-        <v>1875.4</v>
-      </c>
-      <c r="E48" s="8">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>1949.7</v>
-      </c>
-      <c r="D49" s="7">
-        <v>1928.4</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-21.3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>796.35</v>
-      </c>
-      <c r="D50" s="7">
-        <v>795.3</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>3386.6</v>
-      </c>
-      <c r="D51" s="7">
-        <v>3328.1</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-58.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>8148.5</v>
-      </c>
-      <c r="D52" s="7">
-        <v>8376</v>
-      </c>
-      <c r="E52" s="8">
-        <v>227.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="7">
-        <v>71</v>
-      </c>
-      <c r="D53" s="7">
-        <v>57</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="7">
-        <v>57</v>
-      </c>
-      <c r="D54" s="7">
-        <v>71</v>
-      </c>
-      <c r="E54" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>48.85</v>
-      </c>
-      <c r="D55" s="7">
-        <v>48.44</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>44.78</v>
-      </c>
-      <c r="D56" s="7">
-        <v>54.29</v>
-      </c>
-      <c r="E56" s="8">
-        <v>9.51</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>52.85</v>
-      </c>
-      <c r="D57" s="7">
-        <v>53.95</v>
-      </c>
-      <c r="E57" s="8">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>37.69</v>
-      </c>
-      <c r="D58" s="7">
-        <v>35.26</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>52.83</v>
-      </c>
-      <c r="D59" s="7">
-        <v>52.5</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>73.48</v>
-      </c>
-      <c r="D60" s="7">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-4.33</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="7">
-        <v>55.51</v>
-      </c>
-      <c r="D61" s="7">
-        <v>63.07</v>
-      </c>
-      <c r="E61" s="8">
-        <v>7.56</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="7">
-        <v>-56.06</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-43.2</v>
+      <c r="C62" s="6">
+        <v>120.49</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-1.44</v>
       </c>
       <c r="E62" s="8">
-        <v>12.86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-69.25</v>
-      </c>
-      <c r="D63" s="7">
-        <v>102.83</v>
-      </c>
-      <c r="E63" s="8">
-        <v>172.08</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-1.36</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-26.01</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-24.65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>131.47</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-10.9</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-142.37</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-41.67</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-57.6</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-15.93</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>-54.87</v>
-      </c>
-      <c r="D67" s="7">
-        <v>-69.88</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-15.01</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="7">
-        <v>-15.67</v>
-      </c>
-      <c r="D68" s="7">
-        <v>120.49</v>
-      </c>
-      <c r="E68" s="8">
-        <v>136.16</v>
+        <v>-121.93</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3068,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>84</v>
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>60.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>53.8</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>52.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="12">
-        <v>6.6</v>
-      </c>
-      <c r="G2" s="12">
-        <v>14.3</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>6.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>15.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3223,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.61</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3322</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2924</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2126</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1541</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.151</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.07440000000000001</v>
+      <c r="A2" s="14">
+        <v>0.6031</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3287</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2798</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2047</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1587</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1443</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0722</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,16 +190,22 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.4 → 50.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.4</t>
+    <t>50.8 → 49.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.8</t>
+  </si>
+  <si>
+    <t>49.0</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -924,10 +930,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1116.8</v>
+        <v>1106.6</v>
       </c>
       <c r="D2">
-        <v>1.23</v>
+        <v>-0.91</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -936,46 +942,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-10.06</v>
+        <v>-10.88</v>
       </c>
       <c r="H2">
-        <v>49.23</v>
+        <v>47.87</v>
       </c>
       <c r="I2">
-        <v>-4.53</v>
+        <v>-1.39</v>
       </c>
       <c r="J2">
-        <v>6.26</v>
+        <v>4.02</v>
       </c>
       <c r="K2">
-        <v>8.359999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="L2">
-        <v>20.39</v>
+        <v>22.74</v>
       </c>
       <c r="M2">
-        <v>7.22</v>
+        <v>6.27</v>
       </c>
       <c r="N2">
         <v>57</v>
       </c>
       <c r="O2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>1110.92</v>
+        <v>1107.8</v>
       </c>
       <c r="Q2">
-        <v>1120.24</v>
+        <v>1120.8</v>
       </c>
       <c r="R2">
-        <v>1114.71</v>
+        <v>1112.01</v>
       </c>
       <c r="S2">
-        <v>943.38</v>
+        <v>944.48</v>
       </c>
       <c r="T2">
-        <v>18.38</v>
+        <v>17.17</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +996,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>50.81</v>
+        <v>48.99</v>
       </c>
       <c r="Z2">
-        <v>5.64</v>
+        <v>4.28</v>
       </c>
       <c r="AA2">
-        <v>9.06</v>
+        <v>8.1</v>
       </c>
       <c r="AB2">
-        <v>-3.41</v>
+        <v>-3.82</v>
       </c>
       <c r="AC2">
-        <v>13.92</v>
+        <v>14.32</v>
       </c>
       <c r="AD2">
-        <v>13.48</v>
+        <v>13.07</v>
       </c>
       <c r="AE2">
-        <v>42.69</v>
+        <v>42.45</v>
       </c>
       <c r="AF2">
-        <v>-65.68000000000001</v>
+        <v>-31.84</v>
       </c>
       <c r="AG2">
-        <v>1186.31</v>
+        <v>1186.17</v>
       </c>
       <c r="AH2">
-        <v>1054.18</v>
+        <v>1055.43</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1026,7 +1032,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>24.69</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1043,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>889</v>
+        <v>916</v>
       </c>
       <c r="D3">
-        <v>-0.99</v>
+        <v>3.04</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1055,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.960000000000001</v>
+        <v>-6.2</v>
       </c>
       <c r="H3">
-        <v>67.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="I3">
-        <v>2.54</v>
+        <v>4.39</v>
       </c>
       <c r="J3">
-        <v>6.77</v>
+        <v>6.09</v>
       </c>
       <c r="K3">
-        <v>-0.6</v>
+        <v>0.91</v>
       </c>
       <c r="L3">
-        <v>31.57</v>
+        <v>36.75</v>
       </c>
       <c r="M3">
-        <v>60.31</v>
+        <v>60.94</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>881.59</v>
+        <v>889.29</v>
       </c>
       <c r="Q3">
-        <v>879.13</v>
+        <v>883.63</v>
       </c>
       <c r="R3">
-        <v>898.86</v>
+        <v>897.9</v>
       </c>
       <c r="S3">
-        <v>771.97</v>
+        <v>772.86</v>
       </c>
       <c r="T3">
-        <v>15.16</v>
+        <v>18.52</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,43 +1109,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>51.69</v>
+        <v>58.22</v>
       </c>
       <c r="Z3">
-        <v>-1.8</v>
+        <v>1.12</v>
       </c>
       <c r="AA3">
-        <v>-4.02</v>
+        <v>-2.99</v>
       </c>
       <c r="AB3">
-        <v>2.22</v>
+        <v>4.11</v>
       </c>
       <c r="AC3">
-        <v>62.66</v>
+        <v>91.94</v>
       </c>
       <c r="AD3">
-        <v>51.03</v>
+        <v>69.55</v>
       </c>
       <c r="AE3">
-        <v>21.55</v>
+        <v>22.94</v>
       </c>
       <c r="AF3">
-        <v>-17.02</v>
+        <v>28.88</v>
       </c>
       <c r="AG3">
-        <v>911.15</v>
+        <v>908.8</v>
       </c>
       <c r="AH3">
-        <v>847.12</v>
+        <v>858.45</v>
       </c>
       <c r="AI3">
-        <v>909.1900000000001</v>
+        <v>826.96</v>
       </c>
       <c r="AJ3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK3">
-        <v>17.74</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1156,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1862.9</v>
+        <v>1857.4</v>
       </c>
       <c r="D4">
-        <v>-0.67</v>
+        <v>-0.3</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1168,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-3.97</v>
+        <v>-4.26</v>
       </c>
       <c r="H4">
-        <v>37.51</v>
+        <v>37.11</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="J4">
-        <v>5.02</v>
+        <v>0.41</v>
       </c>
       <c r="K4">
-        <v>24.78</v>
+        <v>25.26</v>
       </c>
       <c r="L4">
-        <v>23.51</v>
+        <v>25.92</v>
       </c>
       <c r="M4">
-        <v>27.98</v>
+        <v>27.6</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P4">
-        <v>1865.22</v>
+        <v>1867.36</v>
       </c>
       <c r="Q4">
-        <v>1886.88</v>
+        <v>1885.34</v>
       </c>
       <c r="R4">
-        <v>1822.85</v>
+        <v>1826.13</v>
       </c>
       <c r="S4">
-        <v>1674.09</v>
+        <v>1674.79</v>
       </c>
       <c r="T4">
-        <v>11.28</v>
+        <v>10.9</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,34 +1222,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>51.72</v>
+        <v>50.73</v>
       </c>
       <c r="Z4">
-        <v>16.76</v>
+        <v>14.36</v>
       </c>
       <c r="AA4">
-        <v>25.38</v>
+        <v>23.18</v>
       </c>
       <c r="AB4">
-        <v>-8.619999999999999</v>
+        <v>-8.81</v>
       </c>
       <c r="AC4">
-        <v>23.23</v>
+        <v>17.72</v>
       </c>
       <c r="AD4">
-        <v>21.07</v>
+        <v>22.09</v>
       </c>
       <c r="AE4">
-        <v>44.08</v>
+        <v>44.89</v>
       </c>
       <c r="AF4">
-        <v>-32.49</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AG4">
-        <v>1937.17</v>
+        <v>1937.32</v>
       </c>
       <c r="AH4">
-        <v>1836.58</v>
+        <v>1833.35</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1252,7 +1258,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>16.46</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1269,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1913.7</v>
+        <v>1905.9</v>
       </c>
       <c r="D5">
-        <v>-0.76</v>
+        <v>-0.41</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,49 +1281,49 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-20.22</v>
+        <v>-20.55</v>
       </c>
       <c r="H5">
-        <v>9.630000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="I5">
-        <v>-4.13</v>
+        <v>-1.07</v>
       </c>
       <c r="J5">
-        <v>-6.84</v>
+        <v>-8.09</v>
       </c>
       <c r="K5">
-        <v>7.05</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L5">
-        <v>-19.61</v>
+        <v>-19.33</v>
       </c>
       <c r="M5">
-        <v>20.47</v>
+        <v>20.17</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P5">
-        <v>1926.4</v>
+        <v>1922.26</v>
       </c>
       <c r="Q5">
-        <v>2036.98</v>
+        <v>2026.51</v>
       </c>
       <c r="R5">
-        <v>2029.01</v>
+        <v>2026.83</v>
       </c>
       <c r="S5">
-        <v>2099.01</v>
+        <v>2097.65</v>
       </c>
       <c r="T5">
-        <v>-8.83</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="U5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V5" t="s">
         <v>46</v>
@@ -1326,46 +1332,46 @@
         <v>46</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>33.65</v>
+        <v>32.79</v>
       </c>
       <c r="Z5">
-        <v>-30.09</v>
+        <v>-33.81</v>
       </c>
       <c r="AA5">
-        <v>-10.6</v>
+        <v>-15.24</v>
       </c>
       <c r="AB5">
-        <v>-19.49</v>
+        <v>-18.57</v>
       </c>
       <c r="AC5">
-        <v>19.01</v>
+        <v>13.49</v>
       </c>
       <c r="AD5">
-        <v>14.17</v>
+        <v>15.74</v>
       </c>
       <c r="AE5">
-        <v>50.36</v>
+        <v>48.76</v>
       </c>
       <c r="AF5">
-        <v>-14.01</v>
+        <v>55.77</v>
       </c>
       <c r="AG5">
-        <v>2182.21</v>
+        <v>2178.02</v>
       </c>
       <c r="AH5">
-        <v>1891.74</v>
+        <v>1874.99</v>
       </c>
       <c r="AI5">
-        <v>2060.59</v>
+        <v>2050.28</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>34.33</v>
+        <v>35.49</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,37 +1382,37 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>805.3</v>
+        <v>799.4</v>
       </c>
       <c r="D6">
-        <v>1.26</v>
+        <v>-0.73</v>
       </c>
       <c r="E6">
-        <v>1131.2</v>
+        <v>1129.9</v>
       </c>
       <c r="F6">
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-28.81</v>
+        <v>-29.25</v>
       </c>
       <c r="H6">
-        <v>14.37</v>
+        <v>13.54</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>-2.98</v>
       </c>
       <c r="J6">
-        <v>5.52</v>
+        <v>5.18</v>
       </c>
       <c r="K6">
-        <v>8.65</v>
+        <v>5.84</v>
       </c>
       <c r="L6">
-        <v>-31.49</v>
+        <v>-29.33</v>
       </c>
       <c r="M6">
-        <v>15.87</v>
+        <v>15.78</v>
       </c>
       <c r="N6">
         <v>15</v>
@@ -1415,19 +1421,19 @@
         <v>33</v>
       </c>
       <c r="P6">
-        <v>806.26</v>
+        <v>801.35</v>
       </c>
       <c r="Q6">
-        <v>796.39</v>
+        <v>797.34</v>
       </c>
       <c r="R6">
-        <v>767.4</v>
+        <v>769.3099999999999</v>
       </c>
       <c r="S6">
-        <v>858.09</v>
+        <v>856.85</v>
       </c>
       <c r="T6">
-        <v>-6.15</v>
+        <v>-6.71</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1448,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>55.33</v>
+        <v>53.31</v>
       </c>
       <c r="Z6">
-        <v>9.039999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AA6">
-        <v>9.25</v>
+        <v>9.09</v>
       </c>
       <c r="AB6">
-        <v>-0.22</v>
+        <v>-0.64</v>
       </c>
       <c r="AC6">
-        <v>34.45</v>
+        <v>35.72</v>
       </c>
       <c r="AD6">
-        <v>41.64</v>
+        <v>36.16</v>
       </c>
       <c r="AE6">
-        <v>25.52</v>
+        <v>25.89</v>
       </c>
       <c r="AF6">
-        <v>-33.17</v>
+        <v>12.24</v>
       </c>
       <c r="AG6">
-        <v>826.23</v>
+        <v>826.22</v>
       </c>
       <c r="AH6">
-        <v>766.55</v>
+        <v>768.47</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1478,7 +1484,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>35.45</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1495,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3292.6</v>
+        <v>3281.5</v>
       </c>
       <c r="D7">
-        <v>-1.07</v>
+        <v>-0.34</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,46 +1507,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-4.7</v>
+        <v>-5.02</v>
       </c>
       <c r="H7">
-        <v>74.08</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="I7">
-        <v>-0.79</v>
+        <v>-4.64</v>
       </c>
       <c r="J7">
-        <v>28.8</v>
+        <v>27.17</v>
       </c>
       <c r="K7">
-        <v>38.03</v>
+        <v>34.43</v>
       </c>
       <c r="L7">
-        <v>26.4</v>
+        <v>31.21</v>
       </c>
       <c r="M7">
-        <v>32.87</v>
+        <v>32.34</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P7">
-        <v>3380.7</v>
+        <v>3348.74</v>
       </c>
       <c r="Q7">
-        <v>3014.51</v>
+        <v>3047.18</v>
       </c>
       <c r="R7">
-        <v>2734.21</v>
+        <v>2747.5</v>
       </c>
       <c r="S7">
-        <v>2415.2</v>
+        <v>2419.16</v>
       </c>
       <c r="T7">
-        <v>36.33</v>
+        <v>35.65</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1561,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>66.58</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="Z7">
-        <v>205.68</v>
+        <v>195.78</v>
       </c>
       <c r="AA7">
-        <v>181.1</v>
+        <v>184.03</v>
       </c>
       <c r="AB7">
-        <v>24.58</v>
+        <v>11.75</v>
       </c>
       <c r="AC7">
-        <v>54.82</v>
+        <v>32.46</v>
       </c>
       <c r="AD7">
-        <v>67.15000000000001</v>
+        <v>51.82</v>
       </c>
       <c r="AE7">
-        <v>146.86</v>
+        <v>144.64</v>
       </c>
       <c r="AF7">
-        <v>-56.54</v>
+        <v>-55.28</v>
       </c>
       <c r="AG7">
-        <v>3649.24</v>
+        <v>3665.22</v>
       </c>
       <c r="AH7">
-        <v>2379.78</v>
+        <v>2429.13</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1591,7 +1597,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>65.65000000000001</v>
+        <v>62.52</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1608,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8243.5</v>
+        <v>8170.5</v>
       </c>
       <c r="D8">
-        <v>-1.58</v>
+        <v>-0.89</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1614,46 +1620,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-19.44</v>
+        <v>-20.15</v>
       </c>
       <c r="H8">
-        <v>39.14</v>
+        <v>37.91</v>
       </c>
       <c r="I8">
-        <v>0.75</v>
+        <v>-1.39</v>
       </c>
       <c r="J8">
-        <v>1.72</v>
+        <v>-0.45</v>
       </c>
       <c r="K8">
-        <v>19.64</v>
+        <v>19.5</v>
       </c>
       <c r="L8">
-        <v>-17.03</v>
+        <v>-17.19</v>
       </c>
       <c r="M8">
-        <v>14.43</v>
+        <v>14.28</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P8">
-        <v>8248.6</v>
+        <v>8225.5</v>
       </c>
       <c r="Q8">
-        <v>8103.85</v>
+        <v>8102.08</v>
       </c>
       <c r="R8">
-        <v>7969.33</v>
+        <v>7974.56</v>
       </c>
       <c r="S8">
-        <v>7402.58</v>
+        <v>7401.93</v>
       </c>
       <c r="T8">
-        <v>11.36</v>
+        <v>10.38</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1674,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>56.99</v>
+        <v>53.91</v>
       </c>
       <c r="Z8">
-        <v>92.13</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="AA8">
-        <v>79.48999999999999</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="AB8">
-        <v>12.64</v>
+        <v>5.09</v>
       </c>
       <c r="AC8">
-        <v>67.84999999999999</v>
+        <v>63.11</v>
       </c>
       <c r="AD8">
-        <v>69.37</v>
+        <v>67.03</v>
       </c>
       <c r="AE8">
-        <v>249.32</v>
+        <v>241.48</v>
       </c>
       <c r="AF8">
-        <v>-1.44</v>
+        <v>-19.28</v>
       </c>
       <c r="AG8">
-        <v>8348.209999999999</v>
+        <v>8343.809999999999</v>
       </c>
       <c r="AH8">
-        <v>7859.49</v>
+        <v>7860.34</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1704,7 +1710,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>31.09</v>
+        <v>31.32</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1903,988 +1909,1008 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>4.47</v>
-      </c>
-      <c r="D7" s="6">
-        <v>6.26</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1.79</v>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>8.25</v>
+        <v>6.26</v>
       </c>
       <c r="D8" s="6">
-        <v>6.77</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-1.48</v>
+        <v>4.02</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>4.02</v>
+        <v>6.77</v>
       </c>
       <c r="D9" s="6">
-        <v>5.02</v>
+        <v>6.09</v>
       </c>
       <c r="E9" s="7">
-        <v>1</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.36</v>
+        <v>5.02</v>
       </c>
       <c r="D10" s="6">
-        <v>-6.84</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.48</v>
+        <v>0.41</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-4.61</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>2.11</v>
+        <v>-6.84</v>
       </c>
       <c r="D11" s="6">
-        <v>5.52</v>
+        <v>-8.09</v>
       </c>
       <c r="E11" s="7">
-        <v>3.41</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>30.81</v>
+        <v>5.52</v>
       </c>
       <c r="D12" s="6">
-        <v>28.8</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-2.01</v>
+        <v>5.18</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>1.79</v>
+        <v>28.8</v>
       </c>
       <c r="D13" s="6">
-        <v>1.72</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.07000000000000001</v>
+        <v>27.17</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.02</v>
+        <v>1.72</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.53</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.51</v>
+        <v>-0.45</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>2.46</v>
+        <v>-4.53</v>
       </c>
       <c r="D15" s="6">
-        <v>2.54</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.08</v>
+        <v>-1.39</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3.14</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.71</v>
+        <v>2.54</v>
       </c>
       <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.71</v>
+        <v>4.39</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.85</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.81</v>
+        <v>0</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.13</v>
+        <v>0.58</v>
       </c>
       <c r="E17" s="8">
-        <v>-0.32</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.85</v>
+        <v>-4.13</v>
       </c>
       <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.85</v>
+        <v>-1.07</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3.06</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.79</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-4.79</v>
+        <v>-2.98</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-3.98</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>3.29</v>
+        <v>-0.79</v>
       </c>
       <c r="D20" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.54</v>
+        <v>-4.64</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>19.28</v>
+        <v>0.75</v>
       </c>
       <c r="D21" s="6">
-        <v>20.39</v>
+        <v>-1.39</v>
       </c>
       <c r="E21" s="7">
-        <v>1.11</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>32.37</v>
+        <v>20.39</v>
       </c>
       <c r="D22" s="6">
-        <v>31.57</v>
+        <v>22.74</v>
       </c>
       <c r="E22" s="8">
-        <v>-0.8</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>23.14</v>
+        <v>31.57</v>
       </c>
       <c r="D23" s="6">
-        <v>23.51</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.37</v>
+        <v>36.75</v>
+      </c>
+      <c r="E23" s="8">
+        <v>5.18</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-20.1</v>
+        <v>23.51</v>
       </c>
       <c r="D24" s="6">
-        <v>-19.61</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.49</v>
+        <v>25.92</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2.41</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-32.49</v>
+        <v>-19.61</v>
       </c>
       <c r="D25" s="6">
-        <v>-31.49</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1</v>
+        <v>-19.33</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>21.42</v>
+        <v>-31.49</v>
       </c>
       <c r="D26" s="6">
-        <v>26.4</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4.98</v>
+        <v>-29.33</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2.16</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-16.84</v>
+        <v>26.4</v>
       </c>
       <c r="D27" s="6">
-        <v>-17.03</v>
+        <v>31.21</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.19</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>7.21</v>
+        <v>-17.03</v>
       </c>
       <c r="D28" s="6">
-        <v>8.359999999999999</v>
+        <v>-17.19</v>
       </c>
       <c r="E28" s="7">
-        <v>1.15</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-2.13</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D29" s="6">
-        <v>-0.6</v>
+        <v>8.16</v>
       </c>
       <c r="E29" s="7">
-        <v>1.53</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>21.96</v>
+        <v>-0.6</v>
       </c>
       <c r="D30" s="6">
-        <v>24.78</v>
-      </c>
-      <c r="E30" s="7">
-        <v>2.82</v>
+        <v>0.91</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.51</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>9.970000000000001</v>
+        <v>24.78</v>
       </c>
       <c r="D31" s="6">
-        <v>7.05</v>
+        <v>25.26</v>
       </c>
       <c r="E31" s="8">
-        <v>-2.92</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>5.28</v>
+        <v>7.05</v>
       </c>
       <c r="D32" s="6">
-        <v>8.65</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.37</v>
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.34</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>36.09</v>
+        <v>8.65</v>
       </c>
       <c r="D33" s="6">
-        <v>38.03</v>
+        <v>5.84</v>
       </c>
       <c r="E33" s="7">
-        <v>1.94</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>21.78</v>
+        <v>38.03</v>
       </c>
       <c r="D34" s="6">
-        <v>19.64</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.14</v>
+        <v>34.43</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-11.15</v>
+        <v>19.64</v>
       </c>
       <c r="D35" s="6">
-        <v>-10.06</v>
+        <v>19.5</v>
       </c>
       <c r="E35" s="7">
-        <v>1.09</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-8.050000000000001</v>
+        <v>-10.06</v>
       </c>
       <c r="D36" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.91</v>
+        <v>-10.88</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-3.33</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="D37" s="6">
-        <v>-3.97</v>
+        <v>-6.2</v>
       </c>
       <c r="E37" s="8">
-        <v>-0.64</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-19.61</v>
+        <v>-3.97</v>
       </c>
       <c r="D38" s="6">
-        <v>-20.22</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.61</v>
+        <v>-4.26</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-32.34</v>
+        <v>-20.22</v>
       </c>
       <c r="D39" s="6">
-        <v>-28.81</v>
+        <v>-20.55</v>
       </c>
       <c r="E39" s="7">
-        <v>3.53</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-3.67</v>
+        <v>-28.81</v>
       </c>
       <c r="D40" s="6">
-        <v>-4.7</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.03</v>
+        <v>-29.25</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-18.15</v>
+        <v>-4.7</v>
       </c>
       <c r="D41" s="6">
-        <v>-19.44</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.29</v>
+        <v>-5.02</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>1103.2</v>
+        <v>-19.44</v>
       </c>
       <c r="D42" s="6">
-        <v>1116.8</v>
+        <v>-20.15</v>
       </c>
       <c r="E42" s="7">
-        <v>13.6</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>897.9</v>
+        <v>1116.8</v>
       </c>
       <c r="D43" s="6">
-        <v>889</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-8.9</v>
+        <v>1106.6</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-10.2</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>1875.4</v>
+        <v>889</v>
       </c>
       <c r="D44" s="6">
-        <v>1862.9</v>
+        <v>916</v>
       </c>
       <c r="E44" s="8">
-        <v>-12.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1928.4</v>
+        <v>1862.9</v>
       </c>
       <c r="D45" s="6">
-        <v>1913.7</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-14.7</v>
+        <v>1857.4</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>795.3</v>
+        <v>1913.7</v>
       </c>
       <c r="D46" s="6">
-        <v>805.3</v>
+        <v>1905.9</v>
       </c>
       <c r="E46" s="7">
-        <v>10</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>3328.1</v>
+        <v>805.3</v>
       </c>
       <c r="D47" s="6">
-        <v>3292.6</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-35.5</v>
+        <v>799.4</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-5.9</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>8376</v>
+        <v>3292.6</v>
       </c>
       <c r="D48" s="6">
-        <v>8243.5</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-132.5</v>
+        <v>3281.5</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-11.1</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>48.44</v>
+        <v>8243.5</v>
       </c>
       <c r="D49" s="6">
-        <v>50.81</v>
+        <v>8170.5</v>
       </c>
       <c r="E49" s="7">
-        <v>2.37</v>
+        <v>-73</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>54.29</v>
+        <v>50.81</v>
       </c>
       <c r="D50" s="6">
-        <v>51.69</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-2.6</v>
+        <v>48.99</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="6">
-        <v>53.95</v>
+        <v>51.69</v>
       </c>
       <c r="D51" s="6">
-        <v>51.72</v>
+        <v>58.22</v>
       </c>
       <c r="E51" s="8">
-        <v>-2.23</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>35.26</v>
+        <v>51.72</v>
       </c>
       <c r="D52" s="6">
-        <v>33.65</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-1.61</v>
+        <v>50.73</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>52.5</v>
+        <v>33.65</v>
       </c>
       <c r="D53" s="6">
-        <v>55.33</v>
+        <v>32.79</v>
       </c>
       <c r="E53" s="7">
-        <v>2.83</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>69.15000000000001</v>
+        <v>55.33</v>
       </c>
       <c r="D54" s="6">
-        <v>66.58</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-2.57</v>
+        <v>53.31</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>63.07</v>
+        <v>66.58</v>
       </c>
       <c r="D55" s="6">
-        <v>56.99</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-6.08</v>
+        <v>65.76000000000001</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>-43.2</v>
+        <v>56.99</v>
       </c>
       <c r="D56" s="6">
-        <v>-65.68000000000001</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-22.48</v>
+        <v>53.91</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-3.08</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="6">
-        <v>102.83</v>
+        <v>-65.68000000000001</v>
       </c>
       <c r="D57" s="6">
-        <v>-17.02</v>
+        <v>-31.84</v>
       </c>
       <c r="E57" s="8">
-        <v>-119.85</v>
+        <v>33.84</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="6">
-        <v>-26.01</v>
+        <v>-17.02</v>
       </c>
       <c r="D58" s="6">
-        <v>-32.49</v>
+        <v>28.88</v>
       </c>
       <c r="E58" s="8">
-        <v>-6.48</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>-10.9</v>
+        <v>-32.49</v>
       </c>
       <c r="D59" s="6">
-        <v>-14.01</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E59" s="8">
-        <v>-3.11</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>-57.6</v>
+        <v>-14.01</v>
       </c>
       <c r="D60" s="6">
-        <v>-33.17</v>
-      </c>
-      <c r="E60" s="7">
-        <v>24.43</v>
+        <v>55.77</v>
+      </c>
+      <c r="E60" s="8">
+        <v>69.78</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-69.88</v>
+        <v>-33.17</v>
       </c>
       <c r="D61" s="6">
-        <v>-56.54</v>
-      </c>
-      <c r="E61" s="7">
-        <v>13.34</v>
+        <v>12.24</v>
+      </c>
+      <c r="E61" s="8">
+        <v>45.41</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>120.49</v>
+        <v>-56.54</v>
       </c>
       <c r="D62" s="6">
+        <v>-55.28</v>
+      </c>
+      <c r="E62" s="8">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
         <v>-1.44</v>
       </c>
-      <c r="E62" s="8">
-        <v>-121.93</v>
+      <c r="D63" s="6">
+        <v>-19.28</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-17.84</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2908,28 +2934,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2943,16 +2969,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>52.4</v>
+        <v>52</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="G2" s="11">
-        <v>15.1</v>
+        <v>14.6</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3083,25 +3109,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.6031</v>
+        <v>0.6093999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3287</v>
+        <v>0.3234</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2798</v>
+        <v>0.276</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2047</v>
+        <v>0.2017</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1587</v>
+        <v>0.1578</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1443</v>
+        <v>0.1428</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0722</v>
+        <v>0.06269999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,22 +190,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.8 → 49.0</t>
+    <t>50.7 → 43.7</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>49.0</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>43.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -930,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1106.6</v>
+        <v>1100.5</v>
       </c>
       <c r="D2">
-        <v>-0.91</v>
+        <v>-0.55</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -942,25 +936,25 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-10.88</v>
+        <v>-11.37</v>
       </c>
       <c r="H2">
-        <v>47.87</v>
+        <v>47.06</v>
       </c>
       <c r="I2">
-        <v>-1.39</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J2">
-        <v>4.02</v>
+        <v>0.46</v>
       </c>
       <c r="K2">
-        <v>8.16</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L2">
-        <v>22.74</v>
+        <v>22.08</v>
       </c>
       <c r="M2">
-        <v>6.27</v>
+        <v>6.54</v>
       </c>
       <c r="N2">
         <v>57</v>
@@ -969,19 +963,19 @@
         <v>72</v>
       </c>
       <c r="P2">
-        <v>1107.8</v>
+        <v>1106.56</v>
       </c>
       <c r="Q2">
-        <v>1120.8</v>
+        <v>1121.9</v>
       </c>
       <c r="R2">
-        <v>1112.01</v>
+        <v>1109.79</v>
       </c>
       <c r="S2">
-        <v>944.48</v>
+        <v>945.52</v>
       </c>
       <c r="T2">
-        <v>17.17</v>
+        <v>16.39</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -996,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.99</v>
+        <v>47.89</v>
       </c>
       <c r="Z2">
-        <v>4.28</v>
+        <v>2.67</v>
       </c>
       <c r="AA2">
-        <v>8.1</v>
+        <v>7.02</v>
       </c>
       <c r="AB2">
-        <v>-3.82</v>
+        <v>-4.34</v>
       </c>
       <c r="AC2">
-        <v>14.32</v>
+        <v>13.51</v>
       </c>
       <c r="AD2">
-        <v>13.07</v>
+        <v>13.92</v>
       </c>
       <c r="AE2">
-        <v>42.45</v>
+        <v>41.91</v>
       </c>
       <c r="AF2">
-        <v>-31.84</v>
+        <v>-13.66</v>
       </c>
       <c r="AG2">
-        <v>1186.17</v>
+        <v>1184.98</v>
       </c>
       <c r="AH2">
-        <v>1055.43</v>
+        <v>1058.82</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1032,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>23.1</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>916</v>
+        <v>885.5</v>
       </c>
       <c r="D3">
-        <v>3.04</v>
+        <v>-3.33</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1055,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-6.2</v>
+        <v>-9.32</v>
       </c>
       <c r="H3">
-        <v>73</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="I3">
-        <v>4.39</v>
+        <v>0.8</v>
       </c>
       <c r="J3">
-        <v>6.09</v>
+        <v>7.19</v>
       </c>
       <c r="K3">
-        <v>0.91</v>
+        <v>-2.33</v>
       </c>
       <c r="L3">
-        <v>36.75</v>
+        <v>33.65</v>
       </c>
       <c r="M3">
-        <v>60.94</v>
+        <v>59.89</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>889.29</v>
+        <v>890.6900000000001</v>
       </c>
       <c r="Q3">
-        <v>883.63</v>
+        <v>883.9</v>
       </c>
       <c r="R3">
-        <v>897.9</v>
+        <v>896.36</v>
       </c>
       <c r="S3">
-        <v>772.86</v>
+        <v>773.5700000000001</v>
       </c>
       <c r="T3">
-        <v>18.52</v>
+        <v>14.47</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1109,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>58.22</v>
+        <v>50</v>
       </c>
       <c r="Z3">
-        <v>1.12</v>
+        <v>0.96</v>
       </c>
       <c r="AA3">
-        <v>-2.99</v>
+        <v>-2.2</v>
       </c>
       <c r="AB3">
-        <v>4.11</v>
+        <v>3.16</v>
       </c>
       <c r="AC3">
-        <v>91.94</v>
+        <v>73.27</v>
       </c>
       <c r="AD3">
-        <v>69.55</v>
+        <v>75.95</v>
       </c>
       <c r="AE3">
-        <v>22.94</v>
+        <v>23.76</v>
       </c>
       <c r="AF3">
-        <v>28.88</v>
+        <v>22.4</v>
       </c>
       <c r="AG3">
-        <v>908.8</v>
+        <v>909.03</v>
       </c>
       <c r="AH3">
-        <v>858.45</v>
+        <v>858.77</v>
       </c>
       <c r="AI3">
         <v>826.96</v>
@@ -1145,7 +1139,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>21.36</v>
+        <v>24.49</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1857.4</v>
+        <v>1814.7</v>
       </c>
       <c r="D4">
-        <v>-0.3</v>
+        <v>-2.3</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1168,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-4.26</v>
+        <v>-6.46</v>
       </c>
       <c r="H4">
-        <v>37.11</v>
+        <v>33.96</v>
       </c>
       <c r="I4">
-        <v>0.58</v>
+        <v>-3.11</v>
       </c>
       <c r="J4">
-        <v>0.41</v>
+        <v>-3.89</v>
       </c>
       <c r="K4">
-        <v>25.26</v>
+        <v>23.4</v>
       </c>
       <c r="L4">
-        <v>25.92</v>
+        <v>26.13</v>
       </c>
       <c r="M4">
-        <v>27.6</v>
+        <v>26.34</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P4">
-        <v>1867.36</v>
+        <v>1855.7</v>
       </c>
       <c r="Q4">
-        <v>1885.34</v>
+        <v>1882.32</v>
       </c>
       <c r="R4">
-        <v>1826.13</v>
+        <v>1828.05</v>
       </c>
       <c r="S4">
-        <v>1674.79</v>
+        <v>1675.32</v>
       </c>
       <c r="T4">
-        <v>10.9</v>
+        <v>8.32</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1222,34 +1216,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>50.73</v>
+        <v>43.71</v>
       </c>
       <c r="Z4">
-        <v>14.36</v>
+        <v>8.92</v>
       </c>
       <c r="AA4">
-        <v>23.18</v>
+        <v>20.32</v>
       </c>
       <c r="AB4">
-        <v>-8.81</v>
+        <v>-11.4</v>
       </c>
       <c r="AC4">
-        <v>17.72</v>
+        <v>7.08</v>
       </c>
       <c r="AD4">
-        <v>22.09</v>
+        <v>16.01</v>
       </c>
       <c r="AE4">
-        <v>44.89</v>
+        <v>46.21</v>
       </c>
       <c r="AF4">
-        <v>8.470000000000001</v>
+        <v>71.84</v>
       </c>
       <c r="AG4">
-        <v>1937.32</v>
+        <v>1943.08</v>
       </c>
       <c r="AH4">
-        <v>1833.35</v>
+        <v>1821.56</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1258,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>17.41</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1905.9</v>
+        <v>1922.9</v>
       </c>
       <c r="D5">
-        <v>-0.41</v>
+        <v>0.89</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1281,46 +1275,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-20.55</v>
+        <v>-19.84</v>
       </c>
       <c r="H5">
-        <v>9.18</v>
+        <v>10.16</v>
       </c>
       <c r="I5">
-        <v>-1.07</v>
+        <v>0.49</v>
       </c>
       <c r="J5">
-        <v>-8.09</v>
+        <v>-9.1</v>
       </c>
       <c r="K5">
-        <v>8.390000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="L5">
-        <v>-19.33</v>
+        <v>-14.78</v>
       </c>
       <c r="M5">
-        <v>20.17</v>
+        <v>20.32</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="P5">
-        <v>1922.26</v>
+        <v>1924.12</v>
       </c>
       <c r="Q5">
-        <v>2026.51</v>
+        <v>2016.88</v>
       </c>
       <c r="R5">
-        <v>2026.83</v>
+        <v>2025.53</v>
       </c>
       <c r="S5">
-        <v>2097.65</v>
+        <v>2096.26</v>
       </c>
       <c r="T5">
-        <v>-9.140000000000001</v>
+        <v>-8.27</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1335,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>32.79</v>
+        <v>36.58</v>
       </c>
       <c r="Z5">
-        <v>-33.81</v>
+        <v>-34.98</v>
       </c>
       <c r="AA5">
-        <v>-15.24</v>
+        <v>-19.19</v>
       </c>
       <c r="AB5">
-        <v>-18.57</v>
+        <v>-15.79</v>
       </c>
       <c r="AC5">
-        <v>13.49</v>
+        <v>15.38</v>
       </c>
       <c r="AD5">
-        <v>15.74</v>
+        <v>15.96</v>
       </c>
       <c r="AE5">
-        <v>48.76</v>
+        <v>48.61</v>
       </c>
       <c r="AF5">
-        <v>55.77</v>
+        <v>-57.36</v>
       </c>
       <c r="AG5">
-        <v>2178.02</v>
+        <v>2169.05</v>
       </c>
       <c r="AH5">
-        <v>1874.99</v>
+        <v>1864.7</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1371,7 +1365,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>35.49</v>
+        <v>34.24</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>799.4</v>
+        <v>795.6</v>
       </c>
       <c r="D6">
-        <v>-0.73</v>
+        <v>-0.48</v>
       </c>
       <c r="E6">
         <v>1129.9</v>
@@ -1394,46 +1388,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-29.25</v>
+        <v>-29.59</v>
       </c>
       <c r="H6">
-        <v>13.54</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <v>-2.98</v>
+        <v>-1.83</v>
       </c>
       <c r="J6">
-        <v>5.18</v>
+        <v>1.96</v>
       </c>
       <c r="K6">
-        <v>5.84</v>
+        <v>5.12</v>
       </c>
       <c r="L6">
-        <v>-29.33</v>
+        <v>-29.49</v>
       </c>
       <c r="M6">
-        <v>15.78</v>
+        <v>16.08</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P6">
-        <v>801.35</v>
+        <v>798.39</v>
       </c>
       <c r="Q6">
-        <v>797.34</v>
+        <v>796.97</v>
       </c>
       <c r="R6">
-        <v>769.3099999999999</v>
+        <v>770.9</v>
       </c>
       <c r="S6">
-        <v>856.85</v>
+        <v>855.61</v>
       </c>
       <c r="T6">
-        <v>-6.71</v>
+        <v>-7.01</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1448,34 +1442,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>53.31</v>
+        <v>52</v>
       </c>
       <c r="Z6">
-        <v>8.460000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AA6">
-        <v>9.09</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB6">
-        <v>-0.64</v>
+        <v>-1.19</v>
       </c>
       <c r="AC6">
-        <v>35.72</v>
+        <v>32.7</v>
       </c>
       <c r="AD6">
-        <v>36.16</v>
+        <v>34.29</v>
       </c>
       <c r="AE6">
-        <v>25.89</v>
+        <v>25.31</v>
       </c>
       <c r="AF6">
-        <v>12.24</v>
+        <v>-66.27</v>
       </c>
       <c r="AG6">
-        <v>826.22</v>
+        <v>825.73</v>
       </c>
       <c r="AH6">
-        <v>768.47</v>
+        <v>768.21</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1484,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>37.03</v>
+        <v>36.87</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3281.5</v>
+        <v>3267.5</v>
       </c>
       <c r="D7">
-        <v>-0.34</v>
+        <v>-0.43</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1507,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-5.02</v>
+        <v>-5.42</v>
       </c>
       <c r="H7">
-        <v>73.48999999999999</v>
+        <v>72.75</v>
       </c>
       <c r="I7">
-        <v>-4.64</v>
+        <v>-5.42</v>
       </c>
       <c r="J7">
-        <v>27.17</v>
+        <v>24.32</v>
       </c>
       <c r="K7">
-        <v>34.43</v>
+        <v>34.28</v>
       </c>
       <c r="L7">
-        <v>31.21</v>
+        <v>30.25</v>
       </c>
       <c r="M7">
-        <v>32.34</v>
+        <v>32.82</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P7">
-        <v>3348.74</v>
+        <v>3311.26</v>
       </c>
       <c r="Q7">
-        <v>3047.18</v>
+        <v>3078.61</v>
       </c>
       <c r="R7">
-        <v>2747.5</v>
+        <v>2761.13</v>
       </c>
       <c r="S7">
-        <v>2419.16</v>
+        <v>2423</v>
       </c>
       <c r="T7">
-        <v>35.65</v>
+        <v>34.85</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1561,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>65.76000000000001</v>
+        <v>64.67</v>
       </c>
       <c r="Z7">
-        <v>195.78</v>
+        <v>184.69</v>
       </c>
       <c r="AA7">
-        <v>184.03</v>
+        <v>184.16</v>
       </c>
       <c r="AB7">
-        <v>11.75</v>
+        <v>0.52</v>
       </c>
       <c r="AC7">
-        <v>32.46</v>
+        <v>14.83</v>
       </c>
       <c r="AD7">
-        <v>51.82</v>
+        <v>34.04</v>
       </c>
       <c r="AE7">
-        <v>144.64</v>
+        <v>139.52</v>
       </c>
       <c r="AF7">
-        <v>-55.28</v>
+        <v>-64.36</v>
       </c>
       <c r="AG7">
-        <v>3665.22</v>
+        <v>3672.7</v>
       </c>
       <c r="AH7">
-        <v>2429.13</v>
+        <v>2484.51</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1597,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>62.52</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8170.5</v>
+        <v>8105</v>
       </c>
       <c r="D8">
-        <v>-0.89</v>
+        <v>-0.8</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1620,46 +1614,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-20.15</v>
+        <v>-20.79</v>
       </c>
       <c r="H8">
-        <v>37.91</v>
+        <v>36.8</v>
       </c>
       <c r="I8">
-        <v>-1.39</v>
+        <v>-1.03</v>
       </c>
       <c r="J8">
-        <v>-0.45</v>
+        <v>-1.23</v>
       </c>
       <c r="K8">
-        <v>19.5</v>
+        <v>18.63</v>
       </c>
       <c r="L8">
-        <v>-17.19</v>
+        <v>-17.9</v>
       </c>
       <c r="M8">
-        <v>14.28</v>
+        <v>14.03</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P8">
-        <v>8225.5</v>
+        <v>8208.700000000001</v>
       </c>
       <c r="Q8">
-        <v>8102.08</v>
+        <v>8102.22</v>
       </c>
       <c r="R8">
-        <v>7974.56</v>
+        <v>7981.23</v>
       </c>
       <c r="S8">
-        <v>7401.93</v>
+        <v>7401.09</v>
       </c>
       <c r="T8">
-        <v>10.38</v>
+        <v>9.51</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1674,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>53.91</v>
+        <v>51.23</v>
       </c>
       <c r="Z8">
-        <v>85.84999999999999</v>
+        <v>74.73</v>
       </c>
       <c r="AA8">
-        <v>80.76000000000001</v>
+        <v>79.55</v>
       </c>
       <c r="AB8">
-        <v>5.09</v>
+        <v>-4.82</v>
       </c>
       <c r="AC8">
-        <v>63.11</v>
+        <v>34.45</v>
       </c>
       <c r="AD8">
-        <v>67.03</v>
+        <v>55.14</v>
       </c>
       <c r="AE8">
-        <v>241.48</v>
+        <v>232.09</v>
       </c>
       <c r="AF8">
-        <v>-19.28</v>
+        <v>-37.66</v>
       </c>
       <c r="AG8">
-        <v>8343.809999999999</v>
+        <v>8343.959999999999</v>
       </c>
       <c r="AH8">
-        <v>7860.34</v>
+        <v>7860.49</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1710,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>31.32</v>
+        <v>30.75</v>
       </c>
     </row>
   </sheetData>
@@ -1851,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1891,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1909,1008 +1903,988 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>66</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>4.02</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.46</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-3.56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>6.26</v>
+        <v>6.09</v>
       </c>
       <c r="D8" s="6">
-        <v>4.02</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.24</v>
+        <v>7.19</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>6.77</v>
+        <v>0.41</v>
       </c>
       <c r="D9" s="6">
-        <v>6.09</v>
+        <v>-3.89</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.68</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>5.02</v>
+        <v>-8.09</v>
       </c>
       <c r="D10" s="6">
-        <v>0.41</v>
+        <v>-9.1</v>
       </c>
       <c r="E10" s="7">
-        <v>-4.61</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-6.84</v>
+        <v>5.18</v>
       </c>
       <c r="D11" s="6">
-        <v>-8.09</v>
+        <v>1.96</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.25</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>5.52</v>
+        <v>27.17</v>
       </c>
       <c r="D12" s="6">
-        <v>5.18</v>
+        <v>24.32</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.34</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>28.8</v>
+        <v>-0.45</v>
       </c>
       <c r="D13" s="6">
-        <v>27.17</v>
+        <v>-1.23</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.63</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>1.72</v>
+        <v>-1.39</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.45</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.17</v>
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.83</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.53</v>
+        <v>4.39</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.39</v>
-      </c>
-      <c r="E15" s="8">
-        <v>3.14</v>
+        <v>0.8</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-3.59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>2.54</v>
+        <v>0.58</v>
       </c>
       <c r="D16" s="6">
-        <v>4.39</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.85</v>
+        <v>-3.11</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.69</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>0</v>
+        <v>-1.07</v>
       </c>
       <c r="D17" s="6">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="E17" s="8">
-        <v>0.58</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-4.13</v>
+        <v>-2.98</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.07</v>
+        <v>-1.83</v>
       </c>
       <c r="E18" s="8">
-        <v>3.06</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>1</v>
+        <v>-4.64</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.98</v>
+        <v>-5.42</v>
       </c>
       <c r="E19" s="7">
-        <v>-3.98</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.79</v>
+        <v>-1.39</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.64</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.85</v>
+        <v>-1.03</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>0.75</v>
+        <v>22.74</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.39</v>
+        <v>22.08</v>
       </c>
       <c r="E21" s="7">
-        <v>-2.14</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>20.39</v>
+        <v>36.75</v>
       </c>
       <c r="D22" s="6">
-        <v>22.74</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2.35</v>
+        <v>33.65</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>31.57</v>
+        <v>25.92</v>
       </c>
       <c r="D23" s="6">
-        <v>36.75</v>
+        <v>26.13</v>
       </c>
       <c r="E23" s="8">
-        <v>5.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>23.51</v>
+        <v>-19.33</v>
       </c>
       <c r="D24" s="6">
-        <v>25.92</v>
+        <v>-14.78</v>
       </c>
       <c r="E24" s="8">
-        <v>2.41</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-19.61</v>
+        <v>-29.33</v>
       </c>
       <c r="D25" s="6">
-        <v>-19.33</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.28</v>
+        <v>-29.49</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-31.49</v>
+        <v>31.21</v>
       </c>
       <c r="D26" s="6">
-        <v>-29.33</v>
-      </c>
-      <c r="E26" s="8">
-        <v>2.16</v>
+        <v>30.25</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>26.4</v>
+        <v>-17.19</v>
       </c>
       <c r="D27" s="6">
-        <v>31.21</v>
-      </c>
-      <c r="E27" s="8">
-        <v>4.81</v>
+        <v>-17.9</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-17.03</v>
+        <v>8.16</v>
       </c>
       <c r="D28" s="6">
-        <v>-17.19</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.16</v>
+        <v>8.779999999999999</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.62</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>8.359999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="D29" s="6">
-        <v>8.16</v>
+        <v>-2.33</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.2</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-0.6</v>
+        <v>25.26</v>
       </c>
       <c r="D30" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.51</v>
+        <v>23.4</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>24.78</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="D31" s="6">
-        <v>25.26</v>
+        <v>10.16</v>
       </c>
       <c r="E31" s="8">
-        <v>0.48</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>7.05</v>
+        <v>5.84</v>
       </c>
       <c r="D32" s="6">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="E32" s="8">
-        <v>1.34</v>
+        <v>5.12</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>8.65</v>
+        <v>34.43</v>
       </c>
       <c r="D33" s="6">
-        <v>5.84</v>
+        <v>34.28</v>
       </c>
       <c r="E33" s="7">
-        <v>-2.81</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>38.03</v>
+        <v>19.5</v>
       </c>
       <c r="D34" s="6">
-        <v>34.43</v>
+        <v>18.63</v>
       </c>
       <c r="E34" s="7">
-        <v>-3.6</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>19.64</v>
+        <v>-10.88</v>
       </c>
       <c r="D35" s="6">
-        <v>19.5</v>
+        <v>-11.37</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.14</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-10.06</v>
+        <v>-6.2</v>
       </c>
       <c r="D36" s="6">
-        <v>-10.88</v>
+        <v>-9.32</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.82</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-8.960000000000001</v>
+        <v>-4.26</v>
       </c>
       <c r="D37" s="6">
-        <v>-6.2</v>
-      </c>
-      <c r="E37" s="8">
-        <v>2.76</v>
+        <v>-6.46</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-3.97</v>
+        <v>-20.55</v>
       </c>
       <c r="D38" s="6">
-        <v>-4.26</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.29</v>
+        <v>-19.84</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.71</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-20.22</v>
+        <v>-29.25</v>
       </c>
       <c r="D39" s="6">
-        <v>-20.55</v>
+        <v>-29.59</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-28.81</v>
+        <v>-5.02</v>
       </c>
       <c r="D40" s="6">
-        <v>-29.25</v>
+        <v>-5.42</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.44</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-4.7</v>
+        <v>-20.15</v>
       </c>
       <c r="D41" s="6">
-        <v>-5.02</v>
+        <v>-20.79</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.32</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>-19.44</v>
+        <v>1106.6</v>
       </c>
       <c r="D42" s="6">
-        <v>-20.15</v>
+        <v>1100.5</v>
       </c>
       <c r="E42" s="7">
-        <v>-0.71</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>1116.8</v>
+        <v>916</v>
       </c>
       <c r="D43" s="6">
-        <v>1106.6</v>
+        <v>885.5</v>
       </c>
       <c r="E43" s="7">
-        <v>-10.2</v>
+        <v>-30.5</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>889</v>
+        <v>1857.4</v>
       </c>
       <c r="D44" s="6">
-        <v>916</v>
-      </c>
-      <c r="E44" s="8">
-        <v>27</v>
+        <v>1814.7</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-42.7</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1862.9</v>
+        <v>1905.9</v>
       </c>
       <c r="D45" s="6">
-        <v>1857.4</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-5.5</v>
+        <v>1922.9</v>
+      </c>
+      <c r="E45" s="8">
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>1913.7</v>
+        <v>799.4</v>
       </c>
       <c r="D46" s="6">
-        <v>1905.9</v>
+        <v>795.6</v>
       </c>
       <c r="E46" s="7">
-        <v>-7.8</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>805.3</v>
+        <v>3281.5</v>
       </c>
       <c r="D47" s="6">
-        <v>799.4</v>
+        <v>3267.5</v>
       </c>
       <c r="E47" s="7">
-        <v>-5.9</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>3292.6</v>
+        <v>8170.5</v>
       </c>
       <c r="D48" s="6">
-        <v>3281.5</v>
+        <v>8105</v>
       </c>
       <c r="E48" s="7">
-        <v>-11.1</v>
+        <v>-65.5</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>8243.5</v>
+        <v>48.99</v>
       </c>
       <c r="D49" s="6">
-        <v>8170.5</v>
+        <v>47.89</v>
       </c>
       <c r="E49" s="7">
-        <v>-73</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>50.81</v>
+        <v>58.22</v>
       </c>
       <c r="D50" s="6">
-        <v>48.99</v>
+        <v>50</v>
       </c>
       <c r="E50" s="7">
-        <v>-1.82</v>
+        <v>-8.220000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="6">
-        <v>51.69</v>
+        <v>50.73</v>
       </c>
       <c r="D51" s="6">
-        <v>58.22</v>
-      </c>
-      <c r="E51" s="8">
-        <v>6.53</v>
+        <v>43.71</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-7.02</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>51.72</v>
+        <v>32.79</v>
       </c>
       <c r="D52" s="6">
-        <v>50.73</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.99</v>
+        <v>36.58</v>
+      </c>
+      <c r="E52" s="8">
+        <v>3.79</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>33.65</v>
+        <v>53.31</v>
       </c>
       <c r="D53" s="6">
-        <v>32.79</v>
+        <v>52</v>
       </c>
       <c r="E53" s="7">
-        <v>-0.86</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>55.33</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="D54" s="6">
-        <v>53.31</v>
+        <v>64.67</v>
       </c>
       <c r="E54" s="7">
-        <v>-2.02</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>66.58</v>
+        <v>53.91</v>
       </c>
       <c r="D55" s="6">
-        <v>65.76000000000001</v>
+        <v>51.23</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.82</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C56" s="6">
-        <v>56.99</v>
+        <v>-31.84</v>
       </c>
       <c r="D56" s="6">
-        <v>53.91</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-3.08</v>
+        <v>-13.66</v>
+      </c>
+      <c r="E56" s="8">
+        <v>18.18</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="6">
-        <v>-65.68000000000001</v>
+        <v>28.88</v>
       </c>
       <c r="D57" s="6">
-        <v>-31.84</v>
-      </c>
-      <c r="E57" s="8">
-        <v>33.84</v>
+        <v>22.4</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-6.48</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="6">
-        <v>-17.02</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="D58" s="6">
-        <v>28.88</v>
+        <v>71.84</v>
       </c>
       <c r="E58" s="8">
-        <v>45.9</v>
+        <v>63.37</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>-32.49</v>
+        <v>55.77</v>
       </c>
       <c r="D59" s="6">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="E59" s="8">
-        <v>40.96</v>
+        <v>-57.36</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-113.13</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>-14.01</v>
+        <v>12.24</v>
       </c>
       <c r="D60" s="6">
-        <v>55.77</v>
-      </c>
-      <c r="E60" s="8">
-        <v>69.78</v>
+        <v>-66.27</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-78.51000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-33.17</v>
+        <v>-55.28</v>
       </c>
       <c r="D61" s="6">
-        <v>12.24</v>
-      </c>
-      <c r="E61" s="8">
-        <v>45.41</v>
+        <v>-64.36</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-9.08</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-56.54</v>
+        <v>-19.28</v>
       </c>
       <c r="D62" s="6">
-        <v>-55.28</v>
-      </c>
-      <c r="E62" s="8">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-1.44</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-19.28</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-17.84</v>
+        <v>-37.66</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-18.38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2934,28 +2908,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2969,16 +2943,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>52</v>
+        <v>49.4</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="G2" s="11">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3109,25 +3083,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.6093999999999999</v>
+        <v>0.5989</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3234</v>
+        <v>0.3282</v>
       </c>
       <c r="C2" s="14">
-        <v>0.276</v>
+        <v>0.2634</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2017</v>
+        <v>0.2032</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1578</v>
+        <v>0.1608</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1428</v>
+        <v>0.1403</v>
       </c>
       <c r="G2" s="14">
-        <v>0.06269999999999999</v>
+        <v>0.0654</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,16 +190,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.7 → 43.7</t>
+    <t>50.0 → 48.1</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.7</t>
-  </si>
-  <si>
-    <t>43.7</t>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>48.1</t>
+  </si>
+  <si>
+    <t>51.2 → 46.9</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>46.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -924,10 +933,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1100.5</v>
+        <v>1071.5</v>
       </c>
       <c r="D2">
-        <v>-0.55</v>
+        <v>-2.64</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -936,46 +945,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-11.37</v>
+        <v>-13.71</v>
       </c>
       <c r="H2">
-        <v>47.06</v>
+        <v>43.18</v>
       </c>
       <c r="I2">
-        <v>-0.5600000000000001</v>
+        <v>-3.09</v>
       </c>
       <c r="J2">
-        <v>0.46</v>
+        <v>-0.65</v>
       </c>
       <c r="K2">
-        <v>8.779999999999999</v>
+        <v>4.17</v>
       </c>
       <c r="L2">
-        <v>22.08</v>
+        <v>17.76</v>
       </c>
       <c r="M2">
-        <v>6.54</v>
+        <v>5.92</v>
       </c>
       <c r="N2">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>1106.56</v>
+        <v>1099.72</v>
       </c>
       <c r="Q2">
-        <v>1121.9</v>
+        <v>1121.39</v>
       </c>
       <c r="R2">
-        <v>1109.79</v>
+        <v>1106.98</v>
       </c>
       <c r="S2">
-        <v>945.52</v>
+        <v>946.46</v>
       </c>
       <c r="T2">
-        <v>16.39</v>
+        <v>13.21</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +999,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>47.89</v>
+        <v>42.94</v>
       </c>
       <c r="Z2">
-        <v>2.67</v>
+        <v>-0.93</v>
       </c>
       <c r="AA2">
-        <v>7.02</v>
+        <v>5.43</v>
       </c>
       <c r="AB2">
-        <v>-4.34</v>
+        <v>-6.35</v>
       </c>
       <c r="AC2">
-        <v>13.51</v>
+        <v>6.52</v>
       </c>
       <c r="AD2">
-        <v>13.92</v>
+        <v>11.45</v>
       </c>
       <c r="AE2">
-        <v>41.91</v>
+        <v>41.71</v>
       </c>
       <c r="AF2">
-        <v>-13.66</v>
+        <v>-41.14</v>
       </c>
       <c r="AG2">
-        <v>1184.98</v>
+        <v>1185.98</v>
       </c>
       <c r="AH2">
-        <v>1058.82</v>
+        <v>1056.8</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1026,7 +1035,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>21.03</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1046,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>885.5</v>
+        <v>877.75</v>
       </c>
       <c r="D3">
-        <v>-3.33</v>
+        <v>-0.88</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1058,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.32</v>
+        <v>-10.11</v>
       </c>
       <c r="H3">
-        <v>67.23999999999999</v>
+        <v>65.78</v>
       </c>
       <c r="I3">
-        <v>0.8</v>
+        <v>1.47</v>
       </c>
       <c r="J3">
-        <v>7.19</v>
+        <v>-0.26</v>
       </c>
       <c r="K3">
-        <v>-2.33</v>
+        <v>-6.41</v>
       </c>
       <c r="L3">
-        <v>33.65</v>
+        <v>26.7</v>
       </c>
       <c r="M3">
-        <v>59.89</v>
+        <v>58.07</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>890.6900000000001</v>
+        <v>893.23</v>
       </c>
       <c r="Q3">
-        <v>883.9</v>
+        <v>883.3099999999999</v>
       </c>
       <c r="R3">
-        <v>896.36</v>
+        <v>894.91</v>
       </c>
       <c r="S3">
-        <v>773.5700000000001</v>
+        <v>774.25</v>
       </c>
       <c r="T3">
-        <v>14.47</v>
+        <v>13.37</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,34 +1112,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>50</v>
+        <v>48.14</v>
       </c>
       <c r="Z3">
-        <v>0.96</v>
+        <v>0.2</v>
       </c>
       <c r="AA3">
-        <v>-2.2</v>
+        <v>-1.72</v>
       </c>
       <c r="AB3">
-        <v>3.16</v>
+        <v>1.92</v>
       </c>
       <c r="AC3">
-        <v>73.27</v>
+        <v>58.42</v>
       </c>
       <c r="AD3">
-        <v>75.95</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="AE3">
-        <v>23.76</v>
+        <v>23.17</v>
       </c>
       <c r="AF3">
-        <v>22.4</v>
+        <v>-13.23</v>
       </c>
       <c r="AG3">
-        <v>909.03</v>
+        <v>908.4400000000001</v>
       </c>
       <c r="AH3">
-        <v>858.77</v>
+        <v>858.1799999999999</v>
       </c>
       <c r="AI3">
         <v>826.96</v>
@@ -1139,7 +1148,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>24.49</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1159,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1814.7</v>
+        <v>1825.9</v>
       </c>
       <c r="D4">
-        <v>-2.3</v>
+        <v>0.62</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1171,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-6.46</v>
+        <v>-5.88</v>
       </c>
       <c r="H4">
-        <v>33.96</v>
+        <v>34.78</v>
       </c>
       <c r="I4">
-        <v>-3.11</v>
+        <v>-2.26</v>
       </c>
       <c r="J4">
-        <v>-3.89</v>
+        <v>-2.62</v>
       </c>
       <c r="K4">
-        <v>23.4</v>
+        <v>22.87</v>
       </c>
       <c r="L4">
-        <v>26.13</v>
+        <v>28.62</v>
       </c>
       <c r="M4">
-        <v>26.34</v>
+        <v>25.89</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P4">
-        <v>1855.7</v>
+        <v>1847.26</v>
       </c>
       <c r="Q4">
-        <v>1882.32</v>
+        <v>1879.62</v>
       </c>
       <c r="R4">
-        <v>1828.05</v>
+        <v>1830.05</v>
       </c>
       <c r="S4">
-        <v>1675.32</v>
+        <v>1675.88</v>
       </c>
       <c r="T4">
-        <v>8.32</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,34 +1225,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>43.71</v>
+        <v>45.83</v>
       </c>
       <c r="Z4">
-        <v>8.92</v>
+        <v>5.45</v>
       </c>
       <c r="AA4">
-        <v>20.32</v>
+        <v>17.35</v>
       </c>
       <c r="AB4">
-        <v>-11.4</v>
+        <v>-11.9</v>
       </c>
       <c r="AC4">
-        <v>7.08</v>
+        <v>7.3</v>
       </c>
       <c r="AD4">
-        <v>16.01</v>
+        <v>10.7</v>
       </c>
       <c r="AE4">
-        <v>46.21</v>
+        <v>46.65</v>
       </c>
       <c r="AF4">
-        <v>71.84</v>
+        <v>-20.34</v>
       </c>
       <c r="AG4">
-        <v>1943.08</v>
+        <v>1945.42</v>
       </c>
       <c r="AH4">
-        <v>1821.56</v>
+        <v>1813.81</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1252,7 +1261,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>19.11</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1272,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1922.9</v>
+        <v>1914.6</v>
       </c>
       <c r="D5">
-        <v>0.89</v>
+        <v>-0.43</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,46 +1284,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.84</v>
+        <v>-20.18</v>
       </c>
       <c r="H5">
-        <v>10.16</v>
+        <v>9.68</v>
       </c>
       <c r="I5">
-        <v>0.49</v>
+        <v>-1.8</v>
       </c>
       <c r="J5">
-        <v>-9.1</v>
+        <v>-9.5</v>
       </c>
       <c r="K5">
-        <v>10.16</v>
+        <v>8.6</v>
       </c>
       <c r="L5">
-        <v>-14.78</v>
+        <v>-16.76</v>
       </c>
       <c r="M5">
-        <v>20.32</v>
+        <v>20.02</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P5">
-        <v>1924.12</v>
+        <v>1917.1</v>
       </c>
       <c r="Q5">
-        <v>2016.88</v>
+        <v>2008.29</v>
       </c>
       <c r="R5">
-        <v>2025.53</v>
+        <v>2023.97</v>
       </c>
       <c r="S5">
-        <v>2096.26</v>
+        <v>2094.86</v>
       </c>
       <c r="T5">
-        <v>-8.27</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,34 +1338,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>36.58</v>
+        <v>35.53</v>
       </c>
       <c r="Z5">
-        <v>-34.98</v>
+        <v>-36.17</v>
       </c>
       <c r="AA5">
-        <v>-19.19</v>
+        <v>-22.59</v>
       </c>
       <c r="AB5">
-        <v>-15.79</v>
+        <v>-13.58</v>
       </c>
       <c r="AC5">
-        <v>15.38</v>
+        <v>17.65</v>
       </c>
       <c r="AD5">
-        <v>15.96</v>
+        <v>15.51</v>
       </c>
       <c r="AE5">
-        <v>48.61</v>
+        <v>47.96</v>
       </c>
       <c r="AF5">
-        <v>-57.36</v>
+        <v>-27.65</v>
       </c>
       <c r="AG5">
-        <v>2169.05</v>
+        <v>2163.31</v>
       </c>
       <c r="AH5">
-        <v>1864.7</v>
+        <v>1853.26</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1365,7 +1374,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>34.24</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1385,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>795.6</v>
+        <v>800.65</v>
       </c>
       <c r="D6">
-        <v>-0.48</v>
+        <v>0.63</v>
       </c>
       <c r="E6">
         <v>1129.9</v>
@@ -1388,46 +1397,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-29.59</v>
+        <v>-29.14</v>
       </c>
       <c r="H6">
-        <v>13</v>
+        <v>13.71</v>
       </c>
       <c r="I6">
-        <v>-1.83</v>
+        <v>0.54</v>
       </c>
       <c r="J6">
-        <v>1.96</v>
+        <v>-0.31</v>
       </c>
       <c r="K6">
-        <v>5.12</v>
+        <v>6.57</v>
       </c>
       <c r="L6">
-        <v>-29.49</v>
+        <v>-28.88</v>
       </c>
       <c r="M6">
-        <v>16.08</v>
+        <v>15.59</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P6">
-        <v>798.39</v>
+        <v>799.25</v>
       </c>
       <c r="Q6">
-        <v>796.97</v>
+        <v>795.84</v>
       </c>
       <c r="R6">
-        <v>770.9</v>
+        <v>772.71</v>
       </c>
       <c r="S6">
-        <v>855.61</v>
+        <v>854.48</v>
       </c>
       <c r="T6">
-        <v>-7.01</v>
+        <v>-6.3</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1451,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>52</v>
+        <v>53.64</v>
       </c>
       <c r="Z6">
-        <v>7.6</v>
+        <v>7.25</v>
       </c>
       <c r="AA6">
-        <v>8.800000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="AB6">
-        <v>-1.19</v>
+        <v>-1.24</v>
       </c>
       <c r="AC6">
-        <v>32.7</v>
+        <v>26.83</v>
       </c>
       <c r="AD6">
-        <v>34.29</v>
+        <v>31.75</v>
       </c>
       <c r="AE6">
-        <v>25.31</v>
+        <v>25.16</v>
       </c>
       <c r="AF6">
-        <v>-66.27</v>
+        <v>-60.45</v>
       </c>
       <c r="AG6">
-        <v>825.73</v>
+        <v>821.9299999999999</v>
       </c>
       <c r="AH6">
-        <v>768.21</v>
+        <v>769.76</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1478,7 +1487,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>36.87</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1498,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3267.5</v>
+        <v>3262</v>
       </c>
       <c r="D7">
-        <v>-0.43</v>
+        <v>-0.17</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,25 +1510,25 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-5.42</v>
+        <v>-5.58</v>
       </c>
       <c r="H7">
-        <v>72.75</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="I7">
-        <v>-5.42</v>
+        <v>-3.68</v>
       </c>
       <c r="J7">
-        <v>24.32</v>
+        <v>23.61</v>
       </c>
       <c r="K7">
-        <v>34.28</v>
+        <v>30.09</v>
       </c>
       <c r="L7">
-        <v>30.25</v>
+        <v>33.31</v>
       </c>
       <c r="M7">
-        <v>32.82</v>
+        <v>31.94</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1528,19 +1537,19 @@
         <v>87</v>
       </c>
       <c r="P7">
-        <v>3311.26</v>
+        <v>3286.34</v>
       </c>
       <c r="Q7">
-        <v>3078.61</v>
+        <v>3110.3</v>
       </c>
       <c r="R7">
-        <v>2761.13</v>
+        <v>2774.06</v>
       </c>
       <c r="S7">
-        <v>2423</v>
+        <v>2426.94</v>
       </c>
       <c r="T7">
-        <v>34.85</v>
+        <v>34.41</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1564,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>64.67</v>
+        <v>64.23</v>
       </c>
       <c r="Z7">
-        <v>184.69</v>
+        <v>173.45</v>
       </c>
       <c r="AA7">
-        <v>184.16</v>
+        <v>182.02</v>
       </c>
       <c r="AB7">
-        <v>0.52</v>
+        <v>-8.58</v>
       </c>
       <c r="AC7">
-        <v>14.83</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>34.04</v>
+        <v>15.77</v>
       </c>
       <c r="AE7">
-        <v>139.52</v>
+        <v>135.86</v>
       </c>
       <c r="AF7">
-        <v>-64.36</v>
+        <v>-54.16</v>
       </c>
       <c r="AG7">
-        <v>3672.7</v>
+        <v>3669.84</v>
       </c>
       <c r="AH7">
-        <v>2484.51</v>
+        <v>2550.75</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1591,7 +1600,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>58.93</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1611,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8105</v>
+        <v>7991.5</v>
       </c>
       <c r="D8">
-        <v>-0.8</v>
+        <v>-1.4</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1614,25 +1623,25 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-20.79</v>
+        <v>-21.9</v>
       </c>
       <c r="H8">
-        <v>36.8</v>
+        <v>34.89</v>
       </c>
       <c r="I8">
-        <v>-1.03</v>
+        <v>-1.93</v>
       </c>
       <c r="J8">
-        <v>-1.23</v>
+        <v>-1.36</v>
       </c>
       <c r="K8">
-        <v>18.63</v>
+        <v>16.21</v>
       </c>
       <c r="L8">
-        <v>-17.9</v>
+        <v>-18.32</v>
       </c>
       <c r="M8">
-        <v>14.03</v>
+        <v>13.88</v>
       </c>
       <c r="N8">
         <v>43</v>
@@ -1641,19 +1650,19 @@
         <v>51</v>
       </c>
       <c r="P8">
-        <v>8208.700000000001</v>
+        <v>8177.3</v>
       </c>
       <c r="Q8">
-        <v>8102.22</v>
+        <v>8099.2</v>
       </c>
       <c r="R8">
-        <v>7981.23</v>
+        <v>7984.88</v>
       </c>
       <c r="S8">
-        <v>7401.09</v>
+        <v>7399.85</v>
       </c>
       <c r="T8">
-        <v>9.51</v>
+        <v>8</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1677,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>51.23</v>
+        <v>46.89</v>
       </c>
       <c r="Z8">
-        <v>74.73</v>
+        <v>56.12</v>
       </c>
       <c r="AA8">
-        <v>79.55</v>
+        <v>74.87</v>
       </c>
       <c r="AB8">
-        <v>-4.82</v>
+        <v>-18.75</v>
       </c>
       <c r="AC8">
-        <v>34.45</v>
+        <v>15.83</v>
       </c>
       <c r="AD8">
-        <v>55.14</v>
+        <v>37.8</v>
       </c>
       <c r="AE8">
-        <v>232.09</v>
+        <v>225.12</v>
       </c>
       <c r="AF8">
-        <v>-37.66</v>
+        <v>-38.04</v>
       </c>
       <c r="AG8">
-        <v>8343.959999999999</v>
+        <v>8345.07</v>
       </c>
       <c r="AH8">
-        <v>7860.49</v>
+        <v>7853.33</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1704,7 +1713,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>30.75</v>
+        <v>28.06</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1894,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1903,588 +1912,591 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>4.02</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-3.56</v>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>6.09</v>
+        <v>0.46</v>
       </c>
       <c r="D8" s="6">
-        <v>7.19</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.1</v>
+        <v>-0.65</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.41</v>
+        <v>7.19</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.89</v>
+        <v>-0.26</v>
       </c>
       <c r="E9" s="7">
-        <v>-4.3</v>
+        <v>-7.45</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-8.09</v>
+        <v>-3.89</v>
       </c>
       <c r="D10" s="6">
-        <v>-9.1</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.01</v>
+        <v>-2.62</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.27</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>5.18</v>
+        <v>-9.1</v>
       </c>
       <c r="D11" s="6">
-        <v>1.96</v>
+        <v>-9.5</v>
       </c>
       <c r="E11" s="7">
-        <v>-3.22</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>27.17</v>
+        <v>1.96</v>
       </c>
       <c r="D12" s="6">
-        <v>24.32</v>
+        <v>-0.31</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.85</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.45</v>
+        <v>24.32</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.23</v>
+        <v>23.61</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.78</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.39</v>
+        <v>-1.23</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.83</v>
+        <v>-1.36</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>4.39</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D15" s="6">
-        <v>0.8</v>
+        <v>-3.09</v>
       </c>
       <c r="E15" s="7">
-        <v>-3.59</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.11</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.69</v>
+        <v>1.47</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.67</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.07</v>
+        <v>-3.11</v>
       </c>
       <c r="D17" s="6">
-        <v>0.49</v>
+        <v>-2.26</v>
       </c>
       <c r="E17" s="8">
-        <v>1.56</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.98</v>
+        <v>0.49</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.83</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.15</v>
+        <v>-1.8</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-4.64</v>
+        <v>-1.83</v>
       </c>
       <c r="D19" s="6">
-        <v>-5.42</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.78</v>
+        <v>0.54</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2.37</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.39</v>
+        <v>-5.42</v>
       </c>
       <c r="D20" s="6">
-        <v>-1.03</v>
+        <v>-3.68</v>
       </c>
       <c r="E20" s="8">
-        <v>0.36</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>22.74</v>
+        <v>-1.03</v>
       </c>
       <c r="D21" s="6">
-        <v>22.08</v>
+        <v>-1.93</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.66</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>36.75</v>
+        <v>22.08</v>
       </c>
       <c r="D22" s="6">
-        <v>33.65</v>
+        <v>17.76</v>
       </c>
       <c r="E22" s="7">
-        <v>-3.1</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>25.92</v>
+        <v>33.65</v>
       </c>
       <c r="D23" s="6">
-        <v>26.13</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.21</v>
+        <v>26.7</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-6.95</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-19.33</v>
+        <v>26.13</v>
       </c>
       <c r="D24" s="6">
-        <v>-14.78</v>
+        <v>28.62</v>
       </c>
       <c r="E24" s="8">
-        <v>4.55</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-29.33</v>
+        <v>-14.78</v>
       </c>
       <c r="D25" s="6">
-        <v>-29.49</v>
+        <v>-16.76</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.16</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>31.21</v>
+        <v>-29.49</v>
       </c>
       <c r="D26" s="6">
-        <v>30.25</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.96</v>
+        <v>-28.88</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.61</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-17.19</v>
+        <v>30.25</v>
       </c>
       <c r="D27" s="6">
-        <v>-17.9</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.71</v>
+        <v>33.31</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.06</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>8.16</v>
+        <v>-17.9</v>
       </c>
       <c r="D28" s="6">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.62</v>
+        <v>-18.32</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>0.91</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.33</v>
+        <v>4.17</v>
       </c>
       <c r="E29" s="7">
-        <v>-3.24</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>25.26</v>
+        <v>-2.33</v>
       </c>
       <c r="D30" s="6">
-        <v>23.4</v>
+        <v>-6.41</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.86</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>8.390000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="D31" s="6">
-        <v>10.16</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.77</v>
+        <v>22.87</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>5.84</v>
+        <v>10.16</v>
       </c>
       <c r="D32" s="6">
-        <v>5.12</v>
+        <v>8.6</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.72</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>34.43</v>
+        <v>5.12</v>
       </c>
       <c r="D33" s="6">
-        <v>34.28</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.15</v>
+        <v>6.57</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.45</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>19.5</v>
+        <v>34.28</v>
       </c>
       <c r="D34" s="6">
-        <v>18.63</v>
+        <v>30.09</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.87</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-10.88</v>
+        <v>18.63</v>
       </c>
       <c r="D35" s="6">
-        <v>-11.37</v>
+        <v>16.21</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.49</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-6.2</v>
+        <v>-11.37</v>
       </c>
       <c r="D36" s="6">
-        <v>-9.32</v>
+        <v>-13.71</v>
       </c>
       <c r="E36" s="7">
-        <v>-3.12</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-4.26</v>
+        <v>-9.32</v>
       </c>
       <c r="D37" s="6">
-        <v>-6.46</v>
+        <v>-10.11</v>
       </c>
       <c r="E37" s="7">
-        <v>-2.2</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-20.55</v>
+        <v>-6.46</v>
       </c>
       <c r="D38" s="6">
-        <v>-19.84</v>
+        <v>-5.88</v>
       </c>
       <c r="E38" s="8">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-29.25</v>
+        <v>-19.84</v>
       </c>
       <c r="D39" s="6">
-        <v>-29.59</v>
+        <v>-20.18</v>
       </c>
       <c r="E39" s="7">
         <v>-0.34</v>
@@ -2492,399 +2504,450 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-5.02</v>
+        <v>-29.59</v>
       </c>
       <c r="D40" s="6">
-        <v>-5.42</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.4</v>
+        <v>-29.14</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.45</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-20.15</v>
+        <v>-5.42</v>
       </c>
       <c r="D41" s="6">
-        <v>-20.79</v>
+        <v>-5.58</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.64</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>1106.6</v>
+        <v>-20.79</v>
       </c>
       <c r="D42" s="6">
-        <v>1100.5</v>
+        <v>-21.9</v>
       </c>
       <c r="E42" s="7">
-        <v>-6.1</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>916</v>
+        <v>1100.5</v>
       </c>
       <c r="D43" s="6">
-        <v>885.5</v>
+        <v>1071.5</v>
       </c>
       <c r="E43" s="7">
-        <v>-30.5</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>1857.4</v>
+        <v>885.5</v>
       </c>
       <c r="D44" s="6">
-        <v>1814.7</v>
+        <v>877.75</v>
       </c>
       <c r="E44" s="7">
-        <v>-42.7</v>
+        <v>-7.75</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1905.9</v>
+        <v>1814.7</v>
       </c>
       <c r="D45" s="6">
-        <v>1922.9</v>
+        <v>1825.9</v>
       </c>
       <c r="E45" s="8">
-        <v>17</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>799.4</v>
+        <v>1922.9</v>
       </c>
       <c r="D46" s="6">
-        <v>795.6</v>
+        <v>1914.6</v>
       </c>
       <c r="E46" s="7">
-        <v>-3.8</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>3281.5</v>
+        <v>795.6</v>
       </c>
       <c r="D47" s="6">
-        <v>3267.5</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-14</v>
+        <v>800.65</v>
+      </c>
+      <c r="E47" s="8">
+        <v>5.05</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>8170.5</v>
+        <v>3267.5</v>
       </c>
       <c r="D48" s="6">
-        <v>8105</v>
+        <v>3262</v>
       </c>
       <c r="E48" s="7">
-        <v>-65.5</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>48.99</v>
+        <v>8105</v>
       </c>
       <c r="D49" s="6">
-        <v>47.89</v>
+        <v>7991.5</v>
       </c>
       <c r="E49" s="7">
-        <v>-1.1</v>
+        <v>-113.5</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C50" s="6">
-        <v>58.22</v>
+        <v>57</v>
       </c>
       <c r="D50" s="6">
-        <v>50</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-8.220000000000001</v>
+        <v>71</v>
+      </c>
+      <c r="E50" s="8">
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C51" s="6">
-        <v>50.73</v>
+        <v>71</v>
       </c>
       <c r="D51" s="6">
-        <v>43.71</v>
+        <v>57</v>
       </c>
       <c r="E51" s="7">
-        <v>-7.02</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>32.79</v>
+        <v>47.89</v>
       </c>
       <c r="D52" s="6">
-        <v>36.58</v>
-      </c>
-      <c r="E52" s="8">
-        <v>3.79</v>
+        <v>42.94</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-4.95</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>53.31</v>
+        <v>50</v>
       </c>
       <c r="D53" s="6">
-        <v>52</v>
+        <v>48.14</v>
       </c>
       <c r="E53" s="7">
-        <v>-1.31</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>65.76000000000001</v>
+        <v>43.71</v>
       </c>
       <c r="D54" s="6">
-        <v>64.67</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-1.09</v>
+        <v>45.83</v>
+      </c>
+      <c r="E54" s="8">
+        <v>2.12</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>53.91</v>
+        <v>36.58</v>
       </c>
       <c r="D55" s="6">
-        <v>51.23</v>
+        <v>35.53</v>
       </c>
       <c r="E55" s="7">
-        <v>-2.68</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>-31.84</v>
+        <v>52</v>
       </c>
       <c r="D56" s="6">
-        <v>-13.66</v>
+        <v>53.64</v>
       </c>
       <c r="E56" s="8">
-        <v>18.18</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>28.88</v>
+        <v>64.67</v>
       </c>
       <c r="D57" s="6">
-        <v>22.4</v>
+        <v>64.23</v>
       </c>
       <c r="E57" s="7">
-        <v>-6.48</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>8.470000000000001</v>
+        <v>51.23</v>
       </c>
       <c r="D58" s="6">
-        <v>71.84</v>
-      </c>
-      <c r="E58" s="8">
-        <v>63.37</v>
+        <v>46.89</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-4.34</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>55.77</v>
+        <v>-13.66</v>
       </c>
       <c r="D59" s="6">
-        <v>-57.36</v>
+        <v>-41.14</v>
       </c>
       <c r="E59" s="7">
-        <v>-113.13</v>
+        <v>-27.48</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>12.24</v>
+        <v>22.4</v>
       </c>
       <c r="D60" s="6">
-        <v>-66.27</v>
+        <v>-13.23</v>
       </c>
       <c r="E60" s="7">
-        <v>-78.51000000000001</v>
+        <v>-35.63</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-55.28</v>
+        <v>71.84</v>
       </c>
       <c r="D61" s="6">
-        <v>-64.36</v>
+        <v>-20.34</v>
       </c>
       <c r="E61" s="7">
-        <v>-9.08</v>
+        <v>-92.18000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-19.28</v>
+        <v>-57.36</v>
       </c>
       <c r="D62" s="6">
+        <v>-27.65</v>
+      </c>
+      <c r="E62" s="8">
+        <v>29.71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-66.27</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-60.45</v>
+      </c>
+      <c r="E63" s="8">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-64.36</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-54.16</v>
+      </c>
+      <c r="E64" s="8">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
         <v>-37.66</v>
       </c>
-      <c r="E62" s="7">
-        <v>-18.38</v>
+      <c r="D65" s="6">
+        <v>-38.04</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2908,28 +2971,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2943,16 +3006,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>49.4</v>
+        <v>48.2</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="G2" s="11">
-        <v>14</v>
+        <v>11.7</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3083,25 +3146,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.5989</v>
+        <v>0.5807</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3282</v>
+        <v>0.3194</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2634</v>
+        <v>0.2589</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2032</v>
+        <v>0.2002</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1608</v>
+        <v>0.1559</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1403</v>
+        <v>0.1388</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0654</v>
+        <v>0.0592</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,25 +190,46 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.0 → 48.1</t>
+    <t>48.1 → 52.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.1</t>
+  </si>
+  <si>
+    <t>52.4</t>
+  </si>
+  <si>
+    <t>45.8 → 50.0</t>
+  </si>
+  <si>
+    <t>45.8</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>46.9 → 57.6</t>
+  </si>
+  <si>
+    <t>46.9</t>
+  </si>
+  <si>
+    <t>57.6</t>
+  </si>
+  <si>
+    <t>53.6 → 46.1</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>48.1</t>
-  </si>
-  <si>
-    <t>51.2 → 46.9</t>
-  </si>
-  <si>
-    <t>51.2</t>
-  </si>
-  <si>
-    <t>46.9</t>
+    <t>53.6</t>
+  </si>
+  <si>
+    <t>46.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -294,14 +315,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,13 +355,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -418,6 +439,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -933,10 +955,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1071.5</v>
+        <v>1078</v>
       </c>
       <c r="D2">
-        <v>-2.64</v>
+        <v>0.61</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -945,46 +967,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-13.71</v>
+        <v>-13.18</v>
       </c>
       <c r="H2">
-        <v>43.18</v>
+        <v>44.05</v>
       </c>
       <c r="I2">
-        <v>-3.09</v>
+        <v>-2.28</v>
       </c>
       <c r="J2">
-        <v>-0.65</v>
+        <v>-0.34</v>
       </c>
       <c r="K2">
-        <v>4.17</v>
+        <v>3.67</v>
       </c>
       <c r="L2">
-        <v>17.76</v>
+        <v>15.72</v>
       </c>
       <c r="M2">
-        <v>5.92</v>
+        <v>5.97</v>
       </c>
       <c r="N2">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>1099.72</v>
+        <v>1094.68</v>
       </c>
       <c r="Q2">
-        <v>1121.39</v>
+        <v>1121.83</v>
       </c>
       <c r="R2">
-        <v>1106.98</v>
+        <v>1105.29</v>
       </c>
       <c r="S2">
-        <v>946.46</v>
+        <v>947.49</v>
       </c>
       <c r="T2">
-        <v>13.21</v>
+        <v>13.77</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -999,34 +1021,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>42.94</v>
+        <v>44.33</v>
       </c>
       <c r="Z2">
-        <v>-0.93</v>
+        <v>-3.22</v>
       </c>
       <c r="AA2">
-        <v>5.43</v>
+        <v>3.7</v>
       </c>
       <c r="AB2">
-        <v>-6.35</v>
+        <v>-6.92</v>
       </c>
       <c r="AC2">
-        <v>6.52</v>
+        <v>5.19</v>
       </c>
       <c r="AD2">
-        <v>11.45</v>
+        <v>8.41</v>
       </c>
       <c r="AE2">
-        <v>41.71</v>
+        <v>40.08</v>
       </c>
       <c r="AF2">
-        <v>-41.14</v>
+        <v>-70.72</v>
       </c>
       <c r="AG2">
-        <v>1185.98</v>
+        <v>1185.02</v>
       </c>
       <c r="AH2">
-        <v>1056.8</v>
+        <v>1058.65</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1035,7 +1057,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>20.26</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,10 +1068,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>877.75</v>
+        <v>895</v>
       </c>
       <c r="D3">
-        <v>-0.88</v>
+        <v>1.97</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1058,46 +1080,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-10.11</v>
+        <v>-8.35</v>
       </c>
       <c r="H3">
-        <v>65.78</v>
+        <v>69.03</v>
       </c>
       <c r="I3">
-        <v>1.47</v>
+        <v>-0.32</v>
       </c>
       <c r="J3">
-        <v>-0.26</v>
+        <v>0.62</v>
       </c>
       <c r="K3">
-        <v>-6.41</v>
+        <v>-4.57</v>
       </c>
       <c r="L3">
-        <v>26.7</v>
+        <v>25.07</v>
       </c>
       <c r="M3">
-        <v>58.07</v>
+        <v>58.2</v>
       </c>
       <c r="N3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O3">
         <v>66</v>
       </c>
       <c r="P3">
-        <v>893.23</v>
+        <v>892.65</v>
       </c>
       <c r="Q3">
-        <v>883.3099999999999</v>
+        <v>884.26</v>
       </c>
       <c r="R3">
-        <v>894.91</v>
+        <v>894.42</v>
       </c>
       <c r="S3">
-        <v>774.25</v>
+        <v>774.98</v>
       </c>
       <c r="T3">
-        <v>13.37</v>
+        <v>15.49</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1112,34 +1134,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.14</v>
+        <v>52.39</v>
       </c>
       <c r="Z3">
-        <v>0.2</v>
+        <v>0.98</v>
       </c>
       <c r="AA3">
-        <v>-1.72</v>
+        <v>-1.18</v>
       </c>
       <c r="AB3">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AC3">
-        <v>58.42</v>
+        <v>45.17</v>
       </c>
       <c r="AD3">
-        <v>74.54000000000001</v>
+        <v>58.95</v>
       </c>
       <c r="AE3">
-        <v>23.17</v>
+        <v>23.32</v>
       </c>
       <c r="AF3">
-        <v>-13.23</v>
+        <v>10.48</v>
       </c>
       <c r="AG3">
-        <v>908.4400000000001</v>
+        <v>909.66</v>
       </c>
       <c r="AH3">
-        <v>858.1799999999999</v>
+        <v>858.86</v>
       </c>
       <c r="AI3">
         <v>826.96</v>
@@ -1148,7 +1170,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>23.38</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1159,10 +1181,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1825.9</v>
+        <v>1849.3</v>
       </c>
       <c r="D4">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1171,46 +1193,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-5.88</v>
+        <v>-4.68</v>
       </c>
       <c r="H4">
-        <v>34.78</v>
+        <v>36.51</v>
       </c>
       <c r="I4">
-        <v>-2.26</v>
+        <v>-1.39</v>
       </c>
       <c r="J4">
-        <v>-2.62</v>
+        <v>-1.63</v>
       </c>
       <c r="K4">
-        <v>22.87</v>
+        <v>23.02</v>
       </c>
       <c r="L4">
-        <v>28.62</v>
+        <v>27.3</v>
       </c>
       <c r="M4">
-        <v>25.89</v>
+        <v>26.71</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P4">
-        <v>1847.26</v>
+        <v>1842.04</v>
       </c>
       <c r="Q4">
-        <v>1879.62</v>
+        <v>1875.08</v>
       </c>
       <c r="R4">
-        <v>1830.05</v>
+        <v>1831.18</v>
       </c>
       <c r="S4">
-        <v>1675.88</v>
+        <v>1676.63</v>
       </c>
       <c r="T4">
-        <v>8.949999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1225,34 +1247,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>45.83</v>
+        <v>50.05</v>
       </c>
       <c r="Z4">
-        <v>5.45</v>
+        <v>4.53</v>
       </c>
       <c r="AA4">
-        <v>17.35</v>
+        <v>14.79</v>
       </c>
       <c r="AB4">
-        <v>-11.9</v>
+        <v>-10.25</v>
       </c>
       <c r="AC4">
-        <v>7.3</v>
+        <v>20.2</v>
       </c>
       <c r="AD4">
-        <v>10.7</v>
+        <v>11.53</v>
       </c>
       <c r="AE4">
-        <v>46.65</v>
+        <v>45.61</v>
       </c>
       <c r="AF4">
-        <v>-20.34</v>
+        <v>-23.12</v>
       </c>
       <c r="AG4">
-        <v>1945.42</v>
+        <v>1935.65</v>
       </c>
       <c r="AH4">
-        <v>1813.81</v>
+        <v>1814.51</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1261,7 +1283,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>21.8</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1272,10 +1294,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1914.6</v>
+        <v>1931.3</v>
       </c>
       <c r="D5">
-        <v>-0.43</v>
+        <v>0.87</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1284,46 +1306,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-20.18</v>
+        <v>-19.49</v>
       </c>
       <c r="H5">
-        <v>9.68</v>
+        <v>10.64</v>
       </c>
       <c r="I5">
-        <v>-1.8</v>
+        <v>0.15</v>
       </c>
       <c r="J5">
-        <v>-9.5</v>
+        <v>-7.43</v>
       </c>
       <c r="K5">
-        <v>8.6</v>
+        <v>7.49</v>
       </c>
       <c r="L5">
-        <v>-16.76</v>
+        <v>-17.12</v>
       </c>
       <c r="M5">
-        <v>20.02</v>
+        <v>20.29</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>1917.1</v>
+        <v>1917.68</v>
       </c>
       <c r="Q5">
-        <v>2008.29</v>
+        <v>2000.7</v>
       </c>
       <c r="R5">
-        <v>2023.97</v>
+        <v>2022.92</v>
       </c>
       <c r="S5">
-        <v>2094.86</v>
+        <v>2093.5</v>
       </c>
       <c r="T5">
-        <v>-8.609999999999999</v>
+        <v>-7.75</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1338,34 +1360,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>35.53</v>
+        <v>39.32</v>
       </c>
       <c r="Z5">
-        <v>-36.17</v>
+        <v>-35.35</v>
       </c>
       <c r="AA5">
-        <v>-22.59</v>
+        <v>-25.14</v>
       </c>
       <c r="AB5">
-        <v>-13.58</v>
+        <v>-10.21</v>
       </c>
       <c r="AC5">
-        <v>17.65</v>
+        <v>25.56</v>
       </c>
       <c r="AD5">
-        <v>15.51</v>
+        <v>19.53</v>
       </c>
       <c r="AE5">
-        <v>47.96</v>
+        <v>47.26</v>
       </c>
       <c r="AF5">
-        <v>-27.65</v>
+        <v>-20.12</v>
       </c>
       <c r="AG5">
-        <v>2163.31</v>
+        <v>2155.16</v>
       </c>
       <c r="AH5">
-        <v>1853.26</v>
+        <v>1846.23</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1374,7 +1396,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>33.17</v>
+        <v>29.55</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1385,58 +1407,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>800.65</v>
+        <v>778.25</v>
       </c>
       <c r="D6">
-        <v>0.63</v>
+        <v>-2.8</v>
       </c>
       <c r="E6">
-        <v>1129.9</v>
+        <v>1125.8</v>
       </c>
       <c r="F6">
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-29.14</v>
+        <v>-30.87</v>
       </c>
       <c r="H6">
-        <v>13.71</v>
+        <v>10.53</v>
       </c>
       <c r="I6">
-        <v>0.54</v>
+        <v>-2.14</v>
       </c>
       <c r="J6">
-        <v>-0.31</v>
+        <v>-5.45</v>
       </c>
       <c r="K6">
-        <v>6.57</v>
+        <v>5.86</v>
       </c>
       <c r="L6">
-        <v>-28.88</v>
+        <v>-31.12</v>
       </c>
       <c r="M6">
-        <v>15.59</v>
+        <v>14.86</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P6">
-        <v>799.25</v>
+        <v>795.84</v>
       </c>
       <c r="Q6">
-        <v>795.84</v>
+        <v>794.26</v>
       </c>
       <c r="R6">
-        <v>772.71</v>
+        <v>774.0599999999999</v>
       </c>
       <c r="S6">
-        <v>854.48</v>
+        <v>853.12</v>
       </c>
       <c r="T6">
-        <v>-6.3</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1451,34 +1473,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>53.64</v>
+        <v>46.13</v>
       </c>
       <c r="Z6">
-        <v>7.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA6">
-        <v>8.49</v>
+        <v>7.81</v>
       </c>
       <c r="AB6">
-        <v>-1.24</v>
+        <v>-2.71</v>
       </c>
       <c r="AC6">
-        <v>26.83</v>
+        <v>15.98</v>
       </c>
       <c r="AD6">
-        <v>31.75</v>
+        <v>25.17</v>
       </c>
       <c r="AE6">
-        <v>25.16</v>
+        <v>26.82</v>
       </c>
       <c r="AF6">
-        <v>-60.45</v>
+        <v>-5.33</v>
       </c>
       <c r="AG6">
-        <v>821.9299999999999</v>
+        <v>820.6</v>
       </c>
       <c r="AH6">
-        <v>769.76</v>
+        <v>767.9299999999999</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1487,7 +1509,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>35.25</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1498,10 +1520,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3262</v>
+        <v>3267.4</v>
       </c>
       <c r="D7">
-        <v>-0.17</v>
+        <v>0.17</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1510,46 +1532,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-5.58</v>
+        <v>-5.43</v>
       </c>
       <c r="H7">
-        <v>72.45999999999999</v>
+        <v>72.75</v>
       </c>
       <c r="I7">
-        <v>-3.68</v>
+        <v>-1.82</v>
       </c>
       <c r="J7">
-        <v>23.61</v>
+        <v>24.32</v>
       </c>
       <c r="K7">
-        <v>30.09</v>
+        <v>30.4</v>
       </c>
       <c r="L7">
-        <v>33.31</v>
+        <v>33.17</v>
       </c>
       <c r="M7">
-        <v>31.94</v>
+        <v>32.71</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P7">
-        <v>3286.34</v>
+        <v>3274.2</v>
       </c>
       <c r="Q7">
-        <v>3110.3</v>
+        <v>3141.91</v>
       </c>
       <c r="R7">
-        <v>2774.06</v>
+        <v>2786.58</v>
       </c>
       <c r="S7">
-        <v>2426.94</v>
+        <v>2431.12</v>
       </c>
       <c r="T7">
-        <v>34.41</v>
+        <v>34.4</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1564,34 +1586,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>64.23</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="Z7">
-        <v>173.45</v>
+        <v>163.09</v>
       </c>
       <c r="AA7">
-        <v>182.02</v>
+        <v>178.24</v>
       </c>
       <c r="AB7">
-        <v>-8.58</v>
+        <v>-15.14</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AD7">
-        <v>15.77</v>
+        <v>5.09</v>
       </c>
       <c r="AE7">
-        <v>135.86</v>
+        <v>135.29</v>
       </c>
       <c r="AF7">
-        <v>-54.16</v>
+        <v>-61.05</v>
       </c>
       <c r="AG7">
-        <v>3669.84</v>
+        <v>3658.2</v>
       </c>
       <c r="AH7">
-        <v>2550.75</v>
+        <v>2625.61</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1600,7 +1622,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>55.02</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1611,10 +1633,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7991.5</v>
+        <v>8307</v>
       </c>
       <c r="D8">
-        <v>-1.4</v>
+        <v>3.95</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1623,46 +1645,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-21.9</v>
+        <v>-18.82</v>
       </c>
       <c r="H8">
-        <v>34.89</v>
+        <v>40.21</v>
       </c>
       <c r="I8">
-        <v>-1.93</v>
+        <v>-0.82</v>
       </c>
       <c r="J8">
-        <v>-1.36</v>
+        <v>3.17</v>
       </c>
       <c r="K8">
-        <v>16.21</v>
+        <v>22.14</v>
       </c>
       <c r="L8">
-        <v>-18.32</v>
+        <v>-15.58</v>
       </c>
       <c r="M8">
-        <v>13.88</v>
+        <v>14.67</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P8">
-        <v>8177.3</v>
+        <v>8163.5</v>
       </c>
       <c r="Q8">
-        <v>8099.2</v>
+        <v>8111.38</v>
       </c>
       <c r="R8">
-        <v>7984.88</v>
+        <v>7997.96</v>
       </c>
       <c r="S8">
-        <v>7399.85</v>
+        <v>7400.11</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>12.26</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1677,34 +1699,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>46.89</v>
+        <v>57.64</v>
       </c>
       <c r="Z8">
-        <v>56.12</v>
+        <v>66.06</v>
       </c>
       <c r="AA8">
-        <v>74.87</v>
+        <v>73.11</v>
       </c>
       <c r="AB8">
-        <v>-18.75</v>
+        <v>-7.05</v>
       </c>
       <c r="AC8">
-        <v>15.83</v>
+        <v>26.83</v>
       </c>
       <c r="AD8">
-        <v>37.8</v>
+        <v>25.7</v>
       </c>
       <c r="AE8">
-        <v>225.12</v>
+        <v>241.79</v>
       </c>
       <c r="AF8">
-        <v>-38.04</v>
+        <v>62.76</v>
       </c>
       <c r="AG8">
-        <v>8345.07</v>
+        <v>8373.379999999999</v>
       </c>
       <c r="AH8">
-        <v>7853.33</v>
+        <v>7849.37</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1713,7 +1735,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>28.06</v>
+        <v>29.83</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1914,7 +1936,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>55</v>
@@ -1932,1022 +1954,1062 @@
         <v>62</v>
       </c>
     </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C10" s="7">
         <v>-0.65</v>
       </c>
-      <c r="E8" s="7">
+      <c r="D10" s="7">
+        <v>-0.34</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-0.26</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-2.62</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-1.63</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-9.5</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-7.43</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-0.31</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-5.45</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-5.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>23.61</v>
+      </c>
+      <c r="D15" s="7">
+        <v>24.32</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1.36</v>
+      </c>
+      <c r="D16" s="7">
+        <v>3.17</v>
+      </c>
+      <c r="E16" s="8">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-3.09</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-2.28</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1.47</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-0.32</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-2.26</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-1.39</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.8</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.54</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-2.14</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-3.68</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-1.82</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-1.93</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-0.82</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>17.76</v>
+      </c>
+      <c r="D24" s="7">
+        <v>15.72</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>26.7</v>
+      </c>
+      <c r="D25" s="7">
+        <v>25.07</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>28.62</v>
+      </c>
+      <c r="D26" s="7">
+        <v>27.3</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-16.76</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-17.12</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-28.88</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-31.12</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>33.31</v>
+      </c>
+      <c r="D29" s="7">
+        <v>33.17</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-18.32</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-15.58</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>4.17</v>
+      </c>
+      <c r="D31" s="7">
+        <v>3.67</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-6.41</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-4.57</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>22.87</v>
+      </c>
+      <c r="D33" s="7">
+        <v>23.02</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>8.6</v>
+      </c>
+      <c r="D34" s="7">
+        <v>7.49</v>
+      </c>
+      <c r="E34" s="9">
         <v>-1.11</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>6.57</v>
+      </c>
+      <c r="D35" s="7">
+        <v>5.86</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>30.09</v>
+      </c>
+      <c r="D36" s="7">
+        <v>30.4</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>16.21</v>
+      </c>
+      <c r="D37" s="7">
+        <v>22.14</v>
+      </c>
+      <c r="E37" s="8">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-13.71</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-13.18</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>7.19</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-0.26</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-7.45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-10.11</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-8.35</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-3.89</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-2.62</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-5.88</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-4.68</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-9.1</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-9.5</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-20.18</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-19.49</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1.96</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-0.31</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-29.14</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-30.87</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>24.32</v>
-      </c>
-      <c r="D13" s="6">
-        <v>23.61</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-5.58</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-5.43</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.36</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-21.9</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-18.82</v>
+      </c>
+      <c r="E44" s="8">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.09</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1071.5</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1078</v>
+      </c>
+      <c r="E45" s="8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1.47</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>877.75</v>
+      </c>
+      <c r="D46" s="7">
+        <v>895</v>
+      </c>
+      <c r="E46" s="8">
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.11</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.26</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1825.9</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1849.3</v>
+      </c>
+      <c r="E47" s="8">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.49</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.8</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>1914.6</v>
+      </c>
+      <c r="D48" s="7">
+        <v>1931.3</v>
+      </c>
+      <c r="E48" s="8">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.83</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.54</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>800.65</v>
+      </c>
+      <c r="D49" s="7">
+        <v>778.25</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-22.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-5.42</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-3.68</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>3262</v>
+      </c>
+      <c r="D50" s="7">
+        <v>3267.4</v>
+      </c>
+      <c r="E50" s="8">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>7991.5</v>
+      </c>
+      <c r="D51" s="7">
+        <v>8307</v>
+      </c>
+      <c r="E51" s="8">
+        <v>315.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>22.08</v>
-      </c>
-      <c r="D22" s="6">
-        <v>17.76</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-4.32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B52" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7">
+        <v>71</v>
+      </c>
+      <c r="D52" s="7">
+        <v>57</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>33.65</v>
-      </c>
-      <c r="D23" s="6">
-        <v>26.7</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-6.95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="7">
+        <v>57</v>
+      </c>
+      <c r="D53" s="7">
+        <v>71</v>
+      </c>
+      <c r="E53" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>42.94</v>
+      </c>
+      <c r="D54" s="7">
+        <v>44.33</v>
+      </c>
+      <c r="E54" s="8">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>48.14</v>
+      </c>
+      <c r="D55" s="7">
+        <v>52.39</v>
+      </c>
+      <c r="E55" s="8">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>26.13</v>
-      </c>
-      <c r="D24" s="6">
-        <v>28.62</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>45.83</v>
+      </c>
+      <c r="D56" s="7">
+        <v>50.05</v>
+      </c>
+      <c r="E56" s="8">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-14.78</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-16.76</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>35.53</v>
+      </c>
+      <c r="D57" s="7">
+        <v>39.32</v>
+      </c>
+      <c r="E57" s="8">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-29.49</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-28.88</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>53.64</v>
+      </c>
+      <c r="D58" s="7">
+        <v>46.13</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-7.51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>30.25</v>
-      </c>
-      <c r="D27" s="6">
-        <v>33.31</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>64.23</v>
+      </c>
+      <c r="D59" s="7">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="E59" s="8">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-17.9</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-18.32</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>46.89</v>
+      </c>
+      <c r="D60" s="7">
+        <v>57.64</v>
+      </c>
+      <c r="E60" s="8">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="D29" s="6">
-        <v>4.17</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-4.61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-41.14</v>
+      </c>
+      <c r="D61" s="7">
+        <v>-70.72</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-29.58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-2.33</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.41</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-4.08</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-13.23</v>
+      </c>
+      <c r="D62" s="7">
+        <v>10.48</v>
+      </c>
+      <c r="E62" s="8">
+        <v>23.71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>23.4</v>
-      </c>
-      <c r="D31" s="6">
-        <v>22.87</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-20.34</v>
+      </c>
+      <c r="D63" s="7">
+        <v>-23.12</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>10.16</v>
-      </c>
-      <c r="D32" s="6">
-        <v>8.6</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-27.65</v>
+      </c>
+      <c r="D64" s="7">
+        <v>-20.12</v>
+      </c>
+      <c r="E64" s="8">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>5.12</v>
-      </c>
-      <c r="D33" s="6">
-        <v>6.57</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-60.45</v>
+      </c>
+      <c r="D65" s="7">
+        <v>-5.33</v>
+      </c>
+      <c r="E65" s="8">
+        <v>55.12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>34.28</v>
-      </c>
-      <c r="D34" s="6">
-        <v>30.09</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-4.19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="7">
+        <v>-54.16</v>
+      </c>
+      <c r="D66" s="7">
+        <v>-61.05</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-6.89</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>18.63</v>
-      </c>
-      <c r="D35" s="6">
-        <v>16.21</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-11.37</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-13.71</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-9.32</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-10.11</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-6.46</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-5.88</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-19.84</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-20.18</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-29.59</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-29.14</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-5.42</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-5.58</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-20.79</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-21.9</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>1100.5</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1071.5</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>885.5</v>
-      </c>
-      <c r="D44" s="6">
-        <v>877.75</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-7.75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1814.7</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1825.9</v>
-      </c>
-      <c r="E45" s="8">
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>1922.9</v>
-      </c>
-      <c r="D46" s="6">
-        <v>1914.6</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-8.300000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>795.6</v>
-      </c>
-      <c r="D47" s="6">
-        <v>800.65</v>
-      </c>
-      <c r="E47" s="8">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>3267.5</v>
-      </c>
-      <c r="D48" s="6">
-        <v>3262</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>8105</v>
-      </c>
-      <c r="D49" s="6">
-        <v>7991.5</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-113.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>57</v>
-      </c>
-      <c r="D50" s="6">
-        <v>71</v>
-      </c>
-      <c r="E50" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
-        <v>71</v>
-      </c>
-      <c r="D51" s="6">
-        <v>57</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>47.89</v>
-      </c>
-      <c r="D52" s="6">
-        <v>42.94</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>50</v>
-      </c>
-      <c r="D53" s="6">
-        <v>48.14</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>43.71</v>
-      </c>
-      <c r="D54" s="6">
-        <v>45.83</v>
-      </c>
-      <c r="E54" s="8">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>36.58</v>
-      </c>
-      <c r="D55" s="6">
-        <v>35.53</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>52</v>
-      </c>
-      <c r="D56" s="6">
-        <v>53.64</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>64.67</v>
-      </c>
-      <c r="D57" s="6">
-        <v>64.23</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>51.23</v>
-      </c>
-      <c r="D58" s="6">
-        <v>46.89</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-4.34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="6">
-        <v>-13.66</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-41.14</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-27.48</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>22.4</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-13.23</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-35.63</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>71.84</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-20.34</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-92.18000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-57.36</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-27.65</v>
-      </c>
-      <c r="E62" s="8">
-        <v>29.71</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-66.27</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-60.45</v>
-      </c>
-      <c r="E63" s="8">
-        <v>5.82</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-64.36</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-54.16</v>
-      </c>
-      <c r="E64" s="8">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-37.66</v>
-      </c>
-      <c r="D65" s="6">
+      <c r="C67" s="7">
         <v>-38.04</v>
       </c>
-      <c r="E65" s="7">
-        <v>-0.38</v>
+      <c r="D67" s="7">
+        <v>62.76</v>
+      </c>
+      <c r="E67" s="8">
+        <v>100.8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2967,60 +3029,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>50.6</v>
+      </c>
+      <c r="E2" s="12">
         <v>70</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>48.2</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>1.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>11.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>1.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>12.6</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>60</v>
       </c>
     </row>
@@ -3122,49 +3184,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.5807</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3194</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2589</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2002</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1559</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1388</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0592</v>
+      <c r="A2" s="15">
+        <v>0.5820000000000001</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3271</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2671</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2029</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1486</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1467</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0597</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,46 +190,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.1 → 52.4</t>
+    <t>44.3 → 54.1</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>48.1</t>
-  </si>
-  <si>
-    <t>52.4</t>
-  </si>
-  <si>
-    <t>45.8 → 50.0</t>
-  </si>
-  <si>
-    <t>45.8</t>
+    <t>44.3</t>
+  </si>
+  <si>
+    <t>54.1</t>
+  </si>
+  <si>
+    <t>50.0 → 48.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.0</t>
   </si>
   <si>
-    <t>46.9 → 57.6</t>
-  </si>
-  <si>
-    <t>46.9</t>
-  </si>
-  <si>
-    <t>57.6</t>
-  </si>
-  <si>
-    <t>53.6 → 46.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.6</t>
-  </si>
-  <si>
-    <t>46.1</t>
+    <t>48.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -955,10 +937,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1078</v>
+        <v>1130.6</v>
       </c>
       <c r="D2">
-        <v>0.61</v>
+        <v>4.88</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -967,46 +949,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-13.18</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="H2">
-        <v>44.05</v>
+        <v>51.08</v>
       </c>
       <c r="I2">
-        <v>-2.28</v>
+        <v>1.24</v>
       </c>
       <c r="J2">
-        <v>-0.34</v>
+        <v>5.75</v>
       </c>
       <c r="K2">
-        <v>3.67</v>
+        <v>7.22</v>
       </c>
       <c r="L2">
-        <v>15.72</v>
+        <v>20.54</v>
       </c>
       <c r="M2">
-        <v>5.97</v>
+        <v>6.73</v>
       </c>
       <c r="N2">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="P2">
-        <v>1094.68</v>
+        <v>1097.44</v>
       </c>
       <c r="Q2">
-        <v>1121.83</v>
+        <v>1123.51</v>
       </c>
       <c r="R2">
-        <v>1105.29</v>
+        <v>1105.03</v>
       </c>
       <c r="S2">
-        <v>947.49</v>
+        <v>948.87</v>
       </c>
       <c r="T2">
-        <v>13.77</v>
+        <v>19.15</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1021,34 +1003,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.33</v>
+        <v>54.07</v>
       </c>
       <c r="Z2">
-        <v>-3.22</v>
+        <v>-0.78</v>
       </c>
       <c r="AA2">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="AB2">
-        <v>-6.92</v>
+        <v>-3.58</v>
       </c>
       <c r="AC2">
-        <v>5.19</v>
+        <v>25.82</v>
       </c>
       <c r="AD2">
-        <v>8.41</v>
+        <v>12.51</v>
       </c>
       <c r="AE2">
-        <v>40.08</v>
+        <v>42.28</v>
       </c>
       <c r="AF2">
-        <v>-70.72</v>
+        <v>34.54</v>
       </c>
       <c r="AG2">
-        <v>1185.02</v>
+        <v>1185.7</v>
       </c>
       <c r="AH2">
-        <v>1058.65</v>
+        <v>1061.33</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1057,7 +1039,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>19.6</v>
+        <v>21.03</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1068,10 +1050,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D3">
-        <v>1.97</v>
+        <v>-0.45</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1080,46 +1062,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.35</v>
+        <v>-8.76</v>
       </c>
       <c r="H3">
-        <v>69.03</v>
+        <v>68.28</v>
       </c>
       <c r="I3">
-        <v>-0.32</v>
+        <v>0.22</v>
       </c>
       <c r="J3">
-        <v>0.62</v>
+        <v>1.71</v>
       </c>
       <c r="K3">
-        <v>-4.57</v>
+        <v>-1.37</v>
       </c>
       <c r="L3">
-        <v>25.07</v>
+        <v>20.73</v>
       </c>
       <c r="M3">
-        <v>58.2</v>
+        <v>58.9</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P3">
-        <v>892.65</v>
+        <v>893.05</v>
       </c>
       <c r="Q3">
-        <v>884.26</v>
+        <v>884.86</v>
       </c>
       <c r="R3">
-        <v>894.42</v>
+        <v>893.4</v>
       </c>
       <c r="S3">
-        <v>774.98</v>
+        <v>775.77</v>
       </c>
       <c r="T3">
-        <v>15.49</v>
+        <v>14.85</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1134,34 +1116,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.39</v>
+        <v>51.34</v>
       </c>
       <c r="Z3">
-        <v>0.98</v>
+        <v>1.27</v>
       </c>
       <c r="AA3">
-        <v>-1.18</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AB3">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="AC3">
-        <v>45.17</v>
+        <v>48.2</v>
       </c>
       <c r="AD3">
-        <v>58.95</v>
+        <v>50.6</v>
       </c>
       <c r="AE3">
-        <v>23.32</v>
+        <v>22.49</v>
       </c>
       <c r="AF3">
-        <v>10.48</v>
+        <v>4.68</v>
       </c>
       <c r="AG3">
-        <v>909.66</v>
+        <v>910.3099999999999</v>
       </c>
       <c r="AH3">
-        <v>858.86</v>
+        <v>859.42</v>
       </c>
       <c r="AI3">
         <v>826.96</v>
@@ -1170,7 +1152,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>25.49</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1181,10 +1163,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1849.3</v>
+        <v>1839</v>
       </c>
       <c r="D4">
-        <v>1.28</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1193,46 +1175,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-4.68</v>
+        <v>-5.21</v>
       </c>
       <c r="H4">
-        <v>36.51</v>
+        <v>35.75</v>
       </c>
       <c r="I4">
-        <v>-1.39</v>
+        <v>-1.28</v>
       </c>
       <c r="J4">
-        <v>-1.63</v>
+        <v>-5.21</v>
       </c>
       <c r="K4">
-        <v>23.02</v>
+        <v>26.3</v>
       </c>
       <c r="L4">
-        <v>27.3</v>
+        <v>28.57</v>
       </c>
       <c r="M4">
-        <v>26.71</v>
+        <v>26.62</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P4">
-        <v>1842.04</v>
+        <v>1837.26</v>
       </c>
       <c r="Q4">
-        <v>1875.08</v>
+        <v>1873.72</v>
       </c>
       <c r="R4">
-        <v>1831.18</v>
+        <v>1831.97</v>
       </c>
       <c r="S4">
-        <v>1676.63</v>
+        <v>1677.36</v>
       </c>
       <c r="T4">
-        <v>10.3</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1247,34 +1229,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>50.05</v>
+        <v>48.27</v>
       </c>
       <c r="Z4">
-        <v>4.53</v>
+        <v>2.94</v>
       </c>
       <c r="AA4">
-        <v>14.79</v>
+        <v>12.42</v>
       </c>
       <c r="AB4">
-        <v>-10.25</v>
+        <v>-9.48</v>
       </c>
       <c r="AC4">
-        <v>20.2</v>
+        <v>32.15</v>
       </c>
       <c r="AD4">
-        <v>11.53</v>
+        <v>19.88</v>
       </c>
       <c r="AE4">
-        <v>45.61</v>
+        <v>44.63</v>
       </c>
       <c r="AF4">
-        <v>-23.12</v>
+        <v>-35.15</v>
       </c>
       <c r="AG4">
-        <v>1935.65</v>
+        <v>1936.32</v>
       </c>
       <c r="AH4">
-        <v>1814.51</v>
+        <v>1811.12</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1283,7 +1265,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>20.58</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1294,10 +1276,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1931.3</v>
+        <v>1938.8</v>
       </c>
       <c r="D5">
-        <v>0.87</v>
+        <v>0.39</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1306,46 +1288,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.49</v>
+        <v>-19.17</v>
       </c>
       <c r="H5">
-        <v>10.64</v>
+        <v>11.07</v>
       </c>
       <c r="I5">
-        <v>0.15</v>
+        <v>1.31</v>
       </c>
       <c r="J5">
-        <v>-7.43</v>
+        <v>-6.93</v>
       </c>
       <c r="K5">
-        <v>7.49</v>
+        <v>10.72</v>
       </c>
       <c r="L5">
-        <v>-17.12</v>
+        <v>-15.58</v>
       </c>
       <c r="M5">
-        <v>20.29</v>
+        <v>20.46</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P5">
-        <v>1917.68</v>
+        <v>1922.7</v>
       </c>
       <c r="Q5">
-        <v>2000.7</v>
+        <v>1994.17</v>
       </c>
       <c r="R5">
-        <v>2022.92</v>
+        <v>2021.69</v>
       </c>
       <c r="S5">
-        <v>2093.5</v>
+        <v>2092.08</v>
       </c>
       <c r="T5">
-        <v>-7.75</v>
+        <v>-7.33</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1360,34 +1342,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>39.32</v>
+        <v>41</v>
       </c>
       <c r="Z5">
-        <v>-35.35</v>
+        <v>-33.71</v>
       </c>
       <c r="AA5">
-        <v>-25.14</v>
+        <v>-26.85</v>
       </c>
       <c r="AB5">
-        <v>-10.21</v>
+        <v>-6.86</v>
       </c>
       <c r="AC5">
-        <v>25.56</v>
+        <v>35.27</v>
       </c>
       <c r="AD5">
-        <v>19.53</v>
+        <v>26.16</v>
       </c>
       <c r="AE5">
-        <v>47.26</v>
+        <v>45.4</v>
       </c>
       <c r="AF5">
-        <v>-20.12</v>
+        <v>7.05</v>
       </c>
       <c r="AG5">
-        <v>2155.16</v>
+        <v>2147.45</v>
       </c>
       <c r="AH5">
-        <v>1846.23</v>
+        <v>1840.89</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1396,7 +1378,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>29.55</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1407,10 +1389,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>778.25</v>
+        <v>781.35</v>
       </c>
       <c r="D6">
-        <v>-2.8</v>
+        <v>0.4</v>
       </c>
       <c r="E6">
         <v>1125.8</v>
@@ -1419,46 +1401,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-30.87</v>
+        <v>-30.6</v>
       </c>
       <c r="H6">
-        <v>10.53</v>
+        <v>10.97</v>
       </c>
       <c r="I6">
-        <v>-2.14</v>
+        <v>-2.97</v>
       </c>
       <c r="J6">
-        <v>-5.45</v>
+        <v>-3.52</v>
       </c>
       <c r="K6">
-        <v>5.86</v>
+        <v>8.34</v>
       </c>
       <c r="L6">
-        <v>-31.12</v>
+        <v>-29.23</v>
       </c>
       <c r="M6">
-        <v>14.86</v>
+        <v>15</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P6">
-        <v>795.84</v>
+        <v>791.05</v>
       </c>
       <c r="Q6">
-        <v>794.26</v>
+        <v>793.08</v>
       </c>
       <c r="R6">
-        <v>774.0599999999999</v>
+        <v>775.49</v>
       </c>
       <c r="S6">
-        <v>853.12</v>
+        <v>851.89</v>
       </c>
       <c r="T6">
-        <v>-8.779999999999999</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1473,34 +1455,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>46.13</v>
+        <v>47.23</v>
       </c>
       <c r="Z6">
-        <v>5.1</v>
+        <v>3.61</v>
       </c>
       <c r="AA6">
-        <v>7.81</v>
+        <v>6.97</v>
       </c>
       <c r="AB6">
-        <v>-2.71</v>
+        <v>-3.36</v>
       </c>
       <c r="AC6">
-        <v>15.98</v>
+        <v>12.61</v>
       </c>
       <c r="AD6">
-        <v>25.17</v>
+        <v>18.47</v>
       </c>
       <c r="AE6">
-        <v>26.82</v>
+        <v>25.6</v>
       </c>
       <c r="AF6">
-        <v>-5.33</v>
+        <v>-70.31</v>
       </c>
       <c r="AG6">
-        <v>820.6</v>
+        <v>819.5</v>
       </c>
       <c r="AH6">
-        <v>767.9299999999999</v>
+        <v>766.66</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1509,7 +1491,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>35.56</v>
+        <v>35.84</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1520,10 +1502,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3267.4</v>
+        <v>3194.6</v>
       </c>
       <c r="D7">
-        <v>0.17</v>
+        <v>-2.23</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1532,46 +1514,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-5.43</v>
+        <v>-7.53</v>
       </c>
       <c r="H7">
-        <v>72.75</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I7">
-        <v>-1.82</v>
+        <v>-2.98</v>
       </c>
       <c r="J7">
-        <v>24.32</v>
+        <v>21.23</v>
       </c>
       <c r="K7">
-        <v>30.4</v>
+        <v>27.96</v>
       </c>
       <c r="L7">
-        <v>33.17</v>
+        <v>31.01</v>
       </c>
       <c r="M7">
-        <v>32.71</v>
+        <v>32.58</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P7">
-        <v>3274.2</v>
+        <v>3254.6</v>
       </c>
       <c r="Q7">
-        <v>3141.91</v>
+        <v>3166.96</v>
       </c>
       <c r="R7">
-        <v>2786.58</v>
+        <v>2799.29</v>
       </c>
       <c r="S7">
-        <v>2431.12</v>
+        <v>2435</v>
       </c>
       <c r="T7">
-        <v>34.4</v>
+        <v>31.2</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1586,34 +1568,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>64.48999999999999</v>
+        <v>58.33</v>
       </c>
       <c r="Z7">
-        <v>163.09</v>
+        <v>147.32</v>
       </c>
       <c r="AA7">
-        <v>178.24</v>
+        <v>172.05</v>
       </c>
       <c r="AB7">
-        <v>-15.14</v>
+        <v>-24.73</v>
       </c>
       <c r="AC7">
         <v>0.45</v>
       </c>
       <c r="AD7">
-        <v>5.09</v>
+        <v>0.3</v>
       </c>
       <c r="AE7">
-        <v>135.29</v>
+        <v>139.48</v>
       </c>
       <c r="AF7">
-        <v>-61.05</v>
+        <v>-72.39</v>
       </c>
       <c r="AG7">
-        <v>3658.2</v>
+        <v>3638.32</v>
       </c>
       <c r="AH7">
-        <v>2625.61</v>
+        <v>2695.6</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1622,7 +1604,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>52.99</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1633,10 +1615,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8307</v>
+        <v>8160</v>
       </c>
       <c r="D8">
-        <v>3.95</v>
+        <v>-1.77</v>
       </c>
       <c r="E8">
         <v>10232.91</v>
@@ -1645,46 +1627,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-18.82</v>
+        <v>-20.26</v>
       </c>
       <c r="H8">
-        <v>40.21</v>
+        <v>37.73</v>
       </c>
       <c r="I8">
-        <v>-0.82</v>
+        <v>-1.01</v>
       </c>
       <c r="J8">
-        <v>3.17</v>
+        <v>1.2</v>
       </c>
       <c r="K8">
-        <v>22.14</v>
+        <v>22.7</v>
       </c>
       <c r="L8">
-        <v>-15.58</v>
+        <v>-17.2</v>
       </c>
       <c r="M8">
-        <v>14.67</v>
+        <v>14.46</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P8">
-        <v>8163.5</v>
+        <v>8146.8</v>
       </c>
       <c r="Q8">
-        <v>8111.38</v>
+        <v>8111.82</v>
       </c>
       <c r="R8">
-        <v>7997.96</v>
+        <v>8009.97</v>
       </c>
       <c r="S8">
-        <v>7400.11</v>
+        <v>7400.1</v>
       </c>
       <c r="T8">
-        <v>12.26</v>
+        <v>10.27</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1699,34 +1681,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.64</v>
+        <v>52.33</v>
       </c>
       <c r="Z8">
-        <v>66.06</v>
+        <v>61.37</v>
       </c>
       <c r="AA8">
-        <v>73.11</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="AB8">
-        <v>-7.05</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="AC8">
-        <v>26.83</v>
+        <v>33.36</v>
       </c>
       <c r="AD8">
-        <v>25.7</v>
+        <v>25.34</v>
       </c>
       <c r="AE8">
-        <v>241.79</v>
+        <v>241.37</v>
       </c>
       <c r="AF8">
-        <v>62.76</v>
+        <v>-44.57</v>
       </c>
       <c r="AG8">
-        <v>8373.379999999999</v>
+        <v>8374.15</v>
       </c>
       <c r="AH8">
-        <v>7849.37</v>
+        <v>7849.5</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1735,7 +1717,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>29.83</v>
+        <v>31.37</v>
       </c>
     </row>
   </sheetData>
@@ -1876,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1916,7 +1898,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1935,803 +1917,797 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-0.34</v>
+      </c>
+      <c r="D8" s="7">
+        <v>5.75</v>
+      </c>
+      <c r="E8" s="8">
+        <v>6.09</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>74</v>
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.71</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-0.65</v>
+        <v>-1.63</v>
       </c>
       <c r="D10" s="7">
-        <v>-0.34</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.31</v>
+        <v>-5.21</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-3.58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-0.26</v>
+        <v>-7.43</v>
       </c>
       <c r="D11" s="7">
-        <v>0.62</v>
+        <v>-6.93</v>
       </c>
       <c r="E11" s="8">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-2.62</v>
+        <v>-5.45</v>
       </c>
       <c r="D12" s="7">
-        <v>-1.63</v>
+        <v>-3.52</v>
       </c>
       <c r="E12" s="8">
-        <v>0.99</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-9.5</v>
+        <v>24.32</v>
       </c>
       <c r="D13" s="7">
-        <v>-7.43</v>
-      </c>
-      <c r="E13" s="8">
-        <v>2.07</v>
+        <v>21.23</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-3.09</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-0.31</v>
+        <v>3.17</v>
       </c>
       <c r="D14" s="7">
-        <v>-5.45</v>
+        <v>1.2</v>
       </c>
       <c r="E14" s="9">
-        <v>-5.14</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="7">
-        <v>23.61</v>
+        <v>-2.28</v>
       </c>
       <c r="D15" s="7">
-        <v>24.32</v>
+        <v>1.24</v>
       </c>
       <c r="E15" s="8">
-        <v>0.71</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="7">
-        <v>-1.36</v>
+        <v>-0.32</v>
       </c>
       <c r="D16" s="7">
-        <v>3.17</v>
+        <v>0.22</v>
       </c>
       <c r="E16" s="8">
-        <v>4.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>-3.09</v>
+        <v>-1.39</v>
       </c>
       <c r="D17" s="7">
-        <v>-2.28</v>
+        <v>-1.28</v>
       </c>
       <c r="E17" s="8">
-        <v>0.8100000000000001</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>1.47</v>
+        <v>0.15</v>
       </c>
       <c r="D18" s="7">
-        <v>-0.32</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-1.79</v>
+        <v>1.31</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.16</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-2.26</v>
+        <v>-2.14</v>
       </c>
       <c r="D19" s="7">
-        <v>-1.39</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.87</v>
+        <v>-2.97</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-1.8</v>
+        <v>-1.82</v>
       </c>
       <c r="D20" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.95</v>
+        <v>-2.98</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>0.54</v>
+        <v>-0.82</v>
       </c>
       <c r="D21" s="7">
-        <v>-2.14</v>
+        <v>-1.01</v>
       </c>
       <c r="E21" s="9">
-        <v>-2.68</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C22" s="7">
-        <v>-3.68</v>
+        <v>15.72</v>
       </c>
       <c r="D22" s="7">
-        <v>-1.82</v>
+        <v>20.54</v>
       </c>
       <c r="E22" s="8">
-        <v>1.86</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C23" s="7">
-        <v>-1.93</v>
+        <v>25.07</v>
       </c>
       <c r="D23" s="7">
-        <v>-0.82</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.11</v>
+        <v>20.73</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-4.34</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="7">
-        <v>17.76</v>
+        <v>27.3</v>
       </c>
       <c r="D24" s="7">
-        <v>15.72</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-2.04</v>
+        <v>28.57</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.27</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="7">
-        <v>26.7</v>
+        <v>-17.12</v>
       </c>
       <c r="D25" s="7">
-        <v>25.07</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-1.63</v>
+        <v>-15.58</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.54</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>28.62</v>
+        <v>-31.12</v>
       </c>
       <c r="D26" s="7">
-        <v>27.3</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-1.32</v>
+        <v>-29.23</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>-16.76</v>
+        <v>33.17</v>
       </c>
       <c r="D27" s="7">
-        <v>-17.12</v>
+        <v>31.01</v>
       </c>
       <c r="E27" s="9">
-        <v>-0.36</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>-28.88</v>
+        <v>-15.58</v>
       </c>
       <c r="D28" s="7">
-        <v>-31.12</v>
+        <v>-17.2</v>
       </c>
       <c r="E28" s="9">
-        <v>-2.24</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="7">
-        <v>33.31</v>
+        <v>3.67</v>
       </c>
       <c r="D29" s="7">
-        <v>33.17</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.14</v>
+        <v>7.22</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3.55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" s="7">
-        <v>-18.32</v>
+        <v>-4.57</v>
       </c>
       <c r="D30" s="7">
-        <v>-15.58</v>
+        <v>-1.37</v>
       </c>
       <c r="E30" s="8">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="7">
-        <v>4.17</v>
+        <v>23.02</v>
       </c>
       <c r="D31" s="7">
-        <v>3.67</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-0.5</v>
+        <v>26.3</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.28</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="7">
-        <v>-6.41</v>
+        <v>7.49</v>
       </c>
       <c r="D32" s="7">
-        <v>-4.57</v>
+        <v>10.72</v>
       </c>
       <c r="E32" s="8">
-        <v>1.84</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="7">
-        <v>22.87</v>
+        <v>5.86</v>
       </c>
       <c r="D33" s="7">
-        <v>23.02</v>
+        <v>8.34</v>
       </c>
       <c r="E33" s="8">
-        <v>0.15</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="7">
-        <v>8.6</v>
+        <v>30.4</v>
       </c>
       <c r="D34" s="7">
-        <v>7.49</v>
+        <v>27.96</v>
       </c>
       <c r="E34" s="9">
-        <v>-1.11</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>6.57</v>
+        <v>22.14</v>
       </c>
       <c r="D35" s="7">
-        <v>5.86</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-0.71</v>
+        <v>22.7</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C36" s="7">
-        <v>30.09</v>
+        <v>-13.18</v>
       </c>
       <c r="D36" s="7">
-        <v>30.4</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="E36" s="8">
-        <v>0.31</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C37" s="7">
-        <v>16.21</v>
+        <v>-8.35</v>
       </c>
       <c r="D37" s="7">
-        <v>22.14</v>
-      </c>
-      <c r="E37" s="8">
-        <v>5.93</v>
+        <v>-8.76</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="7">
-        <v>-13.71</v>
+        <v>-4.68</v>
       </c>
       <c r="D38" s="7">
-        <v>-13.18</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.53</v>
+        <v>-5.21</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="7">
-        <v>-10.11</v>
+        <v>-19.49</v>
       </c>
       <c r="D39" s="7">
-        <v>-8.35</v>
+        <v>-19.17</v>
       </c>
       <c r="E39" s="8">
-        <v>1.76</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="7">
-        <v>-5.88</v>
+        <v>-30.87</v>
       </c>
       <c r="D40" s="7">
-        <v>-4.68</v>
+        <v>-30.6</v>
       </c>
       <c r="E40" s="8">
-        <v>1.2</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="7">
-        <v>-20.18</v>
+        <v>-5.43</v>
       </c>
       <c r="D41" s="7">
-        <v>-19.49</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.6899999999999999</v>
+        <v>-7.53</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="7">
-        <v>-29.14</v>
+        <v>-18.82</v>
       </c>
       <c r="D42" s="7">
-        <v>-30.87</v>
+        <v>-20.26</v>
       </c>
       <c r="E42" s="9">
-        <v>-1.73</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C43" s="7">
-        <v>-5.58</v>
+        <v>1078</v>
       </c>
       <c r="D43" s="7">
-        <v>-5.43</v>
+        <v>1130.6</v>
       </c>
       <c r="E43" s="8">
-        <v>0.15</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C44" s="7">
-        <v>-21.9</v>
+        <v>895</v>
       </c>
       <c r="D44" s="7">
-        <v>-18.82</v>
-      </c>
-      <c r="E44" s="8">
-        <v>3.08</v>
+        <v>891</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-4</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="7">
-        <v>1071.5</v>
+        <v>1849.3</v>
       </c>
       <c r="D45" s="7">
-        <v>1078</v>
-      </c>
-      <c r="E45" s="8">
-        <v>6.5</v>
+        <v>1839</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-10.3</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="7">
-        <v>877.75</v>
+        <v>1931.3</v>
       </c>
       <c r="D46" s="7">
-        <v>895</v>
+        <v>1938.8</v>
       </c>
       <c r="E46" s="8">
-        <v>17.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="7">
-        <v>1825.9</v>
+        <v>778.25</v>
       </c>
       <c r="D47" s="7">
-        <v>1849.3</v>
+        <v>781.35</v>
       </c>
       <c r="E47" s="8">
-        <v>23.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="7">
-        <v>1914.6</v>
+        <v>3267.4</v>
       </c>
       <c r="D48" s="7">
-        <v>1931.3</v>
-      </c>
-      <c r="E48" s="8">
-        <v>16.7</v>
+        <v>3194.6</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-72.8</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C49" s="7">
-        <v>800.65</v>
+        <v>8307</v>
       </c>
       <c r="D49" s="7">
-        <v>778.25</v>
+        <v>8160</v>
       </c>
       <c r="E49" s="9">
-        <v>-22.4</v>
+        <v>-147</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C50" s="7">
-        <v>3262</v>
+        <v>57</v>
       </c>
       <c r="D50" s="7">
-        <v>3267.4</v>
+        <v>71</v>
       </c>
       <c r="E50" s="8">
-        <v>5.4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C51" s="7">
-        <v>7991.5</v>
+        <v>71</v>
       </c>
       <c r="D51" s="7">
-        <v>8307</v>
-      </c>
-      <c r="E51" s="8">
-        <v>315.5</v>
+        <v>57</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2739,16 +2715,16 @@
         <v>37</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C52" s="7">
-        <v>71</v>
+        <v>44.33</v>
       </c>
       <c r="D52" s="7">
-        <v>57</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-14</v>
+        <v>54.07</v>
+      </c>
+      <c r="E52" s="8">
+        <v>9.74</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2756,260 +2732,226 @@
         <v>38</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C53" s="7">
-        <v>57</v>
+        <v>52.39</v>
       </c>
       <c r="D53" s="7">
-        <v>71</v>
-      </c>
-      <c r="E53" s="8">
-        <v>14</v>
+        <v>51.34</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="7">
-        <v>42.94</v>
+        <v>50.05</v>
       </c>
       <c r="D54" s="7">
-        <v>44.33</v>
-      </c>
-      <c r="E54" s="8">
-        <v>1.39</v>
+        <v>48.27</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="7">
-        <v>48.14</v>
+        <v>39.32</v>
       </c>
       <c r="D55" s="7">
-        <v>52.39</v>
+        <v>41</v>
       </c>
       <c r="E55" s="8">
-        <v>4.25</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="7">
-        <v>45.83</v>
+        <v>46.13</v>
       </c>
       <c r="D56" s="7">
-        <v>50.05</v>
+        <v>47.23</v>
       </c>
       <c r="E56" s="8">
-        <v>4.22</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="7">
-        <v>35.53</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="D57" s="7">
-        <v>39.32</v>
-      </c>
-      <c r="E57" s="8">
-        <v>3.79</v>
+        <v>58.33</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-6.16</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="7">
-        <v>53.64</v>
+        <v>57.64</v>
       </c>
       <c r="D58" s="7">
-        <v>46.13</v>
+        <v>52.33</v>
       </c>
       <c r="E58" s="9">
-        <v>-7.51</v>
+        <v>-5.31</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C59" s="7">
-        <v>64.23</v>
+        <v>-70.72</v>
       </c>
       <c r="D59" s="7">
-        <v>64.48999999999999</v>
+        <v>34.54</v>
       </c>
       <c r="E59" s="8">
-        <v>0.26</v>
+        <v>105.26</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C60" s="7">
-        <v>46.89</v>
+        <v>10.48</v>
       </c>
       <c r="D60" s="7">
-        <v>57.64</v>
-      </c>
-      <c r="E60" s="8">
-        <v>10.75</v>
+        <v>4.68</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-5.8</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="7">
-        <v>-41.14</v>
+        <v>-23.12</v>
       </c>
       <c r="D61" s="7">
-        <v>-70.72</v>
+        <v>-35.15</v>
       </c>
       <c r="E61" s="9">
-        <v>-29.58</v>
+        <v>-12.03</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="7">
-        <v>-13.23</v>
+        <v>-20.12</v>
       </c>
       <c r="D62" s="7">
-        <v>10.48</v>
+        <v>7.05</v>
       </c>
       <c r="E62" s="8">
-        <v>23.71</v>
+        <v>27.17</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="7">
-        <v>-20.34</v>
+        <v>-5.33</v>
       </c>
       <c r="D63" s="7">
-        <v>-23.12</v>
+        <v>-70.31</v>
       </c>
       <c r="E63" s="9">
-        <v>-2.78</v>
+        <v>-64.98</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C64" s="7">
-        <v>-27.65</v>
+        <v>-61.05</v>
       </c>
       <c r="D64" s="7">
-        <v>-20.12</v>
-      </c>
-      <c r="E64" s="8">
-        <v>7.53</v>
+        <v>-72.39</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-11.34</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="7">
-        <v>-60.45</v>
+        <v>62.76</v>
       </c>
       <c r="D65" s="7">
-        <v>-5.33</v>
-      </c>
-      <c r="E65" s="8">
-        <v>55.12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-54.16</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-61.05</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-6.89</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>-38.04</v>
-      </c>
-      <c r="D67" s="7">
-        <v>62.76</v>
-      </c>
-      <c r="E67" s="8">
-        <v>100.8</v>
+        <v>-44.57</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-107.33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3033,28 +2975,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3068,16 +3010,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="12">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="E2" s="12">
         <v>70</v>
       </c>
       <c r="F2" s="12">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G2" s="12">
-        <v>12.6</v>
+        <v>14.6</v>
       </c>
       <c r="H2" s="12">
         <v>57</v>
@@ -3208,25 +3150,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="15">
-        <v>0.5820000000000001</v>
+        <v>0.589</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3271</v>
+        <v>0.3258</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2671</v>
+        <v>0.2662</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2029</v>
+        <v>0.2046</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1486</v>
+        <v>0.15</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1467</v>
+        <v>0.1446</v>
       </c>
       <c r="G2" s="15">
-        <v>0.0597</v>
+        <v>0.0673</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,28 +190,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>44.3 → 54.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>44.3</t>
+    <t>54.1 → 49.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>54.1</t>
   </si>
   <si>
-    <t>50.0 → 48.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>48.3</t>
+    <t>49.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -297,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -337,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -421,7 +409,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -937,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1130.6</v>
+        <v>1104</v>
       </c>
       <c r="D2">
-        <v>4.88</v>
+        <v>-2.35</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -949,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-8.949999999999999</v>
+        <v>-11.09</v>
       </c>
       <c r="H2">
-        <v>51.08</v>
+        <v>47.52</v>
       </c>
       <c r="I2">
-        <v>1.24</v>
+        <v>-0.23</v>
       </c>
       <c r="J2">
-        <v>5.75</v>
+        <v>0.64</v>
       </c>
       <c r="K2">
-        <v>7.22</v>
+        <v>6.14</v>
       </c>
       <c r="L2">
-        <v>20.54</v>
+        <v>16.76</v>
       </c>
       <c r="M2">
-        <v>6.73</v>
+        <v>6.56</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>1097.44</v>
+        <v>1096.92</v>
       </c>
       <c r="Q2">
-        <v>1123.51</v>
+        <v>1122.66</v>
       </c>
       <c r="R2">
-        <v>1105.03</v>
+        <v>1103.28</v>
       </c>
       <c r="S2">
-        <v>948.87</v>
+        <v>950.2</v>
       </c>
       <c r="T2">
-        <v>19.15</v>
+        <v>16.19</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1003,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>54.07</v>
+        <v>49.37</v>
       </c>
       <c r="Z2">
-        <v>-0.78</v>
+        <v>-0.99</v>
       </c>
       <c r="AA2">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="AB2">
-        <v>-3.58</v>
+        <v>-3.03</v>
       </c>
       <c r="AC2">
-        <v>25.82</v>
+        <v>39.07</v>
       </c>
       <c r="AD2">
-        <v>12.51</v>
+        <v>23.36</v>
       </c>
       <c r="AE2">
-        <v>42.28</v>
+        <v>43.26</v>
       </c>
       <c r="AF2">
-        <v>34.54</v>
+        <v>-10.28</v>
       </c>
       <c r="AG2">
-        <v>1185.7</v>
+        <v>1185.45</v>
       </c>
       <c r="AH2">
-        <v>1061.33</v>
+        <v>1059.88</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1039,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>21.03</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1050,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D3">
-        <v>-0.45</v>
+        <v>0.45</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1062,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.76</v>
+        <v>-8.35</v>
       </c>
       <c r="H3">
-        <v>68.28</v>
+        <v>69.03</v>
       </c>
       <c r="I3">
-        <v>0.22</v>
+        <v>-2.29</v>
       </c>
       <c r="J3">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="K3">
-        <v>-1.37</v>
+        <v>-1.78</v>
       </c>
       <c r="L3">
-        <v>20.73</v>
+        <v>22.32</v>
       </c>
       <c r="M3">
-        <v>58.9</v>
+        <v>57.74</v>
       </c>
       <c r="N3">
         <v>57</v>
       </c>
       <c r="O3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>893.05</v>
+        <v>888.85</v>
       </c>
       <c r="Q3">
-        <v>884.86</v>
+        <v>885.66</v>
       </c>
       <c r="R3">
-        <v>893.4</v>
+        <v>892.17</v>
       </c>
       <c r="S3">
-        <v>775.77</v>
+        <v>776.64</v>
       </c>
       <c r="T3">
-        <v>14.85</v>
+        <v>15.24</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1116,43 +1103,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>51.34</v>
+        <v>52.37</v>
       </c>
       <c r="Z3">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
       <c r="AA3">
-        <v>-0.6899999999999999</v>
+        <v>-0.19</v>
       </c>
       <c r="AB3">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>48.2</v>
+        <v>57.8</v>
       </c>
       <c r="AD3">
-        <v>50.6</v>
+        <v>50.39</v>
       </c>
       <c r="AE3">
-        <v>22.49</v>
+        <v>22.39</v>
       </c>
       <c r="AF3">
-        <v>4.68</v>
+        <v>88.02</v>
       </c>
       <c r="AG3">
-        <v>910.3099999999999</v>
+        <v>911.33</v>
       </c>
       <c r="AH3">
-        <v>859.42</v>
+        <v>859.99</v>
       </c>
       <c r="AI3">
-        <v>826.96</v>
+        <v>835.99</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>27.32</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1163,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1839</v>
+        <v>1848.2</v>
       </c>
       <c r="D4">
-        <v>-0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1175,25 +1162,25 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-5.21</v>
+        <v>-4.73</v>
       </c>
       <c r="H4">
-        <v>35.75</v>
+        <v>36.43</v>
       </c>
       <c r="I4">
-        <v>-1.28</v>
+        <v>-0.5</v>
       </c>
       <c r="J4">
-        <v>-5.21</v>
+        <v>-0.96</v>
       </c>
       <c r="K4">
-        <v>26.3</v>
+        <v>23.59</v>
       </c>
       <c r="L4">
-        <v>28.57</v>
+        <v>28.46</v>
       </c>
       <c r="M4">
-        <v>26.62</v>
+        <v>26.56</v>
       </c>
       <c r="N4">
         <v>85</v>
@@ -1202,19 +1189,19 @@
         <v>80</v>
       </c>
       <c r="P4">
-        <v>1837.26</v>
+        <v>1835.42</v>
       </c>
       <c r="Q4">
-        <v>1873.72</v>
+        <v>1870.13</v>
       </c>
       <c r="R4">
-        <v>1831.97</v>
+        <v>1833.46</v>
       </c>
       <c r="S4">
-        <v>1677.36</v>
+        <v>1678.21</v>
       </c>
       <c r="T4">
-        <v>9.640000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1229,34 +1216,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>48.27</v>
+        <v>49.98</v>
       </c>
       <c r="Z4">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="AA4">
-        <v>12.42</v>
+        <v>10.41</v>
       </c>
       <c r="AB4">
-        <v>-9.48</v>
+        <v>-8.02</v>
       </c>
       <c r="AC4">
-        <v>32.15</v>
+        <v>43.55</v>
       </c>
       <c r="AD4">
-        <v>19.88</v>
+        <v>31.96</v>
       </c>
       <c r="AE4">
-        <v>44.63</v>
+        <v>45.01</v>
       </c>
       <c r="AF4">
-        <v>-35.15</v>
+        <v>-7.81</v>
       </c>
       <c r="AG4">
-        <v>1936.32</v>
+        <v>1929.72</v>
       </c>
       <c r="AH4">
-        <v>1811.12</v>
+        <v>1810.54</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1265,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>19.34</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1276,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1938.8</v>
+        <v>1974.6</v>
       </c>
       <c r="D5">
-        <v>0.39</v>
+        <v>1.85</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1288,25 +1275,25 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.17</v>
+        <v>-17.68</v>
       </c>
       <c r="H5">
-        <v>11.07</v>
+        <v>13.12</v>
       </c>
       <c r="I5">
-        <v>1.31</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
-        <v>-6.93</v>
+        <v>-4.58</v>
       </c>
       <c r="K5">
-        <v>10.72</v>
+        <v>9.27</v>
       </c>
       <c r="L5">
-        <v>-15.58</v>
+        <v>-15.81</v>
       </c>
       <c r="M5">
-        <v>20.46</v>
+        <v>21.15</v>
       </c>
       <c r="N5">
         <v>29</v>
@@ -1315,19 +1302,19 @@
         <v>45</v>
       </c>
       <c r="P5">
-        <v>1922.7</v>
+        <v>1936.44</v>
       </c>
       <c r="Q5">
-        <v>1994.17</v>
+        <v>1987.99</v>
       </c>
       <c r="R5">
-        <v>2021.69</v>
+        <v>2022.91</v>
       </c>
       <c r="S5">
-        <v>2092.08</v>
+        <v>2090.79</v>
       </c>
       <c r="T5">
-        <v>-7.33</v>
+        <v>-5.56</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1342,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>41</v>
+        <v>48.34</v>
       </c>
       <c r="Z5">
-        <v>-33.71</v>
+        <v>-29.18</v>
       </c>
       <c r="AA5">
-        <v>-26.85</v>
+        <v>-27.32</v>
       </c>
       <c r="AB5">
-        <v>-6.86</v>
+        <v>-1.86</v>
       </c>
       <c r="AC5">
-        <v>35.27</v>
+        <v>62.04</v>
       </c>
       <c r="AD5">
-        <v>26.16</v>
+        <v>40.95</v>
       </c>
       <c r="AE5">
-        <v>45.4</v>
+        <v>46.08</v>
       </c>
       <c r="AF5">
-        <v>7.05</v>
+        <v>-36.76</v>
       </c>
       <c r="AG5">
-        <v>2147.45</v>
+        <v>2133.35</v>
       </c>
       <c r="AH5">
-        <v>1840.89</v>
+        <v>1842.62</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1378,7 +1365,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>26.4</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1389,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>781.35</v>
+        <v>777.7</v>
       </c>
       <c r="D6">
-        <v>0.4</v>
+        <v>-0.47</v>
       </c>
       <c r="E6">
         <v>1125.8</v>
@@ -1401,46 +1388,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-30.6</v>
+        <v>-30.92</v>
       </c>
       <c r="H6">
-        <v>10.97</v>
+        <v>10.45</v>
       </c>
       <c r="I6">
-        <v>-2.97</v>
+        <v>-2.71</v>
       </c>
       <c r="J6">
-        <v>-3.52</v>
+        <v>-3.4</v>
       </c>
       <c r="K6">
-        <v>8.34</v>
+        <v>5.68</v>
       </c>
       <c r="L6">
-        <v>-29.23</v>
+        <v>-30.78</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>15.12</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P6">
-        <v>791.05</v>
+        <v>786.71</v>
       </c>
       <c r="Q6">
-        <v>793.08</v>
+        <v>792.4</v>
       </c>
       <c r="R6">
-        <v>775.49</v>
+        <v>776.77</v>
       </c>
       <c r="S6">
-        <v>851.89</v>
+        <v>850.62</v>
       </c>
       <c r="T6">
-        <v>-8.279999999999999</v>
+        <v>-8.57</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1455,34 +1442,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>47.23</v>
+        <v>46.03</v>
       </c>
       <c r="Z6">
-        <v>3.61</v>
+        <v>2.11</v>
       </c>
       <c r="AA6">
-        <v>6.97</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>-3.36</v>
+        <v>-3.89</v>
       </c>
       <c r="AC6">
-        <v>12.61</v>
+        <v>2.33</v>
       </c>
       <c r="AD6">
-        <v>18.47</v>
+        <v>10.31</v>
       </c>
       <c r="AE6">
-        <v>25.6</v>
+        <v>25.59</v>
       </c>
       <c r="AF6">
-        <v>-70.31</v>
+        <v>-67.08</v>
       </c>
       <c r="AG6">
-        <v>819.5</v>
+        <v>819.7</v>
       </c>
       <c r="AH6">
-        <v>766.66</v>
+        <v>765.1</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1491,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>35.84</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1502,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3194.6</v>
+        <v>3166.4</v>
       </c>
       <c r="D7">
-        <v>-2.23</v>
+        <v>-0.88</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1514,25 +1501,25 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-7.53</v>
+        <v>-8.35</v>
       </c>
       <c r="H7">
-        <v>68.90000000000001</v>
+        <v>67.41</v>
       </c>
       <c r="I7">
-        <v>-2.98</v>
+        <v>-3.51</v>
       </c>
       <c r="J7">
-        <v>21.23</v>
+        <v>17.56</v>
       </c>
       <c r="K7">
-        <v>27.96</v>
+        <v>26.39</v>
       </c>
       <c r="L7">
-        <v>31.01</v>
+        <v>27.26</v>
       </c>
       <c r="M7">
-        <v>32.58</v>
+        <v>32.98</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1541,19 +1528,19 @@
         <v>84</v>
       </c>
       <c r="P7">
-        <v>3254.6</v>
+        <v>3231.58</v>
       </c>
       <c r="Q7">
-        <v>3166.96</v>
+        <v>3191.52</v>
       </c>
       <c r="R7">
-        <v>2799.29</v>
+        <v>2810.27</v>
       </c>
       <c r="S7">
-        <v>2435</v>
+        <v>2438.87</v>
       </c>
       <c r="T7">
-        <v>31.2</v>
+        <v>29.83</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1568,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>58.33</v>
+        <v>56.09</v>
       </c>
       <c r="Z7">
-        <v>147.32</v>
+        <v>131.03</v>
       </c>
       <c r="AA7">
-        <v>172.05</v>
+        <v>163.85</v>
       </c>
       <c r="AB7">
-        <v>-24.73</v>
+        <v>-32.82</v>
       </c>
       <c r="AC7">
         <v>0.45</v>
       </c>
       <c r="AD7">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="AE7">
-        <v>139.48</v>
+        <v>138.46</v>
       </c>
       <c r="AF7">
-        <v>-72.39</v>
+        <v>-77.20999999999999</v>
       </c>
       <c r="AG7">
-        <v>3638.32</v>
+        <v>3602.3</v>
       </c>
       <c r="AH7">
-        <v>2695.6</v>
+        <v>2780.73</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1604,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>47.03</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1615,37 +1602,37 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8160</v>
+        <v>8340</v>
       </c>
       <c r="D8">
-        <v>-1.77</v>
+        <v>2.21</v>
       </c>
       <c r="E8">
-        <v>10232.91</v>
+        <v>9904.92</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-20.26</v>
+        <v>-15.8</v>
       </c>
       <c r="H8">
-        <v>37.73</v>
+        <v>40.77</v>
       </c>
       <c r="I8">
-        <v>-1.01</v>
+        <v>2.07</v>
       </c>
       <c r="J8">
-        <v>1.2</v>
+        <v>2.32</v>
       </c>
       <c r="K8">
-        <v>22.7</v>
+        <v>23.18</v>
       </c>
       <c r="L8">
-        <v>-17.2</v>
+        <v>-18.5</v>
       </c>
       <c r="M8">
-        <v>14.46</v>
+        <v>15.11</v>
       </c>
       <c r="N8">
         <v>43</v>
@@ -1654,19 +1641,19 @@
         <v>56</v>
       </c>
       <c r="P8">
-        <v>8146.8</v>
+        <v>8180.7</v>
       </c>
       <c r="Q8">
-        <v>8111.82</v>
+        <v>8122.6</v>
       </c>
       <c r="R8">
-        <v>8009.97</v>
+        <v>8019.05</v>
       </c>
       <c r="S8">
-        <v>7400.1</v>
+        <v>7399.51</v>
       </c>
       <c r="T8">
-        <v>10.27</v>
+        <v>12.71</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1681,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>52.33</v>
+        <v>57.5</v>
       </c>
       <c r="Z8">
-        <v>61.37</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="AA8">
-        <v>70.76000000000001</v>
+        <v>70.88</v>
       </c>
       <c r="AB8">
-        <v>-9.390000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="AC8">
-        <v>33.36</v>
+        <v>55.21</v>
       </c>
       <c r="AD8">
-        <v>25.34</v>
+        <v>38.46</v>
       </c>
       <c r="AE8">
-        <v>241.37</v>
+        <v>246.03</v>
       </c>
       <c r="AF8">
-        <v>-44.57</v>
+        <v>16.34</v>
       </c>
       <c r="AG8">
-        <v>8374.15</v>
+        <v>8404.120000000001</v>
       </c>
       <c r="AH8">
-        <v>7849.5</v>
+        <v>7841.08</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1717,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>31.37</v>
+        <v>33.27</v>
       </c>
     </row>
   </sheetData>
@@ -1858,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1916,1042 +1903,988 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>5.75</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.64</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-5.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1.71</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1.82</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-5.21</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-0.96</v>
+      </c>
+      <c r="E9" s="8">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-6.93</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-4.58</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.4</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>21.23</v>
+      </c>
+      <c r="D12" s="6">
+        <v>17.56</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="D13" s="6">
+        <v>2.32</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-0.34</v>
-      </c>
-      <c r="D8" s="7">
-        <v>5.75</v>
-      </c>
-      <c r="E8" s="8">
-        <v>6.09</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1.24</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.23</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0.62</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.29</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-1.28</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1.31</v>
+      </c>
+      <c r="D17" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-2.71</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.98</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.51</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-1.01</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2.07</v>
+      </c>
+      <c r="E20" s="8">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>20.54</v>
+      </c>
+      <c r="D21" s="6">
+        <v>16.76</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>20.73</v>
+      </c>
+      <c r="D22" s="6">
+        <v>22.32</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>28.57</v>
+      </c>
+      <c r="D23" s="6">
+        <v>28.46</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-15.58</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-15.81</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-29.23</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-30.78</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>31.01</v>
+      </c>
+      <c r="D26" s="6">
+        <v>27.26</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-17.2</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-18.5</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>7.22</v>
+      </c>
+      <c r="D28" s="6">
+        <v>6.14</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-1.37</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-1.78</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>26.3</v>
+      </c>
+      <c r="D30" s="6">
+        <v>23.59</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>10.72</v>
+      </c>
+      <c r="D31" s="6">
+        <v>9.27</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>8.34</v>
+      </c>
+      <c r="D32" s="6">
+        <v>5.68</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>27.96</v>
+      </c>
+      <c r="D33" s="6">
+        <v>26.39</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>22.7</v>
+      </c>
+      <c r="D34" s="6">
+        <v>23.18</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-11.09</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-8.76</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-8.35</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-5.21</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-4.73</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-19.17</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-17.68</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-30.6</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-30.92</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-7.53</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-8.35</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-20.26</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-15.8</v>
+      </c>
+      <c r="E41" s="8">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1130.6</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1104</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-26.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>891</v>
+      </c>
+      <c r="D43" s="6">
+        <v>895</v>
+      </c>
+      <c r="E43" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1839</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1848.2</v>
+      </c>
+      <c r="E44" s="8">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1938.8</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1974.6</v>
+      </c>
+      <c r="E45" s="8">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>781.35</v>
+      </c>
+      <c r="D46" s="6">
+        <v>777.7</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-3.65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>3194.6</v>
+      </c>
+      <c r="D47" s="6">
+        <v>3166.4</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-28.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>8160</v>
+      </c>
+      <c r="D48" s="6">
+        <v>8340</v>
+      </c>
+      <c r="E48" s="8">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>54.07</v>
+      </c>
+      <c r="D49" s="6">
+        <v>49.37</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-4.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>51.34</v>
+      </c>
+      <c r="D50" s="6">
+        <v>52.37</v>
+      </c>
+      <c r="E50" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>48.27</v>
+      </c>
+      <c r="D51" s="6">
+        <v>49.98</v>
+      </c>
+      <c r="E51" s="8">
         <v>1.71</v>
       </c>
-      <c r="E9" s="8">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>41</v>
+      </c>
+      <c r="D52" s="6">
+        <v>48.34</v>
+      </c>
+      <c r="E52" s="8">
+        <v>7.34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>47.23</v>
+      </c>
+      <c r="D53" s="6">
+        <v>46.03</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>58.33</v>
+      </c>
+      <c r="D54" s="6">
+        <v>56.09</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>52.33</v>
+      </c>
+      <c r="D55" s="6">
+        <v>57.5</v>
+      </c>
+      <c r="E55" s="8">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>34.54</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-10.28</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-44.82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>4.68</v>
+      </c>
+      <c r="D57" s="6">
+        <v>88.02</v>
+      </c>
+      <c r="E57" s="8">
+        <v>83.34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-1.63</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-5.21</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-3.58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-35.15</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-7.81</v>
+      </c>
+      <c r="E58" s="8">
+        <v>27.34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-7.43</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-6.93</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>7.05</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-36.76</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-43.81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-5.45</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-3.52</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-70.31</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-67.08</v>
+      </c>
+      <c r="E60" s="8">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>24.32</v>
-      </c>
-      <c r="D13" s="7">
-        <v>21.23</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-72.39</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-77.20999999999999</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-4.82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>3.17</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-2.28</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1.24</v>
-      </c>
-      <c r="E15" s="8">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-0.32</v>
-      </c>
-      <c r="D16" s="7">
-        <v>0.22</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.39</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-1.28</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1.31</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-2.14</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-2.97</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.82</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.98</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-0.82</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-1.01</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>15.72</v>
-      </c>
-      <c r="D22" s="7">
-        <v>20.54</v>
-      </c>
-      <c r="E22" s="8">
-        <v>4.82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>25.07</v>
-      </c>
-      <c r="D23" s="7">
-        <v>20.73</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-4.34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>27.3</v>
-      </c>
-      <c r="D24" s="7">
-        <v>28.57</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-17.12</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-15.58</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-31.12</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-29.23</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>33.17</v>
-      </c>
-      <c r="D27" s="7">
-        <v>31.01</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-15.58</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-17.2</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>3.67</v>
-      </c>
-      <c r="D29" s="7">
-        <v>7.22</v>
-      </c>
-      <c r="E29" s="8">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-4.57</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-1.37</v>
-      </c>
-      <c r="E30" s="8">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>23.02</v>
-      </c>
-      <c r="D31" s="7">
-        <v>26.3</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>7.49</v>
-      </c>
-      <c r="D32" s="7">
-        <v>10.72</v>
-      </c>
-      <c r="E32" s="8">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>5.86</v>
-      </c>
-      <c r="D33" s="7">
-        <v>8.34</v>
-      </c>
-      <c r="E33" s="8">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>30.4</v>
-      </c>
-      <c r="D34" s="7">
-        <v>27.96</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>22.14</v>
-      </c>
-      <c r="D35" s="7">
-        <v>22.7</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-13.18</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E36" s="8">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-8.35</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-8.76</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-4.68</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-5.21</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-19.49</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-19.17</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-30.87</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-30.6</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-5.43</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-7.53</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-18.82</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-20.26</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1078</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1130.6</v>
-      </c>
-      <c r="E43" s="8">
-        <v>52.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>895</v>
-      </c>
-      <c r="D44" s="7">
-        <v>891</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>1849.3</v>
-      </c>
-      <c r="D45" s="7">
-        <v>1839</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-10.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1931.3</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1938.8</v>
-      </c>
-      <c r="E46" s="8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>778.25</v>
-      </c>
-      <c r="D47" s="7">
-        <v>781.35</v>
-      </c>
-      <c r="E47" s="8">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>3267.4</v>
-      </c>
-      <c r="D48" s="7">
-        <v>3194.6</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-72.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>8307</v>
-      </c>
-      <c r="D49" s="7">
-        <v>8160</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-147</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="7">
-        <v>57</v>
-      </c>
-      <c r="D50" s="7">
-        <v>71</v>
-      </c>
-      <c r="E50" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="7">
-        <v>71</v>
-      </c>
-      <c r="D51" s="7">
-        <v>57</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="7">
-        <v>44.33</v>
-      </c>
-      <c r="D52" s="7">
-        <v>54.07</v>
-      </c>
-      <c r="E52" s="8">
-        <v>9.74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>52.39</v>
-      </c>
-      <c r="D53" s="7">
-        <v>51.34</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>50.05</v>
-      </c>
-      <c r="D54" s="7">
-        <v>48.27</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>39.32</v>
-      </c>
-      <c r="D55" s="7">
-        <v>41</v>
-      </c>
-      <c r="E55" s="8">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>46.13</v>
-      </c>
-      <c r="D56" s="7">
-        <v>47.23</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>64.48999999999999</v>
-      </c>
-      <c r="D57" s="7">
-        <v>58.33</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-6.16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>57.64</v>
-      </c>
-      <c r="D58" s="7">
-        <v>52.33</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-5.31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="7">
-        <v>-70.72</v>
-      </c>
-      <c r="D59" s="7">
-        <v>34.54</v>
-      </c>
-      <c r="E59" s="8">
-        <v>105.26</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="7">
-        <v>10.48</v>
-      </c>
-      <c r="D60" s="7">
-        <v>4.68</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-5.8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-23.12</v>
-      </c>
-      <c r="D61" s="7">
-        <v>-35.15</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-12.03</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-20.12</v>
-      </c>
-      <c r="D62" s="7">
-        <v>7.05</v>
+      <c r="C62" s="6">
+        <v>-44.57</v>
+      </c>
+      <c r="D62" s="6">
+        <v>16.34</v>
       </c>
       <c r="E62" s="8">
-        <v>27.17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-5.33</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-70.31</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-64.98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-61.05</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-72.39</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-11.34</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>62.76</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-44.57</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-107.33</v>
+        <v>60.91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2971,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>60.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>50.4</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>51.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="12">
-        <v>2</v>
-      </c>
-      <c r="G2" s="12">
-        <v>14.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>1.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3126,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.589</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3258</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2662</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2046</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.15</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1446</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0673</v>
+      <c r="A2" s="14">
+        <v>0.5774</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3298</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2656</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2115</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1512</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1511</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.06559999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>54.1 → 49.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.1</t>
-  </si>
-  <si>
-    <t>49.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1104</v>
+        <v>1095.9</v>
       </c>
       <c r="D2">
-        <v>-2.35</v>
+        <v>-0.73</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -936,46 +908,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-11.09</v>
+        <v>-11.74</v>
       </c>
       <c r="H2">
-        <v>47.52</v>
+        <v>46.44</v>
       </c>
       <c r="I2">
-        <v>-0.23</v>
+        <v>-0.42</v>
       </c>
       <c r="J2">
-        <v>0.64</v>
+        <v>-2.24</v>
       </c>
       <c r="K2">
-        <v>6.14</v>
+        <v>7.82</v>
       </c>
       <c r="L2">
-        <v>16.76</v>
+        <v>15.97</v>
       </c>
       <c r="M2">
-        <v>6.56</v>
+        <v>5.81</v>
       </c>
       <c r="N2">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>1096.92</v>
+        <v>1096</v>
       </c>
       <c r="Q2">
-        <v>1122.66</v>
+        <v>1118.77</v>
       </c>
       <c r="R2">
-        <v>1103.28</v>
+        <v>1101.63</v>
       </c>
       <c r="S2">
-        <v>950.2</v>
+        <v>951.51</v>
       </c>
       <c r="T2">
-        <v>16.19</v>
+        <v>15.17</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +962,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>49.37</v>
+        <v>48</v>
       </c>
       <c r="Z2">
-        <v>-0.99</v>
+        <v>-1.78</v>
       </c>
       <c r="AA2">
-        <v>2.04</v>
+        <v>1.28</v>
       </c>
       <c r="AB2">
-        <v>-3.03</v>
+        <v>-3.06</v>
       </c>
       <c r="AC2">
-        <v>39.07</v>
+        <v>46.63</v>
       </c>
       <c r="AD2">
-        <v>23.36</v>
+        <v>37.17</v>
       </c>
       <c r="AE2">
-        <v>43.26</v>
+        <v>42.99</v>
       </c>
       <c r="AF2">
-        <v>-10.28</v>
+        <v>-62.45</v>
       </c>
       <c r="AG2">
-        <v>1185.45</v>
+        <v>1177.75</v>
       </c>
       <c r="AH2">
-        <v>1059.88</v>
+        <v>1059.79</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1026,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>23.02</v>
+        <v>23.55</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>895</v>
+        <v>910.7</v>
       </c>
       <c r="D3">
-        <v>0.45</v>
+        <v>1.75</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1021,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.35</v>
+        <v>-6.74</v>
       </c>
       <c r="H3">
-        <v>69.03</v>
+        <v>72</v>
       </c>
       <c r="I3">
-        <v>-2.29</v>
+        <v>2.85</v>
       </c>
       <c r="J3">
-        <v>1.82</v>
+        <v>3.61</v>
       </c>
       <c r="K3">
-        <v>-1.78</v>
+        <v>0.29</v>
       </c>
       <c r="L3">
-        <v>22.32</v>
+        <v>23.31</v>
       </c>
       <c r="M3">
-        <v>57.74</v>
+        <v>58.65</v>
       </c>
       <c r="N3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>888.85</v>
+        <v>893.89</v>
       </c>
       <c r="Q3">
-        <v>885.66</v>
+        <v>887.15</v>
       </c>
       <c r="R3">
-        <v>892.17</v>
+        <v>891.34</v>
       </c>
       <c r="S3">
-        <v>776.64</v>
+        <v>777.59</v>
       </c>
       <c r="T3">
-        <v>15.24</v>
+        <v>17.12</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,43 +1075,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.37</v>
+        <v>56.27</v>
       </c>
       <c r="Z3">
-        <v>1.79</v>
+        <v>3.43</v>
       </c>
       <c r="AA3">
-        <v>-0.19</v>
+        <v>0.53</v>
       </c>
       <c r="AB3">
-        <v>1.99</v>
+        <v>2.9</v>
       </c>
       <c r="AC3">
-        <v>57.8</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AD3">
-        <v>50.39</v>
+        <v>57.4</v>
       </c>
       <c r="AE3">
-        <v>22.39</v>
+        <v>22.43</v>
       </c>
       <c r="AF3">
-        <v>88.02</v>
+        <v>18.55</v>
       </c>
       <c r="AG3">
-        <v>911.33</v>
+        <v>915.02</v>
       </c>
       <c r="AH3">
-        <v>859.99</v>
+        <v>859.27</v>
       </c>
       <c r="AI3">
-        <v>835.99</v>
+        <v>836.2</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>30.44</v>
+        <v>33.47</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1848.2</v>
+        <v>1823.4</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>-1.34</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1134,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-4.73</v>
+        <v>-6.01</v>
       </c>
       <c r="H4">
-        <v>36.43</v>
+        <v>34.6</v>
       </c>
       <c r="I4">
-        <v>-0.5</v>
+        <v>0.48</v>
       </c>
       <c r="J4">
-        <v>-0.96</v>
+        <v>-5.03</v>
       </c>
       <c r="K4">
-        <v>23.59</v>
+        <v>23.82</v>
       </c>
       <c r="L4">
-        <v>28.46</v>
+        <v>24.88</v>
       </c>
       <c r="M4">
-        <v>26.56</v>
+        <v>26.1</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P4">
-        <v>1835.42</v>
+        <v>1837.16</v>
       </c>
       <c r="Q4">
-        <v>1870.13</v>
+        <v>1865.58</v>
       </c>
       <c r="R4">
-        <v>1833.46</v>
+        <v>1834.13</v>
       </c>
       <c r="S4">
-        <v>1678.21</v>
+        <v>1678.82</v>
       </c>
       <c r="T4">
-        <v>10.13</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,34 +1188,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>49.98</v>
+        <v>45.6</v>
       </c>
       <c r="Z4">
-        <v>2.4</v>
+        <v>-0.04</v>
       </c>
       <c r="AA4">
-        <v>10.41</v>
+        <v>8.32</v>
       </c>
       <c r="AB4">
-        <v>-8.02</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="AC4">
-        <v>43.55</v>
+        <v>33.34</v>
       </c>
       <c r="AD4">
-        <v>31.96</v>
+        <v>36.34</v>
       </c>
       <c r="AE4">
-        <v>45.01</v>
+        <v>44.52</v>
       </c>
       <c r="AF4">
-        <v>-7.81</v>
+        <v>13.77</v>
       </c>
       <c r="AG4">
-        <v>1929.72</v>
+        <v>1924.83</v>
       </c>
       <c r="AH4">
-        <v>1810.54</v>
+        <v>1806.33</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1252,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>20.49</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1974.6</v>
+        <v>1951.1</v>
       </c>
       <c r="D5">
-        <v>1.85</v>
+        <v>-1.19</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,46 +1247,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-17.68</v>
+        <v>-18.66</v>
       </c>
       <c r="H5">
-        <v>13.12</v>
+        <v>11.77</v>
       </c>
       <c r="I5">
-        <v>3.6</v>
+        <v>1.47</v>
       </c>
       <c r="J5">
-        <v>-4.58</v>
+        <v>-7.02</v>
       </c>
       <c r="K5">
-        <v>9.27</v>
+        <v>3.74</v>
       </c>
       <c r="L5">
-        <v>-15.81</v>
+        <v>-14.69</v>
       </c>
       <c r="M5">
-        <v>21.15</v>
+        <v>20.85</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P5">
-        <v>1936.44</v>
+        <v>1942.08</v>
       </c>
       <c r="Q5">
-        <v>1987.99</v>
+        <v>1981.28</v>
       </c>
       <c r="R5">
-        <v>2022.91</v>
+        <v>2021.83</v>
       </c>
       <c r="S5">
-        <v>2090.79</v>
+        <v>2089.27</v>
       </c>
       <c r="T5">
-        <v>-5.56</v>
+        <v>-6.61</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,34 +1301,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>48.34</v>
+        <v>44.43</v>
       </c>
       <c r="Z5">
-        <v>-29.18</v>
+        <v>-27.18</v>
       </c>
       <c r="AA5">
-        <v>-27.32</v>
+        <v>-27.29</v>
       </c>
       <c r="AB5">
-        <v>-1.86</v>
+        <v>0.11</v>
       </c>
       <c r="AC5">
-        <v>62.04</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="AD5">
-        <v>40.95</v>
+        <v>58.13</v>
       </c>
       <c r="AE5">
-        <v>46.08</v>
+        <v>45.55</v>
       </c>
       <c r="AF5">
-        <v>-36.76</v>
+        <v>-54.6</v>
       </c>
       <c r="AG5">
-        <v>2133.35</v>
+        <v>2119.99</v>
       </c>
       <c r="AH5">
-        <v>1842.62</v>
+        <v>1842.57</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1365,7 +1337,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>25.32</v>
+        <v>24.38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,58 +1348,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>777.7</v>
+        <v>763.7</v>
       </c>
       <c r="D6">
-        <v>-0.47</v>
+        <v>-1.8</v>
       </c>
       <c r="E6">
-        <v>1125.8</v>
+        <v>1112.8</v>
       </c>
       <c r="F6">
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-30.92</v>
+        <v>-31.37</v>
       </c>
       <c r="H6">
-        <v>10.45</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I6">
-        <v>-2.71</v>
+        <v>-4.01</v>
       </c>
       <c r="J6">
-        <v>-3.4</v>
+        <v>-3.48</v>
       </c>
       <c r="K6">
-        <v>5.68</v>
+        <v>5.59</v>
       </c>
       <c r="L6">
-        <v>-30.78</v>
+        <v>-32.16</v>
       </c>
       <c r="M6">
-        <v>15.12</v>
+        <v>14.58</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P6">
-        <v>786.71</v>
+        <v>780.33</v>
       </c>
       <c r="Q6">
-        <v>792.4</v>
+        <v>791.16</v>
       </c>
       <c r="R6">
-        <v>776.77</v>
+        <v>777.76</v>
       </c>
       <c r="S6">
-        <v>850.62</v>
+        <v>849.3</v>
       </c>
       <c r="T6">
-        <v>-8.57</v>
+        <v>-10.08</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1414,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>46.03</v>
+        <v>41.68</v>
       </c>
       <c r="Z6">
-        <v>2.11</v>
+        <v>-0.21</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>4.76</v>
       </c>
       <c r="AB6">
-        <v>-3.89</v>
+        <v>-4.96</v>
       </c>
       <c r="AC6">
         <v>2.33</v>
       </c>
       <c r="AD6">
-        <v>10.31</v>
+        <v>5.76</v>
       </c>
       <c r="AE6">
-        <v>25.59</v>
+        <v>25.56</v>
       </c>
       <c r="AF6">
-        <v>-67.08</v>
+        <v>-72.75</v>
       </c>
       <c r="AG6">
-        <v>819.7</v>
+        <v>821.3099999999999</v>
       </c>
       <c r="AH6">
-        <v>765.1</v>
+        <v>761.01</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1478,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>37.55</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3166.4</v>
+        <v>3141</v>
       </c>
       <c r="D7">
-        <v>-0.88</v>
+        <v>-0.8</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,46 +1473,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-8.35</v>
+        <v>-9.09</v>
       </c>
       <c r="H7">
-        <v>67.41</v>
+        <v>66.06</v>
       </c>
       <c r="I7">
-        <v>-3.51</v>
+        <v>-3.87</v>
       </c>
       <c r="J7">
-        <v>17.56</v>
+        <v>17.41</v>
       </c>
       <c r="K7">
-        <v>26.39</v>
+        <v>26.44</v>
       </c>
       <c r="L7">
-        <v>27.26</v>
+        <v>27.92</v>
       </c>
       <c r="M7">
-        <v>32.98</v>
+        <v>31.85</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P7">
-        <v>3231.58</v>
+        <v>3206.28</v>
       </c>
       <c r="Q7">
-        <v>3191.52</v>
+        <v>3218.12</v>
       </c>
       <c r="R7">
-        <v>2810.27</v>
+        <v>2821.79</v>
       </c>
       <c r="S7">
-        <v>2438.87</v>
+        <v>2442.31</v>
       </c>
       <c r="T7">
-        <v>29.83</v>
+        <v>28.61</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1527,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>56.09</v>
+        <v>54.08</v>
       </c>
       <c r="Z7">
-        <v>131.03</v>
+        <v>114.75</v>
       </c>
       <c r="AA7">
-        <v>163.85</v>
+        <v>154.03</v>
       </c>
       <c r="AB7">
-        <v>-32.82</v>
+        <v>-39.28</v>
       </c>
       <c r="AC7">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="AE7">
-        <v>138.46</v>
+        <v>137.85</v>
       </c>
       <c r="AF7">
-        <v>-77.20999999999999</v>
+        <v>-70.34</v>
       </c>
       <c r="AG7">
-        <v>3602.3</v>
+        <v>3526.09</v>
       </c>
       <c r="AH7">
-        <v>2780.73</v>
+        <v>2910.15</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1591,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>41.32</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,58 +1574,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8340</v>
+        <v>8419</v>
       </c>
       <c r="D8">
-        <v>2.21</v>
+        <v>0.95</v>
       </c>
       <c r="E8">
-        <v>9904.92</v>
+        <v>9837.629999999999</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-15.8</v>
+        <v>-14.42</v>
       </c>
       <c r="H8">
-        <v>40.77</v>
+        <v>42.1</v>
       </c>
       <c r="I8">
-        <v>2.07</v>
+        <v>3.87</v>
       </c>
       <c r="J8">
-        <v>2.32</v>
+        <v>3.62</v>
       </c>
       <c r="K8">
-        <v>23.18</v>
+        <v>24.4</v>
       </c>
       <c r="L8">
-        <v>-18.5</v>
+        <v>-15</v>
       </c>
       <c r="M8">
-        <v>15.11</v>
+        <v>15.47</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P8">
-        <v>8180.7</v>
+        <v>8243.5</v>
       </c>
       <c r="Q8">
-        <v>8122.6</v>
+        <v>8142.7</v>
       </c>
       <c r="R8">
-        <v>8019.05</v>
+        <v>8022.51</v>
       </c>
       <c r="S8">
-        <v>7399.51</v>
+        <v>7399.91</v>
       </c>
       <c r="T8">
-        <v>12.71</v>
+        <v>13.77</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.5</v>
+        <v>59.57</v>
       </c>
       <c r="Z8">
-        <v>71.34999999999999</v>
+        <v>84.67</v>
       </c>
       <c r="AA8">
-        <v>70.88</v>
+        <v>73.64</v>
       </c>
       <c r="AB8">
-        <v>0.48</v>
+        <v>11.03</v>
       </c>
       <c r="AC8">
-        <v>55.21</v>
+        <v>59.17</v>
       </c>
       <c r="AD8">
-        <v>38.46</v>
+        <v>49.25</v>
       </c>
       <c r="AE8">
-        <v>246.03</v>
+        <v>249.02</v>
       </c>
       <c r="AF8">
-        <v>16.34</v>
+        <v>19.64</v>
       </c>
       <c r="AG8">
-        <v>8404.120000000001</v>
+        <v>8448.799999999999</v>
       </c>
       <c r="AH8">
-        <v>7841.08</v>
+        <v>7836.6</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1704,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>33.27</v>
+        <v>36.23</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1865,47 +1837,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,972 +1850,1006 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>5.75</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>0.64</v>
       </c>
-      <c r="E7" s="7">
-        <v>-5.11</v>
+      <c r="D7" s="5">
+        <v>-2.24</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-2.88</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>1.71</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>1.82</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.11</v>
+      <c r="D8" s="5">
+        <v>3.61</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.79</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-5.21</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-0.96</v>
       </c>
-      <c r="E9" s="8">
-        <v>4.25</v>
+      <c r="D9" s="5">
+        <v>-5.03</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-4.07</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-6.93</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-4.58</v>
       </c>
-      <c r="E10" s="8">
-        <v>2.35</v>
+      <c r="D10" s="5">
+        <v>-7.02</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-3.52</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-3.4</v>
       </c>
-      <c r="E11" s="8">
-        <v>0.12</v>
+      <c r="D11" s="5">
+        <v>-3.48</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>21.23</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>17.56</v>
       </c>
-      <c r="E12" s="7">
-        <v>-3.67</v>
+      <c r="D12" s="5">
+        <v>17.41</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>2.32</v>
       </c>
-      <c r="E13" s="8">
+      <c r="D13" s="5">
+        <v>3.62</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.23</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-0.42</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-2.29</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2.85</v>
+      </c>
+      <c r="E15" s="7">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1.47</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.71</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-4.01</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-3.51</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-3.87</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>2.07</v>
+      </c>
+      <c r="D20" s="5">
+        <v>3.87</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>16.76</v>
+      </c>
+      <c r="D21" s="5">
+        <v>15.97</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>22.32</v>
+      </c>
+      <c r="D22" s="5">
+        <v>23.31</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>28.46</v>
+      </c>
+      <c r="D23" s="5">
+        <v>24.88</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-3.58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-15.81</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-14.69</v>
+      </c>
+      <c r="E24" s="7">
         <v>1.12</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-30.78</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-32.16</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>27.26</v>
+      </c>
+      <c r="D26" s="5">
+        <v>27.92</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-18.5</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-15</v>
+      </c>
+      <c r="E27" s="7">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1.24</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>6.14</v>
+      </c>
+      <c r="D28" s="5">
+        <v>7.82</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.29</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-1.78</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0.29</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>23.59</v>
+      </c>
+      <c r="D30" s="5">
+        <v>23.82</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>9.27</v>
+      </c>
+      <c r="D31" s="5">
+        <v>3.74</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-5.53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>5.68</v>
+      </c>
+      <c r="D32" s="5">
+        <v>5.59</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>26.39</v>
+      </c>
+      <c r="D33" s="5">
+        <v>26.44</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>23.18</v>
+      </c>
+      <c r="D34" s="5">
+        <v>24.4</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-11.09</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-11.74</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-8.35</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-6.74</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-4.73</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-6.01</v>
+      </c>
+      <c r="E37" s="6">
         <v>-1.28</v>
       </c>
-      <c r="D16" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1.31</v>
-      </c>
-      <c r="D17" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-17.68</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-18.66</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-2.97</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.71</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-30.92</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-31.37</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-3.51</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-8.35</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-9.09</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.01</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-15.8</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-14.42</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1104</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1095.9</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-8.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>895</v>
+      </c>
+      <c r="D43" s="5">
+        <v>910.7</v>
+      </c>
+      <c r="E43" s="7">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1848.2</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1823.4</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-24.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1974.6</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1951.1</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-23.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>777.7</v>
+      </c>
+      <c r="D46" s="5">
+        <v>763.7</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>3166.4</v>
+      </c>
+      <c r="D47" s="5">
+        <v>3141</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-25.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>8340</v>
+      </c>
+      <c r="D48" s="5">
+        <v>8419</v>
+      </c>
+      <c r="E48" s="7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>71</v>
+      </c>
+      <c r="D49" s="5">
+        <v>57</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5">
+        <v>57</v>
+      </c>
+      <c r="D50" s="5">
+        <v>71</v>
+      </c>
+      <c r="E50" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>49.37</v>
+      </c>
+      <c r="D51" s="5">
+        <v>48</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>52.37</v>
+      </c>
+      <c r="D52" s="5">
+        <v>56.27</v>
+      </c>
+      <c r="E52" s="7">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>49.98</v>
+      </c>
+      <c r="D53" s="5">
+        <v>45.6</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-4.38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>48.34</v>
+      </c>
+      <c r="D54" s="5">
+        <v>44.43</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>46.03</v>
+      </c>
+      <c r="D55" s="5">
+        <v>41.68</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-4.35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>56.09</v>
+      </c>
+      <c r="D56" s="5">
+        <v>54.08</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>57.5</v>
+      </c>
+      <c r="D57" s="5">
+        <v>59.57</v>
+      </c>
+      <c r="E57" s="7">
         <v>2.07</v>
       </c>
-      <c r="E20" s="8">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>20.54</v>
-      </c>
-      <c r="D21" s="6">
-        <v>16.76</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-10.28</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-62.45</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-52.17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>20.73</v>
-      </c>
-      <c r="D22" s="6">
-        <v>22.32</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>88.02</v>
+      </c>
+      <c r="D59" s="5">
+        <v>18.55</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-69.47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>28.57</v>
-      </c>
-      <c r="D23" s="6">
-        <v>28.46</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-7.81</v>
+      </c>
+      <c r="D60" s="5">
+        <v>13.77</v>
+      </c>
+      <c r="E60" s="7">
+        <v>21.58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-15.58</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-15.81</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-36.76</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-54.6</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-17.84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-29.23</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-30.78</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
+        <v>-67.08</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-72.75</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-5.67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>31.01</v>
-      </c>
-      <c r="D26" s="6">
-        <v>27.26</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-77.20999999999999</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-70.34</v>
+      </c>
+      <c r="E63" s="7">
+        <v>6.87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-17.2</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-18.5</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>7.22</v>
-      </c>
-      <c r="D28" s="6">
-        <v>6.14</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-1.37</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-1.78</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>26.3</v>
-      </c>
-      <c r="D30" s="6">
-        <v>23.59</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>10.72</v>
-      </c>
-      <c r="D31" s="6">
-        <v>9.27</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>8.34</v>
-      </c>
-      <c r="D32" s="6">
-        <v>5.68</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>27.96</v>
-      </c>
-      <c r="D33" s="6">
-        <v>26.39</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>22.7</v>
-      </c>
-      <c r="D34" s="6">
-        <v>23.18</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-11.09</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-8.76</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-8.35</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-5.21</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-4.73</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-19.17</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-17.68</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-30.6</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-30.92</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-7.53</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-8.35</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-20.26</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-15.8</v>
-      </c>
-      <c r="E41" s="8">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1130.6</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1104</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-26.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>891</v>
-      </c>
-      <c r="D43" s="6">
-        <v>895</v>
-      </c>
-      <c r="E43" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1839</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1848.2</v>
-      </c>
-      <c r="E44" s="8">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1938.8</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1974.6</v>
-      </c>
-      <c r="E45" s="8">
-        <v>35.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>781.35</v>
-      </c>
-      <c r="D46" s="6">
-        <v>777.7</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-3.65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>3194.6</v>
-      </c>
-      <c r="D47" s="6">
-        <v>3166.4</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-28.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>8160</v>
-      </c>
-      <c r="D48" s="6">
-        <v>8340</v>
-      </c>
-      <c r="E48" s="8">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>54.07</v>
-      </c>
-      <c r="D49" s="6">
-        <v>49.37</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>51.34</v>
-      </c>
-      <c r="D50" s="6">
-        <v>52.37</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>48.27</v>
-      </c>
-      <c r="D51" s="6">
-        <v>49.98</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>41</v>
-      </c>
-      <c r="D52" s="6">
-        <v>48.34</v>
-      </c>
-      <c r="E52" s="8">
-        <v>7.34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>47.23</v>
-      </c>
-      <c r="D53" s="6">
-        <v>46.03</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>58.33</v>
-      </c>
-      <c r="D54" s="6">
-        <v>56.09</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-2.24</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>52.33</v>
-      </c>
-      <c r="D55" s="6">
-        <v>57.5</v>
-      </c>
-      <c r="E55" s="8">
-        <v>5.17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="B64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>34.54</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-10.28</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-44.82</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>4.68</v>
-      </c>
-      <c r="D57" s="6">
-        <v>88.02</v>
-      </c>
-      <c r="E57" s="8">
-        <v>83.34</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-35.15</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-7.81</v>
-      </c>
-      <c r="E58" s="8">
-        <v>27.34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>7.05</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-36.76</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-43.81</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-70.31</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-67.08</v>
-      </c>
-      <c r="E60" s="8">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-72.39</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-77.20999999999999</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-4.82</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-44.57</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C64" s="5">
         <v>16.34</v>
       </c>
-      <c r="E62" s="8">
-        <v>60.91</v>
+      <c r="D64" s="5">
+        <v>19.64</v>
+      </c>
+      <c r="E64" s="7">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -2904,60 +2875,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="11">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>49.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>51.4</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>1.9</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="F2" s="10">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10">
         <v>13.2</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3059,49 +3030,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.5774</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3298</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2656</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2115</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1512</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1511</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.06559999999999999</v>
+      <c r="A2" s="13">
+        <v>0.5865</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3185</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.261</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.2085</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1547</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.1458</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0581</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -896,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1095.9</v>
+        <v>1094.1</v>
       </c>
       <c r="D2">
-        <v>-0.73</v>
+        <v>-0.16</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -908,25 +908,25 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-11.74</v>
+        <v>-11.89</v>
       </c>
       <c r="H2">
-        <v>46.44</v>
+        <v>46.2</v>
       </c>
       <c r="I2">
-        <v>-0.42</v>
+        <v>2.11</v>
       </c>
       <c r="J2">
-        <v>-2.24</v>
+        <v>-6.79</v>
       </c>
       <c r="K2">
-        <v>7.82</v>
+        <v>9.65</v>
       </c>
       <c r="L2">
-        <v>15.97</v>
+        <v>15.88</v>
       </c>
       <c r="M2">
-        <v>5.81</v>
+        <v>4.01</v>
       </c>
       <c r="N2">
         <v>57</v>
@@ -935,19 +935,19 @@
         <v>66</v>
       </c>
       <c r="P2">
-        <v>1096</v>
+        <v>1100.52</v>
       </c>
       <c r="Q2">
-        <v>1118.77</v>
+        <v>1115.76</v>
       </c>
       <c r="R2">
-        <v>1101.63</v>
+        <v>1100.23</v>
       </c>
       <c r="S2">
-        <v>951.51</v>
+        <v>952.9</v>
       </c>
       <c r="T2">
-        <v>15.17</v>
+        <v>14.82</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +962,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48</v>
+        <v>47.68</v>
       </c>
       <c r="Z2">
-        <v>-1.78</v>
+        <v>-2.53</v>
       </c>
       <c r="AA2">
-        <v>1.28</v>
+        <v>0.52</v>
       </c>
       <c r="AB2">
-        <v>-3.06</v>
+        <v>-3.04</v>
       </c>
       <c r="AC2">
-        <v>46.63</v>
+        <v>33.45</v>
       </c>
       <c r="AD2">
-        <v>37.17</v>
+        <v>39.71</v>
       </c>
       <c r="AE2">
-        <v>42.99</v>
+        <v>41.72</v>
       </c>
       <c r="AF2">
-        <v>-62.45</v>
+        <v>-63.63</v>
       </c>
       <c r="AG2">
-        <v>1177.75</v>
+        <v>1173.25</v>
       </c>
       <c r="AH2">
-        <v>1059.79</v>
+        <v>1058.28</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -998,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>23.55</v>
+        <v>22.95</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>910.7</v>
+        <v>926.95</v>
       </c>
       <c r="D3">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1021,46 +1021,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-6.74</v>
+        <v>-5.07</v>
       </c>
       <c r="H3">
-        <v>72</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="I3">
-        <v>2.85</v>
+        <v>5.61</v>
       </c>
       <c r="J3">
-        <v>3.61</v>
+        <v>5.22</v>
       </c>
       <c r="K3">
-        <v>0.29</v>
+        <v>2.84</v>
       </c>
       <c r="L3">
-        <v>23.31</v>
+        <v>26.17</v>
       </c>
       <c r="M3">
-        <v>58.65</v>
+        <v>59.56</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P3">
-        <v>893.89</v>
+        <v>903.73</v>
       </c>
       <c r="Q3">
-        <v>887.15</v>
+        <v>889.1</v>
       </c>
       <c r="R3">
-        <v>891.34</v>
+        <v>890.35</v>
       </c>
       <c r="S3">
-        <v>777.59</v>
+        <v>778.6799999999999</v>
       </c>
       <c r="T3">
-        <v>17.12</v>
+        <v>19.04</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,43 +1075,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>56.27</v>
+        <v>59.93</v>
       </c>
       <c r="Z3">
-        <v>3.43</v>
+        <v>5.98</v>
       </c>
       <c r="AA3">
-        <v>0.53</v>
+        <v>1.62</v>
       </c>
       <c r="AB3">
-        <v>2.9</v>
+        <v>4.36</v>
       </c>
       <c r="AC3">
-        <v>66.20999999999999</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="AD3">
-        <v>57.4</v>
+        <v>68.62</v>
       </c>
       <c r="AE3">
-        <v>22.43</v>
+        <v>22.3</v>
       </c>
       <c r="AF3">
-        <v>18.55</v>
+        <v>51.79</v>
       </c>
       <c r="AG3">
-        <v>915.02</v>
+        <v>922.1799999999999</v>
       </c>
       <c r="AH3">
-        <v>859.27</v>
+        <v>856.01</v>
       </c>
       <c r="AI3">
-        <v>836.2</v>
+        <v>853.38</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>33.47</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1823.4</v>
+        <v>1829</v>
       </c>
       <c r="D4">
-        <v>-1.34</v>
+        <v>0.31</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1134,46 +1134,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-6.01</v>
+        <v>-5.72</v>
       </c>
       <c r="H4">
-        <v>34.6</v>
+        <v>35.01</v>
       </c>
       <c r="I4">
-        <v>0.48</v>
+        <v>0.17</v>
       </c>
       <c r="J4">
-        <v>-5.03</v>
+        <v>-4.46</v>
       </c>
       <c r="K4">
-        <v>23.82</v>
+        <v>25.71</v>
       </c>
       <c r="L4">
-        <v>24.88</v>
+        <v>22.77</v>
       </c>
       <c r="M4">
-        <v>26.1</v>
+        <v>26.57</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P4">
-        <v>1837.16</v>
+        <v>1837.78</v>
       </c>
       <c r="Q4">
-        <v>1865.58</v>
+        <v>1861.15</v>
       </c>
       <c r="R4">
-        <v>1834.13</v>
+        <v>1834.64</v>
       </c>
       <c r="S4">
-        <v>1678.82</v>
+        <v>1679.67</v>
       </c>
       <c r="T4">
-        <v>8.609999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1188,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>45.6</v>
+        <v>46.73</v>
       </c>
       <c r="Z4">
-        <v>-0.04</v>
+        <v>-1.5</v>
       </c>
       <c r="AA4">
-        <v>8.32</v>
+        <v>6.36</v>
       </c>
       <c r="AB4">
-        <v>-8.359999999999999</v>
+        <v>-7.86</v>
       </c>
       <c r="AC4">
-        <v>33.34</v>
+        <v>31.23</v>
       </c>
       <c r="AD4">
-        <v>36.34</v>
+        <v>36.04</v>
       </c>
       <c r="AE4">
-        <v>44.52</v>
+        <v>43.8</v>
       </c>
       <c r="AF4">
-        <v>13.77</v>
+        <v>21.46</v>
       </c>
       <c r="AG4">
-        <v>1924.83</v>
+        <v>1917.18</v>
       </c>
       <c r="AH4">
-        <v>1806.33</v>
+        <v>1805.12</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1224,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>21.49</v>
+        <v>21.09</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1951.1</v>
+        <v>1962.7</v>
       </c>
       <c r="D5">
-        <v>-1.19</v>
+        <v>0.59</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1247,46 +1247,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-18.66</v>
+        <v>-18.18</v>
       </c>
       <c r="H5">
-        <v>11.77</v>
+        <v>12.44</v>
       </c>
       <c r="I5">
-        <v>1.47</v>
+        <v>2.51</v>
       </c>
       <c r="J5">
-        <v>-7.02</v>
+        <v>-5.87</v>
       </c>
       <c r="K5">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
       <c r="L5">
-        <v>-14.69</v>
+        <v>-12.73</v>
       </c>
       <c r="M5">
-        <v>20.85</v>
+        <v>20.23</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="P5">
-        <v>1942.08</v>
+        <v>1951.7</v>
       </c>
       <c r="Q5">
-        <v>1981.28</v>
+        <v>1975.75</v>
       </c>
       <c r="R5">
-        <v>2021.83</v>
+        <v>2021.22</v>
       </c>
       <c r="S5">
-        <v>2089.27</v>
+        <v>2087.81</v>
       </c>
       <c r="T5">
-        <v>-6.61</v>
+        <v>-5.99</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,34 +1301,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>44.43</v>
+        <v>46.72</v>
       </c>
       <c r="Z5">
-        <v>-27.18</v>
+        <v>-24.37</v>
       </c>
       <c r="AA5">
-        <v>-27.29</v>
+        <v>-26.71</v>
       </c>
       <c r="AB5">
-        <v>0.11</v>
+        <v>2.33</v>
       </c>
       <c r="AC5">
-        <v>77.06999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AD5">
-        <v>58.13</v>
+        <v>76.34</v>
       </c>
       <c r="AE5">
-        <v>45.55</v>
+        <v>45.83</v>
       </c>
       <c r="AF5">
-        <v>-54.6</v>
+        <v>-34.76</v>
       </c>
       <c r="AG5">
-        <v>2119.99</v>
+        <v>2107.66</v>
       </c>
       <c r="AH5">
-        <v>1842.57</v>
+        <v>1843.84</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1337,7 +1337,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>24.38</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,58 +1348,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>763.7</v>
+        <v>756.7</v>
       </c>
       <c r="D6">
-        <v>-1.8</v>
+        <v>-0.92</v>
       </c>
       <c r="E6">
-        <v>1112.8</v>
+        <v>1095.8</v>
       </c>
       <c r="F6">
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-31.37</v>
+        <v>-30.95</v>
       </c>
       <c r="H6">
-        <v>8.460000000000001</v>
+        <v>7.47</v>
       </c>
       <c r="I6">
-        <v>-4.01</v>
+        <v>-5.49</v>
       </c>
       <c r="J6">
-        <v>-3.48</v>
+        <v>-4.03</v>
       </c>
       <c r="K6">
-        <v>5.59</v>
+        <v>6.55</v>
       </c>
       <c r="L6">
-        <v>-32.16</v>
+        <v>-32</v>
       </c>
       <c r="M6">
-        <v>14.58</v>
+        <v>14.39</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P6">
-        <v>780.33</v>
+        <v>771.54</v>
       </c>
       <c r="Q6">
-        <v>791.16</v>
+        <v>790.37</v>
       </c>
       <c r="R6">
-        <v>777.76</v>
+        <v>778.48</v>
       </c>
       <c r="S6">
-        <v>849.3</v>
+        <v>847.99</v>
       </c>
       <c r="T6">
-        <v>-10.08</v>
+        <v>-10.77</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1414,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>41.68</v>
+        <v>39.67</v>
       </c>
       <c r="Z6">
-        <v>-0.21</v>
+        <v>-2.58</v>
       </c>
       <c r="AA6">
-        <v>4.76</v>
+        <v>3.29</v>
       </c>
       <c r="AB6">
-        <v>-4.96</v>
+        <v>-5.87</v>
       </c>
       <c r="AC6">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>5.76</v>
+        <v>1.55</v>
       </c>
       <c r="AE6">
-        <v>25.56</v>
+        <v>25.22</v>
       </c>
       <c r="AF6">
-        <v>-72.75</v>
+        <v>-59.84</v>
       </c>
       <c r="AG6">
-        <v>821.3099999999999</v>
+        <v>823.28</v>
       </c>
       <c r="AH6">
-        <v>761.01</v>
+        <v>757.46</v>
       </c>
       <c r="AI6">
         <v>753.9400000000001</v>
@@ -1450,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>35.91</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3141</v>
+        <v>3170.2</v>
       </c>
       <c r="D7">
-        <v>-0.8</v>
+        <v>0.93</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1473,46 +1473,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-9.09</v>
+        <v>-8.24</v>
       </c>
       <c r="H7">
-        <v>66.06</v>
+        <v>67.61</v>
       </c>
       <c r="I7">
-        <v>-3.87</v>
+        <v>-2.81</v>
       </c>
       <c r="J7">
-        <v>17.41</v>
+        <v>21.51</v>
       </c>
       <c r="K7">
-        <v>26.44</v>
+        <v>26.03</v>
       </c>
       <c r="L7">
-        <v>27.92</v>
+        <v>29.6</v>
       </c>
       <c r="M7">
-        <v>31.85</v>
+        <v>31.77</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P7">
-        <v>3206.28</v>
+        <v>3187.92</v>
       </c>
       <c r="Q7">
-        <v>3218.12</v>
+        <v>3232.72</v>
       </c>
       <c r="R7">
-        <v>2821.79</v>
+        <v>2834.13</v>
       </c>
       <c r="S7">
-        <v>2442.31</v>
+        <v>2446.19</v>
       </c>
       <c r="T7">
-        <v>28.61</v>
+        <v>29.6</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1527,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>54.08</v>
+        <v>56.03</v>
       </c>
       <c r="Z7">
-        <v>114.75</v>
+        <v>103.01</v>
       </c>
       <c r="AA7">
-        <v>154.03</v>
+        <v>143.82</v>
       </c>
       <c r="AB7">
-        <v>-39.28</v>
+        <v>-40.81</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD7">
-        <v>0.3</v>
+        <v>1.03</v>
       </c>
       <c r="AE7">
-        <v>137.85</v>
+        <v>136.65</v>
       </c>
       <c r="AF7">
-        <v>-70.34</v>
+        <v>-31.54</v>
       </c>
       <c r="AG7">
-        <v>3526.09</v>
+        <v>3497.51</v>
       </c>
       <c r="AH7">
-        <v>2910.15</v>
+        <v>2967.92</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1563,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>36.32</v>
+        <v>31.91</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,58 +1574,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8419</v>
+        <v>8230.5</v>
       </c>
       <c r="D8">
-        <v>0.95</v>
+        <v>-2.24</v>
       </c>
       <c r="E8">
-        <v>9837.629999999999</v>
+        <v>9836.639999999999</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-14.42</v>
+        <v>-16.33</v>
       </c>
       <c r="H8">
-        <v>42.1</v>
+        <v>38.92</v>
       </c>
       <c r="I8">
-        <v>3.87</v>
+        <v>2.99</v>
       </c>
       <c r="J8">
-        <v>3.62</v>
+        <v>2.66</v>
       </c>
       <c r="K8">
-        <v>24.4</v>
+        <v>21.34</v>
       </c>
       <c r="L8">
-        <v>-15</v>
+        <v>-16.34</v>
       </c>
       <c r="M8">
-        <v>15.47</v>
+        <v>14.66</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="P8">
-        <v>8243.5</v>
+        <v>8291.299999999999</v>
       </c>
       <c r="Q8">
-        <v>8142.7</v>
+        <v>8156.5</v>
       </c>
       <c r="R8">
-        <v>8022.51</v>
+        <v>8025.05</v>
       </c>
       <c r="S8">
-        <v>7399.91</v>
+        <v>7400.06</v>
       </c>
       <c r="T8">
-        <v>13.77</v>
+        <v>11.22</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>59.57</v>
+        <v>52.94</v>
       </c>
       <c r="Z8">
-        <v>84.67</v>
+        <v>79.09</v>
       </c>
       <c r="AA8">
-        <v>73.64</v>
+        <v>74.73</v>
       </c>
       <c r="AB8">
-        <v>11.03</v>
+        <v>4.37</v>
       </c>
       <c r="AC8">
-        <v>59.17</v>
+        <v>60.43</v>
       </c>
       <c r="AD8">
-        <v>49.25</v>
+        <v>58.27</v>
       </c>
       <c r="AE8">
-        <v>249.02</v>
+        <v>249.09</v>
       </c>
       <c r="AF8">
-        <v>19.64</v>
+        <v>-33.57</v>
       </c>
       <c r="AG8">
-        <v>8448.799999999999</v>
+        <v>8451.57</v>
       </c>
       <c r="AH8">
-        <v>7836.6</v>
+        <v>7861.43</v>
       </c>
       <c r="AI8">
         <v>7724.65</v>
@@ -1676,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>36.23</v>
+        <v>36.59</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1874,13 +1874,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>0.64</v>
+        <v>-2.24</v>
       </c>
       <c r="D7" s="5">
-        <v>-2.24</v>
+        <v>-6.79</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.88</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>1.82</v>
+        <v>3.61</v>
       </c>
       <c r="D8" s="5">
-        <v>3.61</v>
+        <v>5.22</v>
       </c>
       <c r="E8" s="7">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1908,13 +1908,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-0.96</v>
+        <v>-5.03</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.03</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-4.07</v>
+        <v>-4.46</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1925,13 +1925,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-4.58</v>
+        <v>-7.02</v>
       </c>
       <c r="D10" s="5">
-        <v>-7.02</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-2.44</v>
+        <v>-5.87</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.15</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1942,13 +1942,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.4</v>
+        <v>-3.48</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.48</v>
+        <v>-4.03</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.08</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1959,13 +1959,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>17.56</v>
+        <v>17.41</v>
       </c>
       <c r="D12" s="5">
-        <v>17.41</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.15</v>
+        <v>21.51</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4.1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1976,13 +1976,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>2.32</v>
+        <v>3.62</v>
       </c>
       <c r="D13" s="5">
-        <v>3.62</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.3</v>
+        <v>2.66</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1993,13 +1993,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.23</v>
+        <v>-0.42</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.42</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.19</v>
+        <v>2.11</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2010,13 +2010,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-2.29</v>
+        <v>2.85</v>
       </c>
       <c r="D15" s="5">
-        <v>2.85</v>
+        <v>5.61</v>
       </c>
       <c r="E15" s="7">
-        <v>5.14</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2027,13 +2027,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-0.5</v>
+        <v>0.48</v>
       </c>
       <c r="D16" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.98</v>
+        <v>0.17</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2044,13 +2044,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>3.6</v>
+        <v>1.47</v>
       </c>
       <c r="D17" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-2.13</v>
+        <v>2.51</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.04</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2061,13 +2061,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-2.71</v>
+        <v>-4.01</v>
       </c>
       <c r="D18" s="5">
-        <v>-4.01</v>
+        <v>-5.49</v>
       </c>
       <c r="E18" s="6">
-        <v>-1.3</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2078,13 +2078,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-3.51</v>
+        <v>-3.87</v>
       </c>
       <c r="D19" s="5">
-        <v>-3.87</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.36</v>
+        <v>-2.81</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.06</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2095,13 +2095,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>2.07</v>
+        <v>3.87</v>
       </c>
       <c r="D20" s="5">
-        <v>3.87</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.8</v>
+        <v>2.99</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2112,13 +2112,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>16.76</v>
+        <v>15.97</v>
       </c>
       <c r="D21" s="5">
-        <v>15.97</v>
+        <v>15.88</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.79</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2129,13 +2129,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>22.32</v>
+        <v>23.31</v>
       </c>
       <c r="D22" s="5">
-        <v>23.31</v>
+        <v>26.17</v>
       </c>
       <c r="E22" s="7">
-        <v>0.99</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2146,13 +2146,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>28.46</v>
+        <v>24.88</v>
       </c>
       <c r="D23" s="5">
-        <v>24.88</v>
+        <v>22.77</v>
       </c>
       <c r="E23" s="6">
-        <v>-3.58</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2163,13 +2163,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-15.81</v>
+        <v>-14.69</v>
       </c>
       <c r="D24" s="5">
-        <v>-14.69</v>
+        <v>-12.73</v>
       </c>
       <c r="E24" s="7">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2180,13 +2180,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-30.78</v>
+        <v>-32.16</v>
       </c>
       <c r="D25" s="5">
-        <v>-32.16</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.38</v>
+        <v>-32</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.16</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2197,13 +2197,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>27.26</v>
+        <v>27.92</v>
       </c>
       <c r="D26" s="5">
-        <v>27.92</v>
+        <v>29.6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.66</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2214,13 +2214,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>-18.5</v>
+        <v>-15</v>
       </c>
       <c r="D27" s="5">
-        <v>-15</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3.5</v>
+        <v>-16.34</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2231,13 +2231,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>6.14</v>
+        <v>7.82</v>
       </c>
       <c r="D28" s="5">
-        <v>7.82</v>
+        <v>9.65</v>
       </c>
       <c r="E28" s="7">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2248,13 +2248,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-1.78</v>
+        <v>0.29</v>
       </c>
       <c r="D29" s="5">
-        <v>0.29</v>
+        <v>2.84</v>
       </c>
       <c r="E29" s="7">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2265,13 +2265,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>23.59</v>
+        <v>23.82</v>
       </c>
       <c r="D30" s="5">
-        <v>23.82</v>
+        <v>25.71</v>
       </c>
       <c r="E30" s="7">
-        <v>0.23</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2282,13 +2282,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>9.27</v>
+        <v>3.74</v>
       </c>
       <c r="D31" s="5">
-        <v>3.74</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-5.53</v>
+        <v>5.2</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.46</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2299,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>5.68</v>
+        <v>5.59</v>
       </c>
       <c r="D32" s="5">
-        <v>5.59</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.09</v>
+        <v>6.55</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.96</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2316,13 +2316,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>26.39</v>
+        <v>26.44</v>
       </c>
       <c r="D33" s="5">
-        <v>26.44</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.05</v>
+        <v>26.03</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2333,13 +2333,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>23.18</v>
+        <v>24.4</v>
       </c>
       <c r="D34" s="5">
-        <v>24.4</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.22</v>
+        <v>21.34</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2350,13 +2350,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-11.09</v>
+        <v>-11.74</v>
       </c>
       <c r="D35" s="5">
-        <v>-11.74</v>
+        <v>-11.89</v>
       </c>
       <c r="E35" s="6">
-        <v>-0.65</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2367,13 +2367,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-8.35</v>
+        <v>-6.74</v>
       </c>
       <c r="D36" s="5">
-        <v>-6.74</v>
+        <v>-5.07</v>
       </c>
       <c r="E36" s="7">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2384,13 +2384,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-4.73</v>
+        <v>-6.01</v>
       </c>
       <c r="D37" s="5">
-        <v>-6.01</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1.28</v>
+        <v>-5.72</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2401,13 +2401,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-17.68</v>
+        <v>-18.66</v>
       </c>
       <c r="D38" s="5">
-        <v>-18.66</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.98</v>
+        <v>-18.18</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.48</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2418,13 +2418,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-30.92</v>
+        <v>-31.37</v>
       </c>
       <c r="D39" s="5">
-        <v>-31.37</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.45</v>
+        <v>-30.95</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.42</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2435,13 +2435,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-8.35</v>
+        <v>-9.09</v>
       </c>
       <c r="D40" s="5">
-        <v>-9.09</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.74</v>
+        <v>-8.24</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.85</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2452,13 +2452,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-15.8</v>
+        <v>-14.42</v>
       </c>
       <c r="D41" s="5">
-        <v>-14.42</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.38</v>
+        <v>-16.33</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2469,13 +2469,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1104</v>
+        <v>1095.9</v>
       </c>
       <c r="D42" s="5">
-        <v>1095.9</v>
+        <v>1094.1</v>
       </c>
       <c r="E42" s="6">
-        <v>-8.1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2486,13 +2486,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>895</v>
+        <v>910.7</v>
       </c>
       <c r="D43" s="5">
-        <v>910.7</v>
+        <v>926.95</v>
       </c>
       <c r="E43" s="7">
-        <v>15.7</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2503,13 +2503,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>1848.2</v>
+        <v>1823.4</v>
       </c>
       <c r="D44" s="5">
-        <v>1823.4</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-24.8</v>
+        <v>1829</v>
+      </c>
+      <c r="E44" s="7">
+        <v>5.6</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2520,13 +2520,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>1974.6</v>
+        <v>1951.1</v>
       </c>
       <c r="D45" s="5">
-        <v>1951.1</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-23.5</v>
+        <v>1962.7</v>
+      </c>
+      <c r="E45" s="7">
+        <v>11.6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2537,13 +2537,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>777.7</v>
+        <v>763.7</v>
       </c>
       <c r="D46" s="5">
-        <v>763.7</v>
+        <v>756.7</v>
       </c>
       <c r="E46" s="6">
-        <v>-14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2554,13 +2554,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>3166.4</v>
+        <v>3141</v>
       </c>
       <c r="D47" s="5">
-        <v>3141</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-25.4</v>
+        <v>3170.2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>29.2</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2571,13 +2571,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>8340</v>
+        <v>8419</v>
       </c>
       <c r="D48" s="5">
-        <v>8419</v>
-      </c>
-      <c r="E48" s="7">
-        <v>79</v>
+        <v>8230.5</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-188.5</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2585,16 +2585,16 @@
         <v>37</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="D49" s="5">
-        <v>57</v>
+        <v>47.68</v>
       </c>
       <c r="E49" s="6">
-        <v>-14</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2602,254 +2602,220 @@
         <v>38</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>57</v>
+        <v>56.27</v>
       </c>
       <c r="D50" s="5">
-        <v>71</v>
+        <v>59.93</v>
       </c>
       <c r="E50" s="7">
-        <v>14</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>49.37</v>
+        <v>45.6</v>
       </c>
       <c r="D51" s="5">
-        <v>48</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-1.37</v>
+        <v>46.73</v>
+      </c>
+      <c r="E51" s="7">
+        <v>1.13</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>52.37</v>
+        <v>44.43</v>
       </c>
       <c r="D52" s="5">
-        <v>56.27</v>
+        <v>46.72</v>
       </c>
       <c r="E52" s="7">
-        <v>3.9</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>49.98</v>
+        <v>41.68</v>
       </c>
       <c r="D53" s="5">
-        <v>45.6</v>
+        <v>39.67</v>
       </c>
       <c r="E53" s="6">
-        <v>-4.38</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>48.34</v>
+        <v>54.08</v>
       </c>
       <c r="D54" s="5">
-        <v>44.43</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-3.91</v>
+        <v>56.03</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1.95</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>46.03</v>
+        <v>59.57</v>
       </c>
       <c r="D55" s="5">
-        <v>41.68</v>
+        <v>52.94</v>
       </c>
       <c r="E55" s="6">
-        <v>-4.35</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C56" s="5">
-        <v>56.09</v>
+        <v>-62.45</v>
       </c>
       <c r="D56" s="5">
-        <v>54.08</v>
+        <v>-63.63</v>
       </c>
       <c r="E56" s="6">
-        <v>-2.01</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C57" s="5">
-        <v>57.5</v>
+        <v>18.55</v>
       </c>
       <c r="D57" s="5">
-        <v>59.57</v>
+        <v>51.79</v>
       </c>
       <c r="E57" s="7">
-        <v>2.07</v>
+        <v>33.24</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>-10.28</v>
+        <v>13.77</v>
       </c>
       <c r="D58" s="5">
-        <v>-62.45</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-52.17</v>
+        <v>21.46</v>
+      </c>
+      <c r="E58" s="7">
+        <v>7.69</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>88.02</v>
+        <v>-54.6</v>
       </c>
       <c r="D59" s="5">
-        <v>18.55</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-69.47</v>
+        <v>-34.76</v>
+      </c>
+      <c r="E59" s="7">
+        <v>19.84</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>-7.81</v>
+        <v>-72.75</v>
       </c>
       <c r="D60" s="5">
-        <v>13.77</v>
+        <v>-59.84</v>
       </c>
       <c r="E60" s="7">
-        <v>21.58</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>-36.76</v>
+        <v>-70.34</v>
       </c>
       <c r="D61" s="5">
-        <v>-54.6</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-17.84</v>
+        <v>-31.54</v>
+      </c>
+      <c r="E61" s="7">
+        <v>38.8</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>-67.08</v>
+        <v>19.64</v>
       </c>
       <c r="D62" s="5">
-        <v>-72.75</v>
+        <v>-33.57</v>
       </c>
       <c r="E62" s="6">
-        <v>-5.67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-77.20999999999999</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-70.34</v>
-      </c>
-      <c r="E63" s="7">
-        <v>6.87</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>16.34</v>
-      </c>
-      <c r="D64" s="5">
-        <v>19.64</v>
-      </c>
-      <c r="E64" s="7">
-        <v>3.3</v>
+        <v>-53.21</v>
       </c>
     </row>
   </sheetData>
@@ -2914,16 +2880,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E2" s="10">
         <v>70</v>
       </c>
       <c r="F2" s="10">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G2" s="10">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="H2" s="10">
         <v>57</v>
@@ -3054,25 +3020,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.5865</v>
+        <v>0.5956</v>
       </c>
       <c r="B2" s="13">
-        <v>0.3185</v>
+        <v>0.3177</v>
       </c>
       <c r="C2" s="13">
-        <v>0.261</v>
+        <v>0.2657</v>
       </c>
       <c r="D2" s="13">
-        <v>0.2085</v>
+        <v>0.2023</v>
       </c>
       <c r="E2" s="13">
-        <v>0.1547</v>
+        <v>0.1466</v>
       </c>
       <c r="F2" s="13">
-        <v>0.1458</v>
+        <v>0.1439</v>
       </c>
       <c r="G2" s="13">
-        <v>0.0581</v>
+        <v>0.0401</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,40 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>46.7 → 52.5</t>
+  </si>
+  <si>
+    <t>46.7</t>
+  </si>
+  <si>
+    <t>52.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -258,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,14 +407,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -896,10 +930,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1094.1</v>
+        <v>1090.2</v>
       </c>
       <c r="D2">
-        <v>-0.16</v>
+        <v>-0.36</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -908,46 +942,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-11.89</v>
+        <v>-12.2</v>
       </c>
       <c r="H2">
-        <v>46.2</v>
+        <v>45.68</v>
       </c>
       <c r="I2">
-        <v>2.11</v>
+        <v>1.13</v>
       </c>
       <c r="J2">
-        <v>-6.79</v>
+        <v>-5.54</v>
       </c>
       <c r="K2">
-        <v>9.65</v>
+        <v>3.52</v>
       </c>
       <c r="L2">
-        <v>15.88</v>
+        <v>13.14</v>
       </c>
       <c r="M2">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="N2">
         <v>57</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>1100.52</v>
+        <v>1102.96</v>
       </c>
       <c r="Q2">
-        <v>1115.76</v>
+        <v>1111.04</v>
       </c>
       <c r="R2">
-        <v>1100.23</v>
+        <v>1099.2</v>
       </c>
       <c r="S2">
-        <v>952.9</v>
+        <v>954.2</v>
       </c>
       <c r="T2">
-        <v>14.82</v>
+        <v>14.25</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +996,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>47.68</v>
+        <v>46.96</v>
       </c>
       <c r="Z2">
-        <v>-2.53</v>
+        <v>-3.39</v>
       </c>
       <c r="AA2">
-        <v>0.52</v>
+        <v>-0.26</v>
       </c>
       <c r="AB2">
-        <v>-3.04</v>
+        <v>-3.13</v>
       </c>
       <c r="AC2">
-        <v>33.45</v>
+        <v>32.23</v>
       </c>
       <c r="AD2">
-        <v>39.71</v>
+        <v>37.44</v>
       </c>
       <c r="AE2">
-        <v>41.72</v>
+        <v>41.49</v>
       </c>
       <c r="AF2">
-        <v>-63.63</v>
+        <v>-6.42</v>
       </c>
       <c r="AG2">
-        <v>1173.25</v>
+        <v>1159.53</v>
       </c>
       <c r="AH2">
-        <v>1058.28</v>
+        <v>1062.56</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -998,7 +1032,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>22.95</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1043,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>926.95</v>
+        <v>914.55</v>
       </c>
       <c r="D3">
-        <v>1.78</v>
+        <v>-1.34</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1021,88 +1055,88 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-5.07</v>
+        <v>-6.34</v>
       </c>
       <c r="H3">
-        <v>75.06999999999999</v>
+        <v>72.73</v>
       </c>
       <c r="I3">
-        <v>5.61</v>
+        <v>2.18</v>
       </c>
       <c r="J3">
-        <v>5.22</v>
+        <v>2.99</v>
       </c>
       <c r="K3">
-        <v>2.84</v>
+        <v>0.01</v>
       </c>
       <c r="L3">
-        <v>26.17</v>
+        <v>22.81</v>
       </c>
       <c r="M3">
-        <v>59.56</v>
+        <v>59.77</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P3">
-        <v>903.73</v>
+        <v>907.64</v>
       </c>
       <c r="Q3">
-        <v>889.1</v>
+        <v>890.5</v>
       </c>
       <c r="R3">
-        <v>890.35</v>
+        <v>889.46</v>
       </c>
       <c r="S3">
-        <v>778.6799999999999</v>
+        <v>779.85</v>
       </c>
       <c r="T3">
-        <v>19.04</v>
+        <v>17.27</v>
       </c>
       <c r="U3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V3" t="s">
         <v>45</v>
       </c>
       <c r="W3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y3">
-        <v>59.93</v>
+        <v>56.07</v>
       </c>
       <c r="Z3">
-        <v>5.98</v>
+        <v>6.92</v>
       </c>
       <c r="AA3">
-        <v>1.62</v>
+        <v>2.68</v>
       </c>
       <c r="AB3">
-        <v>4.36</v>
+        <v>4.24</v>
       </c>
       <c r="AC3">
-        <v>81.84999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="AD3">
-        <v>68.62</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="AE3">
-        <v>22.3</v>
+        <v>22.56</v>
       </c>
       <c r="AF3">
-        <v>51.79</v>
+        <v>-16.76</v>
       </c>
       <c r="AG3">
-        <v>922.1799999999999</v>
+        <v>925.4400000000001</v>
       </c>
       <c r="AH3">
-        <v>856.01</v>
+        <v>855.55</v>
       </c>
       <c r="AI3">
         <v>853.38</v>
@@ -1111,7 +1145,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>37.55</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1156,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1829</v>
+        <v>1859</v>
       </c>
       <c r="D4">
-        <v>0.31</v>
+        <v>1.64</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1134,25 +1168,25 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-5.72</v>
+        <v>-4.18</v>
       </c>
       <c r="H4">
-        <v>35.01</v>
+        <v>37.23</v>
       </c>
       <c r="I4">
-        <v>0.17</v>
+        <v>0.52</v>
       </c>
       <c r="J4">
-        <v>-4.46</v>
+        <v>-3.06</v>
       </c>
       <c r="K4">
-        <v>25.71</v>
+        <v>18.55</v>
       </c>
       <c r="L4">
-        <v>22.77</v>
+        <v>24.52</v>
       </c>
       <c r="M4">
-        <v>26.57</v>
+        <v>26.32</v>
       </c>
       <c r="N4">
         <v>85</v>
@@ -1161,19 +1195,19 @@
         <v>78</v>
       </c>
       <c r="P4">
-        <v>1837.78</v>
+        <v>1839.72</v>
       </c>
       <c r="Q4">
-        <v>1861.15</v>
+        <v>1857.71</v>
       </c>
       <c r="R4">
-        <v>1834.64</v>
+        <v>1836.05</v>
       </c>
       <c r="S4">
-        <v>1679.67</v>
+        <v>1680.72</v>
       </c>
       <c r="T4">
-        <v>8.890000000000001</v>
+        <v>10.61</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1222,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>46.73</v>
+        <v>52.47</v>
       </c>
       <c r="Z4">
-        <v>-1.5</v>
+        <v>-0.23</v>
       </c>
       <c r="AA4">
-        <v>6.36</v>
+        <v>5.04</v>
       </c>
       <c r="AB4">
-        <v>-7.86</v>
+        <v>-5.27</v>
       </c>
       <c r="AC4">
-        <v>31.23</v>
+        <v>43.28</v>
       </c>
       <c r="AD4">
-        <v>36.04</v>
+        <v>35.95</v>
       </c>
       <c r="AE4">
-        <v>43.8</v>
+        <v>45.24</v>
       </c>
       <c r="AF4">
-        <v>21.46</v>
+        <v>207.75</v>
       </c>
       <c r="AG4">
-        <v>1917.18</v>
+        <v>1904.1</v>
       </c>
       <c r="AH4">
-        <v>1805.12</v>
+        <v>1811.31</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1224,7 +1258,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>21.09</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1269,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1962.7</v>
+        <v>1961.9</v>
       </c>
       <c r="D5">
-        <v>0.59</v>
+        <v>-0.04</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1247,46 +1281,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-18.18</v>
+        <v>-18.21</v>
       </c>
       <c r="H5">
-        <v>12.44</v>
+        <v>12.39</v>
       </c>
       <c r="I5">
-        <v>2.51</v>
+        <v>1.58</v>
       </c>
       <c r="J5">
-        <v>-5.87</v>
+        <v>-5.37</v>
       </c>
       <c r="K5">
-        <v>5.2</v>
+        <v>2.36</v>
       </c>
       <c r="L5">
-        <v>-12.73</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="M5">
-        <v>20.23</v>
+        <v>19.65</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P5">
-        <v>1951.7</v>
+        <v>1957.82</v>
       </c>
       <c r="Q5">
-        <v>1975.75</v>
+        <v>1969.4</v>
       </c>
       <c r="R5">
-        <v>2021.22</v>
+        <v>2020.33</v>
       </c>
       <c r="S5">
-        <v>2087.81</v>
+        <v>2086.16</v>
       </c>
       <c r="T5">
-        <v>-5.99</v>
+        <v>-5.96</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,34 +1335,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>46.72</v>
+        <v>46.58</v>
       </c>
       <c r="Z5">
-        <v>-24.37</v>
+        <v>-21.96</v>
       </c>
       <c r="AA5">
-        <v>-26.71</v>
+        <v>-25.76</v>
       </c>
       <c r="AB5">
-        <v>2.33</v>
+        <v>3.8</v>
       </c>
       <c r="AC5">
-        <v>89.90000000000001</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="AD5">
-        <v>76.34</v>
+        <v>84.55</v>
       </c>
       <c r="AE5">
-        <v>45.83</v>
+        <v>44.34</v>
       </c>
       <c r="AF5">
-        <v>-34.76</v>
+        <v>-70.14</v>
       </c>
       <c r="AG5">
-        <v>2107.66</v>
+        <v>2090.16</v>
       </c>
       <c r="AH5">
-        <v>1843.84</v>
+        <v>1848.65</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1337,7 +1371,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>21.49</v>
+        <v>18.79</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1382,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>756.7</v>
+        <v>733.95</v>
       </c>
       <c r="D6">
-        <v>-0.92</v>
+        <v>-3.01</v>
       </c>
       <c r="E6">
         <v>1095.8</v>
@@ -1360,46 +1394,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-30.95</v>
+        <v>-33.02</v>
       </c>
       <c r="H6">
-        <v>7.47</v>
+        <v>4.24</v>
       </c>
       <c r="I6">
-        <v>-5.49</v>
+        <v>-5.69</v>
       </c>
       <c r="J6">
-        <v>-4.03</v>
+        <v>-4.99</v>
       </c>
       <c r="K6">
-        <v>6.55</v>
+        <v>0.6</v>
       </c>
       <c r="L6">
-        <v>-32</v>
+        <v>-31.23</v>
       </c>
       <c r="M6">
-        <v>14.39</v>
+        <v>12.59</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P6">
-        <v>771.54</v>
+        <v>762.6799999999999</v>
       </c>
       <c r="Q6">
-        <v>790.37</v>
+        <v>788.05</v>
       </c>
       <c r="R6">
-        <v>778.48</v>
+        <v>778.46</v>
       </c>
       <c r="S6">
-        <v>847.99</v>
+        <v>846.5700000000001</v>
       </c>
       <c r="T6">
-        <v>-10.77</v>
+        <v>-13.3</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,43 +1448,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>39.67</v>
+        <v>33.92</v>
       </c>
       <c r="Z6">
-        <v>-2.58</v>
+        <v>-6.22</v>
       </c>
       <c r="AA6">
-        <v>3.29</v>
+        <v>1.39</v>
       </c>
       <c r="AB6">
-        <v>-5.87</v>
+        <v>-7.61</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.55</v>
+        <v>0.78</v>
       </c>
       <c r="AE6">
-        <v>25.22</v>
+        <v>25.52</v>
       </c>
       <c r="AF6">
-        <v>-59.84</v>
+        <v>-59.91</v>
       </c>
       <c r="AG6">
-        <v>823.28</v>
+        <v>829.39</v>
       </c>
       <c r="AH6">
-        <v>757.46</v>
+        <v>746.71</v>
       </c>
       <c r="AI6">
-        <v>753.9400000000001</v>
+        <v>822.87</v>
       </c>
       <c r="AJ6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>31.42</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1495,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3170.2</v>
+        <v>3157.1</v>
       </c>
       <c r="D7">
-        <v>0.93</v>
+        <v>-0.41</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1473,25 +1507,25 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-8.24</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="H7">
-        <v>67.61</v>
+        <v>66.91</v>
       </c>
       <c r="I7">
-        <v>-2.81</v>
+        <v>-3.38</v>
       </c>
       <c r="J7">
-        <v>21.51</v>
+        <v>9.69</v>
       </c>
       <c r="K7">
-        <v>26.03</v>
+        <v>25.86</v>
       </c>
       <c r="L7">
-        <v>29.6</v>
+        <v>29.59</v>
       </c>
       <c r="M7">
-        <v>31.77</v>
+        <v>31.72</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1500,19 +1534,19 @@
         <v>83</v>
       </c>
       <c r="P7">
-        <v>3187.92</v>
+        <v>3165.86</v>
       </c>
       <c r="Q7">
-        <v>3232.72</v>
+        <v>3246.19</v>
       </c>
       <c r="R7">
-        <v>2834.13</v>
+        <v>2846.92</v>
       </c>
       <c r="S7">
-        <v>2446.19</v>
+        <v>2450.28</v>
       </c>
       <c r="T7">
-        <v>29.6</v>
+        <v>28.85</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1561,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>56.03</v>
+        <v>54.91</v>
       </c>
       <c r="Z7">
-        <v>103.01</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AA7">
-        <v>143.82</v>
+        <v>133.38</v>
       </c>
       <c r="AB7">
-        <v>-40.81</v>
+        <v>-41.78</v>
       </c>
       <c r="AC7">
-        <v>2.63</v>
+        <v>3.74</v>
       </c>
       <c r="AD7">
-        <v>1.03</v>
+        <v>2.12</v>
       </c>
       <c r="AE7">
-        <v>136.65</v>
+        <v>134.19</v>
       </c>
       <c r="AF7">
-        <v>-31.54</v>
+        <v>-52.82</v>
       </c>
       <c r="AG7">
-        <v>3497.51</v>
+        <v>3459.46</v>
       </c>
       <c r="AH7">
-        <v>2967.92</v>
+        <v>3032.92</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1563,7 +1597,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>31.91</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,58 +1608,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8230.5</v>
+        <v>8669.5</v>
       </c>
       <c r="D8">
-        <v>-2.24</v>
+        <v>5.33</v>
       </c>
       <c r="E8">
-        <v>9836.639999999999</v>
+        <v>9809.719999999999</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-16.33</v>
+        <v>-11.62</v>
       </c>
       <c r="H8">
-        <v>38.92</v>
+        <v>46.33</v>
       </c>
       <c r="I8">
-        <v>2.99</v>
+        <v>4.36</v>
       </c>
       <c r="J8">
-        <v>2.66</v>
+        <v>8.99</v>
       </c>
       <c r="K8">
-        <v>21.34</v>
+        <v>12.86</v>
       </c>
       <c r="L8">
-        <v>-16.34</v>
+        <v>-11.87</v>
       </c>
       <c r="M8">
-        <v>14.66</v>
+        <v>13.9</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P8">
-        <v>8291.299999999999</v>
+        <v>8363.799999999999</v>
       </c>
       <c r="Q8">
-        <v>8156.5</v>
+        <v>8190.72</v>
       </c>
       <c r="R8">
-        <v>8025.05</v>
+        <v>8036.22</v>
       </c>
       <c r="S8">
-        <v>7400.06</v>
+        <v>7403.64</v>
       </c>
       <c r="T8">
-        <v>11.22</v>
+        <v>17.1</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,43 +1674,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>52.94</v>
+        <v>63.21</v>
       </c>
       <c r="Z8">
-        <v>79.09</v>
+        <v>108.85</v>
       </c>
       <c r="AA8">
-        <v>74.73</v>
+        <v>81.55</v>
       </c>
       <c r="AB8">
-        <v>4.37</v>
+        <v>27.3</v>
       </c>
       <c r="AC8">
-        <v>60.43</v>
+        <v>71.91</v>
       </c>
       <c r="AD8">
-        <v>58.27</v>
+        <v>63.84</v>
       </c>
       <c r="AE8">
-        <v>249.09</v>
+        <v>282.3</v>
       </c>
       <c r="AF8">
-        <v>-33.57</v>
+        <v>1130.31</v>
       </c>
       <c r="AG8">
-        <v>8451.57</v>
+        <v>8553.139999999999</v>
       </c>
       <c r="AH8">
-        <v>7861.43</v>
+        <v>7828.31</v>
       </c>
       <c r="AI8">
-        <v>7724.65</v>
+        <v>7735.1</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>36.59</v>
+        <v>40.16</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,991 +1871,1066 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-2.24</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-6.79</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-4.55</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-6.79</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-5.54</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>3.61</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="6">
         <v>5.22</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="6">
+        <v>2.99</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-5.03</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="6">
         <v>-4.46</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-3.06</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-7.02</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C12" s="6">
         <v>-5.87</v>
       </c>
-      <c r="E10" s="7">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-5.37</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-3.48</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C13" s="6">
         <v>-4.03</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-4.99</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>17.41</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C14" s="6">
         <v>21.51</v>
       </c>
-      <c r="E12" s="7">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D14" s="6">
+        <v>9.69</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-11.82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>3.62</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C15" s="6">
         <v>2.66</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D15" s="6">
+        <v>8.99</v>
+      </c>
+      <c r="E15" s="7">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-0.42</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C16" s="6">
         <v>2.11</v>
       </c>
-      <c r="E14" s="7">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D16" s="6">
+        <v>1.13</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>2.85</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C17" s="6">
         <v>5.61</v>
       </c>
-      <c r="E15" s="7">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D17" s="6">
+        <v>2.18</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-3.43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C18" s="6">
         <v>0.17</v>
       </c>
-      <c r="E16" s="6">
+      <c r="D18" s="6">
+        <v>0.52</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2.51</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1.58</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-5.49</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-5.69</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-2.81</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-3.38</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2.99</v>
+      </c>
+      <c r="D22" s="6">
+        <v>4.36</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>15.88</v>
+      </c>
+      <c r="D23" s="6">
+        <v>13.14</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>26.17</v>
+      </c>
+      <c r="D24" s="6">
+        <v>22.81</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>22.77</v>
+      </c>
+      <c r="D25" s="6">
+        <v>24.52</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-12.73</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-32</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-31.23</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>29.6</v>
+      </c>
+      <c r="D28" s="6">
+        <v>29.59</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-16.34</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-11.87</v>
+      </c>
+      <c r="E29" s="7">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>9.65</v>
+      </c>
+      <c r="D30" s="6">
+        <v>3.52</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-6.13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>2.84</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>25.71</v>
+      </c>
+      <c r="D32" s="6">
+        <v>18.55</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-7.16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="D33" s="6">
+        <v>2.36</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-2.84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>6.55</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-5.95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>26.03</v>
+      </c>
+      <c r="D35" s="6">
+        <v>25.86</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>21.34</v>
+      </c>
+      <c r="D36" s="6">
+        <v>12.86</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-8.48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-11.89</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-12.2</v>
+      </c>
+      <c r="E37" s="8">
         <v>-0.31</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-5.07</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-6.34</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-5.72</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-4.18</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="D17" s="5">
-        <v>2.51</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-18.18</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-18.21</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-4.01</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-5.49</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-30.95</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-33.02</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-3.87</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.81</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-8.24</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>3.87</v>
-      </c>
-      <c r="D20" s="5">
-        <v>2.99</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-16.33</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-11.62</v>
+      </c>
+      <c r="E43" s="7">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>15.97</v>
-      </c>
-      <c r="D21" s="5">
-        <v>15.88</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1094.1</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1090.2</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>23.31</v>
-      </c>
-      <c r="D22" s="5">
-        <v>26.17</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>926.95</v>
+      </c>
+      <c r="D45" s="6">
+        <v>914.55</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-12.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>24.88</v>
-      </c>
-      <c r="D23" s="5">
-        <v>22.77</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>1829</v>
+      </c>
+      <c r="D46" s="6">
+        <v>1859</v>
+      </c>
+      <c r="E46" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-14.69</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-12.73</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1962.7</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1961.9</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-32.16</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-32</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>756.7</v>
+      </c>
+      <c r="D48" s="6">
+        <v>733.95</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-22.75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>27.92</v>
-      </c>
-      <c r="D26" s="5">
-        <v>29.6</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>3170.2</v>
+      </c>
+      <c r="D49" s="6">
+        <v>3157.1</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-13.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-15</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-16.34</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>8230.5</v>
+      </c>
+      <c r="D50" s="6">
+        <v>8669.5</v>
+      </c>
+      <c r="E50" s="7">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>7.82</v>
-      </c>
-      <c r="D28" s="5">
-        <v>9.65</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>47.68</v>
+      </c>
+      <c r="D51" s="6">
+        <v>46.96</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>0.29</v>
-      </c>
-      <c r="D29" s="5">
-        <v>2.84</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>59.93</v>
+      </c>
+      <c r="D52" s="6">
+        <v>56.07</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>23.82</v>
-      </c>
-      <c r="D30" s="5">
-        <v>25.71</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>46.73</v>
+      </c>
+      <c r="D53" s="6">
+        <v>52.47</v>
+      </c>
+      <c r="E53" s="7">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>3.74</v>
-      </c>
-      <c r="D31" s="5">
-        <v>5.2</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>46.72</v>
+      </c>
+      <c r="D54" s="6">
+        <v>46.58</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>5.59</v>
-      </c>
-      <c r="D32" s="5">
-        <v>6.55</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>39.67</v>
+      </c>
+      <c r="D55" s="6">
+        <v>33.92</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-5.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>26.44</v>
-      </c>
-      <c r="D33" s="5">
-        <v>26.03</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>56.03</v>
+      </c>
+      <c r="D56" s="6">
+        <v>54.91</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>24.4</v>
-      </c>
-      <c r="D34" s="5">
-        <v>21.34</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-3.06</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>52.94</v>
+      </c>
+      <c r="D57" s="6">
+        <v>63.21</v>
+      </c>
+      <c r="E57" s="7">
+        <v>10.27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-11.74</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-11.89</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-63.63</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-6.42</v>
+      </c>
+      <c r="E58" s="7">
+        <v>57.21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-6.74</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-5.07</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>51.79</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-16.76</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-68.55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-6.01</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-5.72</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>21.46</v>
+      </c>
+      <c r="D60" s="6">
+        <v>207.75</v>
+      </c>
+      <c r="E60" s="7">
+        <v>186.29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-18.66</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-18.18</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-34.76</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-70.14</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-35.38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-31.37</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-30.95</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-59.84</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-59.91</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-9.09</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-8.24</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-31.54</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-52.82</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-21.28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-14.42</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-16.33</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1095.9</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1094.1</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>910.7</v>
-      </c>
-      <c r="D43" s="5">
-        <v>926.95</v>
-      </c>
-      <c r="E43" s="7">
-        <v>16.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1823.4</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1829</v>
-      </c>
-      <c r="E44" s="7">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1951.1</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1962.7</v>
-      </c>
-      <c r="E45" s="7">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>763.7</v>
-      </c>
-      <c r="D46" s="5">
-        <v>756.7</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>3141</v>
-      </c>
-      <c r="D47" s="5">
-        <v>3170.2</v>
-      </c>
-      <c r="E47" s="7">
-        <v>29.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>8419</v>
-      </c>
-      <c r="D48" s="5">
-        <v>8230.5</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-188.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>48</v>
-      </c>
-      <c r="D49" s="5">
-        <v>47.68</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>56.27</v>
-      </c>
-      <c r="D50" s="5">
-        <v>59.93</v>
-      </c>
-      <c r="E50" s="7">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>45.6</v>
-      </c>
-      <c r="D51" s="5">
-        <v>46.73</v>
-      </c>
-      <c r="E51" s="7">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>44.43</v>
-      </c>
-      <c r="D52" s="5">
-        <v>46.72</v>
-      </c>
-      <c r="E52" s="7">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>41.68</v>
-      </c>
-      <c r="D53" s="5">
-        <v>39.67</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>54.08</v>
-      </c>
-      <c r="D54" s="5">
-        <v>56.03</v>
-      </c>
-      <c r="E54" s="7">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>59.57</v>
-      </c>
-      <c r="D55" s="5">
-        <v>52.94</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-6.63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>-62.45</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-63.63</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>18.55</v>
-      </c>
-      <c r="D57" s="5">
-        <v>51.79</v>
-      </c>
-      <c r="E57" s="7">
-        <v>33.24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>13.77</v>
-      </c>
-      <c r="D58" s="5">
-        <v>21.46</v>
-      </c>
-      <c r="E58" s="7">
-        <v>7.69</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-54.6</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-34.76</v>
-      </c>
-      <c r="E59" s="7">
-        <v>19.84</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-72.75</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-59.84</v>
-      </c>
-      <c r="E60" s="7">
-        <v>12.91</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-70.34</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-31.54</v>
-      </c>
-      <c r="E61" s="7">
-        <v>38.8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>19.64</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C64" s="6">
         <v>-33.57</v>
       </c>
-      <c r="E62" s="6">
-        <v>-53.21</v>
+      <c r="D64" s="6">
+        <v>1130.31</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1163.88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2841,61 +2950,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>50.6</v>
+      </c>
+      <c r="E2" s="11">
+        <v>70</v>
+      </c>
+      <c r="F2" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>9.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>50</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="I2" s="11">
         <v>70</v>
-      </c>
-      <c r="F2" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>13.9</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2996,49 +3105,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.5956</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3177</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2657</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.2023</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1466</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1439</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0401</v>
+      <c r="A2" s="14">
+        <v>0.5977</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3172</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2632</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1965</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.139</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1259</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0394</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,25 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>46.7 → 52.5</t>
-  </si>
-  <si>
-    <t>46.7</t>
+    <t>52.5 → 49.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>52.5</t>
+  </si>
+  <si>
+    <t>49.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -930,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1090.2</v>
+        <v>1075.2</v>
       </c>
       <c r="D2">
-        <v>-0.36</v>
+        <v>-1.38</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -942,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-12.2</v>
+        <v>-13.41</v>
       </c>
       <c r="H2">
-        <v>45.68</v>
+        <v>43.68</v>
       </c>
       <c r="I2">
-        <v>1.13</v>
+        <v>-4.9</v>
       </c>
       <c r="J2">
-        <v>-5.54</v>
+        <v>-9.24</v>
       </c>
       <c r="K2">
-        <v>3.52</v>
+        <v>0.87</v>
       </c>
       <c r="L2">
-        <v>13.14</v>
+        <v>10.61</v>
       </c>
       <c r="M2">
-        <v>3.94</v>
+        <v>3.65</v>
       </c>
       <c r="N2">
         <v>57</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>1102.96</v>
+        <v>1091.88</v>
       </c>
       <c r="Q2">
-        <v>1111.04</v>
+        <v>1107.22</v>
       </c>
       <c r="R2">
-        <v>1099.2</v>
+        <v>1097.92</v>
       </c>
       <c r="S2">
-        <v>954.2</v>
+        <v>955.41</v>
       </c>
       <c r="T2">
-        <v>14.25</v>
+        <v>12.54</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -996,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>46.96</v>
+        <v>44.19</v>
       </c>
       <c r="Z2">
-        <v>-3.39</v>
+        <v>-5.23</v>
       </c>
       <c r="AA2">
-        <v>-0.26</v>
+        <v>-1.26</v>
       </c>
       <c r="AB2">
-        <v>-3.13</v>
+        <v>-3.97</v>
       </c>
       <c r="AC2">
-        <v>32.23</v>
+        <v>25.52</v>
       </c>
       <c r="AD2">
-        <v>37.44</v>
+        <v>30.4</v>
       </c>
       <c r="AE2">
-        <v>41.49</v>
+        <v>41.15</v>
       </c>
       <c r="AF2">
-        <v>-6.42</v>
+        <v>-48.5</v>
       </c>
       <c r="AG2">
-        <v>1159.53</v>
+        <v>1154.27</v>
       </c>
       <c r="AH2">
-        <v>1062.56</v>
+        <v>1060.18</v>
       </c>
       <c r="AI2">
         <v>1042.8</v>
@@ -1032,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>24.14</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>914.55</v>
+        <v>909</v>
       </c>
       <c r="D3">
-        <v>-1.34</v>
+        <v>-0.61</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1055,25 +1049,25 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-6.34</v>
+        <v>-6.91</v>
       </c>
       <c r="H3">
-        <v>72.73</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="I3">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="J3">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="K3">
-        <v>0.01</v>
+        <v>-2.83</v>
       </c>
       <c r="L3">
-        <v>22.81</v>
+        <v>23.09</v>
       </c>
       <c r="M3">
-        <v>59.77</v>
+        <v>59.54</v>
       </c>
       <c r="N3">
         <v>71</v>
@@ -1082,19 +1076,19 @@
         <v>69</v>
       </c>
       <c r="P3">
-        <v>907.64</v>
+        <v>911.24</v>
       </c>
       <c r="Q3">
-        <v>890.5</v>
+        <v>891.4400000000001</v>
       </c>
       <c r="R3">
-        <v>889.46</v>
+        <v>889.78</v>
       </c>
       <c r="S3">
-        <v>779.85</v>
+        <v>780.99</v>
       </c>
       <c r="T3">
-        <v>17.27</v>
+        <v>16.39</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1109,34 +1103,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>56.07</v>
+        <v>54.39</v>
       </c>
       <c r="Z3">
-        <v>6.92</v>
+        <v>7.13</v>
       </c>
       <c r="AA3">
-        <v>2.68</v>
+        <v>3.57</v>
       </c>
       <c r="AB3">
-        <v>4.24</v>
+        <v>3.56</v>
       </c>
       <c r="AC3">
-        <v>86.67</v>
+        <v>79.31</v>
       </c>
       <c r="AD3">
-        <v>78.23999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="AE3">
-        <v>22.56</v>
+        <v>22.78</v>
       </c>
       <c r="AF3">
-        <v>-16.76</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="AG3">
-        <v>925.4400000000001</v>
+        <v>927.35</v>
       </c>
       <c r="AH3">
-        <v>855.55</v>
+        <v>855.53</v>
       </c>
       <c r="AI3">
         <v>853.38</v>
@@ -1145,7 +1139,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>39.34</v>
+        <v>36.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1859</v>
+        <v>1845.9</v>
       </c>
       <c r="D4">
-        <v>1.64</v>
+        <v>-0.7</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1168,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-4.18</v>
+        <v>-4.85</v>
       </c>
       <c r="H4">
-        <v>37.23</v>
+        <v>36.26</v>
       </c>
       <c r="I4">
-        <v>0.52</v>
+        <v>0.38</v>
       </c>
       <c r="J4">
-        <v>-3.06</v>
+        <v>-4.25</v>
       </c>
       <c r="K4">
-        <v>18.55</v>
+        <v>11.63</v>
       </c>
       <c r="L4">
-        <v>24.52</v>
+        <v>22.57</v>
       </c>
       <c r="M4">
-        <v>26.32</v>
+        <v>26.12</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P4">
-        <v>1839.72</v>
+        <v>1841.1</v>
       </c>
       <c r="Q4">
-        <v>1857.71</v>
+        <v>1855.28</v>
       </c>
       <c r="R4">
-        <v>1836.05</v>
+        <v>1837.17</v>
       </c>
       <c r="S4">
-        <v>1680.72</v>
+        <v>1681.53</v>
       </c>
       <c r="T4">
-        <v>10.61</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1222,34 +1216,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>52.47</v>
+        <v>49.94</v>
       </c>
       <c r="Z4">
-        <v>-0.23</v>
+        <v>-0.28</v>
       </c>
       <c r="AA4">
-        <v>5.04</v>
+        <v>3.98</v>
       </c>
       <c r="AB4">
-        <v>-5.27</v>
+        <v>-4.26</v>
       </c>
       <c r="AC4">
-        <v>43.28</v>
+        <v>58.62</v>
       </c>
       <c r="AD4">
-        <v>35.95</v>
+        <v>44.37</v>
       </c>
       <c r="AE4">
-        <v>45.24</v>
+        <v>46.57</v>
       </c>
       <c r="AF4">
-        <v>207.75</v>
+        <v>54.69</v>
       </c>
       <c r="AG4">
-        <v>1904.1</v>
+        <v>1898.57</v>
       </c>
       <c r="AH4">
-        <v>1811.31</v>
+        <v>1811.99</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1258,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>18.7</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1961.9</v>
+        <v>1929</v>
       </c>
       <c r="D5">
-        <v>-0.04</v>
+        <v>-1.68</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1281,46 +1275,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-18.21</v>
+        <v>-19.58</v>
       </c>
       <c r="H5">
-        <v>12.39</v>
+        <v>10.51</v>
       </c>
       <c r="I5">
-        <v>1.58</v>
+        <v>-0.51</v>
       </c>
       <c r="J5">
-        <v>-5.37</v>
+        <v>-7.65</v>
       </c>
       <c r="K5">
-        <v>2.36</v>
+        <v>-2.88</v>
       </c>
       <c r="L5">
-        <v>-9.859999999999999</v>
+        <v>-12.62</v>
       </c>
       <c r="M5">
-        <v>19.65</v>
+        <v>19.24</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>1957.82</v>
+        <v>1955.86</v>
       </c>
       <c r="Q5">
-        <v>1969.4</v>
+        <v>1961.09</v>
       </c>
       <c r="R5">
-        <v>2020.33</v>
+        <v>2018.22</v>
       </c>
       <c r="S5">
-        <v>2086.16</v>
+        <v>2084.33</v>
       </c>
       <c r="T5">
-        <v>-5.96</v>
+        <v>-7.45</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1335,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>46.58</v>
+        <v>41.03</v>
       </c>
       <c r="Z5">
-        <v>-21.96</v>
+        <v>-22.45</v>
       </c>
       <c r="AA5">
-        <v>-25.76</v>
+        <v>-25.1</v>
       </c>
       <c r="AB5">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="AC5">
-        <v>86.68000000000001</v>
+        <v>80.47</v>
       </c>
       <c r="AD5">
-        <v>84.55</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="AE5">
-        <v>44.34</v>
+        <v>44.43</v>
       </c>
       <c r="AF5">
-        <v>-70.14</v>
+        <v>-20.94</v>
       </c>
       <c r="AG5">
-        <v>2090.16</v>
+        <v>2067.37</v>
       </c>
       <c r="AH5">
-        <v>1848.65</v>
+        <v>1854.81</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1371,7 +1365,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>18.79</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>733.95</v>
+        <v>721.05</v>
       </c>
       <c r="D6">
-        <v>-3.01</v>
+        <v>-1.76</v>
       </c>
       <c r="E6">
         <v>1095.8</v>
@@ -1394,46 +1388,46 @@
         <v>704.1</v>
       </c>
       <c r="G6">
-        <v>-33.02</v>
+        <v>-34.2</v>
       </c>
       <c r="H6">
-        <v>4.24</v>
+        <v>2.41</v>
       </c>
       <c r="I6">
-        <v>-5.69</v>
+        <v>-7.72</v>
       </c>
       <c r="J6">
-        <v>-4.99</v>
+        <v>-7.59</v>
       </c>
       <c r="K6">
-        <v>0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="L6">
-        <v>-31.23</v>
+        <v>-32.64</v>
       </c>
       <c r="M6">
-        <v>12.59</v>
+        <v>12.18</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P6">
-        <v>762.6799999999999</v>
+        <v>750.62</v>
       </c>
       <c r="Q6">
-        <v>788.05</v>
+        <v>785.34</v>
       </c>
       <c r="R6">
-        <v>778.46</v>
+        <v>778.03</v>
       </c>
       <c r="S6">
-        <v>846.5700000000001</v>
+        <v>845.05</v>
       </c>
       <c r="T6">
-        <v>-13.3</v>
+        <v>-14.67</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1448,43 +1442,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>33.92</v>
+        <v>31.16</v>
       </c>
       <c r="Z6">
-        <v>-6.22</v>
+        <v>-10.03</v>
       </c>
       <c r="AA6">
-        <v>1.39</v>
+        <v>-0.9</v>
       </c>
       <c r="AB6">
-        <v>-7.61</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>25.52</v>
+        <v>24.77</v>
       </c>
       <c r="AF6">
-        <v>-59.91</v>
+        <v>-60.92</v>
       </c>
       <c r="AG6">
-        <v>829.39</v>
+        <v>836.22</v>
       </c>
       <c r="AH6">
-        <v>746.71</v>
+        <v>734.47</v>
       </c>
       <c r="AI6">
-        <v>822.87</v>
+        <v>800.48</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>29.4</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3157.1</v>
+        <v>3250.2</v>
       </c>
       <c r="D7">
-        <v>-0.41</v>
+        <v>2.95</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1507,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-8.619999999999999</v>
+        <v>-5.92</v>
       </c>
       <c r="H7">
-        <v>66.91</v>
+        <v>71.84</v>
       </c>
       <c r="I7">
-        <v>-3.38</v>
+        <v>1.74</v>
       </c>
       <c r="J7">
-        <v>9.69</v>
+        <v>12.56</v>
       </c>
       <c r="K7">
-        <v>25.86</v>
+        <v>28.4</v>
       </c>
       <c r="L7">
-        <v>29.59</v>
+        <v>33.65</v>
       </c>
       <c r="M7">
-        <v>31.72</v>
+        <v>32.47</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P7">
-        <v>3165.86</v>
+        <v>3176.98</v>
       </c>
       <c r="Q7">
-        <v>3246.19</v>
+        <v>3254.27</v>
       </c>
       <c r="R7">
-        <v>2846.92</v>
+        <v>2861.73</v>
       </c>
       <c r="S7">
-        <v>2450.28</v>
+        <v>2454.62</v>
       </c>
       <c r="T7">
-        <v>28.85</v>
+        <v>32.41</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1561,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>54.91</v>
+        <v>60.92</v>
       </c>
       <c r="Z7">
-        <v>91.59999999999999</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="AA7">
-        <v>133.38</v>
+        <v>124.51</v>
       </c>
       <c r="AB7">
-        <v>-41.78</v>
+        <v>-35.47</v>
       </c>
       <c r="AC7">
-        <v>3.74</v>
+        <v>12.94</v>
       </c>
       <c r="AD7">
-        <v>2.12</v>
+        <v>6.43</v>
       </c>
       <c r="AE7">
-        <v>134.19</v>
+        <v>138.33</v>
       </c>
       <c r="AF7">
-        <v>-52.82</v>
+        <v>-53.76</v>
       </c>
       <c r="AG7">
-        <v>3459.46</v>
+        <v>3454.24</v>
       </c>
       <c r="AH7">
-        <v>3032.92</v>
+        <v>3054.29</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1597,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>28.94</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,58 +1602,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8669.5</v>
+        <v>8812.5</v>
       </c>
       <c r="D8">
-        <v>5.33</v>
+        <v>1.65</v>
       </c>
       <c r="E8">
-        <v>9809.719999999999</v>
+        <v>9788.280000000001</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-11.62</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="H8">
-        <v>46.33</v>
+        <v>48.75</v>
       </c>
       <c r="I8">
-        <v>4.36</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>8.99</v>
+        <v>10.36</v>
       </c>
       <c r="K8">
-        <v>12.86</v>
+        <v>10.72</v>
       </c>
       <c r="L8">
-        <v>-11.87</v>
+        <v>-10.17</v>
       </c>
       <c r="M8">
-        <v>13.9</v>
+        <v>14.27</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P8">
-        <v>8363.799999999999</v>
+        <v>8494.299999999999</v>
       </c>
       <c r="Q8">
-        <v>8190.72</v>
+        <v>8234.75</v>
       </c>
       <c r="R8">
-        <v>8036.22</v>
+        <v>8051.27</v>
       </c>
       <c r="S8">
-        <v>7403.64</v>
+        <v>7407.67</v>
       </c>
       <c r="T8">
-        <v>17.1</v>
+        <v>18.96</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1674,43 +1668,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>63.21</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="Z8">
-        <v>108.85</v>
+        <v>142.33</v>
       </c>
       <c r="AA8">
-        <v>81.55</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="AB8">
-        <v>27.3</v>
+        <v>48.62</v>
       </c>
       <c r="AC8">
-        <v>71.91</v>
+        <v>79.12</v>
       </c>
       <c r="AD8">
-        <v>63.84</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="AE8">
-        <v>282.3</v>
+        <v>293.49</v>
       </c>
       <c r="AF8">
-        <v>1130.31</v>
+        <v>128.26</v>
       </c>
       <c r="AG8">
-        <v>8553.139999999999</v>
+        <v>8671.190000000001</v>
       </c>
       <c r="AH8">
-        <v>7828.31</v>
+        <v>7798.31</v>
       </c>
       <c r="AI8">
-        <v>7735.1</v>
+        <v>7800.02</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>40.16</v>
+        <v>43.26</v>
       </c>
     </row>
   </sheetData>
@@ -1851,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1891,1046 +1885,1006 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-5.54</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-9.24</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>66</v>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2.99</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2.53</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-6.79</v>
+        <v>-3.06</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.54</v>
+        <v>-4.25</v>
       </c>
       <c r="E9" s="7">
-        <v>1.25</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>5.22</v>
+        <v>-5.37</v>
       </c>
       <c r="D10" s="6">
-        <v>2.99</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.23</v>
+        <v>-7.65</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.46</v>
+        <v>-4.99</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.06</v>
+        <v>-7.59</v>
       </c>
       <c r="E11" s="7">
-        <v>1.4</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.87</v>
+        <v>9.69</v>
       </c>
       <c r="D12" s="6">
-        <v>-5.37</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.5</v>
+        <v>12.56</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.87</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-4.03</v>
+        <v>8.99</v>
       </c>
       <c r="D13" s="6">
-        <v>-4.99</v>
+        <v>10.36</v>
       </c>
       <c r="E13" s="8">
-        <v>-0.96</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>21.51</v>
+        <v>1.13</v>
       </c>
       <c r="D14" s="6">
-        <v>9.69</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-11.82</v>
+        <v>-4.9</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-6.03</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="D15" s="6">
-        <v>8.99</v>
+        <v>2.02</v>
       </c>
       <c r="E15" s="7">
-        <v>6.33</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>2.11</v>
+        <v>0.52</v>
       </c>
       <c r="D16" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.98</v>
+        <v>0.38</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>5.61</v>
+        <v>1.58</v>
       </c>
       <c r="D17" s="6">
-        <v>2.18</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-3.43</v>
+        <v>-0.51</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>0.17</v>
+        <v>-5.69</v>
       </c>
       <c r="D18" s="6">
-        <v>0.52</v>
+        <v>-7.72</v>
       </c>
       <c r="E18" s="7">
-        <v>0.35</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>2.51</v>
+        <v>-3.38</v>
       </c>
       <c r="D19" s="6">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.93</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-5.49</v>
+        <v>4.36</v>
       </c>
       <c r="D20" s="6">
-        <v>-5.69</v>
+        <v>8</v>
       </c>
       <c r="E20" s="8">
-        <v>-0.2</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-2.81</v>
+        <v>13.14</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.38</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.57</v>
+        <v>10.61</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.53</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>2.99</v>
+        <v>22.81</v>
       </c>
       <c r="D22" s="6">
-        <v>4.36</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.37</v>
+        <v>23.09</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>15.88</v>
+        <v>24.52</v>
       </c>
       <c r="D23" s="6">
-        <v>13.14</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.74</v>
+        <v>22.57</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>26.17</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="D24" s="6">
-        <v>22.81</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-3.36</v>
+        <v>-12.62</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.76</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>22.77</v>
+        <v>-31.23</v>
       </c>
       <c r="D25" s="6">
-        <v>24.52</v>
+        <v>-32.64</v>
       </c>
       <c r="E25" s="7">
-        <v>1.75</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-12.73</v>
+        <v>29.59</v>
       </c>
       <c r="D26" s="6">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.87</v>
+        <v>33.65</v>
+      </c>
+      <c r="E26" s="8">
+        <v>4.06</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-32</v>
+        <v>-11.87</v>
       </c>
       <c r="D27" s="6">
-        <v>-31.23</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.77</v>
+        <v>-10.17</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.7</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>29.6</v>
+        <v>3.52</v>
       </c>
       <c r="D28" s="6">
-        <v>29.59</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.01</v>
+        <v>0.87</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-16.34</v>
+        <v>0.01</v>
       </c>
       <c r="D29" s="6">
-        <v>-11.87</v>
+        <v>-2.83</v>
       </c>
       <c r="E29" s="7">
-        <v>4.47</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>9.65</v>
+        <v>18.55</v>
       </c>
       <c r="D30" s="6">
-        <v>3.52</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-6.13</v>
+        <v>11.63</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-6.92</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="D31" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-2.83</v>
+        <v>-2.88</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-5.24</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>25.71</v>
+        <v>0.6</v>
       </c>
       <c r="D32" s="6">
-        <v>18.55</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-7.16</v>
+        <v>-0.63</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>5.2</v>
+        <v>25.86</v>
       </c>
       <c r="D33" s="6">
-        <v>2.36</v>
+        <v>28.4</v>
       </c>
       <c r="E33" s="8">
-        <v>-2.84</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>6.55</v>
+        <v>12.86</v>
       </c>
       <c r="D34" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-5.95</v>
+        <v>10.72</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>26.03</v>
+        <v>-12.2</v>
       </c>
       <c r="D35" s="6">
-        <v>25.86</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.17</v>
+        <v>-13.41</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>21.34</v>
+        <v>-6.34</v>
       </c>
       <c r="D36" s="6">
-        <v>12.86</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-8.48</v>
+        <v>-6.91</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-11.89</v>
+        <v>-4.18</v>
       </c>
       <c r="D37" s="6">
-        <v>-12.2</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.31</v>
+        <v>-4.85</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-5.07</v>
+        <v>-18.21</v>
       </c>
       <c r="D38" s="6">
-        <v>-6.34</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.27</v>
+        <v>-19.58</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-5.72</v>
+        <v>-33.02</v>
       </c>
       <c r="D39" s="6">
-        <v>-4.18</v>
+        <v>-34.2</v>
       </c>
       <c r="E39" s="7">
-        <v>1.54</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-18.18</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="D40" s="6">
-        <v>-18.21</v>
+        <v>-5.92</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.03</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-30.95</v>
+        <v>-11.62</v>
       </c>
       <c r="D41" s="6">
-        <v>-33.02</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="E41" s="8">
-        <v>-2.07</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>-8.24</v>
+        <v>1090.2</v>
       </c>
       <c r="D42" s="6">
-        <v>-8.619999999999999</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.38</v>
+        <v>1075.2</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-15</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>-16.33</v>
+        <v>914.55</v>
       </c>
       <c r="D43" s="6">
-        <v>-11.62</v>
+        <v>909</v>
       </c>
       <c r="E43" s="7">
-        <v>4.71</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>1094.1</v>
+        <v>1859</v>
       </c>
       <c r="D44" s="6">
-        <v>1090.2</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-3.9</v>
+        <v>1845.9</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-13.1</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>926.95</v>
+        <v>1961.9</v>
       </c>
       <c r="D45" s="6">
-        <v>914.55</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-12.4</v>
+        <v>1929</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-32.9</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>1829</v>
+        <v>733.95</v>
       </c>
       <c r="D46" s="6">
-        <v>1859</v>
+        <v>721.05</v>
       </c>
       <c r="E46" s="7">
-        <v>30</v>
+        <v>-12.9</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>1962.7</v>
+        <v>3157.1</v>
       </c>
       <c r="D47" s="6">
-        <v>1961.9</v>
+        <v>3250.2</v>
       </c>
       <c r="E47" s="8">
-        <v>-0.8</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>756.7</v>
+        <v>8669.5</v>
       </c>
       <c r="D48" s="6">
-        <v>733.95</v>
+        <v>8812.5</v>
       </c>
       <c r="E48" s="8">
-        <v>-22.75</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>3170.2</v>
+        <v>46.96</v>
       </c>
       <c r="D49" s="6">
-        <v>3157.1</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-13.1</v>
+        <v>44.19</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>8230.5</v>
+        <v>56.07</v>
       </c>
       <c r="D50" s="6">
-        <v>8669.5</v>
+        <v>54.39</v>
       </c>
       <c r="E50" s="7">
-        <v>439</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="6">
-        <v>47.68</v>
+        <v>52.47</v>
       </c>
       <c r="D51" s="6">
-        <v>46.96</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.72</v>
+        <v>49.94</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-2.53</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>59.93</v>
+        <v>46.58</v>
       </c>
       <c r="D52" s="6">
-        <v>56.07</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-3.86</v>
+        <v>41.03</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-5.55</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>46.73</v>
+        <v>33.92</v>
       </c>
       <c r="D53" s="6">
-        <v>52.47</v>
+        <v>31.16</v>
       </c>
       <c r="E53" s="7">
-        <v>5.74</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>46.72</v>
+        <v>54.91</v>
       </c>
       <c r="D54" s="6">
-        <v>46.58</v>
+        <v>60.92</v>
       </c>
       <c r="E54" s="8">
-        <v>-0.14</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>39.67</v>
+        <v>63.21</v>
       </c>
       <c r="D55" s="6">
-        <v>33.92</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E55" s="8">
-        <v>-5.75</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C56" s="6">
-        <v>56.03</v>
+        <v>-6.42</v>
       </c>
       <c r="D56" s="6">
-        <v>54.91</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1.12</v>
+        <v>-48.5</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-42.08</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C57" s="6">
-        <v>52.94</v>
+        <v>-16.76</v>
       </c>
       <c r="D57" s="6">
-        <v>63.21</v>
-      </c>
-      <c r="E57" s="7">
-        <v>10.27</v>
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="E57" s="8">
+        <v>6.8</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="6">
-        <v>-63.63</v>
+        <v>207.75</v>
       </c>
       <c r="D58" s="6">
-        <v>-6.42</v>
+        <v>54.69</v>
       </c>
       <c r="E58" s="7">
-        <v>57.21</v>
+        <v>-153.06</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>51.79</v>
+        <v>-70.14</v>
       </c>
       <c r="D59" s="6">
-        <v>-16.76</v>
+        <v>-20.94</v>
       </c>
       <c r="E59" s="8">
-        <v>-68.55</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>21.46</v>
+        <v>-59.91</v>
       </c>
       <c r="D60" s="6">
-        <v>207.75</v>
+        <v>-60.92</v>
       </c>
       <c r="E60" s="7">
-        <v>186.29</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-34.76</v>
+        <v>-52.82</v>
       </c>
       <c r="D61" s="6">
-        <v>-70.14</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-35.38</v>
+        <v>-53.76</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-59.84</v>
+        <v>1130.31</v>
       </c>
       <c r="D62" s="6">
-        <v>-59.91</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-31.54</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-52.82</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-21.28</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-33.57</v>
-      </c>
-      <c r="D64" s="6">
-        <v>1130.31</v>
-      </c>
-      <c r="E64" s="7">
-        <v>1163.88</v>
+        <v>128.26</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-1002.05</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2954,28 +2908,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2989,16 +2943,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>50.6</v>
+        <v>49.6</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="G2" s="11">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3129,25 +3083,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.5977</v>
+        <v>0.5954</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3172</v>
+        <v>0.3247</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2632</v>
+        <v>0.2612</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1965</v>
+        <v>0.1924</v>
       </c>
       <c r="E2" s="14">
-        <v>0.139</v>
+        <v>0.1427</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1259</v>
+        <v>0.1218</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0394</v>
+        <v>0.0365</v>
       </c>
     </row>
   </sheetData>
